--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.15</v>
+        <v>20.1</v>
       </c>
       <c r="C2" t="n">
-        <v>257.89</v>
+        <v>328.71</v>
       </c>
       <c r="D2" t="n">
-        <v>12798551</v>
+        <v>16353579</v>
       </c>
       <c r="E2" t="n">
-        <v>18097622</v>
+        <v>17817678</v>
       </c>
       <c r="F2" t="n">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21.42</v>
+        <v>21.28</v>
       </c>
       <c r="K2" t="n">
         <v>22.95</v>
       </c>
       <c r="L2" t="n">
-        <v>-12.19</v>
+        <v>-12.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>23.08</v>
+        <v>27.27</v>
       </c>
       <c r="S2" t="n">
-        <v>18.69</v>
+        <v>18.72</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.05</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>486.96</v>
+        <v>501.37</v>
       </c>
       <c r="D3" t="n">
-        <v>25562307</v>
+        <v>26387938</v>
       </c>
       <c r="E3" t="n">
-        <v>22305650</v>
+        <v>22036361</v>
       </c>
       <c r="F3" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         <v>20.17</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.55</v>
+        <v>-5.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>7.27</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>16.34</v>
+        <v>17.39</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -695,23 +695,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="C4" t="n">
-        <v>170.79</v>
+        <v>232.53</v>
       </c>
       <c r="D4" t="n">
-        <v>13037635</v>
+        <v>17615912</v>
       </c>
       <c r="E4" t="n">
-        <v>10451811</v>
+        <v>10534650</v>
       </c>
       <c r="F4" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15.75</v>
+        <v>15.25</v>
       </c>
       <c r="K4" t="n">
-        <v>16.08</v>
+        <v>15.85</v>
       </c>
       <c r="L4" t="n">
-        <v>-18.51</v>
+        <v>-16.72</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>21.62</v>
+        <v>27.27</v>
       </c>
       <c r="S4" t="n">
-        <v>15.83</v>
+        <v>15.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -775,23 +775,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.7</v>
+        <v>57.9</v>
       </c>
       <c r="C5" t="n">
-        <v>445.79</v>
+        <v>707.9400000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>7467170</v>
+        <v>12226887</v>
       </c>
       <c r="E5" t="n">
-        <v>5090596</v>
+        <v>5346285</v>
       </c>
       <c r="F5" t="n">
-        <v>1.47</v>
+        <v>2.29</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -811,7 +811,7 @@
         <v>63.27</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.65</v>
+        <v>-8.49</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>15.38</v>
+        <v>12.54</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -855,23 +855,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.9</v>
+        <v>32.35</v>
       </c>
       <c r="C6" t="n">
-        <v>862.96</v>
+        <v>492.89</v>
       </c>
       <c r="D6" t="n">
-        <v>27052176</v>
+        <v>15236087</v>
       </c>
       <c r="E6" t="n">
-        <v>17168583</v>
+        <v>16475504</v>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>0.92</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -891,7 +891,7 @@
         <v>31.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>53.12</v>
+        <v>51.09</v>
       </c>
       <c r="S6" t="n">
-        <v>53.83</v>
+        <v>62.42</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -939,23 +939,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.9</v>
+        <v>19.05</v>
       </c>
       <c r="C7" t="n">
-        <v>211.57</v>
+        <v>269.47</v>
       </c>
       <c r="D7" t="n">
-        <v>11194407</v>
+        <v>14145209</v>
       </c>
       <c r="E7" t="n">
-        <v>11766385</v>
+        <v>11552185</v>
       </c>
       <c r="F7" t="n">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>20.15</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
         <v>20.57</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.119999999999999</v>
+        <v>-7.39</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>25</v>
+        <v>18.92</v>
       </c>
       <c r="S7" t="n">
-        <v>17.4</v>
+        <v>17.48</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>496.58</v>
+        <v>389.14</v>
       </c>
       <c r="D8" t="n">
-        <v>6525324</v>
+        <v>5126949</v>
       </c>
       <c r="E8" t="n">
-        <v>3107216</v>
+        <v>3085422</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>73.36</v>
       </c>
       <c r="L8" t="n">
-        <v>3.73</v>
+        <v>3.46</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>70.18000000000001</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>83.58</v>
+        <v>76.89</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>228</v>
+        <v>225.5</v>
       </c>
       <c r="C9" t="n">
-        <v>768.92</v>
+        <v>686.14</v>
       </c>
       <c r="D9" t="n">
-        <v>3372436</v>
+        <v>3042771</v>
       </c>
       <c r="E9" t="n">
-        <v>3536881</v>
+        <v>3472303</v>
       </c>
       <c r="F9" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         <v>229.8</v>
       </c>
       <c r="K9" t="n">
-        <v>207.15</v>
+        <v>213.45</v>
       </c>
       <c r="L9" t="n">
-        <v>10.07</v>
+        <v>5.65</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>38.78</v>
+        <v>41.38</v>
       </c>
       <c r="S9" t="n">
-        <v>43.31</v>
+        <v>44.16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -1179,23 +1179,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65.7</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>767.28</v>
+        <v>553.88</v>
       </c>
       <c r="D10" t="n">
-        <v>11678545</v>
+        <v>8392151</v>
       </c>
       <c r="E10" t="n">
-        <v>9179922</v>
+        <v>9208847</v>
       </c>
       <c r="F10" t="n">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1212,17 +1212,21 @@
         <v>71.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>70.18000000000001</v>
+        <v>71.31</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.38</v>
+        <v>-7.44</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
@@ -1231,10 +1235,10 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>35.98</v>
+        <v>43.56</v>
       </c>
       <c r="S10" t="n">
-        <v>42.52</v>
+        <v>46.41</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1248,7 +1252,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>
@@ -1259,19 +1263,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57.9</v>
+        <v>57.7</v>
       </c>
       <c r="C11" t="n">
-        <v>102.41</v>
+        <v>78.45</v>
       </c>
       <c r="D11" t="n">
-        <v>1768758</v>
+        <v>1359671</v>
       </c>
       <c r="E11" t="n">
-        <v>2458982</v>
+        <v>2324558</v>
       </c>
       <c r="F11" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1295,7 +1299,7 @@
         <v>59.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.69</v>
+        <v>-3.03</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1311,10 +1315,10 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>31.03</v>
+        <v>33.75</v>
       </c>
       <c r="S11" t="n">
-        <v>26.48</v>
+        <v>27.61</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1328,7 +1332,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-08 22:48:20</t>
+          <t>2026-10-09 22:30:13</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.1</v>
+        <v>20.45</v>
       </c>
       <c r="C2" t="n">
-        <v>328.71</v>
+        <v>243.4</v>
       </c>
       <c r="D2" t="n">
-        <v>16353579</v>
+        <v>11902095</v>
       </c>
       <c r="E2" t="n">
-        <v>17817678</v>
+        <v>17181794</v>
       </c>
       <c r="F2" t="n">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21.28</v>
+        <v>21.12</v>
       </c>
       <c r="K2" t="n">
         <v>22.95</v>
       </c>
       <c r="L2" t="n">
-        <v>-12.4</v>
+        <v>-10.88</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>27.27</v>
+        <v>36</v>
       </c>
       <c r="S2" t="n">
-        <v>18.72</v>
+        <v>23.34</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -615,23 +615,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="C3" t="n">
-        <v>501.37</v>
+        <v>288.69</v>
       </c>
       <c r="D3" t="n">
-        <v>26387938</v>
+        <v>15274729</v>
       </c>
       <c r="E3" t="n">
-        <v>22036361</v>
+        <v>21557461</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -651,7 +651,7 @@
         <v>20.17</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.8</v>
+        <v>-6.29</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>8.699999999999999</v>
+        <v>6.38</v>
       </c>
       <c r="S3" t="n">
-        <v>17.39</v>
+        <v>17.3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -695,23 +695,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="C4" t="n">
-        <v>232.53</v>
+        <v>138.47</v>
       </c>
       <c r="D4" t="n">
-        <v>17615912</v>
+        <v>10734107</v>
       </c>
       <c r="E4" t="n">
-        <v>10534650</v>
+        <v>10178855</v>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.05</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15.25</v>
+        <v>15.23</v>
       </c>
       <c r="K4" t="n">
         <v>15.85</v>
       </c>
       <c r="L4" t="n">
-        <v>-16.72</v>
+        <v>-18.61</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>27.27</v>
+        <v>21.74</v>
       </c>
       <c r="S4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -775,23 +775,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.9</v>
+        <v>56.3</v>
       </c>
       <c r="C5" t="n">
-        <v>707.9400000000001</v>
+        <v>438.98</v>
       </c>
       <c r="D5" t="n">
-        <v>12226887</v>
+        <v>7797089</v>
       </c>
       <c r="E5" t="n">
-        <v>5346285</v>
+        <v>5400064</v>
       </c>
       <c r="F5" t="n">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -811,7 +811,7 @@
         <v>63.27</v>
       </c>
       <c r="L5" t="n">
-        <v>-8.49</v>
+        <v>-11.02</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>12.54</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -855,23 +855,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.35</v>
+        <v>32.95</v>
       </c>
       <c r="C6" t="n">
-        <v>492.89</v>
+        <v>765.09</v>
       </c>
       <c r="D6" t="n">
-        <v>15236087</v>
+        <v>23219651</v>
       </c>
       <c r="E6" t="n">
-        <v>16475504</v>
+        <v>17046217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.92</v>
+        <v>1.36</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -891,7 +891,7 @@
         <v>31.5</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>51.09</v>
+        <v>56.31</v>
       </c>
       <c r="S6" t="n">
-        <v>62.42</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -942,20 +942,20 @@
         <v>19.05</v>
       </c>
       <c r="C7" t="n">
-        <v>269.47</v>
+        <v>127.09</v>
       </c>
       <c r="D7" t="n">
-        <v>14145209</v>
+        <v>6671584</v>
       </c>
       <c r="E7" t="n">
-        <v>11552185</v>
+        <v>11065949</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>0.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>19.96</v>
       </c>
       <c r="K7" t="n">
         <v>20.57</v>
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>18.92</v>
+        <v>20</v>
       </c>
       <c r="S7" t="n">
-        <v>17.48</v>
+        <v>22.62</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="C8" t="n">
-        <v>389.14</v>
+        <v>747.4</v>
       </c>
       <c r="D8" t="n">
-        <v>5126949</v>
+        <v>9991979</v>
       </c>
       <c r="E8" t="n">
-        <v>3085422</v>
+        <v>3306418</v>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>3.02</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>73.36</v>
       </c>
       <c r="L8" t="n">
-        <v>3.46</v>
+        <v>1.96</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1067,18 +1067,18 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.0x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>74.04000000000001</v>
+        <v>63.81</v>
       </c>
       <c r="S8" t="n">
-        <v>76.89</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>225.5</v>
+        <v>222</v>
       </c>
       <c r="C9" t="n">
-        <v>686.14</v>
+        <v>698.37</v>
       </c>
       <c r="D9" t="n">
-        <v>3042771</v>
+        <v>3145816</v>
       </c>
       <c r="E9" t="n">
-        <v>3472303</v>
+        <v>3421830</v>
       </c>
       <c r="F9" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1125,17 +1125,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>229.8</v>
       </c>
       <c r="K9" t="n">
-        <v>213.45</v>
+        <v>215.6</v>
       </c>
       <c r="L9" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1151,14 +1151,14 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>41.38</v>
+        <v>28.11</v>
       </c>
       <c r="S9" t="n">
-        <v>44.16</v>
+        <v>38.33</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -1179,19 +1179,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>553.88</v>
+        <v>345.16</v>
       </c>
       <c r="D10" t="n">
-        <v>8392151</v>
+        <v>5359692</v>
       </c>
       <c r="E10" t="n">
-        <v>9208847</v>
+        <v>8881614</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>0.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1209,24 +1209,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>71.40000000000001</v>
+        <v>70.95</v>
       </c>
       <c r="K10" t="n">
-        <v>71.31</v>
+        <v>72.78</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.44</v>
+        <v>-11.51</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
@@ -1235,10 +1231,10 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>43.56</v>
+        <v>34.94</v>
       </c>
       <c r="S10" t="n">
-        <v>46.41</v>
+        <v>48.13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1252,7 +1248,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>
@@ -1263,19 +1259,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57.7</v>
+        <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>78.45</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1359671</v>
+        <v>1660137</v>
       </c>
       <c r="E11" t="n">
-        <v>2324558</v>
+        <v>2214716</v>
       </c>
       <c r="F11" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1299,7 +1295,7 @@
         <v>59.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.03</v>
+        <v>-2.52</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1315,10 +1311,10 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>33.75</v>
+        <v>28.38</v>
       </c>
       <c r="S11" t="n">
-        <v>27.61</v>
+        <v>21.56</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1332,7 +1328,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-09 22:30:13</t>
+          <t>2026-10-13 23:16:41</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>20.45</v>
       </c>
       <c r="C2" t="n">
-        <v>243.4</v>
+        <v>100.69</v>
       </c>
       <c r="D2" t="n">
-        <v>11902095</v>
+        <v>4923500</v>
       </c>
       <c r="E2" t="n">
-        <v>17181794</v>
+        <v>7827765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21.12</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>22.95</v>
+        <v>21.58</v>
       </c>
       <c r="L2" t="n">
-        <v>-10.88</v>
+        <v>-5.21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -587,71 +587,71 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>36</v>
+        <v>22.86</v>
       </c>
       <c r="S2" t="n">
-        <v>23.34</v>
+        <v>24.43</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>ACV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.9</v>
+        <v>41.3</v>
       </c>
       <c r="C3" t="n">
-        <v>288.69</v>
+        <v>41.79</v>
       </c>
       <c r="D3" t="n">
-        <v>15274729</v>
+        <v>1011900</v>
       </c>
       <c r="E3" t="n">
-        <v>21557461</v>
+        <v>388775</v>
       </c>
       <c r="F3" t="n">
-        <v>0.71</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>19.47</v>
+        <v>40.25</v>
       </c>
       <c r="K3" t="n">
-        <v>20.17</v>
+        <v>42.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-6.29</v>
+        <v>-1.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -663,75 +663,75 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>6.38</v>
+        <v>74.36</v>
       </c>
       <c r="S3" t="n">
-        <v>17.3</v>
+        <v>70.75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>ANV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.9</v>
+        <v>18.8</v>
       </c>
       <c r="C4" t="n">
-        <v>138.47</v>
+        <v>34.54</v>
       </c>
       <c r="D4" t="n">
-        <v>10734107</v>
+        <v>1837300</v>
       </c>
       <c r="E4" t="n">
-        <v>10178855</v>
+        <v>1005380</v>
       </c>
       <c r="F4" t="n">
-        <v>1.05</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15.23</v>
+        <v>17.4</v>
       </c>
       <c r="K4" t="n">
-        <v>15.85</v>
+        <v>20.35</v>
       </c>
       <c r="L4" t="n">
-        <v>-18.61</v>
+        <v>-7.62</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -747,47 +747,47 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>21.74</v>
+        <v>68.84</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>68.03</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>BAF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.3</v>
+        <v>31.15</v>
       </c>
       <c r="C5" t="n">
-        <v>438.98</v>
+        <v>52.63</v>
       </c>
       <c r="D5" t="n">
-        <v>7797089</v>
+        <v>1689600</v>
       </c>
       <c r="E5" t="n">
-        <v>5400064</v>
+        <v>1663835</v>
       </c>
       <c r="F5" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -796,26 +796,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>61.95</v>
+        <v>30.72</v>
       </c>
       <c r="K5" t="n">
-        <v>63.27</v>
+        <v>29.96</v>
       </c>
       <c r="L5" t="n">
-        <v>-11.02</v>
+        <v>3.97</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -827,82 +827,78 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>57.32</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.95</v>
+        <v>33.1</v>
       </c>
       <c r="C6" t="n">
-        <v>765.09</v>
+        <v>100.68</v>
       </c>
       <c r="D6" t="n">
-        <v>23219651</v>
+        <v>3041800</v>
       </c>
       <c r="E6" t="n">
-        <v>17046217</v>
+        <v>3557405</v>
       </c>
       <c r="F6" t="n">
-        <v>1.36</v>
+        <v>0.86</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>31.5</v>
+        <v>35.04</v>
       </c>
       <c r="K6" t="n">
-        <v>31.5</v>
+        <v>37.54</v>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>-11.83</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
@@ -911,47 +907,47 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>56.31</v>
+        <v>6.25</v>
       </c>
       <c r="S6" t="n">
-        <v>64.15000000000001</v>
+        <v>21.53</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.05</v>
+        <v>30.1</v>
       </c>
       <c r="C7" t="n">
-        <v>127.09</v>
+        <v>171.63</v>
       </c>
       <c r="D7" t="n">
-        <v>6671584</v>
+        <v>5702100</v>
       </c>
       <c r="E7" t="n">
-        <v>11065949</v>
+        <v>11747410</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -960,26 +956,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19.96</v>
+        <v>27.9</v>
       </c>
       <c r="K7" t="n">
-        <v>20.57</v>
+        <v>27.96</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.39</v>
+        <v>7.65</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -991,51 +987,51 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>50.62</v>
       </c>
       <c r="S7" t="n">
-        <v>22.62</v>
+        <v>38.01</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74.8</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>747.4</v>
+        <v>52.23</v>
       </c>
       <c r="D8" t="n">
-        <v>9991979</v>
+        <v>687200</v>
       </c>
       <c r="E8" t="n">
-        <v>3306418</v>
+        <v>1007935</v>
       </c>
       <c r="F8" t="n">
-        <v>3.02</v>
+        <v>0.68</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1049,13 +1045,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>69.02</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>73.36</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.96</v>
+        <v>9.99</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1064,21 +1060,25 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.0x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>63.81</v>
+        <v>71.52</v>
       </c>
       <c r="S8" t="n">
-        <v>64.06999999999999</v>
+        <v>66.56</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1088,30 +1088,30 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222</v>
+        <v>10.7</v>
       </c>
       <c r="C9" t="n">
-        <v>698.37</v>
+        <v>51.83</v>
       </c>
       <c r="D9" t="n">
-        <v>3145816</v>
+        <v>4843900</v>
       </c>
       <c r="E9" t="n">
-        <v>3421830</v>
+        <v>5655700</v>
       </c>
       <c r="F9" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1129,17 +1129,17 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>229.8</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>215.6</v>
+        <v>13.61</v>
       </c>
       <c r="L9" t="n">
-        <v>2.97</v>
+        <v>-21.38</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1151,47 +1151,47 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>28.11</v>
+        <v>35.71</v>
       </c>
       <c r="S9" t="n">
-        <v>38.33</v>
+        <v>51.11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>CII</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64.40000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="C10" t="n">
-        <v>345.16</v>
+        <v>56.78</v>
       </c>
       <c r="D10" t="n">
-        <v>5359692</v>
+        <v>4654400</v>
       </c>
       <c r="E10" t="n">
-        <v>8881614</v>
+        <v>6289675</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>70.95</v>
+        <v>14.02</v>
       </c>
       <c r="K10" t="n">
-        <v>72.78</v>
+        <v>16.08</v>
       </c>
       <c r="L10" t="n">
-        <v>-11.51</v>
+        <v>-24.11</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1231,51 +1231,51 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>34.94</v>
+        <v>43.48</v>
       </c>
       <c r="S10" t="n">
-        <v>48.13</v>
+        <v>41.87</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-13 23:16:41</t>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>23.4</v>
       </c>
       <c r="C11" t="n">
-        <v>96.29000000000001</v>
+        <v>25.81</v>
       </c>
       <c r="D11" t="n">
-        <v>1660137</v>
+        <v>1103200</v>
       </c>
       <c r="E11" t="n">
-        <v>2214716</v>
+        <v>342735</v>
       </c>
       <c r="F11" t="n">
-        <v>0.75</v>
+        <v>3.22</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>59.8</v>
+        <v>22.18</v>
       </c>
       <c r="K11" t="n">
-        <v>59.5</v>
+        <v>24.12</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.52</v>
+        <v>-3.01</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1307,28 +1307,6584 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.2x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>28.38</v>
+        <v>75.86</v>
       </c>
       <c r="S11" t="n">
-        <v>21.56</v>
+        <v>80.11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CTD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="D12" t="n">
+        <v>480900</v>
+      </c>
+      <c r="E12" t="n">
+        <v>305690</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-12.28</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="S12" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CTG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="C13" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4898600</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6923255</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-8.57</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DBC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1590200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1283880</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="K14" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-15.43</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DCL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="D15" t="n">
+        <v>438300</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1400340</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="S15" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DCM</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1868100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2804615</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="K16" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="S16" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DDV</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1250500</v>
+      </c>
+      <c r="E17" t="n">
+        <v>527095</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-18.78</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DGW</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1172200</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1721965</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="K18" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="L18" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DIG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3714200</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3768235</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-17.57</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="S19" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DPM</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>29.31</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1372900</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2805325</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="S20" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DRI</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2117300</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1773295</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="S21" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DXG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2568700</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8471400</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-15.86</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="S22" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EIB</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2596300</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3371210</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="K23" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-18.09</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FPT</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>405.14</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7095300</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5910030</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FRT</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="D25" t="n">
+        <v>424200</v>
+      </c>
+      <c r="E25" t="n">
+        <v>708740</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="S25" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="D26" t="n">
+        <v>690400</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1202260</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="K26" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="S26" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GEE</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>103.15</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1579700</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1588650</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="K27" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-31.86</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="S27" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GEL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="C28" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2018700</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1543645</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="S28" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GEX</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>126.24</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5764300</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6727570</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>28.58</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-23.36</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>GMD</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>53</v>
+      </c>
+      <c r="C30" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1236100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1117695</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="K30" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GVR</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3339200</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2832330</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="K31" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="S31" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HAH</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="C32" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="D32" t="n">
+        <v>465600</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1259950</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="S32" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2648900</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2724680</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="K33" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="S33" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>🟡 Trung tính</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-10-13 23:16:41</t>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HDB</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>351.59</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15154600</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15519155</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="K34" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="S34" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HHP</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3490500</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1227775</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>🟢 Tăng</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="K35" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="L35" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="S35" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>🟢 Tích cực</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>HHV</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2539600</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2299980</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="S36" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="C37" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="D37" t="n">
+        <v>19326400</v>
+      </c>
+      <c r="E37" t="n">
+        <v>18476735</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="K37" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-9.35</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>50</v>
+      </c>
+      <c r="S37" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HSG</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6475100</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2358220</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="K38" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="S38" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IDC</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1726800</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1477050</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="K39" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="S39" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KDH</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2336600</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3819655</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="K40" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-28</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>29.19</v>
+      </c>
+      <c r="S40" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LPB</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1693500</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1991755</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-20.38</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MBB</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="C42" t="n">
+        <v>306.69</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15849800</v>
+      </c>
+      <c r="E42" t="n">
+        <v>11097300</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="K42" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MBS</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2786000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2717580</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="K43" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-15.11</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="S43" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MCH</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>147.02</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1043400</v>
+      </c>
+      <c r="E44" t="n">
+        <v>700320</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>138.53</v>
+      </c>
+      <c r="K44" t="n">
+        <v>134.54</v>
+      </c>
+      <c r="L44" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="S44" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MSB</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="C45" t="n">
+        <v>253.36</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17294400</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11651100</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>🟢 Tăng</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="K45" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="L45" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="S45" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>🟢 Tích cực</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="C46" t="n">
+        <v>213.91</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2983400</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5837975</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="S46" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1092400</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2557130</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="K47" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="L47" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="S47" t="n">
+        <v>64.18000000000001</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MWG</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="C48" t="n">
+        <v>215.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2927900</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2966565</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>69.02</v>
+      </c>
+      <c r="K48" t="n">
+        <v>73.36</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="S48" t="n">
+        <v>68.17</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="C49" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2691000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2080540</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="K49" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NKG</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6064200</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2022125</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="K50" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>🎯 BẮT ĐÁY (Vol 3.0x + giá chiết khấu 129)</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>64.18000000000001</v>
+      </c>
+      <c r="S50" t="n">
+        <v>66.16</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NLG</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1102700</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1434300</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="K51" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-13.08</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>25</v>
+      </c>
+      <c r="S51" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NVB</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>14</v>
+      </c>
+      <c r="C52" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3273200</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2162295</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>14</v>
+      </c>
+      <c r="K52" t="n">
+        <v>14</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="S52" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NVL</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="C53" t="n">
+        <v>242.31</v>
+      </c>
+      <c r="D53" t="n">
+        <v>22540600</v>
+      </c>
+      <c r="E53" t="n">
+        <v>26869994</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="K53" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-25.84</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>32.38</v>
+      </c>
+      <c r="S53" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PDR</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3655100</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4075055</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="K54" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-19.71</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>25</v>
+      </c>
+      <c r="S54" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PLX</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="C55" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2319600</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4573800</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="K55" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="S55" t="n">
+        <v>69.84</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PNJ</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="C56" t="n">
+        <v>126.17</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6764900</v>
+      </c>
+      <c r="E56" t="n">
+        <v>13249310</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="K56" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-60.45</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>POW</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="C57" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4212000</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5194960</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="S57" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>18</v>
+      </c>
+      <c r="C58" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2153000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4316455</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="K58" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="S58" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PVP</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="C59" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1078800</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1483865</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K59" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="L59" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="S59" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PVS</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>33</v>
+      </c>
+      <c r="C60" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1879200</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3657700</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>30.94</v>
+      </c>
+      <c r="K60" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="S60" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PVT</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="C61" t="n">
+        <v>112.38</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4549800</v>
+      </c>
+      <c r="E61" t="n">
+        <v>8034870</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="K61" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="L61" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="S61" t="n">
+        <v>67.02</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SBT</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1173200</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1189190</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K62" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>50</v>
+      </c>
+      <c r="S62" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SHB</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="D63" t="n">
+        <v>32323300</v>
+      </c>
+      <c r="E63" t="n">
+        <v>42441805</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="K63" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-17.93</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="S63" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SHS</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>12</v>
+      </c>
+      <c r="C64" t="n">
+        <v>121.93</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10160800</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8286260</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="K64" t="n">
+        <v>15</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-20.03</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="S64" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SSB</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="C65" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2235600</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3119835</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="K65" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-18.43</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C66" t="n">
+        <v>254.51</v>
+      </c>
+      <c r="D66" t="n">
+        <v>13466000</v>
+      </c>
+      <c r="E66" t="n">
+        <v>21095800</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="K66" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-7.19</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="S66" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STB</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="C67" t="n">
+        <v>187.83</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2907600</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2955350</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-9.33</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="S67" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TCB</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>33</v>
+      </c>
+      <c r="C68" t="n">
+        <v>625.4299999999999</v>
+      </c>
+      <c r="D68" t="n">
+        <v>18952500</v>
+      </c>
+      <c r="E68" t="n">
+        <v>18126715</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="S68" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TCH</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="C69" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2567500</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3988240</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="K69" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-17.46</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="S69" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TCX</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="C70" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2189600</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2367160</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="K70" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-16.39</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="S70" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TLG</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="C71" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="D71" t="n">
+        <v>384300</v>
+      </c>
+      <c r="E71" t="n">
+        <v>272705</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="K71" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="L71" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>67.19</v>
+      </c>
+      <c r="S71" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TPB</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C72" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8995700</v>
+      </c>
+      <c r="E72" t="n">
+        <v>9335380</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="K72" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-8.02</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="S72" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="C73" t="n">
+        <v>121.34</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2155300</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3583060</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>57</v>
+      </c>
+      <c r="K73" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="S73" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VCG</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1935700</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1709225</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K74" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="S74" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VCI</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C75" t="n">
+        <v>155.33</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8351100</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8324800</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="K75" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-20.51</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="S75" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VCK</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="C76" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1046800</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1850930</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="K76" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-16.11</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="S76" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>VEA</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="C77" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="E77" t="n">
+        <v>470910</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>🟢 Tăng</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K77" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="L77" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>88.23999999999999</v>
+      </c>
+      <c r="S77" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>🟢 Tích cực</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>VGC</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="C78" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D78" t="n">
+        <v>539500</v>
+      </c>
+      <c r="E78" t="n">
+        <v>633745</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="K78" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="L78" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="S78" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>61</v>
+      </c>
+      <c r="C79" t="n">
+        <v>696.64</v>
+      </c>
+      <c r="D79" t="n">
+        <v>11420400</v>
+      </c>
+      <c r="E79" t="n">
+        <v>8941585</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="K79" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-13.07</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="S79" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>VIB</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="C80" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="D80" t="n">
+        <v>8666400</v>
+      </c>
+      <c r="E80" t="n">
+        <v>5181375</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="K80" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>63.89</v>
+      </c>
+      <c r="S80" t="n">
+        <v>80.92</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="C81" t="n">
+        <v>680.5599999999999</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3116100</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3296815</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="S81" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>VIX</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C82" t="n">
+        <v>229.92</v>
+      </c>
+      <c r="D82" t="n">
+        <v>19992800</v>
+      </c>
+      <c r="E82" t="n">
+        <v>25983010</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="K82" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-23.08</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S82" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>VJC</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>93.38</v>
+      </c>
+      <c r="D83" t="n">
+        <v>729000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1013185</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="K83" t="n">
+        <v>132.12</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-3.05</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="S83" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>13</v>
+      </c>
+      <c r="C84" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="D84" t="n">
+        <v>8969800</v>
+      </c>
+      <c r="E84" t="n">
+        <v>9767160</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="K84" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-17.98</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="S84" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="C85" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1179000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2155455</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="K85" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>32</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VPB</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="C86" t="n">
+        <v>310.49</v>
+      </c>
+      <c r="D86" t="n">
+        <v>12751000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>21787460</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="K86" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="L86" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="S86" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>VPI</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="C87" t="n">
+        <v>140.16</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2770000</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1515905</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="K87" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-10.08</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="S87" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VPL</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>76</v>
+      </c>
+      <c r="C88" t="n">
+        <v>66.66</v>
+      </c>
+      <c r="D88" t="n">
+        <v>877100</v>
+      </c>
+      <c r="E88" t="n">
+        <v>886715</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="K88" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-11.11</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="S88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VRE</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C89" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2328500</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3671415</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="K89" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-21.57</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R89" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="S89" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VSC</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C90" t="n">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="D90" t="n">
+        <v>6387500</v>
+      </c>
+      <c r="E90" t="n">
+        <v>7274950</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="K90" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-32.54</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R90" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="S90" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>VTP</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="C91" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>473000</v>
+      </c>
+      <c r="E91" t="n">
+        <v>790405</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="K91" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-15.99</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R91" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="S91" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>VTZ</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1035700</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1052705</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="K92" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="S92" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:13:10</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.45</v>
+        <v>20.6</v>
       </c>
       <c r="C2" t="n">
-        <v>100.69</v>
+        <v>122.1</v>
       </c>
       <c r="D2" t="n">
-        <v>4923500</v>
+        <v>5927200</v>
       </c>
       <c r="E2" t="n">
-        <v>7827765</v>
+        <v>7662165</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         <v>21.58</v>
       </c>
       <c r="L2" t="n">
-        <v>-5.21</v>
+        <v>-4.52</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>22.86</v>
+        <v>28.95</v>
       </c>
       <c r="S2" t="n">
-        <v>24.43</v>
+        <v>30.81</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,34 +604,34 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACV</t>
+          <t>BAF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.3</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>41.79</v>
+        <v>26.53</v>
       </c>
       <c r="D3" t="n">
-        <v>1011900</v>
+        <v>855900</v>
       </c>
       <c r="E3" t="n">
-        <v>388775</v>
+        <v>1643195</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>0.52</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -641,21 +641,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40.25</v>
+        <v>30.72</v>
       </c>
       <c r="K3" t="n">
-        <v>42.1</v>
+        <v>29.96</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9</v>
+        <v>3.47</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -663,18 +663,18 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>74.36</v>
+        <v>32.65</v>
       </c>
       <c r="S3" t="n">
-        <v>70.75</v>
+        <v>51.37</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -684,54 +684,54 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANV</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.8</v>
+        <v>33.2</v>
       </c>
       <c r="C4" t="n">
-        <v>34.54</v>
+        <v>103.42</v>
       </c>
       <c r="D4" t="n">
-        <v>1837300</v>
+        <v>3115000</v>
       </c>
       <c r="E4" t="n">
-        <v>1005380</v>
+        <v>3543305</v>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>0.88</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17.4</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>20.35</v>
+        <v>37.54</v>
       </c>
       <c r="L4" t="n">
-        <v>-7.62</v>
+        <v>-11.56</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -747,51 +747,51 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>68.84</v>
+        <v>9.52</v>
       </c>
       <c r="S4" t="n">
-        <v>68.03</v>
+        <v>28.66</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAF</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.15</v>
+        <v>28.2</v>
       </c>
       <c r="C5" t="n">
-        <v>52.63</v>
+        <v>567.49</v>
       </c>
       <c r="D5" t="n">
-        <v>1689600</v>
+        <v>20123900</v>
       </c>
       <c r="E5" t="n">
-        <v>1663835</v>
+        <v>11687295</v>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>30.72</v>
+        <v>27.9</v>
       </c>
       <c r="K5" t="n">
-        <v>29.96</v>
+        <v>27.96</v>
       </c>
       <c r="L5" t="n">
-        <v>3.97</v>
+        <v>0.86</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>40</v>
+        <v>38.54</v>
       </c>
       <c r="S5" t="n">
-        <v>57.32</v>
+        <v>36.63</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -844,58 +844,58 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>100.68</v>
+        <v>103.62</v>
       </c>
       <c r="D6" t="n">
-        <v>3041800</v>
+        <v>1451300</v>
       </c>
       <c r="E6" t="n">
-        <v>3557405</v>
+        <v>1027765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.86</v>
+        <v>1.41</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>35.04</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>37.54</v>
+        <v>67.7</v>
       </c>
       <c r="L6" t="n">
-        <v>-11.83</v>
+        <v>5.47</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -907,75 +907,75 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>6.25</v>
+        <v>56.5</v>
       </c>
       <c r="S6" t="n">
-        <v>21.53</v>
+        <v>62.92</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.1</v>
+        <v>26.5</v>
       </c>
       <c r="C7" t="n">
-        <v>171.63</v>
+        <v>31.03</v>
       </c>
       <c r="D7" t="n">
-        <v>5702100</v>
+        <v>1170900</v>
       </c>
       <c r="E7" t="n">
-        <v>11747410</v>
+        <v>585380</v>
       </c>
       <c r="F7" t="n">
-        <v>0.49</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>27.9</v>
+        <v>28.45</v>
       </c>
       <c r="K7" t="n">
-        <v>27.96</v>
+        <v>29.9</v>
       </c>
       <c r="L7" t="n">
-        <v>7.65</v>
+        <v>-11.37</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -987,135 +987,131 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>50.62</v>
+        <v>38.1</v>
       </c>
       <c r="S7" t="n">
-        <v>38.01</v>
+        <v>39.93</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>52.23</v>
+        <v>113.72</v>
       </c>
       <c r="D8" t="n">
-        <v>687200</v>
+        <v>10337800</v>
       </c>
       <c r="E8" t="n">
-        <v>1007935</v>
+        <v>5935845</v>
       </c>
       <c r="F8" t="n">
-        <v>0.68</v>
+        <v>1.74</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>67.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>69.09999999999999</v>
+        <v>13.61</v>
       </c>
       <c r="L8" t="n">
-        <v>9.99</v>
+        <v>-19.18</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>71.52</v>
+        <v>46.43</v>
       </c>
       <c r="S8" t="n">
-        <v>66.56</v>
+        <v>60.5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CII</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.7</v>
+        <v>12.95</v>
       </c>
       <c r="C9" t="n">
-        <v>51.83</v>
+        <v>247.44</v>
       </c>
       <c r="D9" t="n">
-        <v>4843900</v>
+        <v>19107700</v>
       </c>
       <c r="E9" t="n">
-        <v>5655700</v>
+        <v>6841965</v>
       </c>
       <c r="F9" t="n">
-        <v>0.86</v>
+        <v>2.79</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,13 +1125,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>14.02</v>
       </c>
       <c r="K9" t="n">
-        <v>13.61</v>
+        <v>16.08</v>
       </c>
       <c r="L9" t="n">
-        <v>-21.38</v>
+        <v>-19.44</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1147,14 +1143,14 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.8x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>35.71</v>
+        <v>54.22</v>
       </c>
       <c r="S9" t="n">
-        <v>51.11</v>
+        <v>54.53</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1168,54 +1164,54 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CII</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.2</v>
+        <v>23.6</v>
       </c>
       <c r="C10" t="n">
-        <v>56.78</v>
+        <v>24.28</v>
       </c>
       <c r="D10" t="n">
-        <v>4654400</v>
+        <v>1028700</v>
       </c>
       <c r="E10" t="n">
-        <v>6289675</v>
+        <v>383125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.74</v>
+        <v>2.69</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14.02</v>
+        <v>22.18</v>
       </c>
       <c r="K10" t="n">
-        <v>16.08</v>
+        <v>24.12</v>
       </c>
       <c r="L10" t="n">
-        <v>-24.11</v>
+        <v>-2.18</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1227,55 +1223,55 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>43.48</v>
+        <v>78.63</v>
       </c>
       <c r="S10" t="n">
-        <v>41.87</v>
+        <v>84.38</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23.4</v>
+        <v>63</v>
       </c>
       <c r="C11" t="n">
-        <v>25.81</v>
+        <v>29.23</v>
       </c>
       <c r="D11" t="n">
-        <v>1103200</v>
+        <v>464000</v>
       </c>
       <c r="E11" t="n">
-        <v>342735</v>
+        <v>321035</v>
       </c>
       <c r="F11" t="n">
-        <v>3.22</v>
+        <v>1.45</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1285,17 +1281,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>22.18</v>
+        <v>61.25</v>
       </c>
       <c r="K11" t="n">
-        <v>24.12</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.01</v>
+        <v>-13.1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1307,18 +1303,18 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.2x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>75.86</v>
+        <v>68.75</v>
       </c>
       <c r="S11" t="n">
-        <v>80.11</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1328,54 +1324,54 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CTD</t>
+          <t>CTG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63.6</v>
+        <v>29.8</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59</v>
+        <v>259.24</v>
       </c>
       <c r="D12" t="n">
-        <v>480900</v>
+        <v>8699300</v>
       </c>
       <c r="E12" t="n">
-        <v>305690</v>
+        <v>6795660</v>
       </c>
       <c r="F12" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>61.5</v>
+        <v>30.7</v>
       </c>
       <c r="K12" t="n">
-        <v>72.5</v>
+        <v>32.32</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.28</v>
+        <v>-7.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1391,51 +1387,51 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>70.40000000000001</v>
+        <v>43.86</v>
       </c>
       <c r="S12" t="n">
-        <v>62.08</v>
+        <v>38.58</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CTG</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.55</v>
+        <v>20.45</v>
       </c>
       <c r="C13" t="n">
-        <v>144.75</v>
+        <v>34.72</v>
       </c>
       <c r="D13" t="n">
-        <v>4898600</v>
+        <v>1697900</v>
       </c>
       <c r="E13" t="n">
-        <v>6923255</v>
+        <v>895210</v>
       </c>
       <c r="F13" t="n">
-        <v>0.71</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1449,13 +1445,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>30.8</v>
+        <v>23.38</v>
       </c>
       <c r="K13" t="n">
-        <v>32.32</v>
+        <v>24.1</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.57</v>
+        <v>-15.15</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1471,10 +1467,10 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
       <c r="S13" t="n">
-        <v>29.52</v>
+        <v>17.34</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1488,7 +1484,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
@@ -1499,23 +1495,23 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.35</v>
+        <v>15.65</v>
       </c>
       <c r="C14" t="n">
-        <v>24.41</v>
+        <v>36.93</v>
       </c>
       <c r="D14" t="n">
-        <v>1590200</v>
+        <v>2359900</v>
       </c>
       <c r="E14" t="n">
-        <v>1283880</v>
+        <v>1343330</v>
       </c>
       <c r="F14" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1535,7 +1531,7 @@
         <v>18.15</v>
       </c>
       <c r="L14" t="n">
-        <v>-15.43</v>
+        <v>-13.77</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1551,10 +1547,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>40.48</v>
+        <v>48.94</v>
       </c>
       <c r="S14" t="n">
-        <v>43.38</v>
+        <v>51.36</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1568,7 +1564,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
@@ -1579,19 +1575,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="C15" t="n">
-        <v>20.38</v>
+        <v>28.2</v>
       </c>
       <c r="D15" t="n">
-        <v>438300</v>
+        <v>602500</v>
       </c>
       <c r="E15" t="n">
-        <v>1400340</v>
+        <v>1329525</v>
       </c>
       <c r="F15" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1615,7 +1611,7 @@
         <v>42.32</v>
       </c>
       <c r="L15" t="n">
-        <v>9.859999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1631,10 +1627,10 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>55.07</v>
+        <v>51.28</v>
       </c>
       <c r="S15" t="n">
-        <v>57.52</v>
+        <v>43.52</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1648,7 +1644,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
@@ -1659,19 +1655,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="C16" t="n">
-        <v>63.7</v>
+        <v>57.04</v>
       </c>
       <c r="D16" t="n">
-        <v>1868100</v>
+        <v>1682600</v>
       </c>
       <c r="E16" t="n">
-        <v>2804615</v>
+        <v>2748735</v>
       </c>
       <c r="F16" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1695,7 +1691,7 @@
         <v>36.94</v>
       </c>
       <c r="L16" t="n">
-        <v>-7.69</v>
+        <v>-8.23</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1711,10 +1707,10 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>50.53</v>
+        <v>47.87</v>
       </c>
       <c r="S16" t="n">
-        <v>55.39</v>
+        <v>62.65</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1728,61 +1724,65 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DDV</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.1</v>
+        <v>45.05</v>
       </c>
       <c r="C17" t="n">
-        <v>21.38</v>
+        <v>38.81</v>
       </c>
       <c r="D17" t="n">
-        <v>1250500</v>
+        <v>861500</v>
       </c>
       <c r="E17" t="n">
-        <v>527095</v>
+        <v>1721555</v>
       </c>
       <c r="F17" t="n">
-        <v>2.37</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18.85</v>
+        <v>39.83</v>
       </c>
       <c r="K17" t="n">
-        <v>21.06</v>
+        <v>39.83</v>
       </c>
       <c r="L17" t="n">
-        <v>-18.78</v>
+        <v>13.11</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
@@ -1791,82 +1791,78 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>57.45</v>
+        <v>58.31</v>
       </c>
       <c r="S17" t="n">
-        <v>56.59</v>
+        <v>51.67</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.5</v>
+        <v>9.6</v>
       </c>
       <c r="C18" t="n">
-        <v>53.34</v>
+        <v>70.34</v>
       </c>
       <c r="D18" t="n">
-        <v>1172200</v>
+        <v>7326800</v>
       </c>
       <c r="E18" t="n">
-        <v>1721965</v>
+        <v>3979130</v>
       </c>
       <c r="F18" t="n">
-        <v>0.68</v>
+        <v>1.84</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>39.83</v>
+        <v>10.37</v>
       </c>
       <c r="K18" t="n">
-        <v>39.83</v>
+        <v>11.52</v>
       </c>
       <c r="L18" t="n">
-        <v>14.24</v>
+        <v>-16.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
@@ -1875,47 +1871,47 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>53.49</v>
+        <v>49.2</v>
       </c>
       <c r="S18" t="n">
-        <v>50.6</v>
+        <v>65.05</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.5</v>
+        <v>21.2</v>
       </c>
       <c r="C19" t="n">
-        <v>35.28</v>
+        <v>35.45</v>
       </c>
       <c r="D19" t="n">
-        <v>3714200</v>
+        <v>1672300</v>
       </c>
       <c r="E19" t="n">
-        <v>3768235</v>
+        <v>2673905</v>
       </c>
       <c r="F19" t="n">
-        <v>0.99</v>
+        <v>0.63</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1933,13 +1929,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10.4</v>
+        <v>22.18</v>
       </c>
       <c r="K19" t="n">
-        <v>11.52</v>
+        <v>24.2</v>
       </c>
       <c r="L19" t="n">
-        <v>-17.57</v>
+        <v>-12.41</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1955,10 +1951,10 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>41.62</v>
+        <v>30.56</v>
       </c>
       <c r="S19" t="n">
-        <v>55.99</v>
+        <v>23.61</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1972,30 +1968,30 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.35</v>
+        <v>15.8</v>
       </c>
       <c r="C20" t="n">
-        <v>29.31</v>
+        <v>20.34</v>
       </c>
       <c r="D20" t="n">
-        <v>1372900</v>
+        <v>1287200</v>
       </c>
       <c r="E20" t="n">
-        <v>2805325</v>
+        <v>1816380</v>
       </c>
       <c r="F20" t="n">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2004,29 +2000,33 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>22.18</v>
+        <v>14.34</v>
       </c>
       <c r="K20" t="n">
-        <v>24.2</v>
+        <v>14.34</v>
       </c>
       <c r="L20" t="n">
-        <v>-11.8</v>
+        <v>10.22</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
@@ -2035,82 +2035,78 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>30.99</v>
+        <v>56.36</v>
       </c>
       <c r="S20" t="n">
-        <v>22.47</v>
+        <v>55.55</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>10.25</v>
       </c>
       <c r="C21" t="n">
-        <v>33.88</v>
+        <v>139.6</v>
       </c>
       <c r="D21" t="n">
-        <v>2117300</v>
+        <v>13619100</v>
       </c>
       <c r="E21" t="n">
-        <v>1773295</v>
+        <v>8432400</v>
       </c>
       <c r="F21" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14.34</v>
+        <v>10.88</v>
       </c>
       <c r="K21" t="n">
-        <v>14.34</v>
+        <v>11.89</v>
       </c>
       <c r="L21" t="n">
-        <v>11.61</v>
+        <v>-13.76</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
@@ -2119,51 +2115,51 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>60.71</v>
+        <v>55.24</v>
       </c>
       <c r="S21" t="n">
-        <v>57.61</v>
+        <v>45.85</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>16.45</v>
       </c>
       <c r="C22" t="n">
-        <v>25.69</v>
+        <v>65.77</v>
       </c>
       <c r="D22" t="n">
-        <v>2568700</v>
+        <v>3998300</v>
       </c>
       <c r="E22" t="n">
-        <v>8471400</v>
+        <v>3293455</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3</v>
+        <v>1.21</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2177,13 +2173,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10.88</v>
+        <v>17.65</v>
       </c>
       <c r="K22" t="n">
-        <v>11.89</v>
+        <v>19.9</v>
       </c>
       <c r="L22" t="n">
-        <v>-15.86</v>
+        <v>-17.34</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2199,10 +2195,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>43.9</v>
+        <v>42.86</v>
       </c>
       <c r="S22" t="n">
-        <v>35.77</v>
+        <v>56.86</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2216,34 +2212,34 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>EVF</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.3</v>
+        <v>11.55</v>
       </c>
       <c r="C23" t="n">
-        <v>42.32</v>
+        <v>29.17</v>
       </c>
       <c r="D23" t="n">
-        <v>2596300</v>
+        <v>2525900</v>
       </c>
       <c r="E23" t="n">
-        <v>3371210</v>
+        <v>1187985</v>
       </c>
       <c r="F23" t="n">
-        <v>0.77</v>
+        <v>2.13</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2257,13 +2253,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>17.73</v>
+        <v>11.95</v>
       </c>
       <c r="K23" t="n">
-        <v>19.9</v>
+        <v>12.75</v>
       </c>
       <c r="L23" t="n">
-        <v>-18.09</v>
+        <v>-9.41</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2279,10 +2275,10 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>44.44</v>
+        <v>47.06</v>
       </c>
       <c r="S23" t="n">
-        <v>56.41</v>
+        <v>45.41</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2296,7 +2292,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
@@ -2307,23 +2303,23 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="C24" t="n">
-        <v>405.14</v>
+        <v>287.94</v>
       </c>
       <c r="D24" t="n">
-        <v>7095300</v>
+        <v>4964400</v>
       </c>
       <c r="E24" t="n">
-        <v>5910030</v>
+        <v>5826915</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2340,10 +2336,10 @@
         <v>61.9</v>
       </c>
       <c r="K24" t="n">
-        <v>63.41</v>
+        <v>63.32</v>
       </c>
       <c r="L24" t="n">
-        <v>-9.949999999999999</v>
+        <v>-8.41</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2359,10 +2355,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>8.16</v>
+        <v>16.83</v>
       </c>
       <c r="S24" t="n">
-        <v>8.949999999999999</v>
+        <v>15.14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2376,7 +2372,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
@@ -2387,19 +2383,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>140.6</v>
+        <v>141</v>
       </c>
       <c r="C25" t="n">
-        <v>59.64</v>
+        <v>33.37</v>
       </c>
       <c r="D25" t="n">
-        <v>424200</v>
+        <v>236700</v>
       </c>
       <c r="E25" t="n">
-        <v>708740</v>
+        <v>700170</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2423,7 +2419,7 @@
         <v>126.5</v>
       </c>
       <c r="L25" t="n">
-        <v>11.15</v>
+        <v>11.46</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2443,14 +2439,14 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>48.02</v>
+        <v>48.74</v>
       </c>
       <c r="S25" t="n">
-        <v>71.34999999999999</v>
+        <v>69.86</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2460,58 +2456,58 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>FTS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>78.59999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="C26" t="n">
-        <v>54.27</v>
+        <v>32.75</v>
       </c>
       <c r="D26" t="n">
-        <v>690400</v>
+        <v>1751200</v>
       </c>
       <c r="E26" t="n">
-        <v>1202260</v>
+        <v>636500</v>
       </c>
       <c r="F26" t="n">
-        <v>0.57</v>
+        <v>2.75</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>76.48</v>
+        <v>21.7</v>
       </c>
       <c r="K26" t="n">
-        <v>77.69</v>
+        <v>22.88</v>
       </c>
       <c r="L26" t="n">
-        <v>1.16</v>
+        <v>-18.25</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2519,55 +2515,55 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.8x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>41.75</v>
+        <v>34.78</v>
       </c>
       <c r="S26" t="n">
-        <v>43.69</v>
+        <v>27.31</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65.3</v>
+        <v>76.2</v>
       </c>
       <c r="C27" t="n">
-        <v>103.15</v>
+        <v>111.62</v>
       </c>
       <c r="D27" t="n">
-        <v>1579700</v>
+        <v>1464800</v>
       </c>
       <c r="E27" t="n">
-        <v>1588650</v>
+        <v>1144425</v>
       </c>
       <c r="F27" t="n">
-        <v>0.99</v>
+        <v>1.28</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2577,17 +2573,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>70.04000000000001</v>
+        <v>76.48</v>
       </c>
       <c r="K27" t="n">
-        <v>95.83</v>
+        <v>77.69</v>
       </c>
       <c r="L27" t="n">
-        <v>-31.86</v>
+        <v>-1.92</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2603,10 +2599,10 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>40.54</v>
+        <v>40</v>
       </c>
       <c r="S27" t="n">
-        <v>47.05</v>
+        <v>42.63</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2620,34 +2616,34 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26.95</v>
+        <v>65.5</v>
       </c>
       <c r="C28" t="n">
-        <v>54.4</v>
+        <v>43.4</v>
       </c>
       <c r="D28" t="n">
-        <v>2018700</v>
+        <v>662600</v>
       </c>
       <c r="E28" t="n">
-        <v>1543645</v>
+        <v>1543535</v>
       </c>
       <c r="F28" t="n">
-        <v>1.31</v>
+        <v>0.43</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2661,13 +2657,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>27.15</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>29.58</v>
+        <v>95.83</v>
       </c>
       <c r="L28" t="n">
-        <v>-8.880000000000001</v>
+        <v>-31.65</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2683,10 +2679,10 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>28.12</v>
+        <v>34.33</v>
       </c>
       <c r="S28" t="n">
-        <v>42.24</v>
+        <v>39.6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2700,30 +2696,30 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.9</v>
+        <v>27.3</v>
       </c>
       <c r="C29" t="n">
-        <v>126.24</v>
+        <v>30.51</v>
       </c>
       <c r="D29" t="n">
-        <v>5764300</v>
+        <v>1117400</v>
       </c>
       <c r="E29" t="n">
-        <v>6727570</v>
+        <v>1451565</v>
       </c>
       <c r="F29" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2732,7 +2728,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2741,13 +2737,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>23.45</v>
+        <v>27.15</v>
       </c>
       <c r="K29" t="n">
-        <v>28.58</v>
+        <v>29.58</v>
       </c>
       <c r="L29" t="n">
-        <v>-23.36</v>
+        <v>-7.69</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2763,82 +2759,78 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>23.17</v>
+        <v>29.59</v>
       </c>
       <c r="S29" t="n">
-        <v>25.54</v>
+        <v>35.36</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53</v>
+        <v>22.4</v>
       </c>
       <c r="C30" t="n">
-        <v>65.51000000000001</v>
+        <v>128.85</v>
       </c>
       <c r="D30" t="n">
-        <v>1236100</v>
+        <v>5752100</v>
       </c>
       <c r="E30" t="n">
-        <v>1117695</v>
+        <v>6525795</v>
       </c>
       <c r="F30" t="n">
-        <v>1.11</v>
+        <v>0.88</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>50.34</v>
+        <v>23.45</v>
       </c>
       <c r="K30" t="n">
-        <v>50.34</v>
+        <v>28.58</v>
       </c>
       <c r="L30" t="n">
-        <v>5.29</v>
+        <v>-21.61</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
@@ -2847,51 +2839,51 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>62.4</v>
+        <v>32.22</v>
       </c>
       <c r="S30" t="n">
-        <v>64.14</v>
+        <v>31.78</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.4</v>
+        <v>53</v>
       </c>
       <c r="C31" t="n">
-        <v>104.85</v>
+        <v>50.39</v>
       </c>
       <c r="D31" t="n">
-        <v>3339200</v>
+        <v>950800</v>
       </c>
       <c r="E31" t="n">
-        <v>2832330</v>
+        <v>1134210</v>
       </c>
       <c r="F31" t="n">
-        <v>1.18</v>
+        <v>0.84</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2901,24 +2893,28 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>30.22</v>
+        <v>50.34</v>
       </c>
       <c r="K31" t="n">
-        <v>32.78</v>
+        <v>50.34</v>
       </c>
       <c r="L31" t="n">
-        <v>-4.2</v>
+        <v>5.29</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
@@ -2927,10 +2923,10 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>39.06</v>
+        <v>58.91</v>
       </c>
       <c r="S31" t="n">
-        <v>43.96</v>
+        <v>64.52</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2944,30 +2940,30 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>48.35</v>
+        <v>30.9</v>
       </c>
       <c r="C32" t="n">
-        <v>22.51</v>
+        <v>58.92</v>
       </c>
       <c r="D32" t="n">
-        <v>465600</v>
+        <v>1906800</v>
       </c>
       <c r="E32" t="n">
-        <v>1259950</v>
+        <v>2820785</v>
       </c>
       <c r="F32" t="n">
-        <v>0.37</v>
+        <v>0.68</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2981,17 +2977,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>48.2</v>
+        <v>30.22</v>
       </c>
       <c r="K32" t="n">
-        <v>49.55</v>
+        <v>32.78</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.42</v>
+        <v>-5.72</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -3007,10 +3003,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>46.45</v>
+        <v>35.29</v>
       </c>
       <c r="S32" t="n">
-        <v>55.36</v>
+        <v>38.06</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3024,30 +3020,30 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HAH</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.1</v>
+        <v>48.2</v>
       </c>
       <c r="C33" t="n">
-        <v>61.19</v>
+        <v>41.43</v>
       </c>
       <c r="D33" t="n">
-        <v>2648900</v>
+        <v>859600</v>
       </c>
       <c r="E33" t="n">
-        <v>2724680</v>
+        <v>1246920</v>
       </c>
       <c r="F33" t="n">
-        <v>0.97</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3061,17 +3057,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>24.92</v>
+        <v>48.2</v>
       </c>
       <c r="K33" t="n">
-        <v>24.33</v>
+        <v>49.55</v>
       </c>
       <c r="L33" t="n">
-        <v>-5.04</v>
+        <v>-2.72</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3087,14 +3083,14 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>29.17</v>
+        <v>35.29</v>
       </c>
       <c r="S33" t="n">
-        <v>14.14</v>
+        <v>48.91</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3104,34 +3100,34 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="C34" t="n">
-        <v>351.59</v>
+        <v>111.47</v>
       </c>
       <c r="D34" t="n">
-        <v>15154600</v>
+        <v>4644700</v>
       </c>
       <c r="E34" t="n">
-        <v>15519155</v>
+        <v>2776190</v>
       </c>
       <c r="F34" t="n">
-        <v>0.98</v>
+        <v>1.67</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3141,28 +3137,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>21.13</v>
+        <v>24.92</v>
       </c>
       <c r="K34" t="n">
-        <v>21.13</v>
+        <v>24.39</v>
       </c>
       <c r="L34" t="n">
-        <v>9.800000000000001</v>
+        <v>-1.6</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -3171,14 +3163,14 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>79.33</v>
+        <v>41.82</v>
       </c>
       <c r="S34" t="n">
-        <v>82.34</v>
+        <v>24.94</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3188,39 +3180,39 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HHP</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>18.15</v>
+        <v>22.8</v>
       </c>
       <c r="C35" t="n">
-        <v>63.35</v>
+        <v>407.29</v>
       </c>
       <c r="D35" t="n">
-        <v>3490500</v>
+        <v>17863600</v>
       </c>
       <c r="E35" t="n">
-        <v>1227775</v>
+        <v>15673705</v>
       </c>
       <c r="F35" t="n">
-        <v>2.84</v>
+        <v>1.14</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3229,25 +3221,25 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>16.23</v>
+        <v>21.13</v>
       </c>
       <c r="K35" t="n">
-        <v>15.31</v>
+        <v>21.13</v>
       </c>
       <c r="L35" t="n">
-        <v>18.55</v>
+        <v>7.9</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3255,75 +3247,75 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>69.77</v>
+        <v>69.83</v>
       </c>
       <c r="S35" t="n">
-        <v>83.56</v>
+        <v>74.94</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HHV</t>
+          <t>HHP</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.039999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="C36" t="n">
-        <v>22.96</v>
+        <v>44.52</v>
       </c>
       <c r="D36" t="n">
-        <v>2539600</v>
+        <v>2588500</v>
       </c>
       <c r="E36" t="n">
-        <v>2299980</v>
+        <v>1303410</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1</v>
+        <v>1.99</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9.630000000000001</v>
+        <v>16.34</v>
       </c>
       <c r="K36" t="n">
-        <v>10.68</v>
+        <v>15.31</v>
       </c>
       <c r="L36" t="n">
-        <v>-15.4</v>
+        <v>12.34</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3335,10 +3327,10 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>45.6</v>
+        <v>40.74</v>
       </c>
       <c r="S36" t="n">
-        <v>44.29</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3347,39 +3339,39 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HHV</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.8</v>
+        <v>9.52</v>
       </c>
       <c r="C37" t="n">
-        <v>401.99</v>
+        <v>62.7</v>
       </c>
       <c r="D37" t="n">
-        <v>19326400</v>
+        <v>6586500</v>
       </c>
       <c r="E37" t="n">
-        <v>18476735</v>
+        <v>2526425</v>
       </c>
       <c r="F37" t="n">
-        <v>1.05</v>
+        <v>2.61</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3393,13 +3385,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>21.28</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>22.94</v>
+        <v>10.68</v>
       </c>
       <c r="L37" t="n">
-        <v>-9.35</v>
+        <v>-10.9</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3411,14 +3403,14 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>50</v>
+        <v>62.13</v>
       </c>
       <c r="S37" t="n">
-        <v>35.75</v>
+        <v>55.35</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3432,34 +3424,34 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10.5</v>
+        <v>20.75</v>
       </c>
       <c r="C38" t="n">
-        <v>67.98999999999999</v>
+        <v>439.08</v>
       </c>
       <c r="D38" t="n">
-        <v>6475100</v>
+        <v>21160300</v>
       </c>
       <c r="E38" t="n">
-        <v>2358220</v>
+        <v>18656045</v>
       </c>
       <c r="F38" t="n">
-        <v>2.75</v>
+        <v>1.13</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3473,13 +3465,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10.72</v>
+        <v>21.12</v>
       </c>
       <c r="K38" t="n">
-        <v>11.35</v>
+        <v>22.94</v>
       </c>
       <c r="L38" t="n">
-        <v>-7.49</v>
+        <v>-9.57</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3491,14 +3483,14 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>66.45</v>
+        <v>51.72</v>
       </c>
       <c r="S38" t="n">
-        <v>52.73</v>
+        <v>42.68</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3512,54 +3504,54 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>33.7</v>
+        <v>10.45</v>
       </c>
       <c r="C39" t="n">
-        <v>58.19</v>
+        <v>41.03</v>
       </c>
       <c r="D39" t="n">
-        <v>1726800</v>
+        <v>3926400</v>
       </c>
       <c r="E39" t="n">
-        <v>1477050</v>
+        <v>2449520</v>
       </c>
       <c r="F39" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>32.45</v>
+        <v>10.72</v>
       </c>
       <c r="K39" t="n">
-        <v>36.67</v>
+        <v>11.35</v>
       </c>
       <c r="L39" t="n">
-        <v>-8.1</v>
+        <v>-7.93</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3575,51 +3567,51 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>50.91</v>
+        <v>64.33</v>
       </c>
       <c r="S39" t="n">
-        <v>52.17</v>
+        <v>57.68</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13.5</v>
+        <v>12.2</v>
       </c>
       <c r="C40" t="n">
-        <v>31.54</v>
+        <v>28.61</v>
       </c>
       <c r="D40" t="n">
-        <v>2336600</v>
+        <v>2345200</v>
       </c>
       <c r="E40" t="n">
-        <v>3819655</v>
+        <v>1703580</v>
       </c>
       <c r="F40" t="n">
-        <v>0.61</v>
+        <v>1.38</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3633,13 +3625,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>15.68</v>
+        <v>13.35</v>
       </c>
       <c r="K40" t="n">
-        <v>18.75</v>
+        <v>14.5</v>
       </c>
       <c r="L40" t="n">
-        <v>-28</v>
+        <v>-15.86</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3655,10 +3647,10 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>29.19</v>
+        <v>33.33</v>
       </c>
       <c r="S40" t="n">
-        <v>36.42</v>
+        <v>28.6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3672,30 +3664,30 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38.1</v>
+        <v>33.7</v>
       </c>
       <c r="C41" t="n">
-        <v>64.52</v>
+        <v>30.82</v>
       </c>
       <c r="D41" t="n">
-        <v>1693500</v>
+        <v>914600</v>
       </c>
       <c r="E41" t="n">
-        <v>1991755</v>
+        <v>1415335</v>
       </c>
       <c r="F41" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3704,22 +3696,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>46.6</v>
+        <v>32.45</v>
       </c>
       <c r="K41" t="n">
-        <v>47.85</v>
+        <v>36.67</v>
       </c>
       <c r="L41" t="n">
-        <v>-20.38</v>
+        <v>-8.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3735,47 +3727,47 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>25.44</v>
+        <v>52.83</v>
       </c>
       <c r="S41" t="n">
-        <v>20.34</v>
+        <v>53.21</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.35</v>
+        <v>13.65</v>
       </c>
       <c r="C42" t="n">
-        <v>306.69</v>
+        <v>54.76</v>
       </c>
       <c r="D42" t="n">
-        <v>15849800</v>
+        <v>4011700</v>
       </c>
       <c r="E42" t="n">
-        <v>11097300</v>
+        <v>3680700</v>
       </c>
       <c r="F42" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3793,13 +3785,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>19.49</v>
+        <v>15.57</v>
       </c>
       <c r="K42" t="n">
-        <v>19.74</v>
+        <v>18.75</v>
       </c>
       <c r="L42" t="n">
-        <v>-2</v>
+        <v>-27.2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3815,10 +3807,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>37.5</v>
+        <v>34.5</v>
       </c>
       <c r="S42" t="n">
-        <v>34.36</v>
+        <v>43.49</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3832,30 +3824,30 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.8</v>
+        <v>37.2</v>
       </c>
       <c r="C43" t="n">
-        <v>41.23</v>
+        <v>97.23</v>
       </c>
       <c r="D43" t="n">
-        <v>2786000</v>
+        <v>2613600</v>
       </c>
       <c r="E43" t="n">
-        <v>2717580</v>
+        <v>1978575</v>
       </c>
       <c r="F43" t="n">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3873,13 +3865,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>17.01</v>
+        <v>46.6</v>
       </c>
       <c r="K43" t="n">
-        <v>17.43</v>
+        <v>47.85</v>
       </c>
       <c r="L43" t="n">
-        <v>-15.11</v>
+        <v>-22.26</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3895,10 +3887,10 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>21.43</v>
+        <v>23.94</v>
       </c>
       <c r="S43" t="n">
-        <v>22.27</v>
+        <v>19.33</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3912,34 +3904,34 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>140.9</v>
+        <v>19.9</v>
       </c>
       <c r="C44" t="n">
-        <v>147.02</v>
+        <v>649.17</v>
       </c>
       <c r="D44" t="n">
-        <v>1043400</v>
+        <v>32621600</v>
       </c>
       <c r="E44" t="n">
-        <v>700320</v>
+        <v>11903470</v>
       </c>
       <c r="F44" t="n">
-        <v>1.49</v>
+        <v>2.74</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3949,17 +3941,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>138.53</v>
+        <v>19.49</v>
       </c>
       <c r="K44" t="n">
-        <v>134.54</v>
+        <v>19.74</v>
       </c>
       <c r="L44" t="n">
-        <v>4.73</v>
+        <v>0.79</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3971,14 +3963,14 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="S44" t="n">
-        <v>32.98</v>
+        <v>43.95</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3992,30 +3984,30 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14.65</v>
+        <v>15.2</v>
       </c>
       <c r="C45" t="n">
-        <v>253.36</v>
+        <v>60.06</v>
       </c>
       <c r="D45" t="n">
-        <v>17294400</v>
+        <v>3951000</v>
       </c>
       <c r="E45" t="n">
-        <v>11651100</v>
+        <v>2745270</v>
       </c>
       <c r="F45" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4024,34 +4016,30 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>13.56</v>
+        <v>16.77</v>
       </c>
       <c r="K45" t="n">
-        <v>12.48</v>
+        <v>17.43</v>
       </c>
       <c r="L45" t="n">
-        <v>17.39</v>
+        <v>-12.82</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4059,10 +4047,10 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>59.52</v>
+        <v>33.33</v>
       </c>
       <c r="S45" t="n">
-        <v>62.55</v>
+        <v>31.07</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4071,39 +4059,39 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>71.7</v>
+        <v>139.8</v>
       </c>
       <c r="C46" t="n">
-        <v>213.91</v>
+        <v>108.18</v>
       </c>
       <c r="D46" t="n">
-        <v>2983400</v>
+        <v>773800</v>
       </c>
       <c r="E46" t="n">
-        <v>5837975</v>
+        <v>662330</v>
       </c>
       <c r="F46" t="n">
-        <v>0.51</v>
+        <v>1.17</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4113,21 +4101,21 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>68.90000000000001</v>
+        <v>138.57</v>
       </c>
       <c r="K46" t="n">
-        <v>72.09999999999999</v>
+        <v>134.54</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.55</v>
+        <v>3.91</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4139,14 +4127,14 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>53.24</v>
+        <v>45.16</v>
       </c>
       <c r="S46" t="n">
-        <v>59.59</v>
+        <v>29.87</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4156,39 +4144,39 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64.40000000000001</v>
+        <v>14.65</v>
       </c>
       <c r="C47" t="n">
-        <v>70.34999999999999</v>
+        <v>208.94</v>
       </c>
       <c r="D47" t="n">
-        <v>1092400</v>
+        <v>14262100</v>
       </c>
       <c r="E47" t="n">
-        <v>2557130</v>
+        <v>12230580</v>
       </c>
       <c r="F47" t="n">
-        <v>0.43</v>
+        <v>1.17</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4197,24 +4185,20 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>50.57</v>
+        <v>13.56</v>
       </c>
       <c r="K47" t="n">
-        <v>50.57</v>
+        <v>12.56</v>
       </c>
       <c r="L47" t="n">
-        <v>27.35</v>
+        <v>16.64</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>⚠️</t>
@@ -4227,47 +4211,47 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>67.31999999999999</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="S47" t="n">
-        <v>64.18000000000001</v>
+        <v>61.95</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>73.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>215.2</v>
+        <v>290.03</v>
       </c>
       <c r="D48" t="n">
-        <v>2927900</v>
+        <v>4119800</v>
       </c>
       <c r="E48" t="n">
-        <v>2966565</v>
+        <v>5878965</v>
       </c>
       <c r="F48" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4285,17 +4269,17 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>69.02</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>73.36</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>0.19</v>
+        <v>-2.36</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -4307,10 +4291,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>56.89</v>
+        <v>51.03</v>
       </c>
       <c r="S48" t="n">
-        <v>68.17</v>
+        <v>59.71</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4324,34 +4308,34 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>12.05</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>32.43</v>
+        <v>127.97</v>
       </c>
       <c r="D49" t="n">
-        <v>2691000</v>
+        <v>1941900</v>
       </c>
       <c r="E49" t="n">
-        <v>2080540</v>
+        <v>2556400</v>
       </c>
       <c r="F49" t="n">
-        <v>1.29</v>
+        <v>0.76</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4361,25 +4345,33 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>12.18</v>
+        <v>50.57</v>
       </c>
       <c r="K49" t="n">
-        <v>12.25</v>
+        <v>50.57</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.63</v>
+        <v>30.31</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4387,14 +4379,14 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>51.06</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>50.62</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -4404,34 +4396,34 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10.5</v>
+        <v>72.8</v>
       </c>
       <c r="C50" t="n">
-        <v>63.67</v>
+        <v>201.16</v>
       </c>
       <c r="D50" t="n">
-        <v>6064200</v>
+        <v>2763200</v>
       </c>
       <c r="E50" t="n">
-        <v>2022125</v>
+        <v>2900730</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>0.95</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4441,17 +4433,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>10.45</v>
+        <v>69.02</v>
       </c>
       <c r="K50" t="n">
-        <v>11.48</v>
+        <v>73.36</v>
       </c>
       <c r="L50" t="n">
-        <v>-8.5</v>
+        <v>-0.76</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4463,14 +4455,14 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.0x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>64.18000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="S50" t="n">
-        <v>66.16</v>
+        <v>62.73</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4484,54 +4476,54 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NLG</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21.2</v>
+        <v>12.1</v>
       </c>
       <c r="C51" t="n">
-        <v>23.38</v>
+        <v>25.14</v>
       </c>
       <c r="D51" t="n">
-        <v>1102700</v>
+        <v>2077700</v>
       </c>
       <c r="E51" t="n">
-        <v>1434300</v>
+        <v>2047390</v>
       </c>
       <c r="F51" t="n">
-        <v>0.77</v>
+        <v>1.01</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>22.55</v>
+        <v>12.05</v>
       </c>
       <c r="K51" t="n">
-        <v>24.39</v>
+        <v>12.25</v>
       </c>
       <c r="L51" t="n">
-        <v>-13.08</v>
+        <v>-1.22</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4547,47 +4539,47 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="S51" t="n">
-        <v>33.02</v>
+        <v>49.78</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NVB</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="C52" t="n">
-        <v>45.82</v>
+        <v>48.69</v>
       </c>
       <c r="D52" t="n">
-        <v>3273200</v>
+        <v>4636900</v>
       </c>
       <c r="E52" t="n">
-        <v>2162295</v>
+        <v>2180015</v>
       </c>
       <c r="F52" t="n">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -4601,28 +4593,24 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>14</v>
+        <v>10.45</v>
       </c>
       <c r="K52" t="n">
-        <v>14</v>
+        <v>11.48</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
@@ -4631,14 +4619,14 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>52.08</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="S52" t="n">
-        <v>60.17</v>
+        <v>73.19</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -4648,7 +4636,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
@@ -4659,19 +4647,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10.75</v>
+        <v>10.7</v>
       </c>
       <c r="C53" t="n">
-        <v>242.31</v>
+        <v>291.63</v>
       </c>
       <c r="D53" t="n">
-        <v>22540600</v>
+        <v>27255500</v>
       </c>
       <c r="E53" t="n">
-        <v>26869994</v>
+        <v>27520319</v>
       </c>
       <c r="F53" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4695,7 +4683,7 @@
         <v>14.5</v>
       </c>
       <c r="L53" t="n">
-        <v>-25.84</v>
+        <v>-26.18</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4711,10 +4699,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>32.38</v>
+        <v>35.11</v>
       </c>
       <c r="S53" t="n">
-        <v>35.77</v>
+        <v>34.88</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4728,34 +4716,34 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="C54" t="n">
-        <v>40.57</v>
+        <v>28.2</v>
       </c>
       <c r="D54" t="n">
-        <v>3655100</v>
+        <v>2186200</v>
       </c>
       <c r="E54" t="n">
-        <v>4075055</v>
+        <v>2171530</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9</v>
+        <v>1.01</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4765,17 +4753,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>12.23</v>
+        <v>13.2</v>
       </c>
       <c r="K54" t="n">
-        <v>13.82</v>
+        <v>14</v>
       </c>
       <c r="L54" t="n">
-        <v>-19.71</v>
+        <v>-7.82</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4791,10 +4779,10 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>25</v>
+        <v>43.33</v>
       </c>
       <c r="S54" t="n">
-        <v>42.15</v>
+        <v>56.66</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4808,34 +4796,34 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>36.25</v>
+        <v>13.45</v>
       </c>
       <c r="C55" t="n">
-        <v>84.09</v>
+        <v>54.34</v>
       </c>
       <c r="D55" t="n">
-        <v>2319600</v>
+        <v>4040200</v>
       </c>
       <c r="E55" t="n">
-        <v>4573800</v>
+        <v>1892035</v>
       </c>
       <c r="F55" t="n">
-        <v>0.51</v>
+        <v>2.14</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4845,17 +4833,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>35.15</v>
+        <v>13.78</v>
       </c>
       <c r="K55" t="n">
-        <v>38.08</v>
+        <v>13.75</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.82</v>
+        <v>-2.18</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4871,10 +4859,10 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>57.23</v>
+        <v>51.85</v>
       </c>
       <c r="S55" t="n">
-        <v>69.84</v>
+        <v>59.13</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4888,34 +4876,34 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>18.65</v>
+        <v>11.3</v>
       </c>
       <c r="C56" t="n">
-        <v>126.17</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>6764900</v>
+        <v>5800400</v>
       </c>
       <c r="E56" t="n">
-        <v>13249310</v>
+        <v>4179935</v>
       </c>
       <c r="F56" t="n">
-        <v>0.51</v>
+        <v>1.39</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4929,13 +4917,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>32.08</v>
+        <v>12.2</v>
       </c>
       <c r="K56" t="n">
-        <v>47.16</v>
+        <v>13.82</v>
       </c>
       <c r="L56" t="n">
-        <v>-60.45</v>
+        <v>-18.26</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4951,10 +4939,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>11.95</v>
+        <v>50</v>
       </c>
       <c r="S56" t="n">
-        <v>5.25</v>
+        <v>49.42</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4968,30 +4956,30 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>12.45</v>
+        <v>51</v>
       </c>
       <c r="C57" t="n">
-        <v>52.44</v>
+        <v>34.61</v>
       </c>
       <c r="D57" t="n">
-        <v>4212000</v>
+        <v>678700</v>
       </c>
       <c r="E57" t="n">
-        <v>5194960</v>
+        <v>908530</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5000,30 +4988,34 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>13.1</v>
+        <v>45.2</v>
       </c>
       <c r="K57" t="n">
-        <v>13.6</v>
+        <v>44.22</v>
       </c>
       <c r="L57" t="n">
-        <v>-8.460000000000001</v>
+        <v>15.35</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
@@ -5031,71 +5023,71 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>48.15</v>
+        <v>56.61</v>
       </c>
       <c r="S57" t="n">
-        <v>49.57</v>
+        <v>67.09</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>18</v>
+        <v>35.55</v>
       </c>
       <c r="C58" t="n">
-        <v>38.75</v>
+        <v>168.76</v>
       </c>
       <c r="D58" t="n">
-        <v>2153000</v>
+        <v>4747000</v>
       </c>
       <c r="E58" t="n">
-        <v>4316455</v>
+        <v>4478990</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5</v>
+        <v>1.06</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>19.02</v>
+        <v>35.15</v>
       </c>
       <c r="K58" t="n">
-        <v>19.43</v>
+        <v>38.08</v>
       </c>
       <c r="L58" t="n">
-        <v>-7.36</v>
+        <v>-6.66</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5111,47 +5103,47 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>45.88</v>
+        <v>52.94</v>
       </c>
       <c r="S58" t="n">
-        <v>53.7</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>23.15</v>
+        <v>18.2</v>
       </c>
       <c r="C59" t="n">
-        <v>24.97</v>
+        <v>157.36</v>
       </c>
       <c r="D59" t="n">
-        <v>1078800</v>
+        <v>8646300</v>
       </c>
       <c r="E59" t="n">
-        <v>1483865</v>
+        <v>13536085</v>
       </c>
       <c r="F59" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -5160,34 +5152,30 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>20.6</v>
+        <v>32.08</v>
       </c>
       <c r="K59" t="n">
-        <v>19.51</v>
+        <v>47.16</v>
       </c>
       <c r="L59" t="n">
-        <v>18.66</v>
+        <v>-61.41</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
@@ -5195,75 +5183,75 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>70.47</v>
+        <v>11.86</v>
       </c>
       <c r="S59" t="n">
-        <v>70.95999999999999</v>
+        <v>5.27</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>33</v>
+        <v>12.2</v>
       </c>
       <c r="C60" t="n">
-        <v>62.01</v>
+        <v>138.74</v>
       </c>
       <c r="D60" t="n">
-        <v>1879200</v>
+        <v>11371900</v>
       </c>
       <c r="E60" t="n">
-        <v>3657700</v>
+        <v>5547665</v>
       </c>
       <c r="F60" t="n">
-        <v>0.51</v>
+        <v>2.05</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>30.94</v>
+        <v>13.08</v>
       </c>
       <c r="K60" t="n">
-        <v>31.62</v>
+        <v>13.6</v>
       </c>
       <c r="L60" t="n">
-        <v>4.35</v>
+        <v>-10.29</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -5275,47 +5263,47 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>54.67</v>
+        <v>41.94</v>
       </c>
       <c r="S60" t="n">
-        <v>58.86</v>
+        <v>44.72</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24.7</v>
+        <v>17.7</v>
       </c>
       <c r="C61" t="n">
-        <v>112.38</v>
+        <v>51.01</v>
       </c>
       <c r="D61" t="n">
-        <v>4549800</v>
+        <v>2882200</v>
       </c>
       <c r="E61" t="n">
-        <v>8034870</v>
+        <v>3984475</v>
       </c>
       <c r="F61" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5324,38 +5312,30 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>21.2</v>
+        <v>19.02</v>
       </c>
       <c r="K61" t="n">
-        <v>21.2</v>
+        <v>19.43</v>
       </c>
       <c r="L61" t="n">
-        <v>16.51</v>
+        <v>-8.9</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
@@ -5363,51 +5343,51 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>67.14</v>
+        <v>46.43</v>
       </c>
       <c r="S61" t="n">
-        <v>67.02</v>
+        <v>56.03</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="C62" t="n">
-        <v>26.51</v>
+        <v>65.2</v>
       </c>
       <c r="D62" t="n">
-        <v>1173200</v>
+        <v>2963800</v>
       </c>
       <c r="E62" t="n">
-        <v>1189190</v>
+        <v>1577435</v>
       </c>
       <c r="F62" t="n">
-        <v>0.99</v>
+        <v>1.88</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5417,17 +5397,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="K62" t="n">
-        <v>21.92</v>
+        <v>19.51</v>
       </c>
       <c r="L62" t="n">
-        <v>3.08</v>
+        <v>12.76</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5443,10 +5423,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>50</v>
+        <v>57.89</v>
       </c>
       <c r="S62" t="n">
-        <v>49.1</v>
+        <v>60.28</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5460,54 +5440,54 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10.3</v>
+        <v>31.6</v>
       </c>
       <c r="C63" t="n">
-        <v>332.93</v>
+        <v>189.2</v>
       </c>
       <c r="D63" t="n">
-        <v>32323300</v>
+        <v>5987500</v>
       </c>
       <c r="E63" t="n">
-        <v>42441805</v>
+        <v>3664205</v>
       </c>
       <c r="F63" t="n">
-        <v>0.76</v>
+        <v>1.63</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>11.38</v>
+        <v>30.94</v>
       </c>
       <c r="K63" t="n">
-        <v>12.55</v>
+        <v>31.62</v>
       </c>
       <c r="L63" t="n">
-        <v>-17.93</v>
+        <v>-0.08</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5523,47 +5503,47 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>20.45</v>
+        <v>50</v>
       </c>
       <c r="S63" t="n">
-        <v>11.14</v>
+        <v>55.37</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>12</v>
+        <v>23.65</v>
       </c>
       <c r="C64" t="n">
-        <v>121.93</v>
+        <v>248.63</v>
       </c>
       <c r="D64" t="n">
-        <v>10160800</v>
+        <v>10512800</v>
       </c>
       <c r="E64" t="n">
-        <v>8286260</v>
+        <v>8146535</v>
       </c>
       <c r="F64" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5572,29 +5552,33 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>14.28</v>
+        <v>21.2</v>
       </c>
       <c r="K64" t="n">
-        <v>15</v>
+        <v>21.2</v>
       </c>
       <c r="L64" t="n">
-        <v>-20.03</v>
+        <v>11.56</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
@@ -5603,47 +5587,47 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>28.3</v>
+        <v>53.79</v>
       </c>
       <c r="S64" t="n">
-        <v>29.14</v>
+        <v>59.74</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>15.65</v>
+        <v>22.65</v>
       </c>
       <c r="C65" t="n">
-        <v>34.99</v>
+        <v>24.84</v>
       </c>
       <c r="D65" t="n">
-        <v>2235600</v>
+        <v>1096800</v>
       </c>
       <c r="E65" t="n">
-        <v>3119835</v>
+        <v>1188590</v>
       </c>
       <c r="F65" t="n">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5657,21 +5641,21 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>19.77</v>
+        <v>22.3</v>
       </c>
       <c r="K65" t="n">
-        <v>19.19</v>
+        <v>21.92</v>
       </c>
       <c r="L65" t="n">
-        <v>-18.43</v>
+        <v>3.31</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -5683,14 +5667,14 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>17.29</v>
+        <v>47.62</v>
       </c>
       <c r="S65" t="n">
-        <v>20.98</v>
+        <v>42.08</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -5700,34 +5684,34 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>18.9</v>
+        <v>10.4</v>
       </c>
       <c r="C66" t="n">
-        <v>254.51</v>
+        <v>441.98</v>
       </c>
       <c r="D66" t="n">
-        <v>13466000</v>
+        <v>42498200</v>
       </c>
       <c r="E66" t="n">
-        <v>21095800</v>
+        <v>42196195</v>
       </c>
       <c r="F66" t="n">
-        <v>0.64</v>
+        <v>1.01</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5741,13 +5725,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>19.55</v>
+        <v>11.23</v>
       </c>
       <c r="K66" t="n">
-        <v>20.37</v>
+        <v>12.55</v>
       </c>
       <c r="L66" t="n">
-        <v>-7.19</v>
+        <v>-17.13</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5763,10 +5747,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>8.51</v>
+        <v>23.91</v>
       </c>
       <c r="S66" t="n">
-        <v>18.62</v>
+        <v>11.91</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5780,39 +5764,39 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>64.59999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="C67" t="n">
-        <v>187.83</v>
+        <v>202.7</v>
       </c>
       <c r="D67" t="n">
-        <v>2907600</v>
+        <v>16614500</v>
       </c>
       <c r="E67" t="n">
-        <v>2955350</v>
+        <v>8520945</v>
       </c>
       <c r="F67" t="n">
-        <v>0.98</v>
+        <v>1.95</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5821,13 +5805,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>71.59999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="K67" t="n">
-        <v>71.25</v>
+        <v>15</v>
       </c>
       <c r="L67" t="n">
-        <v>-9.33</v>
+        <v>-18.69</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5843,51 +5827,51 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>8.16</v>
+        <v>34.62</v>
       </c>
       <c r="S67" t="n">
-        <v>16.36</v>
+        <v>38.79</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>33</v>
+        <v>15.9</v>
       </c>
       <c r="C68" t="n">
-        <v>625.4299999999999</v>
+        <v>37.32</v>
       </c>
       <c r="D68" t="n">
-        <v>18952500</v>
+        <v>2347300</v>
       </c>
       <c r="E68" t="n">
-        <v>18126715</v>
+        <v>2984555</v>
       </c>
       <c r="F68" t="n">
-        <v>1.05</v>
+        <v>0.79</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5897,28 +5881,24 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>31.5</v>
+        <v>19.77</v>
       </c>
       <c r="K68" t="n">
-        <v>31.5</v>
+        <v>19.19</v>
       </c>
       <c r="L68" t="n">
-        <v>4.76</v>
+        <v>-17.12</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
@@ -5927,14 +5907,14 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>50.6</v>
+        <v>22.05</v>
       </c>
       <c r="S68" t="n">
-        <v>61.97</v>
+        <v>21.61</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -5944,34 +5924,34 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10.9</v>
+        <v>19.25</v>
       </c>
       <c r="C69" t="n">
-        <v>27.99</v>
+        <v>457.09</v>
       </c>
       <c r="D69" t="n">
-        <v>2567500</v>
+        <v>23744700</v>
       </c>
       <c r="E69" t="n">
-        <v>3988240</v>
+        <v>20234655</v>
       </c>
       <c r="F69" t="n">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5985,13 +5965,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>11.48</v>
+        <v>19.55</v>
       </c>
       <c r="K69" t="n">
-        <v>13.2</v>
+        <v>20.34</v>
       </c>
       <c r="L69" t="n">
-        <v>-17.46</v>
+        <v>-5.38</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -6007,10 +5987,10 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>41.86</v>
+        <v>21.57</v>
       </c>
       <c r="S69" t="n">
-        <v>34.35</v>
+        <v>26.39</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6024,39 +6004,39 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27.25</v>
+        <v>62.8</v>
       </c>
       <c r="C70" t="n">
-        <v>59.67</v>
+        <v>415.59</v>
       </c>
       <c r="D70" t="n">
-        <v>2189600</v>
+        <v>6617700</v>
       </c>
       <c r="E70" t="n">
-        <v>2367160</v>
+        <v>3158465</v>
       </c>
       <c r="F70" t="n">
-        <v>0.92</v>
+        <v>2.1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6065,20 +6045,24 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>31.42</v>
+        <v>70.8</v>
       </c>
       <c r="K70" t="n">
-        <v>32.59</v>
+        <v>70.8</v>
       </c>
       <c r="L70" t="n">
-        <v>-16.39</v>
+        <v>-11.3</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
@@ -6087,51 +6071,51 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>21.65</v>
+        <v>7.45</v>
       </c>
       <c r="S70" t="n">
-        <v>32.78</v>
+        <v>14.93</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TLG</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>55.5</v>
+        <v>32.9</v>
       </c>
       <c r="C71" t="n">
-        <v>21.33</v>
+        <v>528.76</v>
       </c>
       <c r="D71" t="n">
-        <v>384300</v>
+        <v>16071800</v>
       </c>
       <c r="E71" t="n">
-        <v>272705</v>
+        <v>18305860</v>
       </c>
       <c r="F71" t="n">
-        <v>1.41</v>
+        <v>0.88</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6145,13 +6129,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>51.15</v>
+        <v>31.5</v>
       </c>
       <c r="K71" t="n">
-        <v>51.15</v>
+        <v>31.5</v>
       </c>
       <c r="L71" t="n">
-        <v>8.5</v>
+        <v>4.44</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -6171,14 +6155,14 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>67.19</v>
+        <v>45.57</v>
       </c>
       <c r="S71" t="n">
-        <v>73.93000000000001</v>
+        <v>53.32</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -6188,34 +6172,34 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="C72" t="n">
-        <v>105.25</v>
+        <v>90.73</v>
       </c>
       <c r="D72" t="n">
-        <v>8995700</v>
+        <v>8173800</v>
       </c>
       <c r="E72" t="n">
-        <v>9335380</v>
+        <v>4120340</v>
       </c>
       <c r="F72" t="n">
-        <v>0.96</v>
+        <v>1.98</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6229,13 +6213,13 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>12.32</v>
+        <v>11.48</v>
       </c>
       <c r="K72" t="n">
-        <v>12.72</v>
+        <v>13.2</v>
       </c>
       <c r="L72" t="n">
-        <v>-8.02</v>
+        <v>-15.94</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -6251,10 +6235,10 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>21.93</v>
+        <v>45.65</v>
       </c>
       <c r="S72" t="n">
-        <v>35.03</v>
+        <v>46.5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6268,34 +6252,34 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>56.3</v>
+        <v>27.65</v>
       </c>
       <c r="C73" t="n">
-        <v>121.34</v>
+        <v>96.38</v>
       </c>
       <c r="D73" t="n">
-        <v>2155300</v>
+        <v>3485800</v>
       </c>
       <c r="E73" t="n">
-        <v>3583060</v>
+        <v>2408630</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6</v>
+        <v>1.45</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6309,13 +6293,13 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>57</v>
+        <v>31.42</v>
       </c>
       <c r="K73" t="n">
-        <v>59.12</v>
+        <v>32.59</v>
       </c>
       <c r="L73" t="n">
-        <v>-4.78</v>
+        <v>-15.16</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -6331,10 +6315,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>21.87</v>
+        <v>27.88</v>
       </c>
       <c r="S73" t="n">
-        <v>27.19</v>
+        <v>41.48</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -6348,30 +6332,30 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>14.2</v>
+        <v>11.75</v>
       </c>
       <c r="C74" t="n">
-        <v>27.49</v>
+        <v>136.01</v>
       </c>
       <c r="D74" t="n">
-        <v>1935700</v>
+        <v>11575100</v>
       </c>
       <c r="E74" t="n">
-        <v>1709225</v>
+        <v>9473775</v>
       </c>
       <c r="F74" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -6389,13 +6373,13 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>15.7</v>
+        <v>12.2</v>
       </c>
       <c r="K74" t="n">
-        <v>17.1</v>
+        <v>12.72</v>
       </c>
       <c r="L74" t="n">
-        <v>-16.98</v>
+        <v>-7.63</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6411,10 +6395,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>53.66</v>
+        <v>27.27</v>
       </c>
       <c r="S74" t="n">
-        <v>57.7</v>
+        <v>44.21</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -6428,34 +6412,34 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>18.6</v>
+        <v>56.5</v>
       </c>
       <c r="C75" t="n">
-        <v>155.33</v>
+        <v>133.8</v>
       </c>
       <c r="D75" t="n">
-        <v>8351100</v>
+        <v>2368200</v>
       </c>
       <c r="E75" t="n">
-        <v>8324800</v>
+        <v>3431675</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6469,13 +6453,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>21.22</v>
+        <v>57</v>
       </c>
       <c r="K75" t="n">
-        <v>23.4</v>
+        <v>59.12</v>
       </c>
       <c r="L75" t="n">
-        <v>-20.51</v>
+        <v>-4.44</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6491,10 +6475,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>30.77</v>
+        <v>27.27</v>
       </c>
       <c r="S75" t="n">
-        <v>31.57</v>
+        <v>35.51</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6508,34 +6492,34 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26.95</v>
+        <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>28.21</v>
+        <v>76.48</v>
       </c>
       <c r="D76" t="n">
-        <v>1046800</v>
+        <v>5098400</v>
       </c>
       <c r="E76" t="n">
-        <v>1850930</v>
+        <v>1863240</v>
       </c>
       <c r="F76" t="n">
-        <v>0.57</v>
+        <v>2.74</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6549,13 +6533,13 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>29.45</v>
+        <v>15.7</v>
       </c>
       <c r="K76" t="n">
-        <v>32.12</v>
+        <v>17.1</v>
       </c>
       <c r="L76" t="n">
-        <v>-16.11</v>
+        <v>-12.31</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6567,14 +6551,14 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>27.5</v>
+        <v>66.67</v>
       </c>
       <c r="S76" t="n">
-        <v>30.92</v>
+        <v>68.67</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6588,30 +6572,30 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>39.5</v>
+        <v>18.85</v>
       </c>
       <c r="C77" t="n">
-        <v>52.73</v>
+        <v>250.07</v>
       </c>
       <c r="D77" t="n">
-        <v>1335000</v>
+        <v>13266500</v>
       </c>
       <c r="E77" t="n">
-        <v>470910</v>
+        <v>8070955</v>
       </c>
       <c r="F77" t="n">
-        <v>2.83</v>
+        <v>1.64</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6620,26 +6604,26 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>36.7</v>
+        <v>20.98</v>
       </c>
       <c r="K77" t="n">
-        <v>36.4</v>
+        <v>23.28</v>
       </c>
       <c r="L77" t="n">
-        <v>8.52</v>
+        <v>-19.01</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -6651,10 +6635,10 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>88.23999999999999</v>
+        <v>37.66</v>
       </c>
       <c r="S77" t="n">
-        <v>73.53</v>
+        <v>42.44</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6663,70 +6647,66 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VGC</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>43.75</v>
+        <v>27.9</v>
       </c>
       <c r="C78" t="n">
-        <v>23.6</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>539500</v>
+        <v>3336900</v>
       </c>
       <c r="E78" t="n">
-        <v>633745</v>
+        <v>1841350</v>
       </c>
       <c r="F78" t="n">
-        <v>0.85</v>
+        <v>1.81</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>40.17</v>
+        <v>29.32</v>
       </c>
       <c r="K78" t="n">
-        <v>40.17</v>
+        <v>32.12</v>
       </c>
       <c r="L78" t="n">
-        <v>8.9</v>
+        <v>-13.15</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
@@ -6735,75 +6715,75 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>57.54</v>
+        <v>43.62</v>
       </c>
       <c r="S78" t="n">
-        <v>61.53</v>
+        <v>42.82</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>61</v>
+        <v>38.8</v>
       </c>
       <c r="C79" t="n">
-        <v>696.64</v>
+        <v>43.51</v>
       </c>
       <c r="D79" t="n">
-        <v>11420400</v>
+        <v>1121300</v>
       </c>
       <c r="E79" t="n">
-        <v>8941585</v>
+        <v>483735</v>
       </c>
       <c r="F79" t="n">
-        <v>1.28</v>
+        <v>2.32</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>71.34999999999999</v>
+        <v>36.8</v>
       </c>
       <c r="K79" t="n">
-        <v>70.18000000000001</v>
+        <v>36.5</v>
       </c>
       <c r="L79" t="n">
-        <v>-13.07</v>
+        <v>6.3</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -6815,51 +6795,51 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>37.06</v>
+        <v>75</v>
       </c>
       <c r="S79" t="n">
-        <v>45.99</v>
+        <v>62.47</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13.95</v>
+        <v>58.9</v>
       </c>
       <c r="C80" t="n">
-        <v>120.9</v>
+        <v>678.33</v>
       </c>
       <c r="D80" t="n">
-        <v>8666400</v>
+        <v>11516700</v>
       </c>
       <c r="E80" t="n">
-        <v>5181375</v>
+        <v>9108050</v>
       </c>
       <c r="F80" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6869,24 +6849,28 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>13.72</v>
+        <v>70.25</v>
       </c>
       <c r="K80" t="n">
-        <v>14.23</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>-1.97</v>
+        <v>-16.07</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
@@ -6895,14 +6879,14 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>63.89</v>
+        <v>16.88</v>
       </c>
       <c r="S80" t="n">
-        <v>80.92</v>
+        <v>35.14</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -6912,30 +6896,30 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VIB</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>218.4</v>
+        <v>13.8</v>
       </c>
       <c r="C81" t="n">
-        <v>680.5599999999999</v>
+        <v>61.55</v>
       </c>
       <c r="D81" t="n">
-        <v>3116100</v>
+        <v>4460300</v>
       </c>
       <c r="E81" t="n">
-        <v>3296815</v>
+        <v>5150250</v>
       </c>
       <c r="F81" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -6949,21 +6933,21 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>229.8</v>
+        <v>13.6</v>
       </c>
       <c r="K81" t="n">
-        <v>207.1</v>
+        <v>14.23</v>
       </c>
       <c r="L81" t="n">
-        <v>5.46</v>
+        <v>-3.02</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6975,14 +6959,14 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>37.28</v>
+        <v>60.53</v>
       </c>
       <c r="S81" t="n">
-        <v>30.48</v>
+        <v>78.53</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -6992,39 +6976,39 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>11.5</v>
+        <v>218</v>
       </c>
       <c r="C82" t="n">
-        <v>229.92</v>
+        <v>947.99</v>
       </c>
       <c r="D82" t="n">
-        <v>19992800</v>
+        <v>4348600</v>
       </c>
       <c r="E82" t="n">
-        <v>25983010</v>
+        <v>3316670</v>
       </c>
       <c r="F82" t="n">
-        <v>0.77</v>
+        <v>1.31</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7033,17 +7017,17 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>12.86</v>
+        <v>229.8</v>
       </c>
       <c r="K82" t="n">
-        <v>14.95</v>
+        <v>207.15</v>
       </c>
       <c r="L82" t="n">
-        <v>-23.08</v>
+        <v>5.24</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -7055,71 +7039,71 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>23.4</v>
+        <v>34.09</v>
       </c>
       <c r="S82" t="n">
-        <v>23.23</v>
+        <v>24.91</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VJC</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>128.1</v>
+        <v>11.75</v>
       </c>
       <c r="C83" t="n">
-        <v>93.38</v>
+        <v>508.62</v>
       </c>
       <c r="D83" t="n">
-        <v>729000</v>
+        <v>43287200</v>
       </c>
       <c r="E83" t="n">
-        <v>1013185</v>
+        <v>26188705</v>
       </c>
       <c r="F83" t="n">
-        <v>0.72</v>
+        <v>1.65</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>128.05</v>
+        <v>12.82</v>
       </c>
       <c r="K83" t="n">
-        <v>132.12</v>
+        <v>14.95</v>
       </c>
       <c r="L83" t="n">
-        <v>-3.05</v>
+        <v>-21.4</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7135,47 +7119,47 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>28.09</v>
+        <v>32</v>
       </c>
       <c r="S83" t="n">
-        <v>27.78</v>
+        <v>33.38</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>VJC</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>13</v>
+        <v>127.3</v>
       </c>
       <c r="C84" t="n">
-        <v>116.61</v>
+        <v>107.49</v>
       </c>
       <c r="D84" t="n">
-        <v>8969800</v>
+        <v>844400</v>
       </c>
       <c r="E84" t="n">
-        <v>9767160</v>
+        <v>992595</v>
       </c>
       <c r="F84" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7189,17 +7173,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>15.25</v>
+        <v>128.05</v>
       </c>
       <c r="K84" t="n">
-        <v>15.85</v>
+        <v>132.12</v>
       </c>
       <c r="L84" t="n">
-        <v>-17.98</v>
+        <v>-3.65</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -7215,10 +7199,10 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>26.56</v>
+        <v>19.1</v>
       </c>
       <c r="S84" t="n">
-        <v>20.04</v>
+        <v>20.43</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7232,39 +7216,39 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>57.9</v>
+        <v>13.25</v>
       </c>
       <c r="C85" t="n">
-        <v>68.26000000000001</v>
+        <v>177.85</v>
       </c>
       <c r="D85" t="n">
-        <v>1179000</v>
+        <v>13423000</v>
       </c>
       <c r="E85" t="n">
-        <v>2155455</v>
+        <v>9723370</v>
       </c>
       <c r="F85" t="n">
-        <v>0.55</v>
+        <v>1.38</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7273,13 +7257,13 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>59.8</v>
+        <v>15.23</v>
       </c>
       <c r="K85" t="n">
-        <v>59.5</v>
+        <v>15.85</v>
       </c>
       <c r="L85" t="n">
-        <v>-2.69</v>
+        <v>-16.4</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -7295,47 +7279,47 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>32</v>
+        <v>33.33</v>
       </c>
       <c r="S85" t="n">
-        <v>25.94</v>
+        <v>28.73</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VPB</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>24.35</v>
+        <v>57.2</v>
       </c>
       <c r="C86" t="n">
-        <v>310.49</v>
+        <v>113.37</v>
       </c>
       <c r="D86" t="n">
-        <v>12751000</v>
+        <v>1982000</v>
       </c>
       <c r="E86" t="n">
-        <v>21787460</v>
+        <v>2132700</v>
       </c>
       <c r="F86" t="n">
-        <v>0.59</v>
+        <v>0.93</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7349,48 +7333,40 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>21.98</v>
+        <v>59.8</v>
       </c>
       <c r="K86" t="n">
-        <v>21.98</v>
+        <v>59.5</v>
       </c>
       <c r="L86" t="n">
-        <v>10.81</v>
+        <v>-3.87</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>82.61</v>
+        <v>32.43</v>
       </c>
       <c r="S86" t="n">
-        <v>81.8</v>
+        <v>26.04</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -7400,34 +7376,34 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>VPB</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>50.6</v>
+        <v>24.45</v>
       </c>
       <c r="C87" t="n">
-        <v>140.16</v>
+        <v>528.5599999999999</v>
       </c>
       <c r="D87" t="n">
-        <v>2770000</v>
+        <v>21617900</v>
       </c>
       <c r="E87" t="n">
-        <v>1515905</v>
+        <v>21280150</v>
       </c>
       <c r="F87" t="n">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7437,21 +7413,21 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>56.28</v>
+        <v>21.98</v>
       </c>
       <c r="K87" t="n">
-        <v>56.28</v>
+        <v>21.98</v>
       </c>
       <c r="L87" t="n">
-        <v>-10.08</v>
+        <v>11.26</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -7467,14 +7443,14 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>10.56</v>
+        <v>77.36</v>
       </c>
       <c r="S87" t="n">
-        <v>17.09</v>
+        <v>79.83</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -7484,39 +7460,39 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VPL</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>76</v>
+        <v>49.4</v>
       </c>
       <c r="C88" t="n">
-        <v>66.66</v>
+        <v>120.23</v>
       </c>
       <c r="D88" t="n">
-        <v>877100</v>
+        <v>2433900</v>
       </c>
       <c r="E88" t="n">
-        <v>886715</v>
+        <v>1555985</v>
       </c>
       <c r="F88" t="n">
-        <v>0.99</v>
+        <v>1.56</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7525,20 +7501,24 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>79.84999999999999</v>
+        <v>56.18</v>
       </c>
       <c r="K88" t="n">
-        <v>85.5</v>
+        <v>56.18</v>
       </c>
       <c r="L88" t="n">
-        <v>-11.11</v>
+        <v>-12.06</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
@@ -7547,47 +7527,47 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>43.83</v>
+        <v>7.33</v>
       </c>
       <c r="S88" t="n">
-        <v>34.96</v>
+        <v>8.25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VRE</t>
+          <t>VPL</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>22.4</v>
+        <v>77</v>
       </c>
       <c r="C89" t="n">
-        <v>52.16</v>
+        <v>49.1</v>
       </c>
       <c r="D89" t="n">
-        <v>2328500</v>
+        <v>637600</v>
       </c>
       <c r="E89" t="n">
-        <v>3671415</v>
+        <v>853145</v>
       </c>
       <c r="F89" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7605,13 +7585,13 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>24.42</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K89" t="n">
-        <v>28.56</v>
+        <v>85.5</v>
       </c>
       <c r="L89" t="n">
-        <v>-21.57</v>
+        <v>-9.94</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7627,10 +7607,10 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>23.88</v>
+        <v>41.29</v>
       </c>
       <c r="S89" t="n">
-        <v>22.95</v>
+        <v>29.5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -7644,30 +7624,30 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VSC</t>
+          <t>VRE</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>12.8</v>
+        <v>22.6</v>
       </c>
       <c r="C90" t="n">
-        <v>81.76000000000001</v>
+        <v>61.25</v>
       </c>
       <c r="D90" t="n">
-        <v>6387500</v>
+        <v>2710100</v>
       </c>
       <c r="E90" t="n">
-        <v>7274950</v>
+        <v>3581785</v>
       </c>
       <c r="F90" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7685,13 +7665,13 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>14.38</v>
+        <v>24.42</v>
       </c>
       <c r="K90" t="n">
-        <v>18.98</v>
+        <v>28.56</v>
       </c>
       <c r="L90" t="n">
-        <v>-32.54</v>
+        <v>-20.87</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -7707,10 +7687,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>45.16</v>
+        <v>20.31</v>
       </c>
       <c r="S90" t="n">
-        <v>36.43</v>
+        <v>14.07</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7724,30 +7704,30 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VTP</t>
+          <t>VSC</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>45.25</v>
+        <v>12.9</v>
       </c>
       <c r="C91" t="n">
-        <v>21.4</v>
+        <v>83.36</v>
       </c>
       <c r="D91" t="n">
-        <v>473000</v>
+        <v>6461800</v>
       </c>
       <c r="E91" t="n">
-        <v>790405</v>
+        <v>7213130</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7765,13 +7745,13 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>50.75</v>
+        <v>14.15</v>
       </c>
       <c r="K91" t="n">
-        <v>53.86</v>
+        <v>18.98</v>
       </c>
       <c r="L91" t="n">
-        <v>-15.99</v>
+        <v>-32.02</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -7787,10 +7767,10 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>19.25</v>
+        <v>44.26</v>
       </c>
       <c r="S91" t="n">
-        <v>42.33</v>
+        <v>36.7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7804,30 +7784,30 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VTZ</t>
+          <t>VTP</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>20.2</v>
+        <v>46.5</v>
       </c>
       <c r="C92" t="n">
-        <v>20.92</v>
+        <v>26.42</v>
       </c>
       <c r="D92" t="n">
-        <v>1035700</v>
+        <v>568100</v>
       </c>
       <c r="E92" t="n">
-        <v>1052705</v>
+        <v>804005</v>
       </c>
       <c r="F92" t="n">
-        <v>0.98</v>
+        <v>0.71</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -7845,13 +7825,13 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>20.45</v>
+        <v>50.75</v>
       </c>
       <c r="K92" t="n">
-        <v>21.25</v>
+        <v>53.44</v>
       </c>
       <c r="L92" t="n">
-        <v>-4.94</v>
+        <v>-12.99</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -7867,10 +7847,10 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>44.44</v>
+        <v>25.77</v>
       </c>
       <c r="S92" t="n">
-        <v>36.6</v>
+        <v>40.6</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7884,7 +7864,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-14 21:13:10</t>
+          <t>2026-10-15 20:55:47</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V92"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,16 +538,16 @@
         <v>20.6</v>
       </c>
       <c r="C2" t="n">
-        <v>122.1</v>
+        <v>106.3</v>
       </c>
       <c r="D2" t="n">
-        <v>5927200</v>
+        <v>5160300</v>
       </c>
       <c r="E2" t="n">
-        <v>7662165</v>
+        <v>7396385</v>
       </c>
       <c r="F2" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -587,14 +587,14 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>28.95</v>
+        <v>34.38</v>
       </c>
       <c r="S2" t="n">
-        <v>30.81</v>
+        <v>37.53</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -604,34 +604,34 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAF</t>
+          <t>ACV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>41.4</v>
       </c>
       <c r="C3" t="n">
-        <v>26.53</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>855900</v>
+        <v>1679000</v>
       </c>
       <c r="E3" t="n">
-        <v>1643195</v>
+        <v>475280</v>
       </c>
       <c r="F3" t="n">
-        <v>0.52</v>
+        <v>3.53</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -641,21 +641,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>30.72</v>
+        <v>39.9</v>
       </c>
       <c r="K3" t="n">
-        <v>29.96</v>
+        <v>42.1</v>
       </c>
       <c r="L3" t="n">
-        <v>3.47</v>
+        <v>-1.66</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -663,18 +663,18 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.5x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>32.65</v>
+        <v>75</v>
       </c>
       <c r="S3" t="n">
-        <v>51.37</v>
+        <v>74.27</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -684,30 +684,30 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>BAF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.2</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>103.42</v>
+        <v>35.61</v>
       </c>
       <c r="D4" t="n">
-        <v>3115000</v>
+        <v>1148800</v>
       </c>
       <c r="E4" t="n">
-        <v>3543305</v>
+        <v>1619250</v>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -716,26 +716,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>35</v>
+        <v>30.72</v>
       </c>
       <c r="K4" t="n">
-        <v>37.54</v>
+        <v>29.96</v>
       </c>
       <c r="L4" t="n">
-        <v>-11.56</v>
+        <v>3.47</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -747,75 +747,75 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>9.52</v>
+        <v>34.04</v>
       </c>
       <c r="S4" t="n">
-        <v>28.66</v>
+        <v>44.95</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.2</v>
+        <v>33.95</v>
       </c>
       <c r="C5" t="n">
-        <v>567.49</v>
+        <v>116.77</v>
       </c>
       <c r="D5" t="n">
-        <v>20123900</v>
+        <v>3439500</v>
       </c>
       <c r="E5" t="n">
-        <v>11687295</v>
+        <v>3088950</v>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>27.9</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
-        <v>27.96</v>
+        <v>37.54</v>
       </c>
       <c r="L5" t="n">
-        <v>0.86</v>
+        <v>-9.56</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -827,51 +827,51 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>38.54</v>
+        <v>26.92</v>
       </c>
       <c r="S5" t="n">
-        <v>36.63</v>
+        <v>37.95</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71.40000000000001</v>
+        <v>28.35</v>
       </c>
       <c r="C6" t="n">
-        <v>103.62</v>
+        <v>212.64</v>
       </c>
       <c r="D6" t="n">
-        <v>1451300</v>
+        <v>7500700</v>
       </c>
       <c r="E6" t="n">
-        <v>1027765</v>
+        <v>11220065</v>
       </c>
       <c r="F6" t="n">
-        <v>1.41</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>67.09999999999999</v>
+        <v>27.9</v>
       </c>
       <c r="K6" t="n">
-        <v>67.7</v>
+        <v>27.96</v>
       </c>
       <c r="L6" t="n">
-        <v>5.47</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -907,14 +907,14 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>56.5</v>
+        <v>23.87</v>
       </c>
       <c r="S6" t="n">
-        <v>62.92</v>
+        <v>28.68</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -924,61 +924,65 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.5</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>31.03</v>
+        <v>53.78</v>
       </c>
       <c r="D7" t="n">
-        <v>1170900</v>
+        <v>746900</v>
       </c>
       <c r="E7" t="n">
-        <v>585380</v>
+        <v>1030980</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0.72</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28.45</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>29.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-11.37</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
@@ -987,24 +991,24 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>38.1</v>
+        <v>44.94</v>
       </c>
       <c r="S7" t="n">
-        <v>39.93</v>
+        <v>50.47</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
@@ -1018,20 +1022,20 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>113.72</v>
+        <v>57.27</v>
       </c>
       <c r="D8" t="n">
-        <v>10337800</v>
+        <v>5206500</v>
       </c>
       <c r="E8" t="n">
-        <v>5935845</v>
+        <v>5818060</v>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>0.89</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1049,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>11.95</v>
       </c>
       <c r="K8" t="n">
         <v>13.61</v>
@@ -1067,10 +1071,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>46.43</v>
+        <v>50</v>
       </c>
       <c r="S8" t="n">
-        <v>60.5</v>
+        <v>69.7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1084,7 +1088,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
@@ -1095,23 +1099,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.95</v>
+        <v>12.8</v>
       </c>
       <c r="C9" t="n">
-        <v>247.44</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>19107700</v>
+        <v>5454500</v>
       </c>
       <c r="E9" t="n">
-        <v>6841965</v>
+        <v>6863805</v>
       </c>
       <c r="F9" t="n">
-        <v>2.79</v>
+        <v>0.79</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1125,13 +1129,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14.02</v>
+        <v>13.98</v>
       </c>
       <c r="K9" t="n">
         <v>16.08</v>
       </c>
       <c r="L9" t="n">
-        <v>-19.44</v>
+        <v>-20.37</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1143,14 +1147,14 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.8x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>54.22</v>
+        <v>56.96</v>
       </c>
       <c r="S9" t="n">
-        <v>54.53</v>
+        <v>62.05</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1164,30 +1168,30 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>CTG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.6</v>
+        <v>30.6</v>
       </c>
       <c r="C10" t="n">
-        <v>24.28</v>
+        <v>312.12</v>
       </c>
       <c r="D10" t="n">
-        <v>1028700</v>
+        <v>10200000</v>
       </c>
       <c r="E10" t="n">
-        <v>383125</v>
+        <v>6597160</v>
       </c>
       <c r="F10" t="n">
-        <v>2.69</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1196,22 +1200,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>22.18</v>
+        <v>30.7</v>
       </c>
       <c r="K10" t="n">
-        <v>24.12</v>
+        <v>32.32</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.18</v>
+        <v>-5.32</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1223,75 +1227,75 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>78.63</v>
+        <v>61.19</v>
       </c>
       <c r="S10" t="n">
-        <v>84.38</v>
+        <v>51.46</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CTD</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>21.1</v>
       </c>
       <c r="C11" t="n">
-        <v>29.23</v>
+        <v>52.09</v>
       </c>
       <c r="D11" t="n">
-        <v>464000</v>
+        <v>2468600</v>
       </c>
       <c r="E11" t="n">
-        <v>321035</v>
+        <v>967835</v>
       </c>
       <c r="F11" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>61.25</v>
+        <v>23.38</v>
       </c>
       <c r="K11" t="n">
-        <v>72.5</v>
+        <v>24.1</v>
       </c>
       <c r="L11" t="n">
-        <v>-13.1</v>
+        <v>-12.45</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1303,51 +1307,51 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>68.75</v>
+        <v>57.5</v>
       </c>
       <c r="S11" t="n">
-        <v>67.48999999999999</v>
+        <v>34.35</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CTG</t>
+          <t>DCL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29.8</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>259.24</v>
+        <v>90.38</v>
       </c>
       <c r="D12" t="n">
-        <v>8699300</v>
+        <v>1807700</v>
       </c>
       <c r="E12" t="n">
-        <v>6795660</v>
+        <v>1274350</v>
       </c>
       <c r="F12" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1356,30 +1360,34 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>30.7</v>
+        <v>43.2</v>
       </c>
       <c r="K12" t="n">
-        <v>32.32</v>
+        <v>42.32</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.8</v>
+        <v>18.13</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1387,71 +1395,71 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>43.86</v>
+        <v>61.82</v>
       </c>
       <c r="S12" t="n">
-        <v>38.58</v>
+        <v>59.73</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20.45</v>
+        <v>33.9</v>
       </c>
       <c r="C13" t="n">
-        <v>34.72</v>
+        <v>48.15</v>
       </c>
       <c r="D13" t="n">
-        <v>1697900</v>
+        <v>1420400</v>
       </c>
       <c r="E13" t="n">
-        <v>895210</v>
+        <v>2634980</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>0.54</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>23.38</v>
+        <v>31.95</v>
       </c>
       <c r="K13" t="n">
-        <v>24.1</v>
+        <v>36.94</v>
       </c>
       <c r="L13" t="n">
-        <v>-15.15</v>
+        <v>-8.23</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1467,78 +1475,82 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>40.74</v>
+        <v>42.35</v>
       </c>
       <c r="S13" t="n">
-        <v>17.34</v>
+        <v>54.44</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.65</v>
+        <v>44.5</v>
       </c>
       <c r="C14" t="n">
-        <v>36.93</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>2359900</v>
+        <v>1709500</v>
       </c>
       <c r="E14" t="n">
-        <v>1343330</v>
+        <v>1726250</v>
       </c>
       <c r="F14" t="n">
-        <v>1.76</v>
+        <v>0.99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16.38</v>
+        <v>39.83</v>
       </c>
       <c r="K14" t="n">
-        <v>18.15</v>
+        <v>39.83</v>
       </c>
       <c r="L14" t="n">
-        <v>-13.77</v>
+        <v>11.72</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
@@ -1547,47 +1559,47 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>48.94</v>
+        <v>49.71</v>
       </c>
       <c r="S14" t="n">
-        <v>51.36</v>
+        <v>44.05</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46.8</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>28.2</v>
+        <v>30.16</v>
       </c>
       <c r="D15" t="n">
-        <v>602500</v>
+        <v>3165000</v>
       </c>
       <c r="E15" t="n">
-        <v>1329525</v>
+        <v>3986930</v>
       </c>
       <c r="F15" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1596,26 +1608,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>43.2</v>
+        <v>10.32</v>
       </c>
       <c r="K15" t="n">
-        <v>42.32</v>
+        <v>11.52</v>
       </c>
       <c r="L15" t="n">
-        <v>10.57</v>
+        <v>-17.31</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1627,47 +1639,47 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>51.28</v>
+        <v>59.74</v>
       </c>
       <c r="S15" t="n">
-        <v>43.52</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33.9</v>
+        <v>21.2</v>
       </c>
       <c r="C16" t="n">
-        <v>57.04</v>
+        <v>23.15</v>
       </c>
       <c r="D16" t="n">
-        <v>1682600</v>
+        <v>1092200</v>
       </c>
       <c r="E16" t="n">
-        <v>2748735</v>
+        <v>2569690</v>
       </c>
       <c r="F16" t="n">
-        <v>0.61</v>
+        <v>0.43</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1676,22 +1688,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31.95</v>
+        <v>22.18</v>
       </c>
       <c r="K16" t="n">
-        <v>36.94</v>
+        <v>24.2</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.23</v>
+        <v>-12.41</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1707,82 +1719,78 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>47.87</v>
+        <v>24.24</v>
       </c>
       <c r="S16" t="n">
-        <v>62.65</v>
+        <v>25.55</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.05</v>
+        <v>10.15</v>
       </c>
       <c r="C17" t="n">
-        <v>38.81</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>861500</v>
+        <v>9690100</v>
       </c>
       <c r="E17" t="n">
-        <v>1721555</v>
+        <v>8391430</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5</v>
+        <v>1.15</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.83</v>
+        <v>10.88</v>
       </c>
       <c r="K17" t="n">
-        <v>39.83</v>
+        <v>11.89</v>
       </c>
       <c r="L17" t="n">
-        <v>13.11</v>
+        <v>-14.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
@@ -1791,51 +1799,51 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>58.31</v>
+        <v>48.25</v>
       </c>
       <c r="S17" t="n">
-        <v>51.67</v>
+        <v>48.11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9.6</v>
+        <v>16.35</v>
       </c>
       <c r="C18" t="n">
-        <v>70.34</v>
+        <v>47.2</v>
       </c>
       <c r="D18" t="n">
-        <v>7326800</v>
+        <v>2886900</v>
       </c>
       <c r="E18" t="n">
-        <v>3979130</v>
+        <v>3193350</v>
       </c>
       <c r="F18" t="n">
-        <v>1.84</v>
+        <v>0.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1849,13 +1857,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10.37</v>
+        <v>17.65</v>
       </c>
       <c r="K18" t="n">
-        <v>11.52</v>
+        <v>19.65</v>
       </c>
       <c r="L18" t="n">
-        <v>-16.7</v>
+        <v>-16.79</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1871,10 +1879,10 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>49.2</v>
+        <v>38.89</v>
       </c>
       <c r="S18" t="n">
-        <v>65.05</v>
+        <v>48.59</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1888,30 +1896,30 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21.2</v>
+        <v>58.2</v>
       </c>
       <c r="C19" t="n">
-        <v>35.45</v>
+        <v>217.28</v>
       </c>
       <c r="D19" t="n">
-        <v>1672300</v>
+        <v>3733300</v>
       </c>
       <c r="E19" t="n">
-        <v>2673905</v>
+        <v>5238545</v>
       </c>
       <c r="F19" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1929,13 +1937,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>22.18</v>
+        <v>61.9</v>
       </c>
       <c r="K19" t="n">
-        <v>24.2</v>
+        <v>63.22</v>
       </c>
       <c r="L19" t="n">
-        <v>-12.41</v>
+        <v>-7.94</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1951,10 +1959,10 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>30.56</v>
+        <v>20.43</v>
       </c>
       <c r="S19" t="n">
-        <v>23.61</v>
+        <v>20.4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1968,30 +1976,30 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.8</v>
+        <v>141</v>
       </c>
       <c r="C20" t="n">
-        <v>20.34</v>
+        <v>26.55</v>
       </c>
       <c r="D20" t="n">
-        <v>1287200</v>
+        <v>188300</v>
       </c>
       <c r="E20" t="n">
-        <v>1816380</v>
+        <v>687395</v>
       </c>
       <c r="F20" t="n">
-        <v>0.71</v>
+        <v>0.27</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2009,13 +2017,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>14.34</v>
+        <v>126.5</v>
       </c>
       <c r="K20" t="n">
-        <v>14.34</v>
+        <v>126.5</v>
       </c>
       <c r="L20" t="n">
-        <v>10.22</v>
+        <v>11.46</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2035,14 +2043,14 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>56.36</v>
+        <v>51.48</v>
       </c>
       <c r="S20" t="n">
-        <v>55.55</v>
+        <v>73.7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2052,34 +2060,34 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.25</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>139.6</v>
+        <v>62.58</v>
       </c>
       <c r="D21" t="n">
-        <v>13619100</v>
+        <v>822300</v>
       </c>
       <c r="E21" t="n">
-        <v>8432400</v>
+        <v>1114940</v>
       </c>
       <c r="F21" t="n">
-        <v>1.62</v>
+        <v>0.74</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2089,17 +2097,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10.88</v>
+        <v>76.48</v>
       </c>
       <c r="K21" t="n">
-        <v>11.89</v>
+        <v>77.69</v>
       </c>
       <c r="L21" t="n">
-        <v>-13.76</v>
+        <v>-2.05</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2115,10 +2123,10 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>55.24</v>
+        <v>30.11</v>
       </c>
       <c r="S21" t="n">
-        <v>45.85</v>
+        <v>35.37</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2132,34 +2140,34 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.45</v>
+        <v>66</v>
       </c>
       <c r="C22" t="n">
-        <v>65.77</v>
+        <v>48.88</v>
       </c>
       <c r="D22" t="n">
-        <v>3998300</v>
+        <v>740600</v>
       </c>
       <c r="E22" t="n">
-        <v>3293455</v>
+        <v>1520955</v>
       </c>
       <c r="F22" t="n">
-        <v>1.21</v>
+        <v>0.49</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2169,17 +2177,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>17.65</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>19.9</v>
+        <v>95.83</v>
       </c>
       <c r="L22" t="n">
-        <v>-17.34</v>
+        <v>-31.13</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2195,10 +2203,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>42.86</v>
+        <v>37.02</v>
       </c>
       <c r="S22" t="n">
-        <v>56.86</v>
+        <v>45.58</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2212,39 +2220,39 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EVF</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11.55</v>
+        <v>27.5</v>
       </c>
       <c r="C23" t="n">
-        <v>29.17</v>
+        <v>23.43</v>
       </c>
       <c r="D23" t="n">
-        <v>2525900</v>
+        <v>851900</v>
       </c>
       <c r="E23" t="n">
-        <v>1187985</v>
+        <v>1378535</v>
       </c>
       <c r="F23" t="n">
-        <v>2.13</v>
+        <v>0.62</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2253,13 +2261,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11.95</v>
+        <v>27.15</v>
       </c>
       <c r="K23" t="n">
-        <v>12.75</v>
+        <v>29.42</v>
       </c>
       <c r="L23" t="n">
-        <v>-9.41</v>
+        <v>-6.54</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2275,51 +2283,51 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>47.06</v>
+        <v>33</v>
       </c>
       <c r="S23" t="n">
-        <v>45.41</v>
+        <v>40.93</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>58</v>
+        <v>22.5</v>
       </c>
       <c r="C24" t="n">
-        <v>287.94</v>
+        <v>175.16</v>
       </c>
       <c r="D24" t="n">
-        <v>4964400</v>
+        <v>7784900</v>
       </c>
       <c r="E24" t="n">
-        <v>5826915</v>
+        <v>5995305</v>
       </c>
       <c r="F24" t="n">
-        <v>0.85</v>
+        <v>1.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2333,13 +2341,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>61.9</v>
+        <v>23.45</v>
       </c>
       <c r="K24" t="n">
-        <v>63.32</v>
+        <v>28.58</v>
       </c>
       <c r="L24" t="n">
-        <v>-8.41</v>
+        <v>-21.26</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2355,10 +2363,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>16.83</v>
+        <v>34.44</v>
       </c>
       <c r="S24" t="n">
-        <v>15.14</v>
+        <v>40.1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2372,34 +2380,34 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="C25" t="n">
-        <v>33.37</v>
+        <v>95.22</v>
       </c>
       <c r="D25" t="n">
-        <v>236700</v>
+        <v>1763400</v>
       </c>
       <c r="E25" t="n">
-        <v>700170</v>
+        <v>1183475</v>
       </c>
       <c r="F25" t="n">
-        <v>0.34</v>
+        <v>1.49</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2413,13 +2421,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>126.5</v>
+        <v>50.34</v>
       </c>
       <c r="K25" t="n">
-        <v>126.5</v>
+        <v>50.34</v>
       </c>
       <c r="L25" t="n">
-        <v>11.46</v>
+        <v>7.28</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2439,10 +2447,10 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>48.74</v>
+        <v>64.05</v>
       </c>
       <c r="S25" t="n">
-        <v>69.86</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2456,54 +2464,54 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FTS</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18.7</v>
+        <v>31.25</v>
       </c>
       <c r="C26" t="n">
-        <v>32.75</v>
+        <v>35.69</v>
       </c>
       <c r="D26" t="n">
-        <v>1751200</v>
+        <v>1142000</v>
       </c>
       <c r="E26" t="n">
-        <v>636500</v>
+        <v>2788450</v>
       </c>
       <c r="F26" t="n">
-        <v>2.75</v>
+        <v>0.41</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>21.7</v>
+        <v>30.22</v>
       </c>
       <c r="K26" t="n">
-        <v>22.88</v>
+        <v>32.78</v>
       </c>
       <c r="L26" t="n">
-        <v>-18.25</v>
+        <v>-4.65</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2515,75 +2523,75 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.8x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>34.78</v>
+        <v>42.64</v>
       </c>
       <c r="S26" t="n">
-        <v>27.31</v>
+        <v>42.54</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>HAH</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>76.2</v>
+        <v>48.9</v>
       </c>
       <c r="C27" t="n">
-        <v>111.62</v>
+        <v>30.06</v>
       </c>
       <c r="D27" t="n">
-        <v>1464800</v>
+        <v>614700</v>
       </c>
       <c r="E27" t="n">
-        <v>1144425</v>
+        <v>1253470</v>
       </c>
       <c r="F27" t="n">
-        <v>1.28</v>
+        <v>0.49</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>76.48</v>
+        <v>48.2</v>
       </c>
       <c r="K27" t="n">
-        <v>77.69</v>
+        <v>49.55</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.92</v>
+        <v>-1.31</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2599,47 +2607,47 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>40</v>
+        <v>35.83</v>
       </c>
       <c r="S27" t="n">
-        <v>42.63</v>
+        <v>44.11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65.5</v>
+        <v>23.75</v>
       </c>
       <c r="C28" t="n">
-        <v>43.4</v>
+        <v>46.74</v>
       </c>
       <c r="D28" t="n">
-        <v>662600</v>
+        <v>1968100</v>
       </c>
       <c r="E28" t="n">
-        <v>1543535</v>
+        <v>2651300</v>
       </c>
       <c r="F28" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2648,7 +2656,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2657,13 +2665,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>70.04000000000001</v>
+        <v>24.92</v>
       </c>
       <c r="K28" t="n">
-        <v>95.83</v>
+        <v>24.39</v>
       </c>
       <c r="L28" t="n">
-        <v>-31.65</v>
+        <v>-2.62</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2679,51 +2687,51 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>34.33</v>
+        <v>48.42</v>
       </c>
       <c r="S28" t="n">
-        <v>39.6</v>
+        <v>32.38</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27.3</v>
+        <v>22.8</v>
       </c>
       <c r="C29" t="n">
-        <v>30.51</v>
+        <v>553.84</v>
       </c>
       <c r="D29" t="n">
-        <v>1117400</v>
+        <v>24291300</v>
       </c>
       <c r="E29" t="n">
-        <v>1451565</v>
+        <v>15602300</v>
       </c>
       <c r="F29" t="n">
-        <v>0.77</v>
+        <v>1.56</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2733,24 +2741,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>27.15</v>
+        <v>21.13</v>
       </c>
       <c r="K29" t="n">
-        <v>29.58</v>
+        <v>21.13</v>
       </c>
       <c r="L29" t="n">
-        <v>-7.69</v>
+        <v>7.9</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
@@ -2759,14 +2771,14 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>29.59</v>
+        <v>74.63</v>
       </c>
       <c r="S29" t="n">
-        <v>35.36</v>
+        <v>70.33</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -2776,58 +2788,58 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>HHP</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.4</v>
+        <v>17.25</v>
       </c>
       <c r="C30" t="n">
-        <v>128.85</v>
+        <v>29.39</v>
       </c>
       <c r="D30" t="n">
-        <v>5752100</v>
+        <v>1703500</v>
       </c>
       <c r="E30" t="n">
-        <v>6525795</v>
+        <v>1279170</v>
       </c>
       <c r="F30" t="n">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>23.45</v>
+        <v>16.34</v>
       </c>
       <c r="K30" t="n">
-        <v>28.58</v>
+        <v>15.31</v>
       </c>
       <c r="L30" t="n">
-        <v>-21.61</v>
+        <v>12.67</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2839,10 +2851,10 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>32.22</v>
+        <v>39.62</v>
       </c>
       <c r="S30" t="n">
-        <v>31.78</v>
+        <v>60.32</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2851,70 +2863,66 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>HHV</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53</v>
+        <v>9.5</v>
       </c>
       <c r="C31" t="n">
-        <v>50.39</v>
+        <v>26.26</v>
       </c>
       <c r="D31" t="n">
-        <v>950800</v>
+        <v>2764700</v>
       </c>
       <c r="E31" t="n">
-        <v>1134210</v>
+        <v>2555090</v>
       </c>
       <c r="F31" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>50.34</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>50.34</v>
+        <v>10.68</v>
       </c>
       <c r="L31" t="n">
-        <v>5.29</v>
+        <v>-11.09</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
@@ -2923,47 +2931,47 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>58.91</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="S31" t="n">
-        <v>64.52</v>
+        <v>63.2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30.9</v>
+        <v>20.9</v>
       </c>
       <c r="C32" t="n">
-        <v>58.92</v>
+        <v>212.96</v>
       </c>
       <c r="D32" t="n">
-        <v>1906800</v>
+        <v>10189400</v>
       </c>
       <c r="E32" t="n">
-        <v>2820785</v>
+        <v>17609270</v>
       </c>
       <c r="F32" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2972,22 +2980,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>30.22</v>
+        <v>21.12</v>
       </c>
       <c r="K32" t="n">
-        <v>32.78</v>
+        <v>22.94</v>
       </c>
       <c r="L32" t="n">
-        <v>-5.72</v>
+        <v>-8.91</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2996,54 +3004,58 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>35.29</v>
+        <v>63.46</v>
       </c>
       <c r="S32" t="n">
-        <v>38.06</v>
+        <v>48.86</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>48.2</v>
+        <v>10.4</v>
       </c>
       <c r="C33" t="n">
-        <v>41.43</v>
+        <v>21.74</v>
       </c>
       <c r="D33" t="n">
-        <v>859600</v>
+        <v>2090700</v>
       </c>
       <c r="E33" t="n">
-        <v>1246920</v>
+        <v>2464765</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3052,22 +3064,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>48.2</v>
+        <v>10.72</v>
       </c>
       <c r="K33" t="n">
-        <v>49.55</v>
+        <v>11.35</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.72</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3083,47 +3095,47 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>35.29</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="S33" t="n">
-        <v>48.91</v>
+        <v>58.34</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HVN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C34" t="n">
-        <v>111.47</v>
+        <v>28.58</v>
       </c>
       <c r="D34" t="n">
-        <v>4644700</v>
+        <v>1361100</v>
       </c>
       <c r="E34" t="n">
-        <v>2776190</v>
+        <v>555875</v>
       </c>
       <c r="F34" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3132,7 +3144,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3141,13 +3153,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>24.92</v>
+        <v>22.55</v>
       </c>
       <c r="K34" t="n">
-        <v>24.39</v>
+        <v>23.25</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.6</v>
+        <v>-9.68</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3163,82 +3175,78 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>41.82</v>
+        <v>57.14</v>
       </c>
       <c r="S34" t="n">
-        <v>24.94</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>KBC</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.8</v>
+        <v>25.9</v>
       </c>
       <c r="C35" t="n">
-        <v>407.29</v>
+        <v>22.63</v>
       </c>
       <c r="D35" t="n">
-        <v>17863600</v>
+        <v>873600</v>
       </c>
       <c r="E35" t="n">
-        <v>15673705</v>
+        <v>1131565</v>
       </c>
       <c r="F35" t="n">
-        <v>1.14</v>
+        <v>0.77</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>21.13</v>
+        <v>26.55</v>
       </c>
       <c r="K35" t="n">
-        <v>21.13</v>
+        <v>30.05</v>
       </c>
       <c r="L35" t="n">
-        <v>7.9</v>
+        <v>-13.81</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -3247,47 +3255,47 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>69.83</v>
+        <v>52.5</v>
       </c>
       <c r="S35" t="n">
-        <v>74.94</v>
+        <v>39.64</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HHP</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.2</v>
+        <v>14.15</v>
       </c>
       <c r="C36" t="n">
-        <v>44.52</v>
+        <v>107.85</v>
       </c>
       <c r="D36" t="n">
-        <v>2588500</v>
+        <v>7622200</v>
       </c>
       <c r="E36" t="n">
-        <v>1303410</v>
+        <v>3805180</v>
       </c>
       <c r="F36" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3296,26 +3304,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>16.34</v>
+        <v>15.54</v>
       </c>
       <c r="K36" t="n">
-        <v>15.31</v>
+        <v>18.75</v>
       </c>
       <c r="L36" t="n">
-        <v>12.34</v>
+        <v>-24.53</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3327,10 +3335,10 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>40.74</v>
+        <v>55.61</v>
       </c>
       <c r="S36" t="n">
-        <v>68.90000000000001</v>
+        <v>56.82</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3339,39 +3347,39 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HHV</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9.52</v>
+        <v>38</v>
       </c>
       <c r="C37" t="n">
-        <v>62.7</v>
+        <v>77.61</v>
       </c>
       <c r="D37" t="n">
-        <v>6586500</v>
+        <v>2042300</v>
       </c>
       <c r="E37" t="n">
-        <v>2526425</v>
+        <v>1976080</v>
       </c>
       <c r="F37" t="n">
-        <v>2.61</v>
+        <v>1.03</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3385,13 +3393,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9.630000000000001</v>
+        <v>46.6</v>
       </c>
       <c r="K37" t="n">
-        <v>10.68</v>
+        <v>47.85</v>
       </c>
       <c r="L37" t="n">
-        <v>-10.9</v>
+        <v>-20.59</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3403,14 +3411,14 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>62.13</v>
+        <v>28.69</v>
       </c>
       <c r="S37" t="n">
-        <v>55.35</v>
+        <v>25.27</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3424,58 +3432,58 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.75</v>
+        <v>19.85</v>
       </c>
       <c r="C38" t="n">
-        <v>439.08</v>
+        <v>216.75</v>
       </c>
       <c r="D38" t="n">
-        <v>21160300</v>
+        <v>10919400</v>
       </c>
       <c r="E38" t="n">
-        <v>18656045</v>
+        <v>11607255</v>
       </c>
       <c r="F38" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>21.12</v>
+        <v>19.49</v>
       </c>
       <c r="K38" t="n">
-        <v>22.94</v>
+        <v>19.7</v>
       </c>
       <c r="L38" t="n">
-        <v>-9.57</v>
+        <v>0.76</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3487,51 +3495,51 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>51.72</v>
+        <v>51.02</v>
       </c>
       <c r="S38" t="n">
-        <v>42.68</v>
+        <v>50.15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.45</v>
+        <v>15.1</v>
       </c>
       <c r="C39" t="n">
-        <v>41.03</v>
+        <v>33.2</v>
       </c>
       <c r="D39" t="n">
-        <v>3926400</v>
+        <v>2199000</v>
       </c>
       <c r="E39" t="n">
-        <v>2449520</v>
+        <v>2705290</v>
       </c>
       <c r="F39" t="n">
-        <v>1.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3545,13 +3553,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>10.72</v>
+        <v>16.77</v>
       </c>
       <c r="K39" t="n">
-        <v>11.35</v>
+        <v>17.43</v>
       </c>
       <c r="L39" t="n">
-        <v>-7.93</v>
+        <v>-13.39</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3567,10 +3575,10 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>64.33</v>
+        <v>38.46</v>
       </c>
       <c r="S39" t="n">
-        <v>57.68</v>
+        <v>39.2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3584,30 +3592,30 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12.2</v>
+        <v>140</v>
       </c>
       <c r="C40" t="n">
-        <v>28.61</v>
+        <v>83.19</v>
       </c>
       <c r="D40" t="n">
-        <v>2345200</v>
+        <v>594200</v>
       </c>
       <c r="E40" t="n">
-        <v>1703580</v>
+        <v>559540</v>
       </c>
       <c r="F40" t="n">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3616,26 +3624,26 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>13.35</v>
+        <v>138.57</v>
       </c>
       <c r="K40" t="n">
-        <v>14.5</v>
+        <v>134.54</v>
       </c>
       <c r="L40" t="n">
-        <v>-15.86</v>
+        <v>4.06</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3647,47 +3655,47 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>33.33</v>
+        <v>60.42</v>
       </c>
       <c r="S40" t="n">
-        <v>28.6</v>
+        <v>28.73</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>33.7</v>
+        <v>14.8</v>
       </c>
       <c r="C41" t="n">
-        <v>30.82</v>
+        <v>173.85</v>
       </c>
       <c r="D41" t="n">
-        <v>914600</v>
+        <v>11746800</v>
       </c>
       <c r="E41" t="n">
-        <v>1415335</v>
+        <v>12337480</v>
       </c>
       <c r="F41" t="n">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3696,7 +3704,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3705,21 +3713,25 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>32.45</v>
+        <v>13.56</v>
       </c>
       <c r="K41" t="n">
-        <v>36.67</v>
+        <v>12.66</v>
       </c>
       <c r="L41" t="n">
-        <v>-8.1</v>
+        <v>16.86</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3727,71 +3739,71 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>52.83</v>
+        <v>66.67</v>
       </c>
       <c r="S41" t="n">
-        <v>53.21</v>
+        <v>70.03</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13.65</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>54.76</v>
+        <v>215.18</v>
       </c>
       <c r="D42" t="n">
-        <v>4011700</v>
+        <v>3013700</v>
       </c>
       <c r="E42" t="n">
-        <v>3680700</v>
+        <v>5655410</v>
       </c>
       <c r="F42" t="n">
-        <v>1.09</v>
+        <v>0.53</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>15.57</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>18.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>-27.2</v>
+        <v>-0.97</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3807,79 +3819,87 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>34.5</v>
+        <v>58.33</v>
       </c>
       <c r="S42" t="n">
-        <v>43.49</v>
+        <v>64.47</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>37.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>97.23</v>
+        <v>108.27</v>
       </c>
       <c r="D43" t="n">
-        <v>2613600</v>
+        <v>1668200</v>
       </c>
       <c r="E43" t="n">
-        <v>1978575</v>
+        <v>2597615</v>
       </c>
       <c r="F43" t="n">
-        <v>1.32</v>
+        <v>0.64</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>46.6</v>
+        <v>50.57</v>
       </c>
       <c r="K43" t="n">
-        <v>47.85</v>
+        <v>50.57</v>
       </c>
       <c r="L43" t="n">
-        <v>-22.26</v>
+        <v>28.34</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3887,51 +3907,51 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>23.94</v>
+        <v>74.31</v>
       </c>
       <c r="S43" t="n">
-        <v>19.33</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>649.17</v>
+        <v>101.38</v>
       </c>
       <c r="D44" t="n">
-        <v>32621600</v>
+        <v>1371800</v>
       </c>
       <c r="E44" t="n">
-        <v>11903470</v>
+        <v>2873870</v>
       </c>
       <c r="F44" t="n">
-        <v>2.74</v>
+        <v>0.48</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3941,17 +3961,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>19.49</v>
+        <v>69.02</v>
       </c>
       <c r="K44" t="n">
-        <v>19.74</v>
+        <v>73.36</v>
       </c>
       <c r="L44" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3963,14 +3983,14 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>50</v>
+        <v>62.67</v>
       </c>
       <c r="S44" t="n">
-        <v>43.95</v>
+        <v>66.97</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3984,54 +4004,54 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="C45" t="n">
-        <v>60.06</v>
+        <v>23.91</v>
       </c>
       <c r="D45" t="n">
-        <v>3951000</v>
+        <v>1975800</v>
       </c>
       <c r="E45" t="n">
-        <v>2745270</v>
+        <v>2070220</v>
       </c>
       <c r="F45" t="n">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>16.77</v>
+        <v>12.05</v>
       </c>
       <c r="K45" t="n">
-        <v>17.43</v>
+        <v>12.25</v>
       </c>
       <c r="L45" t="n">
-        <v>-12.82</v>
+        <v>-1.22</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4047,75 +4067,75 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>33.33</v>
+        <v>43.59</v>
       </c>
       <c r="S45" t="n">
-        <v>31.07</v>
+        <v>50.1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>139.8</v>
+        <v>10.4</v>
       </c>
       <c r="C46" t="n">
-        <v>108.18</v>
+        <v>20.5</v>
       </c>
       <c r="D46" t="n">
-        <v>773800</v>
+        <v>1971000</v>
       </c>
       <c r="E46" t="n">
-        <v>662330</v>
+        <v>2169110</v>
       </c>
       <c r="F46" t="n">
-        <v>1.17</v>
+        <v>0.91</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>138.57</v>
+        <v>10.45</v>
       </c>
       <c r="K46" t="n">
-        <v>134.54</v>
+        <v>11.48</v>
       </c>
       <c r="L46" t="n">
-        <v>3.91</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4127,83 +4147,79 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>45.16</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="S46" t="n">
-        <v>29.87</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14.65</v>
+        <v>10.65</v>
       </c>
       <c r="C47" t="n">
-        <v>208.94</v>
+        <v>156.66</v>
       </c>
       <c r="D47" t="n">
-        <v>14262100</v>
+        <v>14710300</v>
       </c>
       <c r="E47" t="n">
-        <v>12230580</v>
+        <v>26799159</v>
       </c>
       <c r="F47" t="n">
-        <v>1.17</v>
+        <v>0.55</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>13.56</v>
+        <v>11.88</v>
       </c>
       <c r="K47" t="n">
-        <v>12.56</v>
+        <v>14.5</v>
       </c>
       <c r="L47" t="n">
-        <v>16.64</v>
+        <v>-26.53</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4211,10 +4227,10 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>65.79000000000001</v>
+        <v>44.33</v>
       </c>
       <c r="S47" t="n">
-        <v>61.95</v>
+        <v>35.87</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4223,35 +4239,35 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>70.40000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="C48" t="n">
-        <v>290.03</v>
+        <v>24.69</v>
       </c>
       <c r="D48" t="n">
-        <v>4119800</v>
+        <v>1829000</v>
       </c>
       <c r="E48" t="n">
-        <v>5878965</v>
+        <v>1888120</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4265,17 +4281,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>68.90000000000001</v>
+        <v>13.78</v>
       </c>
       <c r="K48" t="n">
-        <v>72.09999999999999</v>
+        <v>13.75</v>
       </c>
       <c r="L48" t="n">
-        <v>-2.36</v>
+        <v>-1.82</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4291,10 +4307,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>51.03</v>
+        <v>62.5</v>
       </c>
       <c r="S48" t="n">
-        <v>59.71</v>
+        <v>66.69</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4308,30 +4324,30 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65.90000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="C49" t="n">
-        <v>127.97</v>
+        <v>32.59</v>
       </c>
       <c r="D49" t="n">
-        <v>1941900</v>
+        <v>2910000</v>
       </c>
       <c r="E49" t="n">
-        <v>2556400</v>
+        <v>4177185</v>
       </c>
       <c r="F49" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4340,38 +4356,30 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>50.57</v>
+        <v>12.12</v>
       </c>
       <c r="K49" t="n">
-        <v>50.57</v>
+        <v>13.82</v>
       </c>
       <c r="L49" t="n">
-        <v>30.31</v>
+        <v>-18.99</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4379,71 +4387,71 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>74.59999999999999</v>
+        <v>44.44</v>
       </c>
       <c r="S49" t="n">
-        <v>71.34999999999999</v>
+        <v>55.83</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>72.8</v>
+        <v>35.05</v>
       </c>
       <c r="C50" t="n">
-        <v>201.16</v>
+        <v>177.74</v>
       </c>
       <c r="D50" t="n">
-        <v>2763200</v>
+        <v>5070900</v>
       </c>
       <c r="E50" t="n">
-        <v>2900730</v>
+        <v>4457945</v>
       </c>
       <c r="F50" t="n">
-        <v>0.95</v>
+        <v>1.14</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>69.02</v>
+        <v>35.15</v>
       </c>
       <c r="K50" t="n">
-        <v>73.36</v>
+        <v>38.08</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.76</v>
+        <v>-7.97</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4459,71 +4467,71 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>51.6</v>
+        <v>47.03</v>
       </c>
       <c r="S50" t="n">
-        <v>62.73</v>
+        <v>62.03</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12.1</v>
+        <v>18.8</v>
       </c>
       <c r="C51" t="n">
-        <v>25.14</v>
+        <v>114.22</v>
       </c>
       <c r="D51" t="n">
-        <v>2077700</v>
+        <v>6075400</v>
       </c>
       <c r="E51" t="n">
-        <v>2047390</v>
+        <v>13522000</v>
       </c>
       <c r="F51" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>12.05</v>
+        <v>32.02</v>
       </c>
       <c r="K51" t="n">
-        <v>12.25</v>
+        <v>47.16</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.22</v>
+        <v>-60.14</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4539,56 +4547,56 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>42.5</v>
+        <v>16.38</v>
       </c>
       <c r="S51" t="n">
-        <v>49.78</v>
+        <v>7.44</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10.5</v>
+        <v>12.2</v>
       </c>
       <c r="C52" t="n">
-        <v>48.69</v>
+        <v>59.09</v>
       </c>
       <c r="D52" t="n">
-        <v>4636900</v>
+        <v>4843200</v>
       </c>
       <c r="E52" t="n">
-        <v>2180015</v>
+        <v>5579535</v>
       </c>
       <c r="F52" t="n">
-        <v>2.13</v>
+        <v>0.87</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4597,13 +4605,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>10.45</v>
+        <v>13.08</v>
       </c>
       <c r="K52" t="n">
-        <v>11.48</v>
+        <v>13.6</v>
       </c>
       <c r="L52" t="n">
-        <v>-8.5</v>
+        <v>-10.29</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4619,47 +4627,47 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>64.18000000000001</v>
+        <v>33.33</v>
       </c>
       <c r="S52" t="n">
-        <v>73.19</v>
+        <v>38.63</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10.7</v>
+        <v>17.65</v>
       </c>
       <c r="C53" t="n">
-        <v>291.63</v>
+        <v>29.78</v>
       </c>
       <c r="D53" t="n">
-        <v>27255500</v>
+        <v>1687300</v>
       </c>
       <c r="E53" t="n">
-        <v>27520319</v>
+        <v>3730645</v>
       </c>
       <c r="F53" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4677,13 +4685,13 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>11.88</v>
+        <v>19.02</v>
       </c>
       <c r="K53" t="n">
-        <v>14.5</v>
+        <v>19.43</v>
       </c>
       <c r="L53" t="n">
-        <v>-26.18</v>
+        <v>-9.16</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4699,10 +4707,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>35.11</v>
+        <v>36.11</v>
       </c>
       <c r="S53" t="n">
-        <v>34.88</v>
+        <v>49.34</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4716,58 +4724,58 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>12.9</v>
+        <v>22.4</v>
       </c>
       <c r="C54" t="n">
-        <v>28.2</v>
+        <v>24.59</v>
       </c>
       <c r="D54" t="n">
-        <v>2186200</v>
+        <v>1097700</v>
       </c>
       <c r="E54" t="n">
-        <v>2171530</v>
+        <v>1607155</v>
       </c>
       <c r="F54" t="n">
-        <v>1.01</v>
+        <v>0.68</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>13.2</v>
+        <v>20.6</v>
       </c>
       <c r="K54" t="n">
-        <v>14</v>
+        <v>19.51</v>
       </c>
       <c r="L54" t="n">
-        <v>-7.82</v>
+        <v>14.81</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4779,51 +4787,51 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>43.33</v>
+        <v>58.12</v>
       </c>
       <c r="S54" t="n">
-        <v>56.66</v>
+        <v>59.96</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>13.45</v>
+        <v>31.4</v>
       </c>
       <c r="C55" t="n">
-        <v>54.34</v>
+        <v>49.87</v>
       </c>
       <c r="D55" t="n">
-        <v>4040200</v>
+        <v>1588100</v>
       </c>
       <c r="E55" t="n">
-        <v>1892035</v>
+        <v>3635455</v>
       </c>
       <c r="F55" t="n">
-        <v>2.14</v>
+        <v>0.44</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4833,17 +4841,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>13.78</v>
+        <v>30.94</v>
       </c>
       <c r="K55" t="n">
-        <v>13.75</v>
+        <v>31.62</v>
       </c>
       <c r="L55" t="n">
-        <v>-2.18</v>
+        <v>-0.71</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4859,10 +4867,10 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>51.85</v>
+        <v>34.85</v>
       </c>
       <c r="S55" t="n">
-        <v>59.13</v>
+        <v>50.12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4876,61 +4884,65 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11.3</v>
+        <v>23.65</v>
       </c>
       <c r="C56" t="n">
-        <v>65.54000000000001</v>
+        <v>176.82</v>
       </c>
       <c r="D56" t="n">
-        <v>5800400</v>
+        <v>7476700</v>
       </c>
       <c r="E56" t="n">
-        <v>4179935</v>
+        <v>8287035</v>
       </c>
       <c r="F56" t="n">
-        <v>1.39</v>
+        <v>0.9</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>12.2</v>
+        <v>21.2</v>
       </c>
       <c r="K56" t="n">
-        <v>13.82</v>
+        <v>21.2</v>
       </c>
       <c r="L56" t="n">
-        <v>-18.26</v>
+        <v>11.56</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
@@ -4939,47 +4951,47 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>50</v>
+        <v>51.45</v>
       </c>
       <c r="S56" t="n">
-        <v>49.42</v>
+        <v>54.41</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>51</v>
+        <v>22.65</v>
       </c>
       <c r="C57" t="n">
-        <v>34.61</v>
+        <v>23.89</v>
       </c>
       <c r="D57" t="n">
-        <v>678700</v>
+        <v>1054700</v>
       </c>
       <c r="E57" t="n">
-        <v>908530</v>
+        <v>1152145</v>
       </c>
       <c r="F57" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4993,29 +5005,25 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>45.2</v>
+        <v>22.3</v>
       </c>
       <c r="K57" t="n">
-        <v>44.22</v>
+        <v>21.92</v>
       </c>
       <c r="L57" t="n">
-        <v>15.35</v>
+        <v>3.31</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
@@ -5023,10 +5031,10 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>56.61</v>
+        <v>47.62</v>
       </c>
       <c r="S57" t="n">
-        <v>67.09</v>
+        <v>45.79</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5040,30 +5048,30 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>35.55</v>
+        <v>10.65</v>
       </c>
       <c r="C58" t="n">
-        <v>168.76</v>
+        <v>532.22</v>
       </c>
       <c r="D58" t="n">
-        <v>4747000</v>
+        <v>49973400</v>
       </c>
       <c r="E58" t="n">
-        <v>4478990</v>
+        <v>42105920</v>
       </c>
       <c r="F58" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5072,22 +5080,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.15</v>
+        <v>11.23</v>
       </c>
       <c r="K58" t="n">
-        <v>38.08</v>
+        <v>12.55</v>
       </c>
       <c r="L58" t="n">
-        <v>-6.66</v>
+        <v>-15.14</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5103,51 +5111,51 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>52.94</v>
+        <v>32.65</v>
       </c>
       <c r="S58" t="n">
-        <v>68.79000000000001</v>
+        <v>20.09</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>18.2</v>
+        <v>12.3</v>
       </c>
       <c r="C59" t="n">
-        <v>157.36</v>
+        <v>142.95</v>
       </c>
       <c r="D59" t="n">
-        <v>8646300</v>
+        <v>11621600</v>
       </c>
       <c r="E59" t="n">
-        <v>13536085</v>
+        <v>8774690</v>
       </c>
       <c r="F59" t="n">
-        <v>0.64</v>
+        <v>1.32</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5161,13 +5169,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>32.08</v>
+        <v>13.9</v>
       </c>
       <c r="K59" t="n">
-        <v>47.16</v>
+        <v>15</v>
       </c>
       <c r="L59" t="n">
-        <v>-61.41</v>
+        <v>-18.03</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5183,10 +5191,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>11.86</v>
+        <v>43.07</v>
       </c>
       <c r="S59" t="n">
-        <v>5.27</v>
+        <v>48.12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5200,39 +5208,39 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12.2</v>
+        <v>16.15</v>
       </c>
       <c r="C60" t="n">
-        <v>138.74</v>
+        <v>30.84</v>
       </c>
       <c r="D60" t="n">
-        <v>11371900</v>
+        <v>1909700</v>
       </c>
       <c r="E60" t="n">
-        <v>5547665</v>
+        <v>2493315</v>
       </c>
       <c r="F60" t="n">
-        <v>2.05</v>
+        <v>0.77</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5241,13 +5249,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>13.08</v>
+        <v>19.77</v>
       </c>
       <c r="K60" t="n">
-        <v>13.6</v>
+        <v>19.19</v>
       </c>
       <c r="L60" t="n">
-        <v>-10.29</v>
+        <v>-15.82</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5263,47 +5271,47 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>41.94</v>
+        <v>27.5</v>
       </c>
       <c r="S60" t="n">
-        <v>44.72</v>
+        <v>28.55</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>17.7</v>
+        <v>19.45</v>
       </c>
       <c r="C61" t="n">
-        <v>51.01</v>
+        <v>244.83</v>
       </c>
       <c r="D61" t="n">
-        <v>2882200</v>
+        <v>12587800</v>
       </c>
       <c r="E61" t="n">
-        <v>3984475</v>
+        <v>19044040</v>
       </c>
       <c r="F61" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5321,13 +5329,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>19.02</v>
+        <v>19.55</v>
       </c>
       <c r="K61" t="n">
-        <v>19.43</v>
+        <v>20.34</v>
       </c>
       <c r="L61" t="n">
-        <v>-8.9</v>
+        <v>-4.4</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -5343,10 +5351,10 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>46.43</v>
+        <v>34.09</v>
       </c>
       <c r="S61" t="n">
-        <v>56.03</v>
+        <v>33.25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5360,34 +5368,34 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22</v>
+        <v>62.8</v>
       </c>
       <c r="C62" t="n">
-        <v>65.2</v>
+        <v>112.41</v>
       </c>
       <c r="D62" t="n">
-        <v>2963800</v>
+        <v>1790000</v>
       </c>
       <c r="E62" t="n">
-        <v>1577435</v>
+        <v>2994070</v>
       </c>
       <c r="F62" t="n">
-        <v>1.88</v>
+        <v>0.6</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5397,24 +5405,28 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>20.6</v>
+        <v>70.8</v>
       </c>
       <c r="K62" t="n">
-        <v>19.51</v>
+        <v>70.8</v>
       </c>
       <c r="L62" t="n">
-        <v>12.76</v>
+        <v>-11.3</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
@@ -5423,14 +5435,14 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>57.89</v>
+        <v>3.25</v>
       </c>
       <c r="S62" t="n">
-        <v>60.28</v>
+        <v>10.02</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -5440,34 +5452,34 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.6</v>
+        <v>33.2</v>
       </c>
       <c r="C63" t="n">
-        <v>189.2</v>
+        <v>423</v>
       </c>
       <c r="D63" t="n">
-        <v>5987500</v>
+        <v>12740900</v>
       </c>
       <c r="E63" t="n">
-        <v>3664205</v>
+        <v>18159075</v>
       </c>
       <c r="F63" t="n">
-        <v>1.63</v>
+        <v>0.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5481,20 +5493,24 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>30.94</v>
+        <v>31.5</v>
       </c>
       <c r="K63" t="n">
-        <v>31.62</v>
+        <v>31.5</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.08</v>
+        <v>5.4</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
@@ -5503,10 +5519,10 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="S63" t="n">
-        <v>55.37</v>
+        <v>60.9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -5520,65 +5536,61 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>23.65</v>
+        <v>11.2</v>
       </c>
       <c r="C64" t="n">
-        <v>248.63</v>
+        <v>36.73</v>
       </c>
       <c r="D64" t="n">
-        <v>10512800</v>
+        <v>3279600</v>
       </c>
       <c r="E64" t="n">
-        <v>8146535</v>
+        <v>4111775</v>
       </c>
       <c r="F64" t="n">
-        <v>1.29</v>
+        <v>0.8</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>21.2</v>
+        <v>11.34</v>
       </c>
       <c r="K64" t="n">
-        <v>21.2</v>
+        <v>13.2</v>
       </c>
       <c r="L64" t="n">
-        <v>11.56</v>
+        <v>-15.18</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
@@ -5587,47 +5599,47 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>53.79</v>
+        <v>45.65</v>
       </c>
       <c r="S64" t="n">
-        <v>59.74</v>
+        <v>57.13</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>22.65</v>
+        <v>27.6</v>
       </c>
       <c r="C65" t="n">
-        <v>24.84</v>
+        <v>50.13</v>
       </c>
       <c r="D65" t="n">
-        <v>1096800</v>
+        <v>1816200</v>
       </c>
       <c r="E65" t="n">
-        <v>1188590</v>
+        <v>2319895</v>
       </c>
       <c r="F65" t="n">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5636,26 +5648,26 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>22.3</v>
+        <v>31.42</v>
       </c>
       <c r="K65" t="n">
-        <v>21.92</v>
+        <v>32.59</v>
       </c>
       <c r="L65" t="n">
-        <v>3.31</v>
+        <v>-15.31</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -5667,51 +5679,51 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>47.62</v>
+        <v>32.58</v>
       </c>
       <c r="S65" t="n">
-        <v>42.08</v>
+        <v>48.15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="C66" t="n">
-        <v>441.98</v>
+        <v>225.68</v>
       </c>
       <c r="D66" t="n">
-        <v>42498200</v>
+        <v>18806500</v>
       </c>
       <c r="E66" t="n">
-        <v>42196195</v>
+        <v>10071310</v>
       </c>
       <c r="F66" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5725,13 +5737,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>11.23</v>
+        <v>12.15</v>
       </c>
       <c r="K66" t="n">
-        <v>12.55</v>
+        <v>12.68</v>
       </c>
       <c r="L66" t="n">
-        <v>-17.13</v>
+        <v>-5.33</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5747,10 +5759,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>23.91</v>
+        <v>40.74</v>
       </c>
       <c r="S66" t="n">
-        <v>11.91</v>
+        <v>55.96</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5764,34 +5776,34 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>12.2</v>
+        <v>56.9</v>
       </c>
       <c r="C67" t="n">
-        <v>202.7</v>
+        <v>135.92</v>
       </c>
       <c r="D67" t="n">
-        <v>16614500</v>
+        <v>2388700</v>
       </c>
       <c r="E67" t="n">
-        <v>8520945</v>
+        <v>3032980</v>
       </c>
       <c r="F67" t="n">
-        <v>1.95</v>
+        <v>0.79</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5805,13 +5817,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>13.9</v>
+        <v>57</v>
       </c>
       <c r="K67" t="n">
-        <v>15</v>
+        <v>59.12</v>
       </c>
       <c r="L67" t="n">
-        <v>-18.69</v>
+        <v>-3.76</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5827,10 +5839,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>34.62</v>
+        <v>29.41</v>
       </c>
       <c r="S67" t="n">
-        <v>38.79</v>
+        <v>32.62</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5844,39 +5856,39 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>15.9</v>
+        <v>15.15</v>
       </c>
       <c r="C68" t="n">
-        <v>37.32</v>
+        <v>43.49</v>
       </c>
       <c r="D68" t="n">
-        <v>2347300</v>
+        <v>2870900</v>
       </c>
       <c r="E68" t="n">
-        <v>2984555</v>
+        <v>1904045</v>
       </c>
       <c r="F68" t="n">
-        <v>0.79</v>
+        <v>1.51</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5885,13 +5897,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>19.77</v>
+        <v>15.7</v>
       </c>
       <c r="K68" t="n">
-        <v>19.19</v>
+        <v>17.1</v>
       </c>
       <c r="L68" t="n">
-        <v>-17.12</v>
+        <v>-11.43</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5907,51 +5919,51 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>22.05</v>
+        <v>77.36</v>
       </c>
       <c r="S68" t="n">
-        <v>21.61</v>
+        <v>77.14</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>19.25</v>
+        <v>18.95</v>
       </c>
       <c r="C69" t="n">
-        <v>457.09</v>
+        <v>110.91</v>
       </c>
       <c r="D69" t="n">
-        <v>23744700</v>
+        <v>5852900</v>
       </c>
       <c r="E69" t="n">
-        <v>20234655</v>
+        <v>7638185</v>
       </c>
       <c r="F69" t="n">
-        <v>1.17</v>
+        <v>0.77</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5965,13 +5977,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>19.55</v>
+        <v>20.83</v>
       </c>
       <c r="K69" t="n">
-        <v>20.34</v>
+        <v>23.28</v>
       </c>
       <c r="L69" t="n">
-        <v>-5.38</v>
+        <v>-18.58</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -5987,10 +5999,10 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>21.57</v>
+        <v>43.06</v>
       </c>
       <c r="S69" t="n">
-        <v>26.39</v>
+        <v>49.32</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6004,39 +6016,39 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>62.8</v>
+        <v>27.6</v>
       </c>
       <c r="C70" t="n">
-        <v>415.59</v>
+        <v>35.04</v>
       </c>
       <c r="D70" t="n">
-        <v>6617700</v>
+        <v>1269600</v>
       </c>
       <c r="E70" t="n">
-        <v>3158465</v>
+        <v>1541090</v>
       </c>
       <c r="F70" t="n">
-        <v>2.1</v>
+        <v>0.82</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6045,24 +6057,20 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>70.8</v>
+        <v>29.32</v>
       </c>
       <c r="K70" t="n">
-        <v>70.8</v>
+        <v>32.12</v>
       </c>
       <c r="L70" t="n">
-        <v>-11.3</v>
+        <v>-14.09</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
@@ -6071,56 +6079,56 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>7.45</v>
+        <v>41.84</v>
       </c>
       <c r="S70" t="n">
-        <v>14.93</v>
+        <v>49</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>32.9</v>
+        <v>38.8</v>
       </c>
       <c r="C71" t="n">
-        <v>528.76</v>
+        <v>28.91</v>
       </c>
       <c r="D71" t="n">
-        <v>16071800</v>
+        <v>745200</v>
       </c>
       <c r="E71" t="n">
-        <v>18305860</v>
+        <v>504495</v>
       </c>
       <c r="F71" t="n">
-        <v>0.88</v>
+        <v>1.48</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6129,24 +6137,20 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>31.5</v>
+        <v>36.8</v>
       </c>
       <c r="K71" t="n">
-        <v>31.5</v>
+        <v>36.5</v>
       </c>
       <c r="L71" t="n">
-        <v>4.44</v>
+        <v>6.3</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
@@ -6155,56 +6159,56 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>45.57</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="S71" t="n">
-        <v>53.32</v>
+        <v>54.8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11.1</v>
+        <v>61</v>
       </c>
       <c r="C72" t="n">
-        <v>90.73</v>
+        <v>518.15</v>
       </c>
       <c r="D72" t="n">
-        <v>8173800</v>
+        <v>8494300</v>
       </c>
       <c r="E72" t="n">
-        <v>4120340</v>
+        <v>8594035</v>
       </c>
       <c r="F72" t="n">
-        <v>1.98</v>
+        <v>0.99</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6213,20 +6217,24 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>11.48</v>
+        <v>70.25</v>
       </c>
       <c r="K72" t="n">
-        <v>13.2</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>-15.94</v>
+        <v>-13.07</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
@@ -6235,47 +6243,47 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>45.65</v>
+        <v>25.15</v>
       </c>
       <c r="S72" t="n">
-        <v>46.5</v>
+        <v>34.48</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>VIB</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>27.65</v>
+        <v>13.85</v>
       </c>
       <c r="C73" t="n">
-        <v>96.38</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>3485800</v>
+        <v>6624100</v>
       </c>
       <c r="E73" t="n">
-        <v>2408630</v>
+        <v>5270335</v>
       </c>
       <c r="F73" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -6284,22 +6292,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>31.42</v>
+        <v>13.6</v>
       </c>
       <c r="K73" t="n">
-        <v>32.59</v>
+        <v>14.23</v>
       </c>
       <c r="L73" t="n">
-        <v>-15.16</v>
+        <v>-2.67</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -6315,56 +6323,56 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>27.88</v>
+        <v>70.59</v>
       </c>
       <c r="S73" t="n">
-        <v>41.48</v>
+        <v>82.62</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>11.75</v>
+        <v>215</v>
       </c>
       <c r="C74" t="n">
-        <v>136.01</v>
+        <v>520.21</v>
       </c>
       <c r="D74" t="n">
-        <v>11575100</v>
+        <v>2419600</v>
       </c>
       <c r="E74" t="n">
-        <v>9473775</v>
+        <v>2775075</v>
       </c>
       <c r="F74" t="n">
-        <v>1.22</v>
+        <v>0.87</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6373,17 +6381,17 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>12.2</v>
+        <v>229.8</v>
       </c>
       <c r="K74" t="n">
-        <v>12.72</v>
+        <v>207.15</v>
       </c>
       <c r="L74" t="n">
-        <v>-7.63</v>
+        <v>3.79</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -6395,51 +6403,51 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>27.27</v>
+        <v>31.98</v>
       </c>
       <c r="S74" t="n">
-        <v>44.21</v>
+        <v>24.07</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>56.5</v>
+        <v>11.85</v>
       </c>
       <c r="C75" t="n">
-        <v>133.8</v>
+        <v>333.9</v>
       </c>
       <c r="D75" t="n">
-        <v>2368200</v>
+        <v>28177100</v>
       </c>
       <c r="E75" t="n">
-        <v>3431675</v>
+        <v>25410180</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6453,13 +6461,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>57</v>
+        <v>12.82</v>
       </c>
       <c r="K75" t="n">
-        <v>59.12</v>
+        <v>14.95</v>
       </c>
       <c r="L75" t="n">
-        <v>-4.44</v>
+        <v>-20.74</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6475,10 +6483,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>27.27</v>
+        <v>38.3</v>
       </c>
       <c r="S75" t="n">
-        <v>35.51</v>
+        <v>40.97</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6492,34 +6500,34 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>VJC</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>127.5</v>
       </c>
       <c r="C76" t="n">
-        <v>76.48</v>
+        <v>102.52</v>
       </c>
       <c r="D76" t="n">
-        <v>5098400</v>
+        <v>804100</v>
       </c>
       <c r="E76" t="n">
-        <v>1863240</v>
+        <v>932165</v>
       </c>
       <c r="F76" t="n">
-        <v>2.74</v>
+        <v>0.86</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6529,17 +6537,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>15.7</v>
+        <v>128.05</v>
       </c>
       <c r="K76" t="n">
-        <v>17.1</v>
+        <v>132.12</v>
       </c>
       <c r="L76" t="n">
-        <v>-12.31</v>
+        <v>-3.5</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6551,14 +6559,14 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R76" t="n">
-        <v>66.67</v>
+        <v>20</v>
       </c>
       <c r="S76" t="n">
-        <v>68.67</v>
+        <v>27.43</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6572,34 +6580,34 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18.85</v>
+        <v>13.25</v>
       </c>
       <c r="C77" t="n">
-        <v>250.07</v>
+        <v>116.81</v>
       </c>
       <c r="D77" t="n">
-        <v>13266500</v>
+        <v>8816100</v>
       </c>
       <c r="E77" t="n">
-        <v>8070955</v>
+        <v>9362600</v>
       </c>
       <c r="F77" t="n">
-        <v>1.64</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6613,13 +6621,13 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>20.98</v>
+        <v>15.23</v>
       </c>
       <c r="K77" t="n">
-        <v>23.28</v>
+        <v>15.85</v>
       </c>
       <c r="L77" t="n">
-        <v>-19.01</v>
+        <v>-16.4</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -6635,10 +6643,10 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>37.66</v>
+        <v>38.6</v>
       </c>
       <c r="S77" t="n">
-        <v>42.44</v>
+        <v>36.58</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6652,39 +6660,39 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>27.9</v>
+        <v>57.8</v>
       </c>
       <c r="C78" t="n">
-        <v>93.09999999999999</v>
+        <v>93.64</v>
       </c>
       <c r="D78" t="n">
-        <v>3336900</v>
+        <v>1620000</v>
       </c>
       <c r="E78" t="n">
-        <v>1841350</v>
+        <v>1987835</v>
       </c>
       <c r="F78" t="n">
-        <v>1.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6693,13 +6701,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>29.32</v>
+        <v>59.85</v>
       </c>
       <c r="K78" t="n">
-        <v>32.12</v>
+        <v>59.5</v>
       </c>
       <c r="L78" t="n">
-        <v>-13.15</v>
+        <v>-2.86</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -6715,56 +6723,56 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>43.62</v>
+        <v>33.33</v>
       </c>
       <c r="S78" t="n">
-        <v>42.82</v>
+        <v>31.71</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>VPB</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>38.8</v>
+        <v>24.5</v>
       </c>
       <c r="C79" t="n">
-        <v>43.51</v>
+        <v>236.47</v>
       </c>
       <c r="D79" t="n">
-        <v>1121300</v>
+        <v>9651700</v>
       </c>
       <c r="E79" t="n">
-        <v>483735</v>
+        <v>19307615</v>
       </c>
       <c r="F79" t="n">
-        <v>2.32</v>
+        <v>0.5</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6773,73 +6781,81 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>36.8</v>
+        <v>21.98</v>
       </c>
       <c r="K79" t="n">
-        <v>36.5</v>
+        <v>21.98</v>
       </c>
       <c r="L79" t="n">
-        <v>6.3</v>
+        <v>11.49</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>75</v>
+        <v>79.25</v>
       </c>
       <c r="S79" t="n">
-        <v>62.47</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>58.9</v>
+        <v>48.1</v>
       </c>
       <c r="C80" t="n">
-        <v>678.33</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="D80" t="n">
-        <v>11516700</v>
+        <v>1565200</v>
       </c>
       <c r="E80" t="n">
-        <v>9108050</v>
+        <v>1570825</v>
       </c>
       <c r="F80" t="n">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6853,13 +6869,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>70.25</v>
+        <v>55.68</v>
       </c>
       <c r="K80" t="n">
-        <v>70.18000000000001</v>
+        <v>55.68</v>
       </c>
       <c r="L80" t="n">
-        <v>-16.07</v>
+        <v>-13.61</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -6879,10 +6895,10 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>16.88</v>
+        <v>6.83</v>
       </c>
       <c r="S80" t="n">
-        <v>35.14</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6896,54 +6912,54 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>VPL</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>13.8</v>
+        <v>79</v>
       </c>
       <c r="C81" t="n">
-        <v>61.55</v>
+        <v>61.23</v>
       </c>
       <c r="D81" t="n">
-        <v>4460300</v>
+        <v>775100</v>
       </c>
       <c r="E81" t="n">
-        <v>5150250</v>
+        <v>704320</v>
       </c>
       <c r="F81" t="n">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>13.6</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>14.23</v>
+        <v>85.5</v>
       </c>
       <c r="L81" t="n">
-        <v>-3.02</v>
+        <v>-7.6</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6959,56 +6975,56 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>60.53</v>
+        <v>47.09</v>
       </c>
       <c r="S81" t="n">
-        <v>78.53</v>
+        <v>32.01</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VRE</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>218</v>
+        <v>22.85</v>
       </c>
       <c r="C82" t="n">
-        <v>947.99</v>
+        <v>59.02</v>
       </c>
       <c r="D82" t="n">
-        <v>4348600</v>
+        <v>2582800</v>
       </c>
       <c r="E82" t="n">
-        <v>3316670</v>
+        <v>3332535</v>
       </c>
       <c r="F82" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7017,17 +7033,17 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>229.8</v>
+        <v>24.42</v>
       </c>
       <c r="K82" t="n">
-        <v>207.15</v>
+        <v>28.56</v>
       </c>
       <c r="L82" t="n">
-        <v>5.24</v>
+        <v>-19.99</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -7039,51 +7055,51 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>34.09</v>
+        <v>26.87</v>
       </c>
       <c r="S82" t="n">
-        <v>24.91</v>
+        <v>13.91</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VSC</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>11.75</v>
+        <v>13</v>
       </c>
       <c r="C83" t="n">
-        <v>508.62</v>
+        <v>60.16</v>
       </c>
       <c r="D83" t="n">
-        <v>43287200</v>
+        <v>4628000</v>
       </c>
       <c r="E83" t="n">
-        <v>26188705</v>
+        <v>7078810</v>
       </c>
       <c r="F83" t="n">
-        <v>1.65</v>
+        <v>0.65</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7097,13 +7113,13 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>12.82</v>
+        <v>14.1</v>
       </c>
       <c r="K83" t="n">
-        <v>14.95</v>
+        <v>18.95</v>
       </c>
       <c r="L83" t="n">
-        <v>-21.4</v>
+        <v>-31.4</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7119,10 +7135,10 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>32</v>
+        <v>39.29</v>
       </c>
       <c r="S83" t="n">
-        <v>33.38</v>
+        <v>29.67</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7136,735 +7152,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>VJC</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="C84" t="n">
-        <v>107.49</v>
-      </c>
-      <c r="D84" t="n">
-        <v>844400</v>
-      </c>
-      <c r="E84" t="n">
-        <v>992595</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>💤 Tiền Yếu</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>🌫️ Trong Mây</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>128.05</v>
-      </c>
-      <c r="K84" t="n">
-        <v>132.12</v>
-      </c>
-      <c r="L84" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R84" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S84" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="C85" t="n">
-        <v>177.85</v>
-      </c>
-      <c r="D85" t="n">
-        <v>13423000</v>
-      </c>
-      <c r="E85" t="n">
-        <v>9723370</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>⚡ Có Tín Hiệu</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="K85" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="L85" t="n">
-        <v>-16.4</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R85" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="S85" t="n">
-        <v>28.73</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="C86" t="n">
-        <v>113.37</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1982000</v>
-      </c>
-      <c r="E86" t="n">
-        <v>2132700</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>💤 Tiền Yếu</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="K86" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="L86" t="n">
-        <v>-3.87</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R86" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="S86" t="n">
-        <v>26.04</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>🟢 Mua (vùng quá bán)</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>VPB</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>24.45</v>
-      </c>
-      <c r="C87" t="n">
-        <v>528.5599999999999</v>
-      </c>
-      <c r="D87" t="n">
-        <v>21617900</v>
-      </c>
-      <c r="E87" t="n">
-        <v>21280150</v>
-      </c>
-      <c r="F87" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>⚡ Có Tín Hiệu</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>☁️ Trên Mây</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="K87" t="n">
-        <v>21.98</v>
-      </c>
-      <c r="L87" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R87" t="n">
-        <v>77.36</v>
-      </c>
-      <c r="S87" t="n">
-        <v>79.83</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>🔴 Bán (vùng quá mua)</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>VPI</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="C88" t="n">
-        <v>120.23</v>
-      </c>
-      <c r="D88" t="n">
-        <v>2433900</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1555985</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>🔥 Tiền Vào Mạnh</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="K88" t="n">
-        <v>56.18</v>
-      </c>
-      <c r="L88" t="n">
-        <v>-12.06</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R88" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="S88" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>🟢 Mua (vùng quá bán)</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>VPL</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>77</v>
-      </c>
-      <c r="C89" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="D89" t="n">
-        <v>637600</v>
-      </c>
-      <c r="E89" t="n">
-        <v>853145</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>💤 Tiền Yếu</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>79.84999999999999</v>
-      </c>
-      <c r="K89" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="L89" t="n">
-        <v>-9.94</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R89" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="S89" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>VRE</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="C90" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2710100</v>
-      </c>
-      <c r="E90" t="n">
-        <v>3581785</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>💤 Tiền Yếu</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>24.42</v>
-      </c>
-      <c r="K90" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="L90" t="n">
-        <v>-20.87</v>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R90" t="n">
-        <v>20.31</v>
-      </c>
-      <c r="S90" t="n">
-        <v>14.07</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>VSC</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="C91" t="n">
-        <v>83.36</v>
-      </c>
-      <c r="D91" t="n">
-        <v>6461800</v>
-      </c>
-      <c r="E91" t="n">
-        <v>7213130</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>💤 Tiền Yếu</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="K91" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="L91" t="n">
-        <v>-32.02</v>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R91" t="n">
-        <v>44.26</v>
-      </c>
-      <c r="S91" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>VTP</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="C92" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="D92" t="n">
-        <v>568100</v>
-      </c>
-      <c r="E92" t="n">
-        <v>804005</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>💤 Tiền Yếu</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="K92" t="n">
-        <v>53.44</v>
-      </c>
-      <c r="L92" t="n">
-        <v>-12.99</v>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R92" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="S92" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>2026-10-15 20:55:47</t>
+          <t>2026-10-16 20:44:23</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V83"/>
+  <dimension ref="A1:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>AAS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.6</v>
+        <v>10.3</v>
       </c>
       <c r="C2" t="n">
-        <v>106.3</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>5160300</v>
+        <v>7846200</v>
       </c>
       <c r="E2" t="n">
-        <v>7396385</v>
+        <v>1498325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>5.24</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -561,25 +561,33 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="K2" t="n">
-        <v>21.58</v>
+        <v>8.6</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.52</v>
+        <v>19.77</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -587,14 +595,14 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>34.38</v>
+        <v>60.87</v>
       </c>
       <c r="S2" t="n">
-        <v>37.53</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -604,34 +612,34 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACV</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.4</v>
+        <v>20.25</v>
       </c>
       <c r="C3" t="n">
-        <v>69.51000000000001</v>
+        <v>147.36</v>
       </c>
       <c r="D3" t="n">
-        <v>1679000</v>
+        <v>7276900</v>
       </c>
       <c r="E3" t="n">
-        <v>475280</v>
+        <v>7299615</v>
       </c>
       <c r="F3" t="n">
-        <v>3.53</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -641,17 +649,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>39.9</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>42.1</v>
+        <v>21.58</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.66</v>
+        <v>-6.14</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -663,18 +671,18 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.5x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>75</v>
+        <v>28.95</v>
       </c>
       <c r="S3" t="n">
-        <v>74.27</v>
+        <v>37.54</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -684,34 +692,34 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAF</t>
+          <t>ACV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>41.3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.61</v>
+        <v>34.05</v>
       </c>
       <c r="D4" t="n">
-        <v>1148800</v>
+        <v>824500</v>
       </c>
       <c r="E4" t="n">
-        <v>1619250</v>
+        <v>505865</v>
       </c>
       <c r="F4" t="n">
-        <v>0.71</v>
+        <v>1.63</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -721,21 +729,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>30.72</v>
+        <v>39.9</v>
       </c>
       <c r="K4" t="n">
-        <v>29.96</v>
+        <v>42.1</v>
       </c>
       <c r="L4" t="n">
-        <v>3.47</v>
+        <v>-1.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -747,14 +755,14 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>34.04</v>
+        <v>75</v>
       </c>
       <c r="S4" t="n">
-        <v>44.95</v>
+        <v>68.84</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -764,54 +772,54 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ANV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.95</v>
+        <v>18.85</v>
       </c>
       <c r="C5" t="n">
-        <v>116.77</v>
+        <v>40.37</v>
       </c>
       <c r="D5" t="n">
-        <v>3439500</v>
+        <v>2141900</v>
       </c>
       <c r="E5" t="n">
-        <v>3088950</v>
+        <v>1151640</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>35</v>
+        <v>17.4</v>
       </c>
       <c r="K5" t="n">
-        <v>37.54</v>
+        <v>20.35</v>
       </c>
       <c r="L5" t="n">
-        <v>-9.56</v>
+        <v>-7.37</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -827,47 +835,47 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>26.92</v>
+        <v>73.53</v>
       </c>
       <c r="S5" t="n">
-        <v>37.95</v>
+        <v>73.63</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BAF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.35</v>
+        <v>30.95</v>
       </c>
       <c r="C6" t="n">
-        <v>212.64</v>
+        <v>27.84</v>
       </c>
       <c r="D6" t="n">
-        <v>7500700</v>
+        <v>899400</v>
       </c>
       <c r="E6" t="n">
-        <v>11220065</v>
+        <v>1618755</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -881,17 +889,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>27.9</v>
+        <v>30.72</v>
       </c>
       <c r="K6" t="n">
-        <v>27.96</v>
+        <v>29.96</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -900,21 +908,25 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>23.87</v>
+        <v>35.56</v>
       </c>
       <c r="S6" t="n">
-        <v>28.68</v>
+        <v>51.74</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -924,65 +936,61 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>39.2</v>
       </c>
       <c r="C7" t="n">
-        <v>53.78</v>
+        <v>22.67</v>
       </c>
       <c r="D7" t="n">
-        <v>746900</v>
+        <v>578300</v>
       </c>
       <c r="E7" t="n">
-        <v>1030980</v>
+        <v>468860</v>
       </c>
       <c r="F7" t="n">
-        <v>0.72</v>
+        <v>1.23</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>67.09999999999999</v>
+        <v>40.45</v>
       </c>
       <c r="K7" t="n">
-        <v>67.09999999999999</v>
+        <v>45.75</v>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>-14.32</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
@@ -991,51 +999,51 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>44.94</v>
+        <v>46.3</v>
       </c>
       <c r="S7" t="n">
-        <v>50.47</v>
+        <v>46.52</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>33.65</v>
       </c>
       <c r="C8" t="n">
-        <v>57.27</v>
+        <v>111.43</v>
       </c>
       <c r="D8" t="n">
-        <v>5206500</v>
+        <v>3311300</v>
       </c>
       <c r="E8" t="n">
-        <v>5818060</v>
+        <v>3055030</v>
       </c>
       <c r="F8" t="n">
-        <v>0.89</v>
+        <v>1.08</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1049,13 +1057,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11.95</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>13.61</v>
+        <v>37.54</v>
       </c>
       <c r="L8" t="n">
-        <v>-19.18</v>
+        <v>-10.36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1071,10 +1079,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>50</v>
+        <v>22.22</v>
       </c>
       <c r="S8" t="n">
-        <v>69.7</v>
+        <v>39.36</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1088,39 +1096,39 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CII</t>
+          <t>BMP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.8</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>69.81999999999999</v>
+        <v>27.2</v>
       </c>
       <c r="D9" t="n">
-        <v>5454500</v>
+        <v>197100</v>
       </c>
       <c r="E9" t="n">
-        <v>6863805</v>
+        <v>58975</v>
       </c>
       <c r="F9" t="n">
-        <v>0.79</v>
+        <v>3.34</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1129,13 +1137,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13.98</v>
+        <v>146.8</v>
       </c>
       <c r="K9" t="n">
-        <v>16.08</v>
+        <v>142.18</v>
       </c>
       <c r="L9" t="n">
-        <v>-20.37</v>
+        <v>-2.94</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1147,79 +1155,79 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.3x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>56.96</v>
+        <v>27.52</v>
       </c>
       <c r="S9" t="n">
-        <v>62.05</v>
+        <v>30.82</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CTG</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30.6</v>
+        <v>28.85</v>
       </c>
       <c r="C10" t="n">
-        <v>312.12</v>
+        <v>142.17</v>
       </c>
       <c r="D10" t="n">
-        <v>10200000</v>
+        <v>4928000</v>
       </c>
       <c r="E10" t="n">
-        <v>6597160</v>
+        <v>10751945</v>
       </c>
       <c r="F10" t="n">
-        <v>1.55</v>
+        <v>0.46</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>30.7</v>
+        <v>27.9</v>
       </c>
       <c r="K10" t="n">
-        <v>32.32</v>
+        <v>27.96</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.32</v>
+        <v>3.18</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1231,47 +1239,47 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>61.19</v>
+        <v>27.61</v>
       </c>
       <c r="S10" t="n">
-        <v>51.46</v>
+        <v>23.24</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.1</v>
+        <v>70.7</v>
       </c>
       <c r="C11" t="n">
-        <v>52.09</v>
+        <v>116.85</v>
       </c>
       <c r="D11" t="n">
-        <v>2468600</v>
+        <v>1652800</v>
       </c>
       <c r="E11" t="n">
-        <v>967835</v>
+        <v>1062895</v>
       </c>
       <c r="F11" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1280,78 +1288,82 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>23.38</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>24.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-12.45</v>
+        <v>5.37</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>57.5</v>
+        <v>39.39</v>
       </c>
       <c r="S11" t="n">
-        <v>34.35</v>
+        <v>40.99</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>10.9</v>
       </c>
       <c r="C12" t="n">
-        <v>90.38</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1807700</v>
+        <v>7745600</v>
       </c>
       <c r="E12" t="n">
-        <v>1274350</v>
+        <v>5982115</v>
       </c>
       <c r="F12" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1360,34 +1372,30 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>43.2</v>
+        <v>11.75</v>
       </c>
       <c r="K12" t="n">
-        <v>42.32</v>
+        <v>13.61</v>
       </c>
       <c r="L12" t="n">
-        <v>18.13</v>
+        <v>-19.91</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1395,71 +1403,71 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>61.82</v>
+        <v>50</v>
       </c>
       <c r="S12" t="n">
-        <v>59.73</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>CII</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.9</v>
+        <v>12.95</v>
       </c>
       <c r="C13" t="n">
-        <v>48.15</v>
+        <v>118.36</v>
       </c>
       <c r="D13" t="n">
-        <v>1420400</v>
+        <v>9139400</v>
       </c>
       <c r="E13" t="n">
-        <v>2634980</v>
+        <v>7013330</v>
       </c>
       <c r="F13" t="n">
-        <v>0.54</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>31.95</v>
+        <v>13.7</v>
       </c>
       <c r="K13" t="n">
-        <v>36.94</v>
+        <v>16.08</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.23</v>
+        <v>-19.44</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1475,51 +1483,51 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>42.35</v>
+        <v>56.96</v>
       </c>
       <c r="S13" t="n">
-        <v>54.44</v>
+        <v>63.25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44.5</v>
+        <v>63.2</v>
       </c>
       <c r="C14" t="n">
-        <v>76.06999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="D14" t="n">
-        <v>1709500</v>
+        <v>394000</v>
       </c>
       <c r="E14" t="n">
-        <v>1726250</v>
+        <v>335165</v>
       </c>
       <c r="F14" t="n">
-        <v>0.99</v>
+        <v>1.18</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1529,28 +1537,24 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>39.83</v>
+        <v>60.6</v>
       </c>
       <c r="K14" t="n">
-        <v>39.83</v>
+        <v>72.5</v>
       </c>
       <c r="L14" t="n">
-        <v>11.72</v>
+        <v>-12.83</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
@@ -1559,10 +1563,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>49.71</v>
+        <v>63.78</v>
       </c>
       <c r="S14" t="n">
-        <v>44.05</v>
+        <v>62.04</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1576,34 +1580,34 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>CTG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.529999999999999</v>
+        <v>30.5</v>
       </c>
       <c r="C15" t="n">
-        <v>30.16</v>
+        <v>563.98</v>
       </c>
       <c r="D15" t="n">
-        <v>3165000</v>
+        <v>18491300</v>
       </c>
       <c r="E15" t="n">
-        <v>3986930</v>
+        <v>7125130</v>
       </c>
       <c r="F15" t="n">
-        <v>0.79</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1617,13 +1621,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10.32</v>
+        <v>30.7</v>
       </c>
       <c r="K15" t="n">
-        <v>11.52</v>
+        <v>32.32</v>
       </c>
       <c r="L15" t="n">
-        <v>-17.31</v>
+        <v>-5.63</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1635,14 +1639,14 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>59.74</v>
+        <v>61.19</v>
       </c>
       <c r="S15" t="n">
-        <v>67.54000000000001</v>
+        <v>45.54</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1656,34 +1660,34 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="C16" t="n">
-        <v>23.15</v>
+        <v>28.48</v>
       </c>
       <c r="D16" t="n">
-        <v>1092200</v>
+        <v>1362500</v>
       </c>
       <c r="E16" t="n">
-        <v>2569690</v>
+        <v>980210</v>
       </c>
       <c r="F16" t="n">
-        <v>0.43</v>
+        <v>1.39</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1697,13 +1701,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22.18</v>
+        <v>23.38</v>
       </c>
       <c r="K16" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="L16" t="n">
-        <v>-12.41</v>
+        <v>-13.28</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1719,10 +1723,10 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>24.24</v>
+        <v>55.42</v>
       </c>
       <c r="S16" t="n">
-        <v>25.55</v>
+        <v>41.95</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1736,73 +1740,81 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>DCL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10.15</v>
+        <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>98.34999999999999</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>9690100</v>
+        <v>730700</v>
       </c>
       <c r="E17" t="n">
-        <v>8391430</v>
+        <v>1105610</v>
       </c>
       <c r="F17" t="n">
-        <v>1.15</v>
+        <v>0.66</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10.88</v>
+        <v>44.65</v>
       </c>
       <c r="K17" t="n">
-        <v>11.89</v>
+        <v>43.78</v>
       </c>
       <c r="L17" t="n">
-        <v>-14.6</v>
+        <v>18.79</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>48.25</v>
+        <v>67.22</v>
       </c>
       <c r="S17" t="n">
-        <v>48.11</v>
+        <v>59.4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1811,35 +1823,35 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16.35</v>
+        <v>33.85</v>
       </c>
       <c r="C18" t="n">
-        <v>47.2</v>
+        <v>34.46</v>
       </c>
       <c r="D18" t="n">
-        <v>2886900</v>
+        <v>1018100</v>
       </c>
       <c r="E18" t="n">
-        <v>3193350</v>
+        <v>2528590</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1848,22 +1860,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17.65</v>
+        <v>31.95</v>
       </c>
       <c r="K18" t="n">
-        <v>19.65</v>
+        <v>36.58</v>
       </c>
       <c r="L18" t="n">
-        <v>-16.79</v>
+        <v>-7.48</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1879,47 +1891,47 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>38.89</v>
+        <v>43.9</v>
       </c>
       <c r="S18" t="n">
-        <v>48.59</v>
+        <v>53.01</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>58.2</v>
+        <v>45.45</v>
       </c>
       <c r="C19" t="n">
-        <v>217.28</v>
+        <v>47.05</v>
       </c>
       <c r="D19" t="n">
-        <v>3733300</v>
+        <v>1035100</v>
       </c>
       <c r="E19" t="n">
-        <v>5238545</v>
+        <v>1718300</v>
       </c>
       <c r="F19" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1928,29 +1940,33 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>61.9</v>
+        <v>39.83</v>
       </c>
       <c r="K19" t="n">
-        <v>63.22</v>
+        <v>39.83</v>
       </c>
       <c r="L19" t="n">
-        <v>-7.94</v>
+        <v>14.11</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
@@ -1959,82 +1975,78 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>20.43</v>
+        <v>53.45</v>
       </c>
       <c r="S19" t="n">
-        <v>20.4</v>
+        <v>42.86</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>26.55</v>
+        <v>45.81</v>
       </c>
       <c r="D20" t="n">
-        <v>188300</v>
+        <v>4801400</v>
       </c>
       <c r="E20" t="n">
-        <v>687395</v>
+        <v>4105695</v>
       </c>
       <c r="F20" t="n">
-        <v>0.27</v>
+        <v>1.17</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>126.5</v>
+        <v>10.32</v>
       </c>
       <c r="K20" t="n">
-        <v>126.5</v>
+        <v>11.52</v>
       </c>
       <c r="L20" t="n">
-        <v>11.46</v>
+        <v>-17.22</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
@@ -2043,47 +2055,47 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>51.48</v>
+        <v>50.4</v>
       </c>
       <c r="S20" t="n">
-        <v>73.7</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>76.09999999999999</v>
+        <v>21.25</v>
       </c>
       <c r="C21" t="n">
-        <v>62.58</v>
+        <v>25.74</v>
       </c>
       <c r="D21" t="n">
-        <v>822300</v>
+        <v>1211500</v>
       </c>
       <c r="E21" t="n">
-        <v>1114940</v>
+        <v>2485810</v>
       </c>
       <c r="F21" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2097,17 +2109,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>76.48</v>
+        <v>22.18</v>
       </c>
       <c r="K21" t="n">
-        <v>77.69</v>
+        <v>24.11</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.05</v>
+        <v>-11.86</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2123,10 +2135,10 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>30.11</v>
+        <v>23.08</v>
       </c>
       <c r="S21" t="n">
-        <v>35.37</v>
+        <v>20.01</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2140,34 +2152,34 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>66</v>
+        <v>10.25</v>
       </c>
       <c r="C22" t="n">
-        <v>48.88</v>
+        <v>152.14</v>
       </c>
       <c r="D22" t="n">
-        <v>740600</v>
+        <v>14842800</v>
       </c>
       <c r="E22" t="n">
-        <v>1520955</v>
+        <v>8860865</v>
       </c>
       <c r="F22" t="n">
-        <v>0.49</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2177,17 +2189,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>70.04000000000001</v>
+        <v>10.78</v>
       </c>
       <c r="K22" t="n">
-        <v>95.83</v>
+        <v>11.89</v>
       </c>
       <c r="L22" t="n">
-        <v>-31.13</v>
+        <v>-13.76</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2203,10 +2215,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>37.02</v>
+        <v>53.38</v>
       </c>
       <c r="S22" t="n">
-        <v>45.58</v>
+        <v>51.62</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2220,39 +2232,39 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.5</v>
+        <v>16.25</v>
       </c>
       <c r="C23" t="n">
-        <v>23.43</v>
+        <v>55.69</v>
       </c>
       <c r="D23" t="n">
-        <v>851900</v>
+        <v>3427000</v>
       </c>
       <c r="E23" t="n">
-        <v>1378535</v>
+        <v>3170715</v>
       </c>
       <c r="F23" t="n">
-        <v>0.62</v>
+        <v>1.08</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2261,13 +2273,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>27.15</v>
+        <v>17.58</v>
       </c>
       <c r="K23" t="n">
-        <v>29.42</v>
+        <v>19.65</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.54</v>
+        <v>-17.3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2283,51 +2295,51 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>33</v>
+        <v>22.58</v>
       </c>
       <c r="S23" t="n">
-        <v>40.93</v>
+        <v>35.11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22.5</v>
+        <v>57.1</v>
       </c>
       <c r="C24" t="n">
-        <v>175.16</v>
+        <v>239.28</v>
       </c>
       <c r="D24" t="n">
-        <v>7784900</v>
+        <v>4190500</v>
       </c>
       <c r="E24" t="n">
-        <v>5995305</v>
+        <v>5027990</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3</v>
+        <v>0.83</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2341,13 +2353,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>23.45</v>
+        <v>61.9</v>
       </c>
       <c r="K24" t="n">
-        <v>28.58</v>
+        <v>63.22</v>
       </c>
       <c r="L24" t="n">
-        <v>-21.26</v>
+        <v>-9.68</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2363,10 +2375,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>34.44</v>
+        <v>19.19</v>
       </c>
       <c r="S24" t="n">
-        <v>40.1</v>
+        <v>20.2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2380,34 +2392,34 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="C25" t="n">
-        <v>95.22</v>
+        <v>80.02</v>
       </c>
       <c r="D25" t="n">
-        <v>1763400</v>
+        <v>548100</v>
       </c>
       <c r="E25" t="n">
-        <v>1183475</v>
+        <v>702935</v>
       </c>
       <c r="F25" t="n">
-        <v>1.49</v>
+        <v>0.78</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2421,17 +2433,17 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>50.34</v>
+        <v>126.5</v>
       </c>
       <c r="K25" t="n">
-        <v>50.34</v>
+        <v>126.5</v>
       </c>
       <c r="L25" t="n">
-        <v>7.28</v>
+        <v>15.42</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2439,7 +2451,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2447,14 +2463,14 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>64.05</v>
+        <v>55.43</v>
       </c>
       <c r="S25" t="n">
-        <v>66.73999999999999</v>
+        <v>73.14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2464,30 +2480,30 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.25</v>
+        <v>76.7</v>
       </c>
       <c r="C26" t="n">
-        <v>35.69</v>
+        <v>41.09</v>
       </c>
       <c r="D26" t="n">
-        <v>1142000</v>
+        <v>535700</v>
       </c>
       <c r="E26" t="n">
-        <v>2788450</v>
+        <v>1069090</v>
       </c>
       <c r="F26" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2505,13 +2521,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30.22</v>
+        <v>76.48</v>
       </c>
       <c r="K26" t="n">
-        <v>32.78</v>
+        <v>77.69</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.65</v>
+        <v>-1.28</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2527,14 +2543,14 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>42.64</v>
+        <v>26.97</v>
       </c>
       <c r="S26" t="n">
-        <v>42.54</v>
+        <v>29.43</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2544,30 +2560,30 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>48.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>30.06</v>
+        <v>75.3</v>
       </c>
       <c r="D27" t="n">
-        <v>614700</v>
+        <v>1134100</v>
       </c>
       <c r="E27" t="n">
-        <v>1253470</v>
+        <v>1538095</v>
       </c>
       <c r="F27" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2576,22 +2592,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>48.2</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>49.55</v>
+        <v>95.83</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.31</v>
+        <v>-30.71</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2607,47 +2623,47 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>35.83</v>
+        <v>39.15</v>
       </c>
       <c r="S27" t="n">
-        <v>44.11</v>
+        <v>52.5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23.75</v>
+        <v>27.6</v>
       </c>
       <c r="C28" t="n">
-        <v>46.74</v>
+        <v>30.09</v>
       </c>
       <c r="D28" t="n">
-        <v>1968100</v>
+        <v>1090200</v>
       </c>
       <c r="E28" t="n">
-        <v>2651300</v>
+        <v>1365465</v>
       </c>
       <c r="F28" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2661,17 +2677,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>24.92</v>
+        <v>27.15</v>
       </c>
       <c r="K28" t="n">
-        <v>24.39</v>
+        <v>29.42</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.62</v>
+        <v>-6.2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2687,10 +2703,10 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>48.42</v>
+        <v>35</v>
       </c>
       <c r="S28" t="n">
-        <v>32.38</v>
+        <v>41.18</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2704,30 +2720,30 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.8</v>
+        <v>22.75</v>
       </c>
       <c r="C29" t="n">
-        <v>553.84</v>
+        <v>221.58</v>
       </c>
       <c r="D29" t="n">
-        <v>24291300</v>
+        <v>9739600</v>
       </c>
       <c r="E29" t="n">
-        <v>15602300</v>
+        <v>6131730</v>
       </c>
       <c r="F29" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2736,33 +2752,29 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>21.13</v>
+        <v>23.45</v>
       </c>
       <c r="K29" t="n">
-        <v>21.13</v>
+        <v>28.58</v>
       </c>
       <c r="L29" t="n">
-        <v>7.9</v>
+        <v>-20.38</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
@@ -2771,56 +2783,56 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>74.63</v>
+        <v>37.89</v>
       </c>
       <c r="S29" t="n">
-        <v>70.33</v>
+        <v>43.69</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HHP</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17.25</v>
+        <v>54</v>
       </c>
       <c r="C30" t="n">
-        <v>29.39</v>
+        <v>31.69</v>
       </c>
       <c r="D30" t="n">
-        <v>1703500</v>
+        <v>586900</v>
       </c>
       <c r="E30" t="n">
-        <v>1279170</v>
+        <v>1180595</v>
       </c>
       <c r="F30" t="n">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2829,93 +2841,101 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>16.34</v>
+        <v>50.34</v>
       </c>
       <c r="K30" t="n">
-        <v>15.31</v>
+        <v>50.34</v>
       </c>
       <c r="L30" t="n">
-        <v>12.67</v>
+        <v>7.28</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>39.62</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>60.32</v>
+        <v>69.38</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HHV</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9.5</v>
+        <v>31.35</v>
       </c>
       <c r="C31" t="n">
-        <v>26.26</v>
+        <v>40.21</v>
       </c>
       <c r="D31" t="n">
-        <v>2764700</v>
+        <v>1282500</v>
       </c>
       <c r="E31" t="n">
-        <v>2555090</v>
+        <v>2744190</v>
       </c>
       <c r="F31" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>9.630000000000001</v>
+        <v>30.22</v>
       </c>
       <c r="K31" t="n">
-        <v>10.68</v>
+        <v>32.78</v>
       </c>
       <c r="L31" t="n">
-        <v>-11.09</v>
+        <v>-4.35</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2931,47 +2951,47 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>66.04000000000001</v>
+        <v>32.11</v>
       </c>
       <c r="S31" t="n">
-        <v>63.2</v>
+        <v>38.62</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HAH</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20.9</v>
+        <v>49.1</v>
       </c>
       <c r="C32" t="n">
-        <v>212.96</v>
+        <v>34.93</v>
       </c>
       <c r="D32" t="n">
-        <v>10189400</v>
+        <v>711400</v>
       </c>
       <c r="E32" t="n">
-        <v>17609270</v>
+        <v>1266395</v>
       </c>
       <c r="F32" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2980,22 +3000,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>21.12</v>
+        <v>48.2</v>
       </c>
       <c r="K32" t="n">
-        <v>22.94</v>
+        <v>49.55</v>
       </c>
       <c r="L32" t="n">
-        <v>-8.91</v>
+        <v>-0.91</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -3004,67 +3024,63 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>63.46</v>
+        <v>33.62</v>
       </c>
       <c r="S32" t="n">
-        <v>48.86</v>
+        <v>39.48</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10.4</v>
+        <v>24.2</v>
       </c>
       <c r="C33" t="n">
-        <v>21.74</v>
+        <v>69.94</v>
       </c>
       <c r="D33" t="n">
-        <v>2090700</v>
+        <v>2889900</v>
       </c>
       <c r="E33" t="n">
-        <v>2464765</v>
+        <v>2673555</v>
       </c>
       <c r="F33" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3073,13 +3089,13 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>10.72</v>
+        <v>24.92</v>
       </c>
       <c r="K33" t="n">
-        <v>11.35</v>
+        <v>24.76</v>
       </c>
       <c r="L33" t="n">
-        <v>-8.369999999999999</v>
+        <v>-2.24</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3095,78 +3111,82 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>66.01000000000001</v>
+        <v>47.31</v>
       </c>
       <c r="S33" t="n">
-        <v>58.34</v>
+        <v>41.39</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HVN</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21</v>
+        <v>22.75</v>
       </c>
       <c r="C34" t="n">
-        <v>28.58</v>
+        <v>291.56</v>
       </c>
       <c r="D34" t="n">
-        <v>1361100</v>
+        <v>12815800</v>
       </c>
       <c r="E34" t="n">
-        <v>555875</v>
+        <v>15669115</v>
       </c>
       <c r="F34" t="n">
-        <v>2.45</v>
+        <v>0.82</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>22.55</v>
+        <v>21.13</v>
       </c>
       <c r="K34" t="n">
-        <v>23.25</v>
+        <v>21.13</v>
       </c>
       <c r="L34" t="n">
-        <v>-9.68</v>
+        <v>7.67</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -3175,47 +3195,47 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>57.14</v>
+        <v>75.08</v>
       </c>
       <c r="S34" t="n">
-        <v>64.54000000000001</v>
+        <v>74.08</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KBC</t>
+          <t>HHP</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25.9</v>
+        <v>17</v>
       </c>
       <c r="C35" t="n">
-        <v>22.63</v>
+        <v>20.47</v>
       </c>
       <c r="D35" t="n">
-        <v>873600</v>
+        <v>1203900</v>
       </c>
       <c r="E35" t="n">
-        <v>1131565</v>
+        <v>1254710</v>
       </c>
       <c r="F35" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3224,26 +3244,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>26.55</v>
+        <v>16.39</v>
       </c>
       <c r="K35" t="n">
-        <v>30.05</v>
+        <v>15.31</v>
       </c>
       <c r="L35" t="n">
-        <v>-13.81</v>
+        <v>11.04</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -3255,10 +3275,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>52.5</v>
+        <v>36.84</v>
       </c>
       <c r="S35" t="n">
-        <v>39.64</v>
+        <v>54.4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3267,39 +3287,39 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>HHV</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14.15</v>
+        <v>9.33</v>
       </c>
       <c r="C36" t="n">
-        <v>107.85</v>
+        <v>33.95</v>
       </c>
       <c r="D36" t="n">
-        <v>7622200</v>
+        <v>3638700</v>
       </c>
       <c r="E36" t="n">
-        <v>3805180</v>
+        <v>2672735</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3313,13 +3333,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>15.54</v>
+        <v>9.56</v>
       </c>
       <c r="K36" t="n">
-        <v>18.75</v>
+        <v>10.57</v>
       </c>
       <c r="L36" t="n">
-        <v>-24.53</v>
+        <v>-11.69</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3335,10 +3355,10 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>55.61</v>
+        <v>57.74</v>
       </c>
       <c r="S36" t="n">
-        <v>56.82</v>
+        <v>55.48</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3352,34 +3372,34 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>38</v>
+        <v>20.55</v>
       </c>
       <c r="C37" t="n">
-        <v>77.61</v>
+        <v>271.77</v>
       </c>
       <c r="D37" t="n">
-        <v>2042300</v>
+        <v>13224600</v>
       </c>
       <c r="E37" t="n">
-        <v>1976080</v>
+        <v>17479300</v>
       </c>
       <c r="F37" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3393,13 +3413,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>46.6</v>
+        <v>21.12</v>
       </c>
       <c r="K37" t="n">
-        <v>47.85</v>
+        <v>22.94</v>
       </c>
       <c r="L37" t="n">
-        <v>-20.59</v>
+        <v>-10.44</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3415,10 +3435,10 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>28.69</v>
+        <v>54.39</v>
       </c>
       <c r="S37" t="n">
-        <v>25.27</v>
+        <v>49.86</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3432,30 +3452,30 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.85</v>
+        <v>10.45</v>
       </c>
       <c r="C38" t="n">
-        <v>216.75</v>
+        <v>25.55</v>
       </c>
       <c r="D38" t="n">
-        <v>10919400</v>
+        <v>2444500</v>
       </c>
       <c r="E38" t="n">
-        <v>11607255</v>
+        <v>2513535</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3464,26 +3484,26 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>19.49</v>
+        <v>10.65</v>
       </c>
       <c r="K38" t="n">
-        <v>19.7</v>
+        <v>11.35</v>
       </c>
       <c r="L38" t="n">
-        <v>0.76</v>
+        <v>-7.93</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3495,51 +3515,51 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>51.02</v>
+        <v>62.59</v>
       </c>
       <c r="S38" t="n">
-        <v>50.15</v>
+        <v>58.79</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15.1</v>
+        <v>12.3</v>
       </c>
       <c r="C39" t="n">
-        <v>33.2</v>
+        <v>29.44</v>
       </c>
       <c r="D39" t="n">
-        <v>2199000</v>
+        <v>2393800</v>
       </c>
       <c r="E39" t="n">
-        <v>2705290</v>
+        <v>1733390</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3553,13 +3573,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>16.77</v>
+        <v>13.35</v>
       </c>
       <c r="K39" t="n">
-        <v>17.43</v>
+        <v>14.45</v>
       </c>
       <c r="L39" t="n">
-        <v>-13.39</v>
+        <v>-14.88</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3575,10 +3595,10 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>38.46</v>
+        <v>40</v>
       </c>
       <c r="S39" t="n">
-        <v>39.2</v>
+        <v>38.6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3592,34 +3612,34 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>140</v>
+        <v>33.9</v>
       </c>
       <c r="C40" t="n">
-        <v>83.19</v>
+        <v>36.55</v>
       </c>
       <c r="D40" t="n">
-        <v>594200</v>
+        <v>1078100</v>
       </c>
       <c r="E40" t="n">
-        <v>559540</v>
+        <v>1328020</v>
       </c>
       <c r="F40" t="n">
-        <v>1.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3629,21 +3649,21 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>138.57</v>
+        <v>32.45</v>
       </c>
       <c r="K40" t="n">
-        <v>134.54</v>
+        <v>36.67</v>
       </c>
       <c r="L40" t="n">
-        <v>4.06</v>
+        <v>-7.55</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3655,14 +3675,14 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>60.42</v>
+        <v>53.7</v>
       </c>
       <c r="S40" t="n">
-        <v>28.73</v>
+        <v>57.98</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -3672,30 +3692,30 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>14.8</v>
+        <v>14.15</v>
       </c>
       <c r="C41" t="n">
-        <v>173.85</v>
+        <v>43.48</v>
       </c>
       <c r="D41" t="n">
-        <v>11746800</v>
+        <v>3073100</v>
       </c>
       <c r="E41" t="n">
-        <v>12337480</v>
+        <v>3745420</v>
       </c>
       <c r="F41" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3704,34 +3724,30 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>13.56</v>
+        <v>15.41</v>
       </c>
       <c r="K41" t="n">
-        <v>12.66</v>
+        <v>18.75</v>
       </c>
       <c r="L41" t="n">
-        <v>16.86</v>
+        <v>-24.53</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3739,10 +3755,10 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>66.67</v>
+        <v>54.76</v>
       </c>
       <c r="S41" t="n">
-        <v>70.03</v>
+        <v>55.62</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3751,39 +3767,39 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>71.40000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="C42" t="n">
-        <v>215.18</v>
+        <v>30.22</v>
       </c>
       <c r="D42" t="n">
-        <v>3013700</v>
+        <v>2222100</v>
       </c>
       <c r="E42" t="n">
-        <v>5655410</v>
+        <v>583485</v>
       </c>
       <c r="F42" t="n">
-        <v>0.53</v>
+        <v>3.81</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3793,17 +3809,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>68.90000000000001</v>
+        <v>13.48</v>
       </c>
       <c r="K42" t="n">
-        <v>72.09999999999999</v>
+        <v>14.68</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.97</v>
+        <v>-7.33</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3815,18 +3831,18 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.8x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>58.33</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="S42" t="n">
-        <v>64.47</v>
+        <v>77.05</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -3836,30 +3852,30 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>64.90000000000001</v>
+        <v>38.45</v>
       </c>
       <c r="C43" t="n">
-        <v>108.27</v>
+        <v>51.25</v>
       </c>
       <c r="D43" t="n">
-        <v>1668200</v>
+        <v>1332900</v>
       </c>
       <c r="E43" t="n">
-        <v>2597615</v>
+        <v>1918225</v>
       </c>
       <c r="F43" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3868,38 +3884,30 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>50.57</v>
+        <v>46.6</v>
       </c>
       <c r="K43" t="n">
-        <v>50.57</v>
+        <v>47.85</v>
       </c>
       <c r="L43" t="n">
-        <v>28.34</v>
+        <v>-19.64</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3907,51 +3915,51 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>74.31</v>
+        <v>34.27</v>
       </c>
       <c r="S43" t="n">
-        <v>72.45999999999999</v>
+        <v>32.15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>73.90000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="C44" t="n">
-        <v>101.38</v>
+        <v>236.98</v>
       </c>
       <c r="D44" t="n">
-        <v>1371800</v>
+        <v>12029200</v>
       </c>
       <c r="E44" t="n">
-        <v>2873870</v>
+        <v>11513845</v>
       </c>
       <c r="F44" t="n">
-        <v>0.48</v>
+        <v>1.04</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3961,21 +3969,21 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>69.02</v>
+        <v>19.49</v>
       </c>
       <c r="K44" t="n">
-        <v>73.36</v>
+        <v>19.7</v>
       </c>
       <c r="L44" t="n">
-        <v>0.74</v>
+        <v>-0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3987,10 +3995,10 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>62.67</v>
+        <v>52.08</v>
       </c>
       <c r="S44" t="n">
-        <v>66.97</v>
+        <v>49.36</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4004,54 +4012,54 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12.1</v>
+        <v>15.4</v>
       </c>
       <c r="C45" t="n">
-        <v>23.91</v>
+        <v>52.2</v>
       </c>
       <c r="D45" t="n">
-        <v>1975800</v>
+        <v>3389500</v>
       </c>
       <c r="E45" t="n">
-        <v>2070220</v>
+        <v>2747085</v>
       </c>
       <c r="F45" t="n">
-        <v>0.95</v>
+        <v>1.23</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>12.05</v>
+        <v>16.44</v>
       </c>
       <c r="K45" t="n">
-        <v>12.25</v>
+        <v>17.43</v>
       </c>
       <c r="L45" t="n">
-        <v>-1.22</v>
+        <v>-11.67</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4067,75 +4075,75 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>43.59</v>
+        <v>48.15</v>
       </c>
       <c r="S45" t="n">
-        <v>50.1</v>
+        <v>48.07</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10.4</v>
+        <v>139.8</v>
       </c>
       <c r="C46" t="n">
-        <v>20.5</v>
+        <v>116.17</v>
       </c>
       <c r="D46" t="n">
-        <v>1971000</v>
+        <v>831000</v>
       </c>
       <c r="E46" t="n">
-        <v>2169110</v>
+        <v>542515</v>
       </c>
       <c r="F46" t="n">
-        <v>0.91</v>
+        <v>1.53</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>10.45</v>
+        <v>138.57</v>
       </c>
       <c r="K46" t="n">
-        <v>11.48</v>
+        <v>134.54</v>
       </c>
       <c r="L46" t="n">
-        <v>-9.369999999999999</v>
+        <v>3.91</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4147,47 +4155,47 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>67.54000000000001</v>
+        <v>59.18</v>
       </c>
       <c r="S46" t="n">
-        <v>77.15000000000001</v>
+        <v>29.78</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>10.65</v>
+        <v>14.8</v>
       </c>
       <c r="C47" t="n">
-        <v>156.66</v>
+        <v>148.24</v>
       </c>
       <c r="D47" t="n">
-        <v>14710300</v>
+        <v>10016500</v>
       </c>
       <c r="E47" t="n">
-        <v>26799159</v>
+        <v>12654445</v>
       </c>
       <c r="F47" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4196,30 +4204,34 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>11.88</v>
+        <v>13.56</v>
       </c>
       <c r="K47" t="n">
-        <v>14.5</v>
+        <v>12.66</v>
       </c>
       <c r="L47" t="n">
-        <v>-26.53</v>
+        <v>16.86</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4227,10 +4239,10 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>44.33</v>
+        <v>70.27</v>
       </c>
       <c r="S47" t="n">
-        <v>35.87</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4239,35 +4251,35 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>24.69</v>
+        <v>303.75</v>
       </c>
       <c r="D48" t="n">
-        <v>1829000</v>
+        <v>4195500</v>
       </c>
       <c r="E48" t="n">
-        <v>1888120</v>
+        <v>5683590</v>
       </c>
       <c r="F48" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4281,21 +4293,21 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>13.78</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>13.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.82</v>
+        <v>0.42</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -4307,10 +4319,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="S48" t="n">
-        <v>66.69</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4324,30 +4336,30 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>11.2</v>
+        <v>65.5</v>
       </c>
       <c r="C49" t="n">
-        <v>32.59</v>
+        <v>54.67</v>
       </c>
       <c r="D49" t="n">
-        <v>2910000</v>
+        <v>834700</v>
       </c>
       <c r="E49" t="n">
-        <v>4177185</v>
+        <v>2438835</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4356,30 +4368,38 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>12.12</v>
+        <v>50.57</v>
       </c>
       <c r="K49" t="n">
-        <v>13.82</v>
+        <v>50.57</v>
       </c>
       <c r="L49" t="n">
-        <v>-18.99</v>
+        <v>29.52</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4387,75 +4407,75 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>44.44</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>55.83</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>35.05</v>
+        <v>74.2</v>
       </c>
       <c r="C50" t="n">
-        <v>177.74</v>
+        <v>127.68</v>
       </c>
       <c r="D50" t="n">
-        <v>5070900</v>
+        <v>1720700</v>
       </c>
       <c r="E50" t="n">
-        <v>4457945</v>
+        <v>2847185</v>
       </c>
       <c r="F50" t="n">
-        <v>1.14</v>
+        <v>0.6</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>35.15</v>
+        <v>69.02</v>
       </c>
       <c r="K50" t="n">
-        <v>38.08</v>
+        <v>73.36</v>
       </c>
       <c r="L50" t="n">
-        <v>-7.97</v>
+        <v>1.15</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -4467,71 +4487,71 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>47.03</v>
+        <v>64.19</v>
       </c>
       <c r="S50" t="n">
-        <v>62.03</v>
+        <v>70.8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>18.8</v>
+        <v>12</v>
       </c>
       <c r="C51" t="n">
-        <v>114.22</v>
+        <v>26.54</v>
       </c>
       <c r="D51" t="n">
-        <v>6075400</v>
+        <v>2211900</v>
       </c>
       <c r="E51" t="n">
-        <v>13522000</v>
+        <v>2115730</v>
       </c>
       <c r="F51" t="n">
-        <v>0.45</v>
+        <v>1.05</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>32.02</v>
+        <v>12.05</v>
       </c>
       <c r="K51" t="n">
-        <v>47.16</v>
+        <v>12.25</v>
       </c>
       <c r="L51" t="n">
-        <v>-60.14</v>
+        <v>-2.04</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4547,56 +4567,56 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>16.38</v>
+        <v>42.5</v>
       </c>
       <c r="S51" t="n">
-        <v>7.44</v>
+        <v>48.98</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.2</v>
+        <v>10.6</v>
       </c>
       <c r="C52" t="n">
-        <v>59.09</v>
+        <v>35.06</v>
       </c>
       <c r="D52" t="n">
-        <v>4843200</v>
+        <v>3307300</v>
       </c>
       <c r="E52" t="n">
-        <v>5579535</v>
+        <v>2270965</v>
       </c>
       <c r="F52" t="n">
-        <v>0.87</v>
+        <v>1.46</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4605,13 +4625,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>13.08</v>
+        <v>10.38</v>
       </c>
       <c r="K52" t="n">
-        <v>13.6</v>
+        <v>11.48</v>
       </c>
       <c r="L52" t="n">
-        <v>-10.29</v>
+        <v>-7.63</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4627,47 +4647,47 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>33.33</v>
+        <v>69.37</v>
       </c>
       <c r="S52" t="n">
-        <v>38.63</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>NVB</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>17.65</v>
+        <v>13.3</v>
       </c>
       <c r="C53" t="n">
-        <v>29.78</v>
+        <v>28.77</v>
       </c>
       <c r="D53" t="n">
-        <v>1687300</v>
+        <v>2163000</v>
       </c>
       <c r="E53" t="n">
-        <v>3730645</v>
+        <v>2173210</v>
       </c>
       <c r="F53" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4676,29 +4696,33 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>19.02</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>19.43</v>
+        <v>14</v>
       </c>
       <c r="L53" t="n">
-        <v>-9.16</v>
+        <v>-5</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
@@ -4707,75 +4731,75 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>36.11</v>
+        <v>48.98</v>
       </c>
       <c r="S53" t="n">
-        <v>49.34</v>
+        <v>54.62</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.4</v>
+        <v>10.75</v>
       </c>
       <c r="C54" t="n">
-        <v>24.59</v>
+        <v>296.37</v>
       </c>
       <c r="D54" t="n">
-        <v>1097700</v>
+        <v>27569200</v>
       </c>
       <c r="E54" t="n">
-        <v>1607155</v>
+        <v>27259249</v>
       </c>
       <c r="F54" t="n">
-        <v>0.68</v>
+        <v>1.01</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>20.6</v>
+        <v>11.88</v>
       </c>
       <c r="K54" t="n">
-        <v>19.51</v>
+        <v>14.5</v>
       </c>
       <c r="L54" t="n">
-        <v>14.81</v>
+        <v>-25.84</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4787,47 +4811,47 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>58.12</v>
+        <v>61.93</v>
       </c>
       <c r="S54" t="n">
-        <v>59.96</v>
+        <v>41.63</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31.4</v>
+        <v>13.5</v>
       </c>
       <c r="C55" t="n">
-        <v>49.87</v>
+        <v>20.92</v>
       </c>
       <c r="D55" t="n">
-        <v>1588100</v>
+        <v>1549700</v>
       </c>
       <c r="E55" t="n">
-        <v>3635455</v>
+        <v>1888125</v>
       </c>
       <c r="F55" t="n">
-        <v>0.44</v>
+        <v>0.82</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4841,17 +4865,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>30.94</v>
+        <v>13.78</v>
       </c>
       <c r="K55" t="n">
-        <v>31.62</v>
+        <v>13.75</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.71</v>
+        <v>-1.82</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4867,10 +4891,10 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>34.85</v>
+        <v>62.5</v>
       </c>
       <c r="S55" t="n">
-        <v>50.12</v>
+        <v>67.22</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4884,30 +4908,30 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23.65</v>
+        <v>11.25</v>
       </c>
       <c r="C56" t="n">
-        <v>176.82</v>
+        <v>40.55</v>
       </c>
       <c r="D56" t="n">
-        <v>7476700</v>
+        <v>3604600</v>
       </c>
       <c r="E56" t="n">
-        <v>8287035</v>
+        <v>4266725</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4916,33 +4940,29 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>21.2</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>21.2</v>
+        <v>13.82</v>
       </c>
       <c r="L56" t="n">
-        <v>11.56</v>
+        <v>-18.63</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
@@ -4951,47 +4971,47 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>51.45</v>
+        <v>47.37</v>
       </c>
       <c r="S56" t="n">
-        <v>54.41</v>
+        <v>55.63</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>22.65</v>
+        <v>50</v>
       </c>
       <c r="C57" t="n">
-        <v>23.89</v>
+        <v>24.96</v>
       </c>
       <c r="D57" t="n">
-        <v>1054700</v>
+        <v>499300</v>
       </c>
       <c r="E57" t="n">
-        <v>1152145</v>
+        <v>922955</v>
       </c>
       <c r="F57" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5005,17 +5025,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>22.3</v>
+        <v>45.2</v>
       </c>
       <c r="K57" t="n">
-        <v>21.92</v>
+        <v>44.22</v>
       </c>
       <c r="L57" t="n">
-        <v>3.31</v>
+        <v>13.08</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5031,10 +5051,10 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>47.62</v>
+        <v>38.7</v>
       </c>
       <c r="S57" t="n">
-        <v>45.79</v>
+        <v>54.21</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5048,54 +5068,54 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10.65</v>
+        <v>35.15</v>
       </c>
       <c r="C58" t="n">
-        <v>532.22</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>49973400</v>
+        <v>1968200</v>
       </c>
       <c r="E58" t="n">
-        <v>42105920</v>
+        <v>4314300</v>
       </c>
       <c r="F58" t="n">
-        <v>1.19</v>
+        <v>0.46</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>11.23</v>
+        <v>35.15</v>
       </c>
       <c r="K58" t="n">
-        <v>12.55</v>
+        <v>38.08</v>
       </c>
       <c r="L58" t="n">
-        <v>-15.14</v>
+        <v>-7.71</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5111,51 +5131,51 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>32.65</v>
+        <v>42.35</v>
       </c>
       <c r="S58" t="n">
-        <v>20.09</v>
+        <v>59.85</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="C59" t="n">
-        <v>142.95</v>
+        <v>116.31</v>
       </c>
       <c r="D59" t="n">
-        <v>11621600</v>
+        <v>6287100</v>
       </c>
       <c r="E59" t="n">
-        <v>8774690</v>
+        <v>13748640</v>
       </c>
       <c r="F59" t="n">
-        <v>1.32</v>
+        <v>0.46</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5169,13 +5189,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>13.9</v>
+        <v>31.4</v>
       </c>
       <c r="K59" t="n">
-        <v>15</v>
+        <v>47.16</v>
       </c>
       <c r="L59" t="n">
-        <v>-18.03</v>
+        <v>-60.77</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5191,10 +5211,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>43.07</v>
+        <v>18.24</v>
       </c>
       <c r="S59" t="n">
-        <v>48.12</v>
+        <v>9.6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5208,30 +5228,30 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>16.15</v>
+        <v>12.25</v>
       </c>
       <c r="C60" t="n">
-        <v>30.84</v>
+        <v>32.81</v>
       </c>
       <c r="D60" t="n">
-        <v>1909700</v>
+        <v>2678100</v>
       </c>
       <c r="E60" t="n">
-        <v>2493315</v>
+        <v>5550795</v>
       </c>
       <c r="F60" t="n">
-        <v>0.77</v>
+        <v>0.48</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5240,7 +5260,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5249,13 +5269,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>19.77</v>
+        <v>13.08</v>
       </c>
       <c r="K60" t="n">
-        <v>19.19</v>
+        <v>13.6</v>
       </c>
       <c r="L60" t="n">
-        <v>-15.82</v>
+        <v>-9.93</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5271,47 +5291,47 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>27.5</v>
+        <v>33.33</v>
       </c>
       <c r="S60" t="n">
-        <v>28.55</v>
+        <v>37.19</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>19.45</v>
+        <v>17.7</v>
       </c>
       <c r="C61" t="n">
-        <v>244.83</v>
+        <v>46.46</v>
       </c>
       <c r="D61" t="n">
-        <v>12587800</v>
+        <v>2625100</v>
       </c>
       <c r="E61" t="n">
-        <v>19044040</v>
+        <v>3617750</v>
       </c>
       <c r="F61" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5329,13 +5349,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>19.55</v>
+        <v>18.88</v>
       </c>
       <c r="K61" t="n">
-        <v>20.34</v>
+        <v>19.43</v>
       </c>
       <c r="L61" t="n">
-        <v>-4.4</v>
+        <v>-8.9</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -5351,10 +5371,10 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>34.09</v>
+        <v>31.34</v>
       </c>
       <c r="S61" t="n">
-        <v>33.25</v>
+        <v>47</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5368,30 +5388,30 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>62.8</v>
+        <v>31.8</v>
       </c>
       <c r="C62" t="n">
-        <v>112.41</v>
+        <v>52.03</v>
       </c>
       <c r="D62" t="n">
-        <v>1790000</v>
+        <v>1636200</v>
       </c>
       <c r="E62" t="n">
-        <v>2994070</v>
+        <v>3569320</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -5405,28 +5425,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>70.8</v>
+        <v>30.94</v>
       </c>
       <c r="K62" t="n">
-        <v>70.8</v>
+        <v>31.62</v>
       </c>
       <c r="L62" t="n">
-        <v>-11.3</v>
+        <v>0.55</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
@@ -5435,14 +5451,14 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>3.25</v>
+        <v>31.75</v>
       </c>
       <c r="S62" t="n">
-        <v>10.02</v>
+        <v>44.1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -5452,30 +5468,30 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>33.2</v>
+        <v>24.1</v>
       </c>
       <c r="C63" t="n">
-        <v>423</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>12740900</v>
+        <v>3236800</v>
       </c>
       <c r="E63" t="n">
-        <v>18159075</v>
+        <v>8123490</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -5493,13 +5509,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>31.5</v>
+        <v>21.2</v>
       </c>
       <c r="K63" t="n">
-        <v>31.5</v>
+        <v>21.2</v>
       </c>
       <c r="L63" t="n">
-        <v>5.4</v>
+        <v>13.68</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5519,10 +5535,10 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>54.55</v>
+        <v>42.74</v>
       </c>
       <c r="S63" t="n">
-        <v>60.9</v>
+        <v>48.95</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -5536,30 +5552,30 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>11.2</v>
+        <v>22.5</v>
       </c>
       <c r="C64" t="n">
-        <v>36.73</v>
+        <v>25.08</v>
       </c>
       <c r="D64" t="n">
-        <v>3279600</v>
+        <v>1114600</v>
       </c>
       <c r="E64" t="n">
-        <v>4111775</v>
+        <v>1152650</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5568,26 +5584,26 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>11.34</v>
+        <v>22.3</v>
       </c>
       <c r="K64" t="n">
-        <v>13.2</v>
+        <v>21.92</v>
       </c>
       <c r="L64" t="n">
-        <v>-15.18</v>
+        <v>2.62</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5599,47 +5615,47 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>45.65</v>
+        <v>37.5</v>
       </c>
       <c r="S64" t="n">
-        <v>57.13</v>
+        <v>37.54</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>27.6</v>
+        <v>10.55</v>
       </c>
       <c r="C65" t="n">
-        <v>50.13</v>
+        <v>324.03</v>
       </c>
       <c r="D65" t="n">
-        <v>1816200</v>
+        <v>30713900</v>
       </c>
       <c r="E65" t="n">
-        <v>2319895</v>
+        <v>41274225</v>
       </c>
       <c r="F65" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5657,13 +5673,13 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>31.42</v>
+        <v>11.15</v>
       </c>
       <c r="K65" t="n">
-        <v>32.59</v>
+        <v>12.55</v>
       </c>
       <c r="L65" t="n">
-        <v>-15.31</v>
+        <v>-15.94</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -5679,10 +5695,10 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>32.58</v>
+        <v>32</v>
       </c>
       <c r="S65" t="n">
-        <v>48.15</v>
+        <v>20.02</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5696,30 +5712,30 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="C66" t="n">
-        <v>225.68</v>
+        <v>249.65</v>
       </c>
       <c r="D66" t="n">
-        <v>18806500</v>
+        <v>19971800</v>
       </c>
       <c r="E66" t="n">
-        <v>10071310</v>
+        <v>9517510</v>
       </c>
       <c r="F66" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5737,13 +5753,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>12.15</v>
+        <v>13.61</v>
       </c>
       <c r="K66" t="n">
-        <v>12.68</v>
+        <v>15</v>
       </c>
       <c r="L66" t="n">
-        <v>-5.33</v>
+        <v>-16.69</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5759,10 +5775,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>40.74</v>
+        <v>48.59</v>
       </c>
       <c r="S66" t="n">
-        <v>55.96</v>
+        <v>57.22</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5776,30 +5792,30 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>56.9</v>
+        <v>15.95</v>
       </c>
       <c r="C67" t="n">
-        <v>135.92</v>
+        <v>26.82</v>
       </c>
       <c r="D67" t="n">
-        <v>2388700</v>
+        <v>1681800</v>
       </c>
       <c r="E67" t="n">
-        <v>3032980</v>
+        <v>2459970</v>
       </c>
       <c r="F67" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5808,7 +5824,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5817,13 +5833,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>57</v>
+        <v>19.77</v>
       </c>
       <c r="K67" t="n">
-        <v>59.12</v>
+        <v>19.19</v>
       </c>
       <c r="L67" t="n">
-        <v>-3.76</v>
+        <v>-16.86</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5839,71 +5855,71 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>29.41</v>
+        <v>23.53</v>
       </c>
       <c r="S67" t="n">
-        <v>32.62</v>
+        <v>21.34</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>15.15</v>
+        <v>19.8</v>
       </c>
       <c r="C68" t="n">
-        <v>43.49</v>
+        <v>502.57</v>
       </c>
       <c r="D68" t="n">
-        <v>2870900</v>
+        <v>25382200</v>
       </c>
       <c r="E68" t="n">
-        <v>1904045</v>
+        <v>18637650</v>
       </c>
       <c r="F68" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>15.7</v>
+        <v>19.55</v>
       </c>
       <c r="K68" t="n">
-        <v>17.1</v>
+        <v>20.34</v>
       </c>
       <c r="L68" t="n">
-        <v>-11.43</v>
+        <v>-2.68</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5919,47 +5935,47 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>77.36</v>
+        <v>43.14</v>
       </c>
       <c r="S68" t="n">
-        <v>77.14</v>
+        <v>41.67</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>18.95</v>
+        <v>61.8</v>
       </c>
       <c r="C69" t="n">
-        <v>110.91</v>
+        <v>134.76</v>
       </c>
       <c r="D69" t="n">
-        <v>5852900</v>
+        <v>2180600</v>
       </c>
       <c r="E69" t="n">
-        <v>7638185</v>
+        <v>3007705</v>
       </c>
       <c r="F69" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5968,7 +5984,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5977,20 +5993,24 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20.83</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>23.28</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>-18.58</v>
+        <v>-12.15</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
@@ -5999,78 +6019,82 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>43.06</v>
+        <v>3.33</v>
       </c>
       <c r="S69" t="n">
-        <v>49.32</v>
+        <v>10.15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27.6</v>
+        <v>33.25</v>
       </c>
       <c r="C70" t="n">
-        <v>35.04</v>
+        <v>653.4400000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>1269600</v>
+        <v>19652200</v>
       </c>
       <c r="E70" t="n">
-        <v>1541090</v>
+        <v>18410665</v>
       </c>
       <c r="F70" t="n">
-        <v>0.82</v>
+        <v>1.07</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>29.32</v>
+        <v>31.5</v>
       </c>
       <c r="K70" t="n">
-        <v>32.12</v>
+        <v>31.5</v>
       </c>
       <c r="L70" t="n">
-        <v>-14.09</v>
+        <v>5.56</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
@@ -6079,47 +6103,47 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>41.84</v>
+        <v>58.9</v>
       </c>
       <c r="S70" t="n">
-        <v>49</v>
+        <v>68.06</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>38.8</v>
+        <v>11.25</v>
       </c>
       <c r="C71" t="n">
-        <v>28.91</v>
+        <v>62.58</v>
       </c>
       <c r="D71" t="n">
-        <v>745200</v>
+        <v>5562500</v>
       </c>
       <c r="E71" t="n">
-        <v>504495</v>
+        <v>4187395</v>
       </c>
       <c r="F71" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6128,26 +6152,26 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>36.8</v>
+        <v>11.16</v>
       </c>
       <c r="K71" t="n">
-        <v>36.5</v>
+        <v>13.2</v>
       </c>
       <c r="L71" t="n">
-        <v>6.3</v>
+        <v>-14.8</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -6159,56 +6183,56 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>73.68000000000001</v>
+        <v>44.44</v>
       </c>
       <c r="S71" t="n">
-        <v>54.8</v>
+        <v>58.85</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>61</v>
+        <v>27.8</v>
       </c>
       <c r="C72" t="n">
-        <v>518.15</v>
+        <v>117.29</v>
       </c>
       <c r="D72" t="n">
-        <v>8494300</v>
+        <v>4219200</v>
       </c>
       <c r="E72" t="n">
-        <v>8594035</v>
+        <v>2436305</v>
       </c>
       <c r="F72" t="n">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6217,24 +6241,20 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>70.25</v>
+        <v>31.42</v>
       </c>
       <c r="K72" t="n">
-        <v>70.18000000000001</v>
+        <v>32.59</v>
       </c>
       <c r="L72" t="n">
-        <v>-13.07</v>
+        <v>-14.7</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
@@ -6243,51 +6263,51 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>25.15</v>
+        <v>34.78</v>
       </c>
       <c r="S72" t="n">
-        <v>34.48</v>
+        <v>58.36</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>TNG</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>13.85</v>
+        <v>18.5</v>
       </c>
       <c r="C73" t="n">
-        <v>91.73999999999999</v>
+        <v>30.26</v>
       </c>
       <c r="D73" t="n">
-        <v>6624100</v>
+        <v>1635900</v>
       </c>
       <c r="E73" t="n">
-        <v>5270335</v>
+        <v>823355</v>
       </c>
       <c r="F73" t="n">
-        <v>1.26</v>
+        <v>1.99</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6297,21 +6317,21 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>13.6</v>
+        <v>16.68</v>
       </c>
       <c r="K73" t="n">
-        <v>14.23</v>
+        <v>17.92</v>
       </c>
       <c r="L73" t="n">
-        <v>-2.67</v>
+        <v>3.24</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -6323,10 +6343,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>70.59</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="S73" t="n">
-        <v>82.62</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -6340,30 +6360,30 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>215</v>
+        <v>11.95</v>
       </c>
       <c r="C74" t="n">
-        <v>520.21</v>
+        <v>104.49</v>
       </c>
       <c r="D74" t="n">
-        <v>2419600</v>
+        <v>8744200</v>
       </c>
       <c r="E74" t="n">
-        <v>2775075</v>
+        <v>10198630</v>
       </c>
       <c r="F74" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -6372,7 +6392,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6381,17 +6401,17 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>229.8</v>
+        <v>12.13</v>
       </c>
       <c r="K74" t="n">
-        <v>207.15</v>
+        <v>12.68</v>
       </c>
       <c r="L74" t="n">
-        <v>3.79</v>
+        <v>-5.72</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -6403,47 +6423,47 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>31.98</v>
+        <v>41.67</v>
       </c>
       <c r="S74" t="n">
-        <v>24.07</v>
+        <v>59.31</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>11.85</v>
+        <v>56.2</v>
       </c>
       <c r="C75" t="n">
-        <v>333.9</v>
+        <v>234.1</v>
       </c>
       <c r="D75" t="n">
-        <v>28177100</v>
+        <v>4165400</v>
       </c>
       <c r="E75" t="n">
-        <v>25410180</v>
+        <v>2967205</v>
       </c>
       <c r="F75" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -6461,13 +6481,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>12.82</v>
+        <v>57</v>
       </c>
       <c r="K75" t="n">
-        <v>14.95</v>
+        <v>59.12</v>
       </c>
       <c r="L75" t="n">
-        <v>-20.74</v>
+        <v>-4.95</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6483,10 +6503,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>38.3</v>
+        <v>26.32</v>
       </c>
       <c r="S75" t="n">
-        <v>40.97</v>
+        <v>29.05</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6500,34 +6520,34 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VJC</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>127.5</v>
+        <v>15.05</v>
       </c>
       <c r="C76" t="n">
-        <v>102.52</v>
+        <v>35.39</v>
       </c>
       <c r="D76" t="n">
-        <v>804100</v>
+        <v>2351800</v>
       </c>
       <c r="E76" t="n">
-        <v>932165</v>
+        <v>1964725</v>
       </c>
       <c r="F76" t="n">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6537,17 +6557,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>128.05</v>
+        <v>15.48</v>
       </c>
       <c r="K76" t="n">
-        <v>132.12</v>
+        <v>17.1</v>
       </c>
       <c r="L76" t="n">
-        <v>-3.5</v>
+        <v>-12.01</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6563,10 +6583,10 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>20</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="S76" t="n">
-        <v>27.43</v>
+        <v>73.62</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6580,34 +6600,34 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>13.25</v>
+        <v>19.05</v>
       </c>
       <c r="C77" t="n">
-        <v>116.81</v>
+        <v>170.34</v>
       </c>
       <c r="D77" t="n">
-        <v>8816100</v>
+        <v>8941700</v>
       </c>
       <c r="E77" t="n">
-        <v>9362600</v>
+        <v>7555940</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6621,13 +6641,13 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>15.23</v>
+        <v>20.6</v>
       </c>
       <c r="K77" t="n">
-        <v>15.85</v>
+        <v>23.28</v>
       </c>
       <c r="L77" t="n">
-        <v>-16.4</v>
+        <v>-18.15</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -6643,10 +6663,10 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>38.6</v>
+        <v>44.59</v>
       </c>
       <c r="S77" t="n">
-        <v>36.58</v>
+        <v>50.2</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6660,39 +6680,39 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>57.8</v>
+        <v>28</v>
       </c>
       <c r="C78" t="n">
-        <v>93.64</v>
+        <v>66.23</v>
       </c>
       <c r="D78" t="n">
-        <v>1620000</v>
+        <v>2365500</v>
       </c>
       <c r="E78" t="n">
-        <v>1987835</v>
+        <v>1595335</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6701,13 +6721,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>59.85</v>
+        <v>29.22</v>
       </c>
       <c r="K78" t="n">
-        <v>59.5</v>
+        <v>31.8</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.86</v>
+        <v>-11.95</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -6723,56 +6743,56 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>33.33</v>
+        <v>49</v>
       </c>
       <c r="S78" t="n">
-        <v>31.71</v>
+        <v>56.63</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VPB</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>24.5</v>
+        <v>39</v>
       </c>
       <c r="C79" t="n">
-        <v>236.47</v>
+        <v>34.32</v>
       </c>
       <c r="D79" t="n">
-        <v>9651700</v>
+        <v>880100</v>
       </c>
       <c r="E79" t="n">
-        <v>19307615</v>
+        <v>528245</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5</v>
+        <v>1.67</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6781,86 +6801,78 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>21.98</v>
+        <v>36.8</v>
       </c>
       <c r="K79" t="n">
-        <v>21.98</v>
+        <v>36.5</v>
       </c>
       <c r="L79" t="n">
-        <v>11.49</v>
+        <v>6.85</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R79" t="n">
-        <v>79.25</v>
+        <v>76.92</v>
       </c>
       <c r="S79" t="n">
-        <v>76.26000000000001</v>
+        <v>61.57</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>VHC</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>48.1</v>
+        <v>51.4</v>
       </c>
       <c r="C80" t="n">
-        <v>75.29000000000001</v>
+        <v>20.95</v>
       </c>
       <c r="D80" t="n">
-        <v>1565200</v>
+        <v>407600</v>
       </c>
       <c r="E80" t="n">
-        <v>1570825</v>
+        <v>340055</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6869,24 +6881,20 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>55.68</v>
+        <v>52.7</v>
       </c>
       <c r="K80" t="n">
-        <v>55.68</v>
+        <v>55.45</v>
       </c>
       <c r="L80" t="n">
-        <v>-13.61</v>
+        <v>-7.3</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
@@ -6895,56 +6903,56 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>6.83</v>
+        <v>66.84</v>
       </c>
       <c r="S80" t="n">
-        <v>8.210000000000001</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VPL</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>79</v>
+        <v>60.3</v>
       </c>
       <c r="C81" t="n">
-        <v>61.23</v>
+        <v>368.47</v>
       </c>
       <c r="D81" t="n">
-        <v>775100</v>
+        <v>6110600</v>
       </c>
       <c r="E81" t="n">
-        <v>704320</v>
+        <v>8039075</v>
       </c>
       <c r="F81" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6953,13 +6961,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>79.84999999999999</v>
+        <v>70.25</v>
       </c>
       <c r="K81" t="n">
-        <v>85.5</v>
+        <v>71.12</v>
       </c>
       <c r="L81" t="n">
-        <v>-7.6</v>
+        <v>-15.21</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6975,47 +6983,47 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>47.09</v>
+        <v>22.86</v>
       </c>
       <c r="S81" t="n">
-        <v>32.01</v>
+        <v>27.35</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VRE</t>
+          <t>VIB</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>22.85</v>
+        <v>13.75</v>
       </c>
       <c r="C82" t="n">
-        <v>59.02</v>
+        <v>65.73</v>
       </c>
       <c r="D82" t="n">
-        <v>2582800</v>
+        <v>4780100</v>
       </c>
       <c r="E82" t="n">
-        <v>3332535</v>
+        <v>5192390</v>
       </c>
       <c r="F82" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -7024,22 +7032,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>24.42</v>
+        <v>13.54</v>
       </c>
       <c r="K82" t="n">
-        <v>28.56</v>
+        <v>14.16</v>
       </c>
       <c r="L82" t="n">
-        <v>-19.99</v>
+        <v>-2.93</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -7055,47 +7063,47 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>26.87</v>
+        <v>61.29</v>
       </c>
       <c r="S82" t="n">
-        <v>13.91</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-16 20:44:23</t>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VSC</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="C83" t="n">
-        <v>60.16</v>
+        <v>434</v>
       </c>
       <c r="D83" t="n">
-        <v>4628000</v>
+        <v>2096600</v>
       </c>
       <c r="E83" t="n">
-        <v>7078810</v>
+        <v>2695640</v>
       </c>
       <c r="F83" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7104,7 +7112,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7113,13 +7121,13 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>14.1</v>
+        <v>229.8</v>
       </c>
       <c r="K83" t="n">
-        <v>18.95</v>
+        <v>213.45</v>
       </c>
       <c r="L83" t="n">
-        <v>-31.4</v>
+        <v>-3.02</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7135,24 +7143,832 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>39.29</v>
+        <v>28.3</v>
       </c>
       <c r="S83" t="n">
-        <v>29.67</v>
+        <v>23.57</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>VIX</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="C84" t="n">
+        <v>490.03</v>
+      </c>
+      <c r="D84" t="n">
+        <v>40666600</v>
+      </c>
+      <c r="E84" t="n">
+        <v>26094990</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="K84" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>42</v>
+      </c>
+      <c r="S84" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
           <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>🔴 Tiêu cực</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>2026-10-16 20:44:23</t>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>VJC</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>176.86</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1387100</v>
+      </c>
+      <c r="E85" t="n">
+        <v>908310</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="K85" t="n">
+        <v>132.12</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="S85" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C86" t="n">
+        <v>230.42</v>
+      </c>
+      <c r="D86" t="n">
+        <v>17068500</v>
+      </c>
+      <c r="E86" t="n">
+        <v>9718365</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="K86" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-14.83</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="S86" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="C87" t="n">
+        <v>83.38</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1450100</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1934225</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="K87" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="S87" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VPB</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>24</v>
+      </c>
+      <c r="C88" t="n">
+        <v>738.4</v>
+      </c>
+      <c r="D88" t="n">
+        <v>30766500</v>
+      </c>
+      <c r="E88" t="n">
+        <v>19181405</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="K88" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="S88" t="n">
+        <v>64.63</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VPI</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="C89" t="n">
+        <v>103.26</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2056900</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1604425</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="K89" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R89" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="S89" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>🟢 Mua (vùng quá bán)</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VPL</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>80</v>
+      </c>
+      <c r="C90" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="D90" t="n">
+        <v>762700</v>
+      </c>
+      <c r="E90" t="n">
+        <v>678490</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="K90" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R90" t="n">
+        <v>52</v>
+      </c>
+      <c r="S90" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>VRE</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="C91" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2264400</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3091355</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="K91" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-19.29</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R91" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="S91" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>VSC</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>63.81</v>
+      </c>
+      <c r="D92" t="n">
+        <v>4871200</v>
+      </c>
+      <c r="E92" t="n">
+        <v>7113795</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="K92" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-30.87</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="S92" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>VVS</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="C93" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="D93" t="n">
+        <v>267600</v>
+      </c>
+      <c r="E93" t="n">
+        <v>154440</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="K93" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R93" t="n">
+        <v>46.07</v>
+      </c>
+      <c r="S93" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:05:17</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V93"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,16 +538,16 @@
         <v>10.3</v>
       </c>
       <c r="C2" t="n">
-        <v>80.81999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="D2" t="n">
-        <v>7846200</v>
+        <v>6501600</v>
       </c>
       <c r="E2" t="n">
-        <v>1498325</v>
+        <v>1798840</v>
       </c>
       <c r="F2" t="n">
-        <v>5.24</v>
+        <v>3.61</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -595,14 +595,14 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>60.87</v>
+        <v>57.14</v>
       </c>
       <c r="S2" t="n">
-        <v>75.56999999999999</v>
+        <v>54.96</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -626,16 +626,16 @@
         <v>20.25</v>
       </c>
       <c r="C3" t="n">
-        <v>147.36</v>
+        <v>102.78</v>
       </c>
       <c r="D3" t="n">
-        <v>7276900</v>
+        <v>5075700</v>
       </c>
       <c r="E3" t="n">
-        <v>7299615</v>
+        <v>7191550</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>28.95</v>
+        <v>27.03</v>
       </c>
       <c r="S3" t="n">
-        <v>37.54</v>
+        <v>31.21</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -703,23 +703,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="C4" t="n">
-        <v>34.05</v>
+        <v>21.58</v>
       </c>
       <c r="D4" t="n">
-        <v>824500</v>
+        <v>523900</v>
       </c>
       <c r="E4" t="n">
-        <v>505865</v>
+        <v>525005</v>
       </c>
       <c r="F4" t="n">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -739,7 +739,7 @@
         <v>42.1</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.9</v>
+        <v>-2.14</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>75</v>
+        <v>72.73</v>
       </c>
       <c r="S4" t="n">
-        <v>68.84</v>
+        <v>64.11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -783,23 +783,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.85</v>
+        <v>18.9</v>
       </c>
       <c r="C5" t="n">
-        <v>40.37</v>
+        <v>25.47</v>
       </c>
       <c r="D5" t="n">
-        <v>2141900</v>
+        <v>1347400</v>
       </c>
       <c r="E5" t="n">
-        <v>1151640</v>
+        <v>1206260</v>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>1.12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -819,7 +819,7 @@
         <v>20.35</v>
       </c>
       <c r="L5" t="n">
-        <v>-7.37</v>
+        <v>-7.13</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>73.53</v>
+        <v>74.81</v>
       </c>
       <c r="S5" t="n">
-        <v>73.63</v>
+        <v>75.11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -866,20 +866,20 @@
         <v>30.95</v>
       </c>
       <c r="C6" t="n">
-        <v>27.84</v>
+        <v>100.95</v>
       </c>
       <c r="D6" t="n">
-        <v>899400</v>
+        <v>3261600</v>
       </c>
       <c r="E6" t="n">
-        <v>1618755</v>
+        <v>1684570</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -908,21 +908,17 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>35.56</v>
+        <v>37.21</v>
       </c>
       <c r="S6" t="n">
-        <v>51.74</v>
+        <v>62.66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -936,7 +932,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -947,28 +943,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.2</v>
+        <v>40.9</v>
       </c>
       <c r="C7" t="n">
-        <v>22.67</v>
+        <v>35.06</v>
       </c>
       <c r="D7" t="n">
-        <v>578300</v>
+        <v>857100</v>
       </c>
       <c r="E7" t="n">
-        <v>468860</v>
+        <v>493325</v>
       </c>
       <c r="F7" t="n">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -983,7 +979,7 @@
         <v>45.75</v>
       </c>
       <c r="L7" t="n">
-        <v>-14.32</v>
+        <v>-10.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -999,24 +995,24 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>46.3</v>
+        <v>58.57</v>
       </c>
       <c r="S7" t="n">
-        <v>46.52</v>
+        <v>49.31</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -1030,20 +1026,20 @@
         <v>33.65</v>
       </c>
       <c r="C8" t="n">
-        <v>111.43</v>
+        <v>75.52</v>
       </c>
       <c r="D8" t="n">
-        <v>3311300</v>
+        <v>2244400</v>
       </c>
       <c r="E8" t="n">
-        <v>3055030</v>
+        <v>3009360</v>
       </c>
       <c r="F8" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1079,10 +1075,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>22.22</v>
+        <v>21.25</v>
       </c>
       <c r="S8" t="n">
-        <v>39.36</v>
+        <v>33.16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1096,34 +1092,34 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BMP</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>28.7</v>
       </c>
       <c r="C9" t="n">
-        <v>27.2</v>
+        <v>118.78</v>
       </c>
       <c r="D9" t="n">
-        <v>197100</v>
+        <v>4138700</v>
       </c>
       <c r="E9" t="n">
-        <v>58975</v>
+        <v>10411575</v>
       </c>
       <c r="F9" t="n">
-        <v>3.34</v>
+        <v>0.4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1133,21 +1129,21 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>146.8</v>
+        <v>27.9</v>
       </c>
       <c r="K9" t="n">
-        <v>142.18</v>
+        <v>27.96</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.94</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1155,14 +1151,14 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.3x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>27.52</v>
+        <v>31.25</v>
       </c>
       <c r="S9" t="n">
-        <v>30.82</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1176,30 +1172,30 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.85</v>
+        <v>69.7</v>
       </c>
       <c r="C10" t="n">
-        <v>142.17</v>
+        <v>40.6</v>
       </c>
       <c r="D10" t="n">
-        <v>4928000</v>
+        <v>582500</v>
       </c>
       <c r="E10" t="n">
-        <v>10751945</v>
+        <v>1058095</v>
       </c>
       <c r="F10" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1217,20 +1213,24 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>27.96</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>3.18</v>
+        <v>3.87</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
@@ -1239,14 +1239,14 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>27.61</v>
+        <v>36.05</v>
       </c>
       <c r="S10" t="n">
-        <v>23.24</v>
+        <v>32.63</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1256,65 +1256,61 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70.7</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>116.85</v>
+        <v>68.34</v>
       </c>
       <c r="D11" t="n">
-        <v>1652800</v>
+        <v>6213100</v>
       </c>
       <c r="E11" t="n">
-        <v>1062895</v>
+        <v>6125685</v>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>67.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="K11" t="n">
-        <v>67.09999999999999</v>
+        <v>13.61</v>
       </c>
       <c r="L11" t="n">
-        <v>5.37</v>
+        <v>-19.18</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
@@ -1323,47 +1319,47 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>39.39</v>
+        <v>53.85</v>
       </c>
       <c r="S11" t="n">
-        <v>40.99</v>
+        <v>65.44</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CII</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.9</v>
+        <v>13.2</v>
       </c>
       <c r="C12" t="n">
-        <v>84.43000000000001</v>
+        <v>144.58</v>
       </c>
       <c r="D12" t="n">
-        <v>7745600</v>
+        <v>10952800</v>
       </c>
       <c r="E12" t="n">
-        <v>5982115</v>
+        <v>7370500</v>
       </c>
       <c r="F12" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1381,13 +1377,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11.75</v>
+        <v>13.7</v>
       </c>
       <c r="K12" t="n">
-        <v>13.61</v>
+        <v>15.88</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.91</v>
+        <v>-16.85</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1403,10 +1399,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>50</v>
+        <v>63.29</v>
       </c>
       <c r="S12" t="n">
-        <v>67.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1420,54 +1416,54 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CII</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12.95</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>118.36</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>9139400</v>
+        <v>1272800</v>
       </c>
       <c r="E13" t="n">
-        <v>7013330</v>
+        <v>386240</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13.7</v>
+        <v>60.45</v>
       </c>
       <c r="K13" t="n">
-        <v>16.08</v>
+        <v>72.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.44</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1479,75 +1475,75 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.3x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>56.96</v>
+        <v>75.69</v>
       </c>
       <c r="S13" t="n">
-        <v>63.25</v>
+        <v>73.63</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CTD</t>
+          <t>CTG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63.2</v>
+        <v>30.45</v>
       </c>
       <c r="C14" t="n">
-        <v>24.9</v>
+        <v>209.31</v>
       </c>
       <c r="D14" t="n">
-        <v>394000</v>
+        <v>6874000</v>
       </c>
       <c r="E14" t="n">
-        <v>335165</v>
+        <v>7277875</v>
       </c>
       <c r="F14" t="n">
-        <v>1.18</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>60.6</v>
+        <v>30.7</v>
       </c>
       <c r="K14" t="n">
-        <v>72.5</v>
+        <v>32.32</v>
       </c>
       <c r="L14" t="n">
-        <v>-12.83</v>
+        <v>-5.79</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1563,47 +1559,47 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>63.78</v>
+        <v>57.14</v>
       </c>
       <c r="S14" t="n">
-        <v>62.04</v>
+        <v>39.83</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CTG</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.5</v>
+        <v>21.8</v>
       </c>
       <c r="C15" t="n">
-        <v>563.98</v>
+        <v>59.72</v>
       </c>
       <c r="D15" t="n">
-        <v>18491300</v>
+        <v>2739500</v>
       </c>
       <c r="E15" t="n">
-        <v>7125130</v>
+        <v>1087365</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1621,13 +1617,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30.7</v>
+        <v>23.38</v>
       </c>
       <c r="K15" t="n">
-        <v>32.32</v>
+        <v>24.1</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.63</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1639,14 +1635,14 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.5x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>61.19</v>
+        <v>64</v>
       </c>
       <c r="S15" t="n">
-        <v>45.54</v>
+        <v>53.34</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1660,34 +1656,34 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.9</v>
+        <v>16.05</v>
       </c>
       <c r="C16" t="n">
-        <v>28.48</v>
+        <v>41.77</v>
       </c>
       <c r="D16" t="n">
-        <v>1362500</v>
+        <v>2602200</v>
       </c>
       <c r="E16" t="n">
-        <v>980210</v>
+        <v>1471010</v>
       </c>
       <c r="F16" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1701,13 +1697,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>23.38</v>
+        <v>16.32</v>
       </c>
       <c r="K16" t="n">
-        <v>24.1</v>
+        <v>18.13</v>
       </c>
       <c r="L16" t="n">
-        <v>-13.28</v>
+        <v>-11.47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1723,10 +1719,10 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>55.42</v>
+        <v>65.31</v>
       </c>
       <c r="S16" t="n">
-        <v>41.95</v>
+        <v>61.35</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1740,30 +1736,30 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52</v>
+        <v>34.4</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>730700</v>
+        <v>2150800</v>
       </c>
       <c r="E17" t="n">
-        <v>1105610</v>
+        <v>2498025</v>
       </c>
       <c r="F17" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1772,7 +1768,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1781,101 +1777,93 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>44.65</v>
+        <v>31.95</v>
       </c>
       <c r="K17" t="n">
-        <v>43.78</v>
+        <v>36.33</v>
       </c>
       <c r="L17" t="n">
-        <v>18.79</v>
+        <v>-5.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>67.22</v>
+        <v>56.08</v>
       </c>
       <c r="S17" t="n">
-        <v>59.4</v>
+        <v>63.07</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DDV</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33.85</v>
+        <v>17.8</v>
       </c>
       <c r="C18" t="n">
-        <v>34.46</v>
+        <v>20.53</v>
       </c>
       <c r="D18" t="n">
-        <v>1018100</v>
+        <v>1153200</v>
       </c>
       <c r="E18" t="n">
-        <v>2528590</v>
+        <v>598730</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4</v>
+        <v>1.93</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31.95</v>
+        <v>18.35</v>
       </c>
       <c r="K18" t="n">
-        <v>36.58</v>
+        <v>21.06</v>
       </c>
       <c r="L18" t="n">
-        <v>-7.48</v>
+        <v>-15.46</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1891,24 +1879,24 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>43.9</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>53.01</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -1919,19 +1907,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45.45</v>
+        <v>46</v>
       </c>
       <c r="C19" t="n">
-        <v>47.05</v>
+        <v>49.87</v>
       </c>
       <c r="D19" t="n">
-        <v>1035100</v>
+        <v>1084200</v>
       </c>
       <c r="E19" t="n">
-        <v>1718300</v>
+        <v>1697560</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1955,11 +1943,11 @@
         <v>39.83</v>
       </c>
       <c r="L19" t="n">
-        <v>14.11</v>
+        <v>15.49</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1967,7 +1955,11 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1975,10 +1967,10 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>53.45</v>
+        <v>59.53</v>
       </c>
       <c r="S19" t="n">
-        <v>42.86</v>
+        <v>52.12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1992,7 +1984,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -2003,23 +1995,23 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.539999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="C20" t="n">
-        <v>45.81</v>
+        <v>39.13</v>
       </c>
       <c r="D20" t="n">
-        <v>4801400</v>
+        <v>4084400</v>
       </c>
       <c r="E20" t="n">
-        <v>4105695</v>
+        <v>4218015</v>
       </c>
       <c r="F20" t="n">
-        <v>1.17</v>
+        <v>0.97</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2039,7 +2031,7 @@
         <v>11.52</v>
       </c>
       <c r="L20" t="n">
-        <v>-17.22</v>
+        <v>-16.88</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2058,7 +2050,7 @@
         <v>50.4</v>
       </c>
       <c r="S20" t="n">
-        <v>67.81999999999999</v>
+        <v>61.85</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2072,54 +2064,54 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>DPG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.25</v>
+        <v>29.5</v>
       </c>
       <c r="C21" t="n">
-        <v>25.74</v>
+        <v>37.98</v>
       </c>
       <c r="D21" t="n">
-        <v>1211500</v>
+        <v>1287300</v>
       </c>
       <c r="E21" t="n">
-        <v>2485810</v>
+        <v>369635</v>
       </c>
       <c r="F21" t="n">
-        <v>0.49</v>
+        <v>3.48</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>22.18</v>
+        <v>28.82</v>
       </c>
       <c r="K21" t="n">
-        <v>24.11</v>
+        <v>35.3</v>
       </c>
       <c r="L21" t="n">
-        <v>-11.86</v>
+        <v>-16.44</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2131,55 +2123,55 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.5x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>23.08</v>
+        <v>66.94</v>
       </c>
       <c r="S21" t="n">
-        <v>20.01</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10.25</v>
+        <v>21.5</v>
       </c>
       <c r="C22" t="n">
-        <v>152.14</v>
+        <v>30.97</v>
       </c>
       <c r="D22" t="n">
-        <v>14842800</v>
+        <v>1440300</v>
       </c>
       <c r="E22" t="n">
-        <v>8860865</v>
+        <v>2463330</v>
       </c>
       <c r="F22" t="n">
-        <v>1.68</v>
+        <v>0.58</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2193,13 +2185,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10.78</v>
+        <v>22.18</v>
       </c>
       <c r="K22" t="n">
-        <v>11.89</v>
+        <v>24.08</v>
       </c>
       <c r="L22" t="n">
-        <v>-13.76</v>
+        <v>-10.73</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2215,10 +2207,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>53.38</v>
+        <v>34.48</v>
       </c>
       <c r="S22" t="n">
-        <v>51.62</v>
+        <v>25.7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2232,34 +2224,34 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>DSE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.25</v>
+        <v>19.2</v>
       </c>
       <c r="C23" t="n">
-        <v>55.69</v>
+        <v>25.81</v>
       </c>
       <c r="D23" t="n">
-        <v>3427000</v>
+        <v>1344400</v>
       </c>
       <c r="E23" t="n">
-        <v>3170715</v>
+        <v>557725</v>
       </c>
       <c r="F23" t="n">
-        <v>1.08</v>
+        <v>2.41</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2273,13 +2265,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>17.58</v>
+        <v>21.35</v>
       </c>
       <c r="K23" t="n">
-        <v>19.65</v>
+        <v>21.75</v>
       </c>
       <c r="L23" t="n">
-        <v>-17.3</v>
+        <v>-11.72</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2295,10 +2287,10 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>22.58</v>
+        <v>8.06</v>
       </c>
       <c r="S23" t="n">
-        <v>35.11</v>
+        <v>26.9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2312,30 +2304,30 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>57.1</v>
+        <v>10.25</v>
       </c>
       <c r="C24" t="n">
-        <v>239.28</v>
+        <v>64.67</v>
       </c>
       <c r="D24" t="n">
-        <v>4190500</v>
+        <v>6309400</v>
       </c>
       <c r="E24" t="n">
-        <v>5027990</v>
+        <v>8910585</v>
       </c>
       <c r="F24" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2353,13 +2345,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>61.9</v>
+        <v>10.78</v>
       </c>
       <c r="K24" t="n">
-        <v>63.22</v>
+        <v>11.89</v>
       </c>
       <c r="L24" t="n">
-        <v>-9.68</v>
+        <v>-13.76</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2375,10 +2367,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>19.19</v>
+        <v>53.38</v>
       </c>
       <c r="S24" t="n">
-        <v>20.2</v>
+        <v>48.91</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2392,30 +2384,30 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>146</v>
+        <v>16.3</v>
       </c>
       <c r="C25" t="n">
-        <v>80.02</v>
+        <v>41.28</v>
       </c>
       <c r="D25" t="n">
-        <v>548100</v>
+        <v>2532500</v>
       </c>
       <c r="E25" t="n">
-        <v>702935</v>
+        <v>3100665</v>
       </c>
       <c r="F25" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2424,38 +2416,30 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>126.5</v>
+        <v>17.4</v>
       </c>
       <c r="K25" t="n">
-        <v>126.5</v>
+        <v>19.58</v>
       </c>
       <c r="L25" t="n">
-        <v>15.42</v>
+        <v>-16.73</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2463,47 +2447,47 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>55.43</v>
+        <v>25.81</v>
       </c>
       <c r="S25" t="n">
-        <v>73.14</v>
+        <v>24.53</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>76.7</v>
+        <v>57.4</v>
       </c>
       <c r="C26" t="n">
-        <v>41.09</v>
+        <v>200.18</v>
       </c>
       <c r="D26" t="n">
-        <v>535700</v>
+        <v>3487400</v>
       </c>
       <c r="E26" t="n">
-        <v>1069090</v>
+        <v>4957110</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2512,22 +2496,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>76.48</v>
+        <v>61.9</v>
       </c>
       <c r="K26" t="n">
-        <v>77.69</v>
+        <v>63.22</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.28</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2543,47 +2527,47 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>26.97</v>
+        <v>22</v>
       </c>
       <c r="S26" t="n">
-        <v>29.43</v>
+        <v>20.17</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>66.40000000000001</v>
+        <v>149.4</v>
       </c>
       <c r="C27" t="n">
-        <v>75.3</v>
+        <v>39.76</v>
       </c>
       <c r="D27" t="n">
-        <v>1134100</v>
+        <v>266100</v>
       </c>
       <c r="E27" t="n">
-        <v>1538095</v>
+        <v>695425</v>
       </c>
       <c r="F27" t="n">
-        <v>0.74</v>
+        <v>0.38</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2592,78 +2576,90 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>70.04000000000001</v>
+        <v>126.5</v>
       </c>
       <c r="K27" t="n">
-        <v>95.83</v>
+        <v>126.5</v>
       </c>
       <c r="L27" t="n">
-        <v>-30.71</v>
+        <v>18.1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>39.15</v>
+        <v>53.41</v>
       </c>
       <c r="S27" t="n">
-        <v>52.5</v>
+        <v>69.87</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.6</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>30.09</v>
+        <v>21.12</v>
       </c>
       <c r="D28" t="n">
-        <v>1090200</v>
+        <v>276400</v>
       </c>
       <c r="E28" t="n">
-        <v>1365465</v>
+        <v>1042265</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8</v>
+        <v>0.27</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2672,7 +2668,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2681,13 +2677,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>27.15</v>
+        <v>76.48</v>
       </c>
       <c r="K28" t="n">
-        <v>29.42</v>
+        <v>77.69</v>
       </c>
       <c r="L28" t="n">
-        <v>-6.2</v>
+        <v>-1.67</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2703,51 +2699,51 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>35</v>
+        <v>31.58</v>
       </c>
       <c r="S28" t="n">
-        <v>41.18</v>
+        <v>31.79</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.75</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>221.58</v>
+        <v>47.05</v>
       </c>
       <c r="D29" t="n">
-        <v>9739600</v>
+        <v>708600</v>
       </c>
       <c r="E29" t="n">
-        <v>6131730</v>
+        <v>1438190</v>
       </c>
       <c r="F29" t="n">
-        <v>1.59</v>
+        <v>0.49</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2757,17 +2753,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>23.45</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>28.58</v>
+        <v>95.83</v>
       </c>
       <c r="L29" t="n">
-        <v>-20.38</v>
+        <v>-30.71</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2783,10 +2779,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>37.89</v>
+        <v>28.96</v>
       </c>
       <c r="S29" t="n">
-        <v>43.69</v>
+        <v>39.84</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2800,30 +2796,30 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54</v>
+        <v>27.25</v>
       </c>
       <c r="C30" t="n">
-        <v>31.69</v>
+        <v>29.05</v>
       </c>
       <c r="D30" t="n">
-        <v>586900</v>
+        <v>1065900</v>
       </c>
       <c r="E30" t="n">
-        <v>1180595</v>
+        <v>1351655</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2837,48 +2833,40 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>50.34</v>
+        <v>27.15</v>
       </c>
       <c r="K30" t="n">
-        <v>50.34</v>
+        <v>29.42</v>
       </c>
       <c r="L30" t="n">
-        <v>7.28</v>
+        <v>-7.39</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>64.48999999999999</v>
+        <v>27.27</v>
       </c>
       <c r="S30" t="n">
-        <v>69.38</v>
+        <v>28.76</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -2888,30 +2876,30 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.35</v>
+        <v>22.75</v>
       </c>
       <c r="C31" t="n">
-        <v>40.21</v>
+        <v>130.38</v>
       </c>
       <c r="D31" t="n">
-        <v>1282500</v>
+        <v>5731000</v>
       </c>
       <c r="E31" t="n">
-        <v>2744190</v>
+        <v>6139365</v>
       </c>
       <c r="F31" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2920,22 +2908,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>30.22</v>
+        <v>23.45</v>
       </c>
       <c r="K31" t="n">
-        <v>32.78</v>
+        <v>28.58</v>
       </c>
       <c r="L31" t="n">
-        <v>-4.35</v>
+        <v>-20.38</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2951,51 +2939,51 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>32.11</v>
+        <v>35.16</v>
       </c>
       <c r="S31" t="n">
-        <v>38.62</v>
+        <v>35.39</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>49.1</v>
+        <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>34.93</v>
+        <v>140.93</v>
       </c>
       <c r="D32" t="n">
-        <v>711400</v>
+        <v>2562400</v>
       </c>
       <c r="E32" t="n">
-        <v>1266395</v>
+        <v>1284265</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5600000000000001</v>
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3009,20 +2997,24 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>48.2</v>
+        <v>50.34</v>
       </c>
       <c r="K32" t="n">
-        <v>49.55</v>
+        <v>50.34</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.91</v>
+        <v>9.27</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
@@ -3031,14 +3023,14 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>33.62</v>
+        <v>66.05</v>
       </c>
       <c r="S32" t="n">
-        <v>39.48</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3048,34 +3040,34 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24.2</v>
+        <v>31.8</v>
       </c>
       <c r="C33" t="n">
-        <v>69.94</v>
+        <v>42.47</v>
       </c>
       <c r="D33" t="n">
-        <v>2889900</v>
+        <v>1335600</v>
       </c>
       <c r="E33" t="n">
-        <v>2673555</v>
+        <v>2729375</v>
       </c>
       <c r="F33" t="n">
-        <v>1.08</v>
+        <v>0.49</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3085,17 +3077,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>24.92</v>
+        <v>30.22</v>
       </c>
       <c r="K33" t="n">
-        <v>24.76</v>
+        <v>32.78</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.24</v>
+        <v>-2.97</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3111,10 +3103,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>47.31</v>
+        <v>37.29</v>
       </c>
       <c r="S33" t="n">
-        <v>41.39</v>
+        <v>31.14</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3128,30 +3120,30 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.75</v>
+        <v>23.9</v>
       </c>
       <c r="C34" t="n">
-        <v>291.56</v>
+        <v>26.76</v>
       </c>
       <c r="D34" t="n">
-        <v>12815800</v>
+        <v>1119700</v>
       </c>
       <c r="E34" t="n">
-        <v>15669115</v>
+        <v>2656475</v>
       </c>
       <c r="F34" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3165,28 +3157,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>21.13</v>
+        <v>24.92</v>
       </c>
       <c r="K34" t="n">
-        <v>21.13</v>
+        <v>24.8</v>
       </c>
       <c r="L34" t="n">
-        <v>7.67</v>
+        <v>-3.63</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -3195,14 +3183,14 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>75.08</v>
+        <v>51.16</v>
       </c>
       <c r="S34" t="n">
-        <v>74.08</v>
+        <v>41.74</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3212,30 +3200,30 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HHP</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17</v>
+        <v>22.1</v>
       </c>
       <c r="C35" t="n">
-        <v>20.47</v>
+        <v>270.53</v>
       </c>
       <c r="D35" t="n">
-        <v>1203900</v>
+        <v>12241000</v>
       </c>
       <c r="E35" t="n">
-        <v>1254710</v>
+        <v>15892740</v>
       </c>
       <c r="F35" t="n">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3244,7 +3232,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3253,20 +3241,24 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>16.39</v>
+        <v>21.13</v>
       </c>
       <c r="K35" t="n">
-        <v>15.31</v>
+        <v>21.13</v>
       </c>
       <c r="L35" t="n">
-        <v>11.04</v>
+        <v>4.59</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -3275,24 +3267,24 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>36.84</v>
+        <v>62.15</v>
       </c>
       <c r="S35" t="n">
-        <v>54.4</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -3303,19 +3295,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.33</v>
+        <v>9.48</v>
       </c>
       <c r="C36" t="n">
-        <v>33.95</v>
+        <v>29.39</v>
       </c>
       <c r="D36" t="n">
-        <v>3638700</v>
+        <v>3100400</v>
       </c>
       <c r="E36" t="n">
-        <v>2672735</v>
+        <v>2770315</v>
       </c>
       <c r="F36" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3333,13 +3325,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9.56</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K36" t="n">
         <v>10.57</v>
       </c>
       <c r="L36" t="n">
-        <v>-11.69</v>
+        <v>-10.27</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3355,11 +3347,11 @@
         </is>
       </c>
       <c r="R36" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="S36" t="n">
         <v>57.74</v>
       </c>
-      <c r="S36" t="n">
-        <v>55.48</v>
-      </c>
       <c r="T36" t="inlineStr">
         <is>
           <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
@@ -3372,7 +3364,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -3383,23 +3375,23 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20.55</v>
+        <v>21.1</v>
       </c>
       <c r="C37" t="n">
-        <v>271.77</v>
+        <v>537.55</v>
       </c>
       <c r="D37" t="n">
-        <v>13224600</v>
+        <v>25476200</v>
       </c>
       <c r="E37" t="n">
-        <v>17479300</v>
+        <v>18347885</v>
       </c>
       <c r="F37" t="n">
-        <v>0.76</v>
+        <v>1.39</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3419,7 +3411,7 @@
         <v>22.94</v>
       </c>
       <c r="L37" t="n">
-        <v>-10.44</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3435,10 +3427,10 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>54.39</v>
+        <v>64.62</v>
       </c>
       <c r="S37" t="n">
-        <v>49.86</v>
+        <v>57.14</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3452,7 +3444,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -3463,43 +3455,43 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10.45</v>
+        <v>10.75</v>
       </c>
       <c r="C38" t="n">
-        <v>25.55</v>
+        <v>60.55</v>
       </c>
       <c r="D38" t="n">
-        <v>2444500</v>
+        <v>5632600</v>
       </c>
       <c r="E38" t="n">
-        <v>2513535</v>
+        <v>2727390</v>
       </c>
       <c r="F38" t="n">
-        <v>0.97</v>
+        <v>2.07</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10.65</v>
+        <v>10.62</v>
       </c>
       <c r="K38" t="n">
         <v>11.35</v>
       </c>
       <c r="L38" t="n">
-        <v>-7.93</v>
+        <v>-5.29</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3515,71 +3507,71 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>62.59</v>
+        <v>73.58</v>
       </c>
       <c r="S38" t="n">
-        <v>58.79</v>
+        <v>65.92</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12.3</v>
+        <v>35.2</v>
       </c>
       <c r="C39" t="n">
-        <v>29.44</v>
+        <v>39.39</v>
       </c>
       <c r="D39" t="n">
-        <v>2393800</v>
+        <v>1119000</v>
       </c>
       <c r="E39" t="n">
-        <v>1733390</v>
+        <v>1287090</v>
       </c>
       <c r="F39" t="n">
-        <v>1.38</v>
+        <v>0.87</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>13.35</v>
+        <v>32.45</v>
       </c>
       <c r="K39" t="n">
-        <v>14.45</v>
+        <v>36.67</v>
       </c>
       <c r="L39" t="n">
-        <v>-14.88</v>
+        <v>-4.01</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3595,51 +3587,51 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>40</v>
+        <v>62.12</v>
       </c>
       <c r="S39" t="n">
-        <v>38.6</v>
+        <v>56.3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>KBC</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>33.9</v>
+        <v>26.8</v>
       </c>
       <c r="C40" t="n">
-        <v>36.55</v>
+        <v>56.66</v>
       </c>
       <c r="D40" t="n">
-        <v>1078100</v>
+        <v>2114100</v>
       </c>
       <c r="E40" t="n">
-        <v>1328020</v>
+        <v>1161730</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3649,17 +3641,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>32.45</v>
+        <v>26.55</v>
       </c>
       <c r="K40" t="n">
-        <v>36.67</v>
+        <v>30.05</v>
       </c>
       <c r="L40" t="n">
-        <v>-7.55</v>
+        <v>-10.82</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3675,14 +3667,14 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>53.7</v>
+        <v>78</v>
       </c>
       <c r="S40" t="n">
-        <v>57.98</v>
+        <v>54.45</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -3692,7 +3684,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -3706,16 +3698,16 @@
         <v>14.15</v>
       </c>
       <c r="C41" t="n">
-        <v>43.48</v>
+        <v>43.93</v>
       </c>
       <c r="D41" t="n">
-        <v>3073100</v>
+        <v>3104800</v>
       </c>
       <c r="E41" t="n">
-        <v>3745420</v>
+        <v>3755140</v>
       </c>
       <c r="F41" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3733,7 +3725,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>15.41</v>
+        <v>15.18</v>
       </c>
       <c r="K41" t="n">
         <v>18.75</v>
@@ -3758,7 +3750,7 @@
         <v>54.76</v>
       </c>
       <c r="S41" t="n">
-        <v>55.62</v>
+        <v>49.9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3772,54 +3764,54 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13.6</v>
+        <v>37.85</v>
       </c>
       <c r="C42" t="n">
-        <v>30.22</v>
+        <v>55.05</v>
       </c>
       <c r="D42" t="n">
-        <v>2222100</v>
+        <v>1454300</v>
       </c>
       <c r="E42" t="n">
-        <v>583485</v>
+        <v>1908380</v>
       </c>
       <c r="F42" t="n">
-        <v>3.81</v>
+        <v>0.76</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>13.48</v>
+        <v>46.6</v>
       </c>
       <c r="K42" t="n">
-        <v>14.68</v>
+        <v>47.85</v>
       </c>
       <c r="L42" t="n">
-        <v>-7.33</v>
+        <v>-20.9</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3831,51 +3823,51 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.8x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>67.56999999999999</v>
+        <v>30.96</v>
       </c>
       <c r="S42" t="n">
-        <v>77.05</v>
+        <v>32.01</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>38.45</v>
+        <v>19.65</v>
       </c>
       <c r="C43" t="n">
-        <v>51.25</v>
+        <v>150.32</v>
       </c>
       <c r="D43" t="n">
-        <v>1332900</v>
+        <v>7650000</v>
       </c>
       <c r="E43" t="n">
-        <v>1918225</v>
+        <v>11413285</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3884,22 +3876,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>46.6</v>
+        <v>19.49</v>
       </c>
       <c r="K43" t="n">
-        <v>47.85</v>
+        <v>19.7</v>
       </c>
       <c r="L43" t="n">
-        <v>-19.64</v>
+        <v>-0.25</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3908,78 +3900,82 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>34.27</v>
+        <v>50</v>
       </c>
       <c r="S43" t="n">
-        <v>32.15</v>
+        <v>45.18</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.7</v>
+        <v>15.3</v>
       </c>
       <c r="C44" t="n">
-        <v>236.98</v>
+        <v>33.14</v>
       </c>
       <c r="D44" t="n">
-        <v>12029200</v>
+        <v>2166000</v>
       </c>
       <c r="E44" t="n">
-        <v>11513845</v>
+        <v>2775675</v>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>0.78</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>19.49</v>
+        <v>16.44</v>
       </c>
       <c r="K44" t="n">
-        <v>19.7</v>
+        <v>17.43</v>
       </c>
       <c r="L44" t="n">
-        <v>-0</v>
+        <v>-12.25</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3995,47 +3991,47 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>52.08</v>
+        <v>44.44</v>
       </c>
       <c r="S44" t="n">
-        <v>49.36</v>
+        <v>47.97</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.4</v>
+        <v>139.9</v>
       </c>
       <c r="C45" t="n">
-        <v>52.2</v>
+        <v>104.02</v>
       </c>
       <c r="D45" t="n">
-        <v>3389500</v>
+        <v>743500</v>
       </c>
       <c r="E45" t="n">
-        <v>2747085</v>
+        <v>542685</v>
       </c>
       <c r="F45" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4044,26 +4040,26 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>16.44</v>
+        <v>138.57</v>
       </c>
       <c r="K45" t="n">
-        <v>17.43</v>
+        <v>134.54</v>
       </c>
       <c r="L45" t="n">
-        <v>-11.67</v>
+        <v>3.99</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4075,79 +4071,83 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>48.15</v>
+        <v>55.06</v>
       </c>
       <c r="S45" t="n">
-        <v>48.07</v>
+        <v>25.62</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>139.8</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>116.17</v>
+        <v>171.27</v>
       </c>
       <c r="D46" t="n">
-        <v>831000</v>
+        <v>11418100</v>
       </c>
       <c r="E46" t="n">
-        <v>542515</v>
+        <v>12257765</v>
       </c>
       <c r="F46" t="n">
-        <v>1.53</v>
+        <v>0.93</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>138.57</v>
+        <v>13.61</v>
       </c>
       <c r="K46" t="n">
-        <v>134.54</v>
+        <v>12.72</v>
       </c>
       <c r="L46" t="n">
-        <v>3.91</v>
+        <v>17.97</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4155,44 +4155,44 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>59.18</v>
+        <v>71.05</v>
       </c>
       <c r="S46" t="n">
-        <v>29.78</v>
+        <v>77.66</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>148.24</v>
+        <v>315.46</v>
       </c>
       <c r="D47" t="n">
-        <v>10016500</v>
+        <v>4286100</v>
       </c>
       <c r="E47" t="n">
-        <v>12654445</v>
+        <v>5451285</v>
       </c>
       <c r="F47" t="n">
         <v>0.79</v>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4213,25 +4213,21 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>13.56</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>12.66</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>16.86</v>
+        <v>2.08</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4239,47 +4235,47 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>70.27</v>
+        <v>64.56</v>
       </c>
       <c r="S47" t="n">
-        <v>77.15000000000001</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>72.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>303.75</v>
+        <v>48.12</v>
       </c>
       <c r="D48" t="n">
-        <v>4195500</v>
+        <v>739100</v>
       </c>
       <c r="E48" t="n">
-        <v>5683590</v>
+        <v>2365925</v>
       </c>
       <c r="F48" t="n">
-        <v>0.74</v>
+        <v>0.31</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4297,21 +4293,29 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>68.90000000000001</v>
+        <v>50.57</v>
       </c>
       <c r="K48" t="n">
-        <v>72.09999999999999</v>
+        <v>50.57</v>
       </c>
       <c r="L48" t="n">
-        <v>0.42</v>
+        <v>28.73</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4319,14 +4323,14 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>60</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="S48" t="n">
-        <v>65.48999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -4336,30 +4340,30 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>54.67</v>
+        <v>149.52</v>
       </c>
       <c r="D49" t="n">
-        <v>834700</v>
+        <v>1996300</v>
       </c>
       <c r="E49" t="n">
-        <v>2438835</v>
+        <v>2810655</v>
       </c>
       <c r="F49" t="n">
-        <v>0.34</v>
+        <v>0.71</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4377,29 +4381,21 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>50.57</v>
+        <v>69.02</v>
       </c>
       <c r="K49" t="n">
-        <v>50.57</v>
+        <v>73.36</v>
       </c>
       <c r="L49" t="n">
-        <v>29.52</v>
+        <v>2.1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4407,10 +4403,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>72.45999999999999</v>
+        <v>64.81</v>
       </c>
       <c r="S49" t="n">
-        <v>69.31999999999999</v>
+        <v>70.22</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4424,30 +4420,30 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>74.2</v>
+        <v>11.95</v>
       </c>
       <c r="C50" t="n">
-        <v>127.68</v>
+        <v>22.26</v>
       </c>
       <c r="D50" t="n">
-        <v>1720700</v>
+        <v>1863000</v>
       </c>
       <c r="E50" t="n">
-        <v>2847185</v>
+        <v>2134440</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4456,26 +4452,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>69.02</v>
+        <v>12.05</v>
       </c>
       <c r="K50" t="n">
-        <v>73.36</v>
+        <v>12.25</v>
       </c>
       <c r="L50" t="n">
-        <v>1.15</v>
+        <v>-2.45</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -4487,51 +4483,51 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>64.19</v>
+        <v>41.46</v>
       </c>
       <c r="S50" t="n">
-        <v>70.8</v>
+        <v>46.12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="C51" t="n">
-        <v>26.54</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>2211900</v>
+        <v>8168500</v>
       </c>
       <c r="E51" t="n">
-        <v>2115730</v>
+        <v>2608645</v>
       </c>
       <c r="F51" t="n">
-        <v>1.05</v>
+        <v>3.13</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4541,17 +4537,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>12.05</v>
+        <v>10.28</v>
       </c>
       <c r="K51" t="n">
-        <v>12.25</v>
+        <v>11.48</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.04</v>
+        <v>-2.4</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4563,18 +4559,18 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.1x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R51" t="n">
-        <v>42.5</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="S51" t="n">
-        <v>48.98</v>
+        <v>85.98</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4584,39 +4580,39 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>NLG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10.6</v>
+        <v>21.4</v>
       </c>
       <c r="C52" t="n">
-        <v>35.06</v>
+        <v>23.36</v>
       </c>
       <c r="D52" t="n">
-        <v>3307300</v>
+        <v>1091400</v>
       </c>
       <c r="E52" t="n">
-        <v>2270965</v>
+        <v>1401430</v>
       </c>
       <c r="F52" t="n">
-        <v>1.46</v>
+        <v>0.78</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4625,13 +4621,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>10.38</v>
+        <v>22.55</v>
       </c>
       <c r="K52" t="n">
-        <v>11.48</v>
+        <v>24.1</v>
       </c>
       <c r="L52" t="n">
-        <v>-7.63</v>
+        <v>-11.18</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4647,47 +4643,47 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>69.37</v>
+        <v>42.55</v>
       </c>
       <c r="S52" t="n">
-        <v>82.73999999999999</v>
+        <v>39.95</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVB</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>13.3</v>
+        <v>10.75</v>
       </c>
       <c r="C53" t="n">
-        <v>28.77</v>
+        <v>80.17</v>
       </c>
       <c r="D53" t="n">
-        <v>2163000</v>
+        <v>7458000</v>
       </c>
       <c r="E53" t="n">
-        <v>2173210</v>
+        <v>27243324</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.27</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4696,33 +4692,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>11.88</v>
       </c>
       <c r="K53" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="L53" t="n">
-        <v>-5</v>
+        <v>-25.84</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
@@ -4731,51 +4723,51 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>48.98</v>
+        <v>62.79</v>
       </c>
       <c r="S53" t="n">
-        <v>54.62</v>
+        <v>51.45</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.75</v>
+        <v>10.05</v>
       </c>
       <c r="C54" t="n">
-        <v>296.37</v>
+        <v>34.52</v>
       </c>
       <c r="D54" t="n">
-        <v>27569200</v>
+        <v>3435200</v>
       </c>
       <c r="E54" t="n">
-        <v>27259249</v>
+        <v>1135140</v>
       </c>
       <c r="F54" t="n">
-        <v>1.01</v>
+        <v>3.03</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4789,13 +4781,13 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>11.88</v>
+        <v>10.46</v>
       </c>
       <c r="K54" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="L54" t="n">
-        <v>-25.84</v>
+        <v>-4.24</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4807,14 +4799,14 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.0x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R54" t="n">
-        <v>61.93</v>
+        <v>45.45</v>
       </c>
       <c r="S54" t="n">
-        <v>41.63</v>
+        <v>27.7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4828,7 +4820,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -4839,23 +4831,23 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="C55" t="n">
-        <v>20.92</v>
+        <v>42.84</v>
       </c>
       <c r="D55" t="n">
-        <v>1549700</v>
+        <v>3127300</v>
       </c>
       <c r="E55" t="n">
-        <v>1888125</v>
+        <v>1873675</v>
       </c>
       <c r="F55" t="n">
-        <v>0.82</v>
+        <v>1.67</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4865,7 +4857,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -4875,7 +4867,7 @@
         <v>13.75</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.82</v>
+        <v>-0.36</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4891,14 +4883,14 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>62.5</v>
+        <v>70.37</v>
       </c>
       <c r="S55" t="n">
-        <v>67.22</v>
+        <v>75.47</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -4908,7 +4900,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -4919,23 +4911,23 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11.25</v>
+        <v>11.35</v>
       </c>
       <c r="C56" t="n">
-        <v>40.55</v>
+        <v>56.64</v>
       </c>
       <c r="D56" t="n">
-        <v>3604600</v>
+        <v>4990700</v>
       </c>
       <c r="E56" t="n">
-        <v>4266725</v>
+        <v>4268585</v>
       </c>
       <c r="F56" t="n">
-        <v>0.84</v>
+        <v>1.17</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4949,13 +4941,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>12</v>
+        <v>11.98</v>
       </c>
       <c r="K56" t="n">
         <v>13.82</v>
       </c>
       <c r="L56" t="n">
-        <v>-18.63</v>
+        <v>-17.9</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4971,10 +4963,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>47.37</v>
+        <v>55</v>
       </c>
       <c r="S56" t="n">
-        <v>55.63</v>
+        <v>56.98</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4988,30 +4980,30 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>50</v>
+        <v>35.1</v>
       </c>
       <c r="C57" t="n">
-        <v>24.96</v>
+        <v>100.69</v>
       </c>
       <c r="D57" t="n">
-        <v>499300</v>
+        <v>2868700</v>
       </c>
       <c r="E57" t="n">
-        <v>922955</v>
+        <v>4178350</v>
       </c>
       <c r="F57" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5020,26 +5012,26 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>45.2</v>
+        <v>35.15</v>
       </c>
       <c r="K57" t="n">
-        <v>44.22</v>
+        <v>38.08</v>
       </c>
       <c r="L57" t="n">
-        <v>13.08</v>
+        <v>-7.84</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -5051,71 +5043,71 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>38.7</v>
+        <v>46.75</v>
       </c>
       <c r="S57" t="n">
-        <v>54.21</v>
+        <v>59.75</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>35.15</v>
+        <v>19.75</v>
       </c>
       <c r="C58" t="n">
-        <v>69.18000000000001</v>
+        <v>322.87</v>
       </c>
       <c r="D58" t="n">
-        <v>1968200</v>
+        <v>16347700</v>
       </c>
       <c r="E58" t="n">
-        <v>4314300</v>
+        <v>14296450</v>
       </c>
       <c r="F58" t="n">
-        <v>0.46</v>
+        <v>1.14</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.15</v>
+        <v>31.4</v>
       </c>
       <c r="K58" t="n">
-        <v>38.08</v>
+        <v>47.16</v>
       </c>
       <c r="L58" t="n">
-        <v>-7.71</v>
+        <v>-58.12</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5131,51 +5123,51 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>42.35</v>
+        <v>27.39</v>
       </c>
       <c r="S58" t="n">
-        <v>59.85</v>
+        <v>14.96</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="C59" t="n">
-        <v>116.31</v>
+        <v>102.71</v>
       </c>
       <c r="D59" t="n">
-        <v>6287100</v>
+        <v>8216900</v>
       </c>
       <c r="E59" t="n">
-        <v>13748640</v>
+        <v>5672170</v>
       </c>
       <c r="F59" t="n">
-        <v>0.46</v>
+        <v>1.45</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5189,13 +5181,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>31.4</v>
+        <v>13.08</v>
       </c>
       <c r="K59" t="n">
-        <v>47.16</v>
+        <v>13.6</v>
       </c>
       <c r="L59" t="n">
-        <v>-60.77</v>
+        <v>-8.09</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5211,10 +5203,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>18.24</v>
+        <v>30.77</v>
       </c>
       <c r="S59" t="n">
-        <v>9.6</v>
+        <v>28.24</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5228,30 +5220,30 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12.25</v>
+        <v>18</v>
       </c>
       <c r="C60" t="n">
-        <v>32.81</v>
+        <v>40</v>
       </c>
       <c r="D60" t="n">
-        <v>2678100</v>
+        <v>2222400</v>
       </c>
       <c r="E60" t="n">
-        <v>5550795</v>
+        <v>3550820</v>
       </c>
       <c r="F60" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5269,13 +5261,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>13.08</v>
+        <v>18.88</v>
       </c>
       <c r="K60" t="n">
-        <v>13.6</v>
+        <v>19.43</v>
       </c>
       <c r="L60" t="n">
-        <v>-9.93</v>
+        <v>-7.36</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5291,10 +5283,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>33.33</v>
+        <v>45</v>
       </c>
       <c r="S60" t="n">
-        <v>37.19</v>
+        <v>53.24</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5308,30 +5300,30 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>17.7</v>
+        <v>32</v>
       </c>
       <c r="C61" t="n">
-        <v>46.46</v>
+        <v>38.55</v>
       </c>
       <c r="D61" t="n">
-        <v>2625100</v>
+        <v>1204600</v>
       </c>
       <c r="E61" t="n">
-        <v>3617750</v>
+        <v>3442240</v>
       </c>
       <c r="F61" t="n">
-        <v>0.73</v>
+        <v>0.35</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5340,26 +5332,26 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>18.88</v>
+        <v>30.94</v>
       </c>
       <c r="K61" t="n">
-        <v>19.43</v>
+        <v>31.62</v>
       </c>
       <c r="L61" t="n">
-        <v>-8.9</v>
+        <v>1.19</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -5371,47 +5363,47 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>31.34</v>
+        <v>37.29</v>
       </c>
       <c r="S61" t="n">
-        <v>47</v>
+        <v>46.49</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.8</v>
+        <v>24.2</v>
       </c>
       <c r="C62" t="n">
-        <v>52.03</v>
+        <v>75.25</v>
       </c>
       <c r="D62" t="n">
-        <v>1636200</v>
+        <v>3109300</v>
       </c>
       <c r="E62" t="n">
-        <v>3569320</v>
+        <v>7697575</v>
       </c>
       <c r="F62" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -5429,20 +5421,24 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>30.94</v>
+        <v>21.2</v>
       </c>
       <c r="K62" t="n">
-        <v>31.62</v>
+        <v>21.2</v>
       </c>
       <c r="L62" t="n">
-        <v>0.55</v>
+        <v>14.15</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
@@ -5451,10 +5447,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>31.75</v>
+        <v>54.17</v>
       </c>
       <c r="S62" t="n">
-        <v>44.1</v>
+        <v>54.38</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5468,34 +5464,34 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24.1</v>
+        <v>21.1</v>
       </c>
       <c r="C63" t="n">
-        <v>78.01000000000001</v>
+        <v>60.66</v>
       </c>
       <c r="D63" t="n">
-        <v>3236800</v>
+        <v>2874800</v>
       </c>
       <c r="E63" t="n">
-        <v>8123490</v>
+        <v>1241130</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4</v>
+        <v>2.32</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5505,28 +5501,24 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="K63" t="n">
-        <v>21.2</v>
+        <v>21.92</v>
       </c>
       <c r="L63" t="n">
-        <v>13.68</v>
+        <v>-3.76</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
@@ -5535,14 +5527,14 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>42.74</v>
+        <v>23.81</v>
       </c>
       <c r="S63" t="n">
-        <v>48.95</v>
+        <v>34.12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -5552,58 +5544,58 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>SCS</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.5</v>
+        <v>39</v>
       </c>
       <c r="C64" t="n">
-        <v>25.08</v>
+        <v>21.03</v>
       </c>
       <c r="D64" t="n">
-        <v>1114600</v>
+        <v>539200</v>
       </c>
       <c r="E64" t="n">
-        <v>1152650</v>
+        <v>144850</v>
       </c>
       <c r="F64" t="n">
-        <v>0.97</v>
+        <v>3.72</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>22.3</v>
+        <v>42.68</v>
       </c>
       <c r="K64" t="n">
-        <v>21.92</v>
+        <v>45.3</v>
       </c>
       <c r="L64" t="n">
-        <v>2.62</v>
+        <v>-13.9</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5611,28 +5603,28 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R64" t="n">
-        <v>37.5</v>
+        <v>7.08</v>
       </c>
       <c r="S64" t="n">
-        <v>37.54</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -5646,16 +5638,16 @@
         <v>10.55</v>
       </c>
       <c r="C65" t="n">
-        <v>324.03</v>
+        <v>399.19</v>
       </c>
       <c r="D65" t="n">
-        <v>30713900</v>
+        <v>37837600</v>
       </c>
       <c r="E65" t="n">
-        <v>41274225</v>
+        <v>42392330</v>
       </c>
       <c r="F65" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5698,7 +5690,7 @@
         <v>32</v>
       </c>
       <c r="S65" t="n">
-        <v>20.02</v>
+        <v>19.83</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5712,7 +5704,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -5723,23 +5715,23 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="C66" t="n">
-        <v>249.65</v>
+        <v>110.51</v>
       </c>
       <c r="D66" t="n">
-        <v>19971800</v>
+        <v>8770500</v>
       </c>
       <c r="E66" t="n">
-        <v>9517510</v>
+        <v>9743690</v>
       </c>
       <c r="F66" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5759,7 +5751,7 @@
         <v>15</v>
       </c>
       <c r="L66" t="n">
-        <v>-16.69</v>
+        <v>-16.03</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5775,10 +5767,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>48.59</v>
+        <v>52.11</v>
       </c>
       <c r="S66" t="n">
-        <v>57.22</v>
+        <v>51.6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5792,7 +5784,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -5803,19 +5795,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>15.95</v>
+        <v>15.75</v>
       </c>
       <c r="C67" t="n">
-        <v>26.82</v>
+        <v>30.75</v>
       </c>
       <c r="D67" t="n">
-        <v>1681800</v>
+        <v>1952500</v>
       </c>
       <c r="E67" t="n">
-        <v>2459970</v>
+        <v>2367585</v>
       </c>
       <c r="F67" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5839,7 +5831,7 @@
         <v>19.19</v>
       </c>
       <c r="L67" t="n">
-        <v>-16.86</v>
+        <v>-17.9</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5855,10 +5847,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>23.53</v>
+        <v>26.42</v>
       </c>
       <c r="S67" t="n">
-        <v>21.34</v>
+        <v>21.54</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5872,7 +5864,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -5883,23 +5875,23 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.8</v>
+        <v>19.95</v>
       </c>
       <c r="C68" t="n">
-        <v>502.57</v>
+        <v>261.54</v>
       </c>
       <c r="D68" t="n">
-        <v>25382200</v>
+        <v>13109700</v>
       </c>
       <c r="E68" t="n">
-        <v>18637650</v>
+        <v>18687685</v>
       </c>
       <c r="F68" t="n">
-        <v>1.36</v>
+        <v>0.7</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5919,7 +5911,7 @@
         <v>20.34</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.68</v>
+        <v>-1.94</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5935,10 +5927,10 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>43.14</v>
+        <v>47.17</v>
       </c>
       <c r="S68" t="n">
-        <v>41.67</v>
+        <v>38.05</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5952,7 +5944,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -5963,23 +5955,23 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>61.8</v>
+        <v>62.3</v>
       </c>
       <c r="C69" t="n">
-        <v>134.76</v>
+        <v>261.45</v>
       </c>
       <c r="D69" t="n">
-        <v>2180600</v>
+        <v>4196600</v>
       </c>
       <c r="E69" t="n">
-        <v>3007705</v>
+        <v>3128615</v>
       </c>
       <c r="F69" t="n">
-        <v>0.73</v>
+        <v>1.34</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5993,13 +5985,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>70.34999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="K69" t="n">
-        <v>70.34999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="L69" t="n">
-        <v>-12.15</v>
+        <v>-11.06</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -6019,10 +6011,10 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>3.33</v>
+        <v>7.3</v>
       </c>
       <c r="S69" t="n">
-        <v>10.15</v>
+        <v>9.98</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6036,7 +6028,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6047,23 +6039,23 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>33.25</v>
+        <v>33.95</v>
       </c>
       <c r="C70" t="n">
-        <v>653.4400000000001</v>
+        <v>1032</v>
       </c>
       <c r="D70" t="n">
-        <v>19652200</v>
+        <v>30397600</v>
       </c>
       <c r="E70" t="n">
-        <v>18410665</v>
+        <v>19374275</v>
       </c>
       <c r="F70" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6083,7 +6075,7 @@
         <v>31.5</v>
       </c>
       <c r="L70" t="n">
-        <v>5.56</v>
+        <v>7.78</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6103,10 +6095,10 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>58.9</v>
+        <v>66.28</v>
       </c>
       <c r="S70" t="n">
-        <v>68.06</v>
+        <v>69.94</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6120,7 +6112,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6131,19 +6123,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="C71" t="n">
-        <v>62.58</v>
+        <v>57.37</v>
       </c>
       <c r="D71" t="n">
-        <v>5562500</v>
+        <v>5077400</v>
       </c>
       <c r="E71" t="n">
-        <v>4187395</v>
+        <v>4334725</v>
       </c>
       <c r="F71" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6161,13 +6153,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>11.16</v>
+        <v>11.09</v>
       </c>
       <c r="K71" t="n">
         <v>13.2</v>
       </c>
       <c r="L71" t="n">
-        <v>-14.8</v>
+        <v>-14.43</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -6186,7 +6178,7 @@
         <v>44.44</v>
       </c>
       <c r="S71" t="n">
-        <v>58.85</v>
+        <v>49.97</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -6200,7 +6192,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6211,23 +6203,23 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="C72" t="n">
-        <v>117.29</v>
+        <v>67.66</v>
       </c>
       <c r="D72" t="n">
-        <v>4219200</v>
+        <v>2425200</v>
       </c>
       <c r="E72" t="n">
-        <v>2436305</v>
+        <v>2486855</v>
       </c>
       <c r="F72" t="n">
-        <v>1.73</v>
+        <v>0.98</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6247,7 +6239,7 @@
         <v>32.59</v>
       </c>
       <c r="L72" t="n">
-        <v>-14.7</v>
+        <v>-14.39</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -6263,10 +6255,10 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>34.78</v>
+        <v>36.56</v>
       </c>
       <c r="S72" t="n">
-        <v>58.36</v>
+        <v>52.73</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6280,7 +6272,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6291,19 +6283,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="C73" t="n">
-        <v>30.26</v>
+        <v>37.21</v>
       </c>
       <c r="D73" t="n">
-        <v>1635900</v>
+        <v>1958500</v>
       </c>
       <c r="E73" t="n">
-        <v>823355</v>
+        <v>908150</v>
       </c>
       <c r="F73" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -6321,13 +6313,13 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>16.68</v>
+        <v>16.83</v>
       </c>
       <c r="K73" t="n">
         <v>17.92</v>
       </c>
       <c r="L73" t="n">
-        <v>3.24</v>
+        <v>6.03</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -6343,10 +6335,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>67.73999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="S73" t="n">
-        <v>73.79000000000001</v>
+        <v>76.89</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -6360,7 +6352,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6371,23 +6363,23 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>11.95</v>
+        <v>12</v>
       </c>
       <c r="C74" t="n">
-        <v>104.49</v>
+        <v>154.91</v>
       </c>
       <c r="D74" t="n">
-        <v>8744200</v>
+        <v>12909100</v>
       </c>
       <c r="E74" t="n">
-        <v>10198630</v>
+        <v>10333220</v>
       </c>
       <c r="F74" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6407,7 +6399,7 @@
         <v>12.68</v>
       </c>
       <c r="L74" t="n">
-        <v>-5.72</v>
+        <v>-5.33</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6423,10 +6415,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>41.67</v>
+        <v>45.11</v>
       </c>
       <c r="S74" t="n">
-        <v>59.31</v>
+        <v>55.89</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -6440,7 +6432,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6451,19 +6443,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="C75" t="n">
-        <v>234.1</v>
+        <v>204.89</v>
       </c>
       <c r="D75" t="n">
-        <v>4165400</v>
+        <v>3671900</v>
       </c>
       <c r="E75" t="n">
-        <v>2967205</v>
+        <v>3022235</v>
       </c>
       <c r="F75" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -6487,7 +6479,7 @@
         <v>59.12</v>
       </c>
       <c r="L75" t="n">
-        <v>-4.95</v>
+        <v>-5.62</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6503,10 +6495,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>26.32</v>
+        <v>23.81</v>
       </c>
       <c r="S75" t="n">
-        <v>29.05</v>
+        <v>22.25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6520,7 +6512,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6531,43 +6523,43 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15.05</v>
+        <v>15.5</v>
       </c>
       <c r="C76" t="n">
-        <v>35.39</v>
+        <v>56.02</v>
       </c>
       <c r="D76" t="n">
-        <v>2351800</v>
+        <v>3614200</v>
       </c>
       <c r="E76" t="n">
-        <v>1964725</v>
+        <v>2094605</v>
       </c>
       <c r="F76" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>15.48</v>
+        <v>15.25</v>
       </c>
       <c r="K76" t="n">
         <v>17.1</v>
       </c>
       <c r="L76" t="n">
-        <v>-12.01</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6583,24 +6575,24 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>75.93000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="S76" t="n">
-        <v>73.62</v>
+        <v>79.11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6606,20 @@
         <v>19.05</v>
       </c>
       <c r="C77" t="n">
-        <v>170.34</v>
+        <v>145.36</v>
       </c>
       <c r="D77" t="n">
-        <v>8941700</v>
+        <v>7630600</v>
       </c>
       <c r="E77" t="n">
-        <v>7555940</v>
+        <v>7710745</v>
       </c>
       <c r="F77" t="n">
-        <v>1.18</v>
+        <v>0.99</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6644,10 +6636,10 @@
         <v>20.6</v>
       </c>
       <c r="K77" t="n">
-        <v>23.28</v>
+        <v>23.18</v>
       </c>
       <c r="L77" t="n">
-        <v>-18.15</v>
+        <v>-17.8</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -6663,10 +6655,10 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>44.59</v>
+        <v>45.83</v>
       </c>
       <c r="S77" t="n">
-        <v>50.2</v>
+        <v>48.51</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6680,7 +6672,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6691,23 +6683,23 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="C78" t="n">
-        <v>66.23</v>
+        <v>30.54</v>
       </c>
       <c r="D78" t="n">
-        <v>2365500</v>
+        <v>1098500</v>
       </c>
       <c r="E78" t="n">
-        <v>1595335</v>
+        <v>1593445</v>
       </c>
       <c r="F78" t="n">
-        <v>1.48</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6724,10 +6716,10 @@
         <v>29.22</v>
       </c>
       <c r="K78" t="n">
-        <v>31.8</v>
+        <v>31.62</v>
       </c>
       <c r="L78" t="n">
-        <v>-11.95</v>
+        <v>-12.09</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -6743,10 +6735,10 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>49</v>
+        <v>48.51</v>
       </c>
       <c r="S78" t="n">
-        <v>56.63</v>
+        <v>57.32</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -6760,7 +6752,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6774,16 +6766,16 @@
         <v>39</v>
       </c>
       <c r="C79" t="n">
-        <v>34.32</v>
+        <v>43.33</v>
       </c>
       <c r="D79" t="n">
-        <v>880100</v>
+        <v>1111000</v>
       </c>
       <c r="E79" t="n">
-        <v>528245</v>
+        <v>571580</v>
       </c>
       <c r="F79" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -6823,10 +6815,10 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>76.92</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="S79" t="n">
-        <v>61.57</v>
+        <v>66.05</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6840,61 +6832,65 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VHC</t>
+          <t>VGC</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>51.4</v>
+        <v>44.9</v>
       </c>
       <c r="C80" t="n">
-        <v>20.95</v>
+        <v>22.24</v>
       </c>
       <c r="D80" t="n">
-        <v>407600</v>
+        <v>495400</v>
       </c>
       <c r="E80" t="n">
-        <v>340055</v>
+        <v>642990</v>
       </c>
       <c r="F80" t="n">
-        <v>1.2</v>
+        <v>0.77</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>52.7</v>
+        <v>40.17</v>
       </c>
       <c r="K80" t="n">
-        <v>55.45</v>
+        <v>40.17</v>
       </c>
       <c r="L80" t="n">
-        <v>-7.3</v>
+        <v>11.76</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
@@ -6903,24 +6899,24 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>66.84</v>
+        <v>49.4</v>
       </c>
       <c r="S80" t="n">
-        <v>68.73999999999999</v>
+        <v>47.69</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -6931,23 +6927,23 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="C81" t="n">
-        <v>368.47</v>
+        <v>740.71</v>
       </c>
       <c r="D81" t="n">
-        <v>6110600</v>
+        <v>12815000</v>
       </c>
       <c r="E81" t="n">
-        <v>8039075</v>
+        <v>8312985</v>
       </c>
       <c r="F81" t="n">
-        <v>0.76</v>
+        <v>1.54</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6961,13 +6957,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>70.25</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>71.12</v>
+        <v>70.52</v>
       </c>
       <c r="L81" t="n">
-        <v>-15.21</v>
+        <v>-18.04</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6983,10 +6979,10 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>22.86</v>
+        <v>21.39</v>
       </c>
       <c r="S81" t="n">
-        <v>27.35</v>
+        <v>26.13</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -7000,7 +6996,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7014,16 +7010,16 @@
         <v>13.75</v>
       </c>
       <c r="C82" t="n">
-        <v>65.73</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="D82" t="n">
-        <v>4780100</v>
+        <v>4802600</v>
       </c>
       <c r="E82" t="n">
-        <v>5192390</v>
+        <v>5319070</v>
       </c>
       <c r="F82" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -7041,13 +7037,13 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>13.54</v>
+        <v>13.52</v>
       </c>
       <c r="K82" t="n">
         <v>14.16</v>
       </c>
       <c r="L82" t="n">
-        <v>-2.93</v>
+        <v>-2.86</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -7063,10 +7059,10 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>61.29</v>
+        <v>63.33</v>
       </c>
       <c r="S82" t="n">
-        <v>76.56999999999999</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -7080,7 +7076,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7091,19 +7087,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C83" t="n">
-        <v>434</v>
+        <v>408.14</v>
       </c>
       <c r="D83" t="n">
-        <v>2096600</v>
+        <v>1952800</v>
       </c>
       <c r="E83" t="n">
-        <v>2695640</v>
+        <v>2718610</v>
       </c>
       <c r="F83" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7124,10 +7120,10 @@
         <v>229.8</v>
       </c>
       <c r="K83" t="n">
-        <v>213.45</v>
+        <v>215.6</v>
       </c>
       <c r="L83" t="n">
-        <v>-3.02</v>
+        <v>-3.06</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7143,10 +7139,10 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>28.3</v>
+        <v>32.14</v>
       </c>
       <c r="S83" t="n">
-        <v>23.57</v>
+        <v>23.46</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7160,7 +7156,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7171,23 +7167,23 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>12.05</v>
+        <v>12.15</v>
       </c>
       <c r="C84" t="n">
-        <v>490.03</v>
+        <v>318.43</v>
       </c>
       <c r="D84" t="n">
-        <v>40666600</v>
+        <v>26208200</v>
       </c>
       <c r="E84" t="n">
-        <v>26094990</v>
+        <v>26421705</v>
       </c>
       <c r="F84" t="n">
-        <v>1.56</v>
+        <v>0.99</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7207,7 +7203,7 @@
         <v>14.95</v>
       </c>
       <c r="L84" t="n">
-        <v>-19.4</v>
+        <v>-18.73</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -7223,10 +7219,10 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>42</v>
+        <v>46.94</v>
       </c>
       <c r="S84" t="n">
-        <v>49.38</v>
+        <v>48.81</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7240,7 +7236,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7251,19 +7247,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>127.5</v>
+        <v>127.4</v>
       </c>
       <c r="C85" t="n">
-        <v>176.86</v>
+        <v>222.68</v>
       </c>
       <c r="D85" t="n">
-        <v>1387100</v>
+        <v>1747900</v>
       </c>
       <c r="E85" t="n">
-        <v>908310</v>
+        <v>937575</v>
       </c>
       <c r="F85" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7287,7 +7283,7 @@
         <v>132.12</v>
       </c>
       <c r="L85" t="n">
-        <v>-3.5</v>
+        <v>-3.58</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -7303,10 +7299,10 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>14.29</v>
+        <v>17.14</v>
       </c>
       <c r="S85" t="n">
-        <v>18.9</v>
+        <v>17.67</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7320,7 +7316,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7331,23 +7327,23 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="C86" t="n">
-        <v>230.42</v>
+        <v>95.45</v>
       </c>
       <c r="D86" t="n">
-        <v>17068500</v>
+        <v>7018700</v>
       </c>
       <c r="E86" t="n">
-        <v>9718365</v>
+        <v>9807545</v>
       </c>
       <c r="F86" t="n">
-        <v>1.76</v>
+        <v>0.72</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7367,7 +7363,7 @@
         <v>15.85</v>
       </c>
       <c r="L86" t="n">
-        <v>-14.83</v>
+        <v>-14.2</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -7383,10 +7379,10 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>41.67</v>
+        <v>45.76</v>
       </c>
       <c r="S86" t="n">
-        <v>46.25</v>
+        <v>45.66</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -7400,7 +7396,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7411,19 +7407,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="C87" t="n">
-        <v>83.38</v>
+        <v>49.45</v>
       </c>
       <c r="D87" t="n">
-        <v>1450100</v>
+        <v>857000</v>
       </c>
       <c r="E87" t="n">
-        <v>1934225</v>
+        <v>1888345</v>
       </c>
       <c r="F87" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -7441,13 +7437,13 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>59.85</v>
+        <v>60.3</v>
       </c>
       <c r="K87" t="n">
         <v>59.5</v>
       </c>
       <c r="L87" t="n">
-        <v>-3.36</v>
+        <v>-3.03</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -7463,14 +7459,14 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>32.05</v>
+        <v>38.03</v>
       </c>
       <c r="S87" t="n">
-        <v>27.09</v>
+        <v>31.03</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -7480,7 +7476,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7494,20 +7490,20 @@
         <v>24</v>
       </c>
       <c r="C88" t="n">
-        <v>738.4</v>
+        <v>287.2</v>
       </c>
       <c r="D88" t="n">
-        <v>30766500</v>
+        <v>11966600</v>
       </c>
       <c r="E88" t="n">
-        <v>19181405</v>
+        <v>18971400</v>
       </c>
       <c r="F88" t="n">
-        <v>1.6</v>
+        <v>0.63</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7540,17 +7536,21 @@
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>66.67</v>
+        <v>61.11</v>
       </c>
       <c r="S88" t="n">
-        <v>64.63</v>
+        <v>58.78</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7575,19 +7575,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>50.2</v>
+        <v>51.3</v>
       </c>
       <c r="C89" t="n">
-        <v>103.26</v>
+        <v>120.67</v>
       </c>
       <c r="D89" t="n">
-        <v>2056900</v>
+        <v>2352300</v>
       </c>
       <c r="E89" t="n">
-        <v>1604425</v>
+        <v>1664000</v>
       </c>
       <c r="F89" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>55.52</v>
       </c>
       <c r="L89" t="n">
-        <v>-9.59</v>
+        <v>-7.61</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>19.05</v>
+        <v>25.9</v>
       </c>
       <c r="S89" t="n">
-        <v>15.8</v>
+        <v>24.02</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7659,19 +7659,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>80</v>
+        <v>80.5</v>
       </c>
       <c r="C90" t="n">
-        <v>61.02</v>
+        <v>78.42</v>
       </c>
       <c r="D90" t="n">
-        <v>762700</v>
+        <v>974200</v>
       </c>
       <c r="E90" t="n">
-        <v>678490</v>
+        <v>677275</v>
       </c>
       <c r="F90" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>85.5</v>
       </c>
       <c r="L90" t="n">
-        <v>-6.43</v>
+        <v>-5.85</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>52</v>
+        <v>53.63</v>
       </c>
       <c r="S90" t="n">
-        <v>39.74</v>
+        <v>48.51</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7739,23 +7739,23 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23.05</v>
+        <v>23.35</v>
       </c>
       <c r="C91" t="n">
-        <v>52.19</v>
+        <v>84.47</v>
       </c>
       <c r="D91" t="n">
-        <v>2264400</v>
+        <v>3617600</v>
       </c>
       <c r="E91" t="n">
-        <v>3091355</v>
+        <v>3133000</v>
       </c>
       <c r="F91" t="n">
-        <v>0.73</v>
+        <v>1.15</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7775,7 +7775,7 @@
         <v>28.56</v>
       </c>
       <c r="L91" t="n">
-        <v>-19.29</v>
+        <v>-18.24</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>33.33</v>
+        <v>35.29</v>
       </c>
       <c r="S91" t="n">
-        <v>19.73</v>
+        <v>20.36</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>
@@ -7819,19 +7819,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="C92" t="n">
-        <v>63.81</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="D92" t="n">
-        <v>4871200</v>
+        <v>6865100</v>
       </c>
       <c r="E92" t="n">
-        <v>7113795</v>
+        <v>7170715</v>
       </c>
       <c r="F92" t="n">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -7852,10 +7852,10 @@
         <v>14.02</v>
       </c>
       <c r="K92" t="n">
-        <v>18.95</v>
+        <v>18.62</v>
       </c>
       <c r="L92" t="n">
-        <v>-30.87</v>
+        <v>-28.05</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -7871,10 +7871,10 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>42.11</v>
+        <v>54.55</v>
       </c>
       <c r="S92" t="n">
-        <v>35.71</v>
+        <v>43.69</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7888,87 +7888,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-19 23:05:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>VVS</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="C93" t="n">
-        <v>22.72</v>
-      </c>
-      <c r="D93" t="n">
-        <v>267600</v>
-      </c>
-      <c r="E93" t="n">
-        <v>154440</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>🔥 Tiền Vào Mạnh</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>94.15000000000001</v>
-      </c>
-      <c r="K93" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="L93" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R93" t="n">
-        <v>46.07</v>
-      </c>
-      <c r="S93" t="n">
-        <v>36.79</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>2026-10-19 23:05:17</t>
+          <t>2026-10-20 21:01:55</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>AAS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.5</v>
+        <v>10.6</v>
       </c>
       <c r="C2" t="n">
-        <v>113.3</v>
+        <v>25.31</v>
       </c>
       <c r="D2" t="n">
-        <v>5526600</v>
+        <v>2388000</v>
       </c>
       <c r="E2" t="n">
-        <v>6885120</v>
+        <v>1991905</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -561,25 +561,33 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21.65</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>21.58</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.98</v>
+        <v>21.84</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -587,10 +595,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>35.71</v>
+        <v>70</v>
       </c>
       <c r="S2" t="n">
-        <v>41.65</v>
+        <v>65.14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,30 +612,30 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACV</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>21.3</v>
       </c>
       <c r="C3" t="n">
-        <v>102.37</v>
+        <v>873.13</v>
       </c>
       <c r="D3" t="n">
-        <v>2380600</v>
+        <v>40992200</v>
       </c>
       <c r="E3" t="n">
-        <v>698630</v>
+        <v>8630695</v>
       </c>
       <c r="F3" t="n">
-        <v>3.41</v>
+        <v>4.75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -641,21 +649,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40.45</v>
+        <v>21.62</v>
       </c>
       <c r="K3" t="n">
-        <v>41.85</v>
+        <v>21.58</v>
       </c>
       <c r="L3" t="n">
-        <v>2.75</v>
+        <v>-1.27</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -663,18 +671,18 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.4x + giá chiết khấu 129)</t>
+          <t>🎯 BẮT ĐÁY (Vol 4.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>80.65000000000001</v>
+        <v>55.36</v>
       </c>
       <c r="S3" t="n">
-        <v>77.59999999999999</v>
+        <v>61.06</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -684,30 +692,30 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANV</t>
+          <t>ACV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.9</v>
+        <v>42.9</v>
       </c>
       <c r="C4" t="n">
-        <v>37.36</v>
+        <v>37.76</v>
       </c>
       <c r="D4" t="n">
-        <v>1976800</v>
+        <v>880200</v>
       </c>
       <c r="E4" t="n">
-        <v>1377380</v>
+        <v>733215</v>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -725,17 +733,17 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17.4</v>
+        <v>40.45</v>
       </c>
       <c r="K4" t="n">
-        <v>20.35</v>
+        <v>41.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-7.13</v>
+        <v>3.12</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -747,14 +755,14 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>64.84</v>
+        <v>79.37</v>
       </c>
       <c r="S4" t="n">
-        <v>66.62</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -764,30 +772,30 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAF</t>
+          <t>ANV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.5</v>
+        <v>19.05</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>27.55</v>
       </c>
       <c r="D5" t="n">
-        <v>1904800</v>
+        <v>1446100</v>
       </c>
       <c r="E5" t="n">
-        <v>1754375</v>
+        <v>1437380</v>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -801,21 +809,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>30.72</v>
+        <v>17.4</v>
       </c>
       <c r="K5" t="n">
-        <v>29.96</v>
+        <v>20.35</v>
       </c>
       <c r="L5" t="n">
-        <v>5.14</v>
+        <v>-6.39</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -827,14 +835,14 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>67.5</v>
+        <v>63.41</v>
       </c>
       <c r="S5" t="n">
-        <v>77.34999999999999</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -844,34 +852,34 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>BAF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.8</v>
+        <v>31.5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.58</v>
+        <v>106.87</v>
       </c>
       <c r="D6" t="n">
-        <v>651500</v>
+        <v>3392600</v>
       </c>
       <c r="E6" t="n">
-        <v>499320</v>
+        <v>1833620</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,21 +889,21 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>40.45</v>
+        <v>30.72</v>
       </c>
       <c r="K6" t="n">
-        <v>45.75</v>
+        <v>29.96</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.82</v>
+        <v>5.14</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -907,14 +915,14 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>65.67</v>
+        <v>62.86</v>
       </c>
       <c r="S6" t="n">
-        <v>57.89</v>
+        <v>77.89</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -924,39 +932,39 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.8</v>
+        <v>41.65</v>
       </c>
       <c r="C7" t="n">
-        <v>128.21</v>
+        <v>54.08</v>
       </c>
       <c r="D7" t="n">
-        <v>3793200</v>
+        <v>1298500</v>
       </c>
       <c r="E7" t="n">
-        <v>3066200</v>
+        <v>543370</v>
       </c>
       <c r="F7" t="n">
-        <v>1.24</v>
+        <v>2.39</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -965,13 +973,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>35</v>
+        <v>40.45</v>
       </c>
       <c r="K7" t="n">
-        <v>37.54</v>
+        <v>45.75</v>
       </c>
       <c r="L7" t="n">
-        <v>-9.960000000000001</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -987,56 +995,56 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>36.11</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>40.5</v>
+        <v>67.23</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BMP</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>138.1</v>
+        <v>34.25</v>
       </c>
       <c r="C8" t="n">
-        <v>20.33</v>
+        <v>121.7</v>
       </c>
       <c r="D8" t="n">
-        <v>147200</v>
+        <v>3553400</v>
       </c>
       <c r="E8" t="n">
-        <v>64770</v>
+        <v>3095320</v>
       </c>
       <c r="F8" t="n">
-        <v>2.27</v>
+        <v>1.15</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1045,13 +1053,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>146.5</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>143.8</v>
+        <v>37.54</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.96</v>
+        <v>-8.76</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1067,24 +1075,24 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>35.05</v>
+        <v>45.45</v>
       </c>
       <c r="S8" t="n">
-        <v>46.17</v>
+        <v>47.53</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
@@ -1095,19 +1103,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>29.05</v>
       </c>
       <c r="C9" t="n">
-        <v>256.76</v>
+        <v>205.43</v>
       </c>
       <c r="D9" t="n">
-        <v>8793200</v>
+        <v>7071600</v>
       </c>
       <c r="E9" t="n">
-        <v>10228275</v>
+        <v>9912855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1131,7 +1139,7 @@
         <v>27.96</v>
       </c>
       <c r="L9" t="n">
-        <v>4.43</v>
+        <v>3.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1147,10 +1155,10 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>42.14</v>
+        <v>41.61</v>
       </c>
       <c r="S9" t="n">
-        <v>32.2</v>
+        <v>37.37</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1164,7 +1172,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
@@ -1178,16 +1186,16 @@
         <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>52.47</v>
+        <v>34.78</v>
       </c>
       <c r="D10" t="n">
-        <v>760500</v>
+        <v>504100</v>
       </c>
       <c r="E10" t="n">
-        <v>1091520</v>
+        <v>1087455</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1234,7 +1242,7 @@
         <v>30.9</v>
       </c>
       <c r="S10" t="n">
-        <v>23.7</v>
+        <v>27.16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
@@ -1262,20 +1270,20 @@
         <v>11.5</v>
       </c>
       <c r="C11" t="n">
-        <v>95.81999999999999</v>
+        <v>74.27</v>
       </c>
       <c r="D11" t="n">
-        <v>8332500</v>
+        <v>6458200</v>
       </c>
       <c r="E11" t="n">
-        <v>6845985</v>
+        <v>6870825</v>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1311,10 +1319,10 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>79.7</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1328,7 +1336,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1347,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14.05</v>
+        <v>13.95</v>
       </c>
       <c r="C12" t="n">
-        <v>236.7</v>
+        <v>141.36</v>
       </c>
       <c r="D12" t="n">
-        <v>16847100</v>
+        <v>10133300</v>
       </c>
       <c r="E12" t="n">
-        <v>8495550</v>
+        <v>8765315</v>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.16</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1375,7 +1383,7 @@
         <v>15.85</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.36</v>
+        <v>-11.99</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1391,10 +1399,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>77.38</v>
+        <v>75.58</v>
       </c>
       <c r="S12" t="n">
-        <v>85.51000000000001</v>
+        <v>89.52</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1408,34 +1416,34 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.85</v>
+        <v>67</v>
       </c>
       <c r="C13" t="n">
-        <v>28.63</v>
+        <v>39.75</v>
       </c>
       <c r="D13" t="n">
-        <v>1200400</v>
+        <v>593300</v>
       </c>
       <c r="E13" t="n">
-        <v>566460</v>
+        <v>444575</v>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1449,17 +1457,17 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21.88</v>
+        <v>61.25</v>
       </c>
       <c r="K13" t="n">
-        <v>23.55</v>
+        <v>72.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27</v>
+        <v>-7.59</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1471,10 +1479,10 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>75.33</v>
+        <v>79.87</v>
       </c>
       <c r="S13" t="n">
-        <v>74.01000000000001</v>
+        <v>79.14</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1488,30 +1496,30 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CTD</t>
+          <t>CTG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>65.5</v>
+        <v>30.95</v>
       </c>
       <c r="C14" t="n">
-        <v>38.46</v>
+        <v>262.51</v>
       </c>
       <c r="D14" t="n">
-        <v>587100</v>
+        <v>8481600</v>
       </c>
       <c r="E14" t="n">
-        <v>423895</v>
+        <v>7483410</v>
       </c>
       <c r="F14" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1525,17 +1533,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>61.25</v>
+        <v>30.7</v>
       </c>
       <c r="K14" t="n">
-        <v>72.5</v>
+        <v>32.32</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.66</v>
+        <v>-4.24</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1551,10 +1559,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>78.09999999999999</v>
+        <v>70.31</v>
       </c>
       <c r="S14" t="n">
-        <v>75.13</v>
+        <v>53.44</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1568,30 +1576,30 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CTG</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.55</v>
+        <v>21.95</v>
       </c>
       <c r="C15" t="n">
-        <v>235.3</v>
+        <v>36.44</v>
       </c>
       <c r="D15" t="n">
-        <v>7702000</v>
+        <v>1660000</v>
       </c>
       <c r="E15" t="n">
-        <v>7386350</v>
+        <v>1279785</v>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1600,7 +1608,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1609,13 +1617,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30.7</v>
+        <v>21.4</v>
       </c>
       <c r="K15" t="n">
-        <v>32.32</v>
+        <v>24.1</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.48</v>
+        <v>-8.92</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1631,47 +1639,47 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>63.79</v>
+        <v>69.52</v>
       </c>
       <c r="S15" t="n">
-        <v>48.05</v>
+        <v>64.5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21.65</v>
+        <v>16.45</v>
       </c>
       <c r="C16" t="n">
-        <v>40.11</v>
+        <v>58.08</v>
       </c>
       <c r="D16" t="n">
-        <v>1852500</v>
+        <v>3530700</v>
       </c>
       <c r="E16" t="n">
-        <v>1228400</v>
+        <v>1694805</v>
       </c>
       <c r="F16" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1689,13 +1697,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>21.5</v>
+        <v>16.32</v>
       </c>
       <c r="K16" t="n">
-        <v>24.1</v>
+        <v>17.77</v>
       </c>
       <c r="L16" t="n">
-        <v>-10.17</v>
+        <v>-7.45</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1711,14 +1719,14 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>67.68000000000001</v>
+        <v>73.91</v>
       </c>
       <c r="S16" t="n">
-        <v>59.38</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1728,30 +1736,30 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>DCL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.05</v>
+        <v>47.95</v>
       </c>
       <c r="C17" t="n">
-        <v>24.87</v>
+        <v>25.48</v>
       </c>
       <c r="D17" t="n">
-        <v>1549600</v>
+        <v>531300</v>
       </c>
       <c r="E17" t="n">
-        <v>1562695</v>
+        <v>757230</v>
       </c>
       <c r="F17" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1760,26 +1768,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>16.32</v>
+        <v>44.65</v>
       </c>
       <c r="K17" t="n">
-        <v>17.93</v>
+        <v>44.05</v>
       </c>
       <c r="L17" t="n">
-        <v>-10.49</v>
+        <v>8.85</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1791,10 +1799,10 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>66.67</v>
+        <v>52.89</v>
       </c>
       <c r="S17" t="n">
-        <v>60.69</v>
+        <v>44.6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1803,44 +1811,44 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.5</v>
+        <v>35.5</v>
       </c>
       <c r="C18" t="n">
-        <v>31.25</v>
+        <v>104.5</v>
       </c>
       <c r="D18" t="n">
-        <v>631400</v>
+        <v>2943700</v>
       </c>
       <c r="E18" t="n">
-        <v>866815</v>
+        <v>2422035</v>
       </c>
       <c r="F18" t="n">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1849,17 +1857,17 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>44.65</v>
+        <v>32.2</v>
       </c>
       <c r="K18" t="n">
-        <v>44.05</v>
+        <v>36.04</v>
       </c>
       <c r="L18" t="n">
-        <v>12.37</v>
+        <v>-1.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1871,51 +1879,51 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>59.74</v>
+        <v>70.83</v>
       </c>
       <c r="S18" t="n">
-        <v>42.45</v>
+        <v>86.25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35.25</v>
+        <v>46.2</v>
       </c>
       <c r="C19" t="n">
-        <v>138.1</v>
+        <v>57.98</v>
       </c>
       <c r="D19" t="n">
-        <v>3917600</v>
+        <v>1254900</v>
       </c>
       <c r="E19" t="n">
-        <v>2434870</v>
+        <v>1584040</v>
       </c>
       <c r="F19" t="n">
-        <v>1.61</v>
+        <v>0.79</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1929,21 +1937,29 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>31.95</v>
+        <v>39.83</v>
       </c>
       <c r="K19" t="n">
-        <v>36.33</v>
+        <v>39.83</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.96</v>
+        <v>15.99</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1951,14 +1967,14 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>67.36</v>
+        <v>42.21</v>
       </c>
       <c r="S19" t="n">
-        <v>79.90000000000001</v>
+        <v>44.11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -1968,34 +1984,34 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DDV</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17.8</v>
+        <v>10.15</v>
       </c>
       <c r="C20" t="n">
-        <v>22.67</v>
+        <v>53.2</v>
       </c>
       <c r="D20" t="n">
-        <v>1273800</v>
+        <v>5241700</v>
       </c>
       <c r="E20" t="n">
-        <v>693105</v>
+        <v>4929445</v>
       </c>
       <c r="F20" t="n">
-        <v>1.84</v>
+        <v>1.06</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2005,17 +2021,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17.8</v>
+        <v>9.82</v>
       </c>
       <c r="K20" t="n">
-        <v>20.82</v>
+        <v>11.52</v>
       </c>
       <c r="L20" t="n">
-        <v>-14.51</v>
+        <v>-11.93</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2031,14 +2047,14 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>67.86</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>66.78</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2048,34 +2064,34 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DPG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>45.7</v>
+        <v>30.8</v>
       </c>
       <c r="C21" t="n">
-        <v>59.79</v>
+        <v>32.6</v>
       </c>
       <c r="D21" t="n">
-        <v>1308300</v>
+        <v>1058400</v>
       </c>
       <c r="E21" t="n">
-        <v>1592330</v>
+        <v>453140</v>
       </c>
       <c r="F21" t="n">
-        <v>0.82</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2085,28 +2101,24 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>39.83</v>
+        <v>28.82</v>
       </c>
       <c r="K21" t="n">
-        <v>39.83</v>
+        <v>35.3</v>
       </c>
       <c r="L21" t="n">
-        <v>14.74</v>
+        <v>-12.76</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
@@ -2115,14 +2127,14 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>55.5</v>
+        <v>90.52</v>
       </c>
       <c r="S21" t="n">
-        <v>50.64</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2132,39 +2144,39 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10.15</v>
+        <v>21.65</v>
       </c>
       <c r="C22" t="n">
-        <v>48.78</v>
+        <v>51.14</v>
       </c>
       <c r="D22" t="n">
-        <v>4805800</v>
+        <v>2362200</v>
       </c>
       <c r="E22" t="n">
-        <v>4873935</v>
+        <v>2287590</v>
       </c>
       <c r="F22" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2173,13 +2185,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9.82</v>
+        <v>22.18</v>
       </c>
       <c r="K22" t="n">
-        <v>11.52</v>
+        <v>23.94</v>
       </c>
       <c r="L22" t="n">
-        <v>-11.93</v>
+        <v>-9.58</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2195,71 +2207,71 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>78.13</v>
+        <v>50.94</v>
       </c>
       <c r="S22" t="n">
-        <v>76.66</v>
+        <v>43.41</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DPG</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30.4</v>
+        <v>10.45</v>
       </c>
       <c r="C23" t="n">
-        <v>25.72</v>
+        <v>65.61</v>
       </c>
       <c r="D23" t="n">
-        <v>846200</v>
+        <v>6278200</v>
       </c>
       <c r="E23" t="n">
-        <v>413155</v>
+        <v>9536255</v>
       </c>
       <c r="F23" t="n">
-        <v>2.05</v>
+        <v>0.66</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>28.82</v>
+        <v>10.73</v>
       </c>
       <c r="K23" t="n">
-        <v>35.3</v>
+        <v>11.89</v>
       </c>
       <c r="L23" t="n">
-        <v>-13.89</v>
+        <v>-12.07</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2268,78 +2280,82 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>90.18000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="S23" t="n">
-        <v>85.76000000000001</v>
+        <v>66.39</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21.85</v>
+        <v>17.85</v>
       </c>
       <c r="C24" t="n">
-        <v>50.7</v>
+        <v>358.13</v>
       </c>
       <c r="D24" t="n">
-        <v>2320300</v>
+        <v>20063400</v>
       </c>
       <c r="E24" t="n">
-        <v>2333570</v>
+        <v>4456890</v>
       </c>
       <c r="F24" t="n">
-        <v>0.99</v>
+        <v>4.5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>22.18</v>
+        <v>17.2</v>
       </c>
       <c r="K24" t="n">
-        <v>24.08</v>
+        <v>19.58</v>
       </c>
       <c r="L24" t="n">
-        <v>-9.279999999999999</v>
+        <v>-8.81</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2351,86 +2367,82 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 4.5x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>50</v>
+        <v>79.59</v>
       </c>
       <c r="S24" t="n">
-        <v>44.01</v>
+        <v>69.69</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.3</v>
+        <v>57</v>
       </c>
       <c r="C25" t="n">
-        <v>24.41</v>
+        <v>404.16</v>
       </c>
       <c r="D25" t="n">
-        <v>1595500</v>
+        <v>7090600</v>
       </c>
       <c r="E25" t="n">
-        <v>1879115</v>
+        <v>5682025</v>
       </c>
       <c r="F25" t="n">
-        <v>0.85</v>
+        <v>1.25</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>14.34</v>
+        <v>61.9</v>
       </c>
       <c r="K25" t="n">
-        <v>14.34</v>
+        <v>63.22</v>
       </c>
       <c r="L25" t="n">
-        <v>6.73</v>
+        <v>-9.84</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
@@ -2439,47 +2451,47 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>40.43</v>
+        <v>23.66</v>
       </c>
       <c r="S25" t="n">
-        <v>40.27</v>
+        <v>36.8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10.6</v>
+        <v>150</v>
       </c>
       <c r="C26" t="n">
-        <v>84.20999999999999</v>
+        <v>70.42</v>
       </c>
       <c r="D26" t="n">
-        <v>7944600</v>
+        <v>469500</v>
       </c>
       <c r="E26" t="n">
-        <v>9573040</v>
+        <v>623825</v>
       </c>
       <c r="F26" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2488,30 +2500,38 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>10.73</v>
+        <v>127.5</v>
       </c>
       <c r="K26" t="n">
-        <v>11.89</v>
+        <v>127.5</v>
       </c>
       <c r="L26" t="n">
-        <v>-10.81</v>
+        <v>17.65</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2519,56 +2539,56 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>69.43000000000001</v>
+        <v>54.75</v>
       </c>
       <c r="S26" t="n">
-        <v>64.08</v>
+        <v>65.37</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.95</v>
+        <v>78.3</v>
       </c>
       <c r="C27" t="n">
-        <v>105.95</v>
+        <v>60.68</v>
       </c>
       <c r="D27" t="n">
-        <v>6250600</v>
+        <v>775000</v>
       </c>
       <c r="E27" t="n">
-        <v>3629040</v>
+        <v>952220</v>
       </c>
       <c r="F27" t="n">
-        <v>1.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2577,17 +2597,17 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>17.2</v>
+        <v>76.48</v>
       </c>
       <c r="K27" t="n">
-        <v>19.58</v>
+        <v>77.69</v>
       </c>
       <c r="L27" t="n">
-        <v>-13.41</v>
+        <v>0.78</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2599,47 +2619,47 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>63.64</v>
+        <v>47.45</v>
       </c>
       <c r="S27" t="n">
-        <v>53.53</v>
+        <v>54.79</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57.4</v>
+        <v>72.5</v>
       </c>
       <c r="C28" t="n">
-        <v>579.08</v>
+        <v>183.35</v>
       </c>
       <c r="D28" t="n">
-        <v>10088500</v>
+        <v>2528900</v>
       </c>
       <c r="E28" t="n">
-        <v>5504690</v>
+        <v>1487265</v>
       </c>
       <c r="F28" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2648,22 +2668,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>61.9</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>63.22</v>
+        <v>95.83</v>
       </c>
       <c r="L28" t="n">
-        <v>-9.210000000000001</v>
+        <v>-24.35</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2679,51 +2699,51 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>24.18</v>
+        <v>53.13</v>
       </c>
       <c r="S28" t="n">
-        <v>38.56</v>
+        <v>54.11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>151.5</v>
+        <v>28.75</v>
       </c>
       <c r="C29" t="n">
-        <v>55.12</v>
+        <v>50.39</v>
       </c>
       <c r="D29" t="n">
-        <v>363800</v>
+        <v>1752800</v>
       </c>
       <c r="E29" t="n">
-        <v>638145</v>
+        <v>1340250</v>
       </c>
       <c r="F29" t="n">
-        <v>0.57</v>
+        <v>1.31</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2737,48 +2757,36 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>127.5</v>
+        <v>27.15</v>
       </c>
       <c r="K29" t="n">
-        <v>127.5</v>
+        <v>29.42</v>
       </c>
       <c r="L29" t="n">
-        <v>18.82</v>
+        <v>-2.29</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>62.57</v>
+        <v>54.02</v>
       </c>
       <c r="S29" t="n">
-        <v>71.84999999999999</v>
+        <v>49.33</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -2788,30 +2796,30 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>78.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="C30" t="n">
-        <v>78.47</v>
+        <v>246.48</v>
       </c>
       <c r="D30" t="n">
-        <v>1004700</v>
+        <v>10227200</v>
       </c>
       <c r="E30" t="n">
-        <v>965605</v>
+        <v>7294120</v>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2825,21 +2833,21 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>76.48</v>
+        <v>23.45</v>
       </c>
       <c r="K30" t="n">
-        <v>77.69</v>
+        <v>28.58</v>
       </c>
       <c r="L30" t="n">
-        <v>0.52</v>
+        <v>-15.66</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2851,10 +2859,10 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>47.45</v>
+        <v>59.38</v>
       </c>
       <c r="S30" t="n">
-        <v>48.15</v>
+        <v>62.35</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2868,34 +2876,34 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>73</v>
+        <v>57.1</v>
       </c>
       <c r="C31" t="n">
-        <v>200.95</v>
+        <v>108.21</v>
       </c>
       <c r="D31" t="n">
-        <v>2752800</v>
+        <v>1895100</v>
       </c>
       <c r="E31" t="n">
-        <v>1461450</v>
+        <v>1518730</v>
       </c>
       <c r="F31" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2905,24 +2913,28 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>66.81999999999999</v>
+        <v>51.28</v>
       </c>
       <c r="K31" t="n">
-        <v>95.83</v>
+        <v>51.28</v>
       </c>
       <c r="L31" t="n">
-        <v>-23.82</v>
+        <v>11.34</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
@@ -2931,14 +2943,14 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>60.47</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>65.81</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -2948,30 +2960,30 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28.55</v>
+        <v>31.75</v>
       </c>
       <c r="C32" t="n">
-        <v>36.34</v>
+        <v>50.33</v>
       </c>
       <c r="D32" t="n">
-        <v>1272800</v>
+        <v>1585300</v>
       </c>
       <c r="E32" t="n">
-        <v>1407475</v>
+        <v>2475770</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9</v>
+        <v>0.64</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2989,13 +3001,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>27.15</v>
+        <v>30.22</v>
       </c>
       <c r="K32" t="n">
-        <v>29.42</v>
+        <v>32.78</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.97</v>
+        <v>-3.13</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -3011,10 +3023,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>56.99</v>
+        <v>41.44</v>
       </c>
       <c r="S32" t="n">
-        <v>49.05</v>
+        <v>50.78</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3028,34 +3040,34 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>HAH</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.65</v>
+        <v>51.3</v>
       </c>
       <c r="C33" t="n">
-        <v>217.55</v>
+        <v>26.91</v>
       </c>
       <c r="D33" t="n">
-        <v>9198800</v>
+        <v>524600</v>
       </c>
       <c r="E33" t="n">
-        <v>6997770</v>
+        <v>1056585</v>
       </c>
       <c r="F33" t="n">
-        <v>1.31</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3065,21 +3077,21 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>23.45</v>
+        <v>48.2</v>
       </c>
       <c r="K33" t="n">
-        <v>28.58</v>
+        <v>49.55</v>
       </c>
       <c r="L33" t="n">
-        <v>-17.24</v>
+        <v>3.53</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3091,10 +3103,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>58.06</v>
+        <v>49.15</v>
       </c>
       <c r="S33" t="n">
-        <v>60.19</v>
+        <v>57.55</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3108,34 +3120,34 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>57.5</v>
+        <v>24</v>
       </c>
       <c r="C34" t="n">
-        <v>201.03</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>3496200</v>
+        <v>3626600</v>
       </c>
       <c r="E34" t="n">
-        <v>1462520</v>
+        <v>2709910</v>
       </c>
       <c r="F34" t="n">
-        <v>2.39</v>
+        <v>1.34</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3145,28 +3157,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>51.28</v>
+        <v>24.92</v>
       </c>
       <c r="K34" t="n">
-        <v>51.28</v>
+        <v>24.8</v>
       </c>
       <c r="L34" t="n">
-        <v>12.12</v>
+        <v>-3.23</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -3175,14 +3183,14 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>76.79000000000001</v>
+        <v>56.67</v>
       </c>
       <c r="S34" t="n">
-        <v>79.69</v>
+        <v>45.29</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3192,30 +3200,30 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.9</v>
+        <v>22.55</v>
       </c>
       <c r="C35" t="n">
-        <v>45.8</v>
+        <v>272.94</v>
       </c>
       <c r="D35" t="n">
-        <v>1435600</v>
+        <v>12103900</v>
       </c>
       <c r="E35" t="n">
-        <v>2540285</v>
+        <v>16255645</v>
       </c>
       <c r="F35" t="n">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3233,20 +3241,24 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>30.22</v>
+        <v>21.13</v>
       </c>
       <c r="K35" t="n">
-        <v>32.78</v>
+        <v>21.13</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.67</v>
+        <v>6.72</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -3255,10 +3267,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>42.2</v>
+        <v>64.56</v>
       </c>
       <c r="S35" t="n">
-        <v>44.76</v>
+        <v>66.5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3272,34 +3284,34 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HDC</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24.1</v>
+        <v>11.8</v>
       </c>
       <c r="C36" t="n">
-        <v>38.42</v>
+        <v>37.87</v>
       </c>
       <c r="D36" t="n">
-        <v>1594100</v>
+        <v>3209700</v>
       </c>
       <c r="E36" t="n">
-        <v>2626640</v>
+        <v>1582150</v>
       </c>
       <c r="F36" t="n">
-        <v>0.61</v>
+        <v>2.03</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3309,17 +3321,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>24.92</v>
+        <v>11.18</v>
       </c>
       <c r="K36" t="n">
-        <v>24.8</v>
+        <v>13.34</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.82</v>
+        <v>-11.58</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3335,14 +3347,14 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>56.67</v>
+        <v>91.67</v>
       </c>
       <c r="S36" t="n">
-        <v>52</v>
+        <v>78.55</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -3352,34 +3364,34 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>HHV</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22.35</v>
+        <v>9.66</v>
       </c>
       <c r="C37" t="n">
-        <v>339.91</v>
+        <v>29.39</v>
       </c>
       <c r="D37" t="n">
-        <v>15208500</v>
+        <v>3042100</v>
       </c>
       <c r="E37" t="n">
-        <v>16152880</v>
+        <v>3028800</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3389,28 +3401,24 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>21.13</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>21.13</v>
+        <v>10.54</v>
       </c>
       <c r="L37" t="n">
-        <v>5.77</v>
+        <v>-8.35</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
@@ -3419,14 +3427,14 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>56.85</v>
+        <v>70.92</v>
       </c>
       <c r="S37" t="n">
-        <v>62.92</v>
+        <v>68.45</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3436,39 +3444,39 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HDC</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.65</v>
+        <v>20.95</v>
       </c>
       <c r="C38" t="n">
-        <v>60.76</v>
+        <v>271.28</v>
       </c>
       <c r="D38" t="n">
-        <v>5215200</v>
+        <v>12949000</v>
       </c>
       <c r="E38" t="n">
-        <v>1457850</v>
+        <v>18984740</v>
       </c>
       <c r="F38" t="n">
-        <v>3.58</v>
+        <v>0.68</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3477,13 +3485,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>11.18</v>
+        <v>21.12</v>
       </c>
       <c r="K38" t="n">
-        <v>13.34</v>
+        <v>22.94</v>
       </c>
       <c r="L38" t="n">
-        <v>-12.7</v>
+        <v>-8.69</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3492,54 +3500,58 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.6x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>80.37</v>
+        <v>57.14</v>
       </c>
       <c r="S38" t="n">
-        <v>71.05</v>
+        <v>66.28</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HHP</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.3</v>
+        <v>11.05</v>
       </c>
       <c r="C39" t="n">
-        <v>21.91</v>
+        <v>40.36</v>
       </c>
       <c r="D39" t="n">
-        <v>1266300</v>
+        <v>3652600</v>
       </c>
       <c r="E39" t="n">
-        <v>1246230</v>
+        <v>3138060</v>
       </c>
       <c r="F39" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3548,7 +3560,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3557,17 +3569,17 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>16.39</v>
+        <v>10.48</v>
       </c>
       <c r="K39" t="n">
-        <v>15.45</v>
+        <v>11.35</v>
       </c>
       <c r="L39" t="n">
-        <v>11.97</v>
+        <v>-2.64</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3579,56 +3591,56 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>39.29</v>
+        <v>78.38</v>
       </c>
       <c r="S39" t="n">
-        <v>58.63</v>
+        <v>72.87</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HHV</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9.74</v>
+        <v>12.5</v>
       </c>
       <c r="C40" t="n">
-        <v>26.23</v>
+        <v>34.6</v>
       </c>
       <c r="D40" t="n">
-        <v>2693500</v>
+        <v>2768100</v>
       </c>
       <c r="E40" t="n">
-        <v>2945195</v>
+        <v>2002995</v>
       </c>
       <c r="F40" t="n">
-        <v>0.91</v>
+        <v>1.38</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3637,13 +3649,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>9.529999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="K40" t="n">
-        <v>10.54</v>
+        <v>14.25</v>
       </c>
       <c r="L40" t="n">
-        <v>-7.59</v>
+        <v>-12.28</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3659,51 +3671,51 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>74.06999999999999</v>
+        <v>63.16</v>
       </c>
       <c r="S40" t="n">
-        <v>70.61</v>
+        <v>60.03</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>21.25</v>
+        <v>36</v>
       </c>
       <c r="C41" t="n">
-        <v>309.21</v>
+        <v>48.3</v>
       </c>
       <c r="D41" t="n">
-        <v>14551200</v>
+        <v>1341700</v>
       </c>
       <c r="E41" t="n">
-        <v>19068485</v>
+        <v>1295215</v>
       </c>
       <c r="F41" t="n">
-        <v>0.76</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3713,21 +3725,21 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>21.12</v>
+        <v>32.55</v>
       </c>
       <c r="K41" t="n">
-        <v>22.94</v>
+        <v>35.98</v>
       </c>
       <c r="L41" t="n">
-        <v>-7.39</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3739,10 +3751,10 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>68.18000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="S41" t="n">
-        <v>73.65000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3756,34 +3768,34 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>KBC</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10.95</v>
+        <v>27</v>
       </c>
       <c r="C42" t="n">
-        <v>34.02</v>
+        <v>20.84</v>
       </c>
       <c r="D42" t="n">
-        <v>3107000</v>
+        <v>771900</v>
       </c>
       <c r="E42" t="n">
-        <v>3041070</v>
+        <v>1272305</v>
       </c>
       <c r="F42" t="n">
-        <v>1.02</v>
+        <v>0.61</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3793,17 +3805,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>10.48</v>
+        <v>26.55</v>
       </c>
       <c r="K42" t="n">
-        <v>11.35</v>
+        <v>30.05</v>
       </c>
       <c r="L42" t="n">
-        <v>-3.52</v>
+        <v>-10.15</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3812,17 +3824,21 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>77.40000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="S42" t="n">
-        <v>72.27</v>
+        <v>75.84</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3836,34 +3852,34 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>35.8</v>
+        <v>15.1</v>
       </c>
       <c r="C43" t="n">
-        <v>41.68</v>
+        <v>119.07</v>
       </c>
       <c r="D43" t="n">
-        <v>1164300</v>
+        <v>7885300</v>
       </c>
       <c r="E43" t="n">
-        <v>1291860</v>
+        <v>4500095</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9</v>
+        <v>1.75</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3873,17 +3889,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>32.45</v>
+        <v>15.04</v>
       </c>
       <c r="K43" t="n">
-        <v>36.67</v>
+        <v>18.43</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.37</v>
+        <v>-18.07</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3899,14 +3915,14 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>63.64</v>
+        <v>76.64</v>
       </c>
       <c r="S43" t="n">
-        <v>69.01000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -3916,54 +3932,54 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KBC</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27.1</v>
+        <v>40.4</v>
       </c>
       <c r="C44" t="n">
-        <v>38.82</v>
+        <v>139.82</v>
       </c>
       <c r="D44" t="n">
-        <v>1432400</v>
+        <v>3460900</v>
       </c>
       <c r="E44" t="n">
-        <v>1271125</v>
+        <v>2106095</v>
       </c>
       <c r="F44" t="n">
-        <v>1.13</v>
+        <v>1.64</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>26.55</v>
+        <v>46.6</v>
       </c>
       <c r="K44" t="n">
-        <v>30.05</v>
+        <v>47.85</v>
       </c>
       <c r="L44" t="n">
-        <v>-9.82</v>
+        <v>-15.57</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3979,75 +3995,75 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>86.54000000000001</v>
+        <v>40.37</v>
       </c>
       <c r="S44" t="n">
-        <v>73.31</v>
+        <v>49.71</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14.9</v>
+        <v>19.8</v>
       </c>
       <c r="C45" t="n">
-        <v>94.73999999999999</v>
+        <v>215.84</v>
       </c>
       <c r="D45" t="n">
-        <v>6358600</v>
+        <v>10901100</v>
       </c>
       <c r="E45" t="n">
-        <v>4251830</v>
+        <v>11694455</v>
       </c>
       <c r="F45" t="n">
-        <v>1.5</v>
+        <v>0.93</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>15.04</v>
+        <v>19.49</v>
       </c>
       <c r="K45" t="n">
-        <v>18.52</v>
+        <v>19.7</v>
       </c>
       <c r="L45" t="n">
-        <v>-19.57</v>
+        <v>0.51</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4059,47 +4075,47 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>72.23999999999999</v>
+        <v>63.83</v>
       </c>
       <c r="S45" t="n">
-        <v>69.05</v>
+        <v>51.39</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>39</v>
+        <v>15.7</v>
       </c>
       <c r="C46" t="n">
-        <v>66.12</v>
+        <v>45.09</v>
       </c>
       <c r="D46" t="n">
-        <v>1695500</v>
+        <v>2871900</v>
       </c>
       <c r="E46" t="n">
-        <v>1972415</v>
+        <v>2973375</v>
       </c>
       <c r="F46" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4117,13 +4133,13 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>46.6</v>
+        <v>16.02</v>
       </c>
       <c r="K46" t="n">
-        <v>47.85</v>
+        <v>17.43</v>
       </c>
       <c r="L46" t="n">
-        <v>-18.5</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -4139,10 +4155,10 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>45.97</v>
+        <v>58.06</v>
       </c>
       <c r="S46" t="n">
-        <v>48.01</v>
+        <v>53.08</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4156,30 +4172,30 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>19.9</v>
+        <v>141.9</v>
       </c>
       <c r="C47" t="n">
-        <v>154.8</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>7779000</v>
+        <v>519000</v>
       </c>
       <c r="E47" t="n">
-        <v>11542115</v>
+        <v>626625</v>
       </c>
       <c r="F47" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4193,17 +4209,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>19.49</v>
+        <v>138.57</v>
       </c>
       <c r="K47" t="n">
-        <v>19.7</v>
+        <v>134.54</v>
       </c>
       <c r="L47" t="n">
-        <v>1.02</v>
+        <v>5.47</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4212,21 +4228,17 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>67.39</v>
+        <v>59.79</v>
       </c>
       <c r="S47" t="n">
-        <v>51.97</v>
+        <v>38.45</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4240,30 +4252,30 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="C48" t="n">
-        <v>42.83</v>
+        <v>124.35</v>
       </c>
       <c r="D48" t="n">
-        <v>2745600</v>
+        <v>8022500</v>
       </c>
       <c r="E48" t="n">
-        <v>2952445</v>
+        <v>10699300</v>
       </c>
       <c r="F48" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4272,30 +4284,34 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>16.02</v>
+        <v>13.86</v>
       </c>
       <c r="K48" t="n">
-        <v>17.43</v>
+        <v>12.96</v>
       </c>
       <c r="L48" t="n">
-        <v>-10.52</v>
+        <v>19.55</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4303,10 +4319,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>54.84</v>
+        <v>83.33</v>
       </c>
       <c r="S48" t="n">
-        <v>54.41</v>
+        <v>87.83</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4315,39 +4331,39 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>141</v>
+        <v>74.2</v>
       </c>
       <c r="C49" t="n">
-        <v>139.86</v>
+        <v>348.82</v>
       </c>
       <c r="D49" t="n">
-        <v>991900</v>
+        <v>4701100</v>
       </c>
       <c r="E49" t="n">
-        <v>608720</v>
+        <v>5470510</v>
       </c>
       <c r="F49" t="n">
-        <v>1.63</v>
+        <v>0.86</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4361,13 +4377,13 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>138.57</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>134.54</v>
+        <v>72.05</v>
       </c>
       <c r="L49" t="n">
-        <v>4.81</v>
+        <v>2.98</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4383,14 +4399,14 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>59.38</v>
+        <v>60.58</v>
       </c>
       <c r="S49" t="n">
-        <v>36.85</v>
+        <v>70.66</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -4400,30 +4416,30 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>15.4</v>
+        <v>63.6</v>
       </c>
       <c r="C50" t="n">
-        <v>90.77</v>
+        <v>76.92</v>
       </c>
       <c r="D50" t="n">
-        <v>5893900</v>
+        <v>1209500</v>
       </c>
       <c r="E50" t="n">
-        <v>10973145</v>
+        <v>2181935</v>
       </c>
       <c r="F50" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4432,7 +4448,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4441,81 +4457,81 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>13.86</v>
+        <v>50.57</v>
       </c>
       <c r="K50" t="n">
-        <v>12.96</v>
+        <v>50.57</v>
       </c>
       <c r="L50" t="n">
-        <v>18.78</v>
+        <v>25.77</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>77.55</v>
+        <v>58.06</v>
       </c>
       <c r="S50" t="n">
-        <v>82.70999999999999</v>
+        <v>54.7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>73.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="C51" t="n">
-        <v>406.59</v>
+        <v>160.61</v>
       </c>
       <c r="D51" t="n">
-        <v>5501900</v>
+        <v>2127300</v>
       </c>
       <c r="E51" t="n">
-        <v>5450725</v>
+        <v>2802570</v>
       </c>
       <c r="F51" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4529,13 +4545,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>68.90000000000001</v>
+        <v>69.02</v>
       </c>
       <c r="K51" t="n">
-        <v>72.09999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="L51" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4551,10 +4567,10 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>61.43</v>
+        <v>59.22</v>
       </c>
       <c r="S51" t="n">
-        <v>64.95999999999999</v>
+        <v>63</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -4568,34 +4584,34 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63</v>
+        <v>12.6</v>
       </c>
       <c r="C52" t="n">
-        <v>126.01</v>
+        <v>52.51</v>
       </c>
       <c r="D52" t="n">
-        <v>2000200</v>
+        <v>4167200</v>
       </c>
       <c r="E52" t="n">
-        <v>2272540</v>
+        <v>2404815</v>
       </c>
       <c r="F52" t="n">
-        <v>0.88</v>
+        <v>1.73</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4609,29 +4625,21 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>50.57</v>
+        <v>12.05</v>
       </c>
       <c r="K52" t="n">
-        <v>50.57</v>
+        <v>12.25</v>
       </c>
       <c r="L52" t="n">
-        <v>24.58</v>
+        <v>2.86</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4639,10 +4647,10 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>56.34</v>
+        <v>52</v>
       </c>
       <c r="S52" t="n">
-        <v>49.89</v>
+        <v>55.26</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4656,34 +4664,34 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>75.3</v>
+        <v>12</v>
       </c>
       <c r="C53" t="n">
-        <v>124.83</v>
+        <v>70.11</v>
       </c>
       <c r="D53" t="n">
-        <v>1657800</v>
+        <v>5842600</v>
       </c>
       <c r="E53" t="n">
-        <v>2785135</v>
+        <v>3626080</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4697,13 +4705,13 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>69.02</v>
+        <v>10.52</v>
       </c>
       <c r="K53" t="n">
-        <v>73.36</v>
+        <v>11.41</v>
       </c>
       <c r="L53" t="n">
-        <v>2.64</v>
+        <v>5.17</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4712,25 +4720,21 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>62.48</v>
+        <v>84.25</v>
       </c>
       <c r="S53" t="n">
-        <v>69.78</v>
+        <v>96.55</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -4740,34 +4744,34 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>NLG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>12.25</v>
+        <v>23.3</v>
       </c>
       <c r="C54" t="n">
-        <v>26.3</v>
+        <v>56.98</v>
       </c>
       <c r="D54" t="n">
-        <v>2146600</v>
+        <v>2445300</v>
       </c>
       <c r="E54" t="n">
-        <v>2321700</v>
+        <v>1582055</v>
       </c>
       <c r="F54" t="n">
-        <v>0.92</v>
+        <v>1.55</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4781,13 +4785,13 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>12.05</v>
+        <v>22.55</v>
       </c>
       <c r="K54" t="n">
-        <v>12.25</v>
+        <v>23.88</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-2.41</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4803,14 +4807,14 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>44.19</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="S54" t="n">
-        <v>49.53</v>
+        <v>68.28</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -4820,58 +4824,58 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>12</v>
+        <v>10.6</v>
       </c>
       <c r="C55" t="n">
-        <v>93.41</v>
+        <v>128.29</v>
       </c>
       <c r="D55" t="n">
-        <v>7784500</v>
+        <v>12102900</v>
       </c>
       <c r="E55" t="n">
-        <v>3388900</v>
+        <v>27947159</v>
       </c>
       <c r="F55" t="n">
-        <v>2.3</v>
+        <v>0.43</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>10.5</v>
+        <v>11.88</v>
       </c>
       <c r="K55" t="n">
-        <v>11.41</v>
+        <v>14.5</v>
       </c>
       <c r="L55" t="n">
-        <v>5.17</v>
+        <v>-26.87</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4883,47 +4887,47 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>85.53</v>
+        <v>51.28</v>
       </c>
       <c r="S55" t="n">
-        <v>96.29000000000001</v>
+        <v>54.48</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NLG</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23.15</v>
+        <v>10.8</v>
       </c>
       <c r="C56" t="n">
-        <v>72.7</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>3140500</v>
+        <v>6482500</v>
       </c>
       <c r="E56" t="n">
-        <v>1528380</v>
+        <v>1548800</v>
       </c>
       <c r="F56" t="n">
-        <v>2.05</v>
+        <v>4.19</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4937,21 +4941,21 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>22.55</v>
+        <v>10.46</v>
       </c>
       <c r="K56" t="n">
-        <v>23.88</v>
+        <v>10.5</v>
       </c>
       <c r="L56" t="n">
-        <v>-3.04</v>
+        <v>2.91</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4959,18 +4963,18 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 4.2x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>65.81999999999999</v>
+        <v>90</v>
       </c>
       <c r="S56" t="n">
-        <v>58.21</v>
+        <v>66.84</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -4980,30 +4984,30 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10.7</v>
+        <v>13.1</v>
       </c>
       <c r="C57" t="n">
-        <v>166.05</v>
+        <v>20.36</v>
       </c>
       <c r="D57" t="n">
-        <v>15518400</v>
+        <v>1553900</v>
       </c>
       <c r="E57" t="n">
-        <v>28067634</v>
+        <v>1694055</v>
       </c>
       <c r="F57" t="n">
-        <v>0.55</v>
+        <v>0.92</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5021,13 +5025,13 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>11.88</v>
+        <v>13.2</v>
       </c>
       <c r="K57" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="L57" t="n">
-        <v>-26.18</v>
+        <v>-6.4</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5043,10 +5047,10 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>56.41</v>
+        <v>48</v>
       </c>
       <c r="S57" t="n">
-        <v>56.36</v>
+        <v>58.18</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5060,30 +5064,30 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10.35</v>
+        <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>20.71</v>
+        <v>180.83</v>
       </c>
       <c r="D58" t="n">
-        <v>2001400</v>
+        <v>11301600</v>
       </c>
       <c r="E58" t="n">
-        <v>1265500</v>
+        <v>3382455</v>
       </c>
       <c r="F58" t="n">
-        <v>1.58</v>
+        <v>3.34</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5092,26 +5096,26 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>10.46</v>
+        <v>14.28</v>
       </c>
       <c r="K58" t="n">
-        <v>10.5</v>
+        <v>14.25</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.38</v>
+        <v>12.28</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5123,10 +5127,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>69.23</v>
+        <v>93.55</v>
       </c>
       <c r="S58" t="n">
-        <v>45.97</v>
+        <v>91.92</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5135,59 +5139,59 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13.3</v>
+        <v>18.1</v>
       </c>
       <c r="C59" t="n">
-        <v>21.1</v>
+        <v>20.22</v>
       </c>
       <c r="D59" t="n">
-        <v>1586400</v>
+        <v>1117000</v>
       </c>
       <c r="E59" t="n">
-        <v>1703170</v>
+        <v>866865</v>
       </c>
       <c r="F59" t="n">
-        <v>0.93</v>
+        <v>1.29</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>13.2</v>
+        <v>19.55</v>
       </c>
       <c r="K59" t="n">
-        <v>14</v>
+        <v>21.66</v>
       </c>
       <c r="L59" t="n">
-        <v>-4.97</v>
+        <v>-16.42</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5203,47 +5207,47 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>50</v>
+        <v>40.3</v>
       </c>
       <c r="S59" t="n">
-        <v>51.76</v>
+        <v>35.86</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>15.6</v>
+        <v>12.15</v>
       </c>
       <c r="C60" t="n">
-        <v>157.63</v>
+        <v>102.12</v>
       </c>
       <c r="D60" t="n">
-        <v>10104600</v>
+        <v>8405300</v>
       </c>
       <c r="E60" t="n">
-        <v>2891885</v>
+        <v>5114055</v>
       </c>
       <c r="F60" t="n">
-        <v>3.49</v>
+        <v>1.64</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5252,26 +5256,26 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>14.08</v>
+        <v>11.68</v>
       </c>
       <c r="K60" t="n">
-        <v>14.05</v>
+        <v>13.82</v>
       </c>
       <c r="L60" t="n">
-        <v>11.03</v>
+        <v>-12.12</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -5283,47 +5287,47 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>90.91</v>
+        <v>77.14</v>
       </c>
       <c r="S60" t="n">
-        <v>87.54000000000001</v>
+        <v>77</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>18.3</v>
+        <v>56.7</v>
       </c>
       <c r="C61" t="n">
-        <v>70.66</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>3861400</v>
+        <v>1470900</v>
       </c>
       <c r="E61" t="n">
-        <v>818920</v>
+        <v>734905</v>
       </c>
       <c r="F61" t="n">
-        <v>4.72</v>
+        <v>2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5332,82 +5336,86 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>19.55</v>
+        <v>45.2</v>
       </c>
       <c r="K61" t="n">
-        <v>21.66</v>
+        <v>44.22</v>
       </c>
       <c r="L61" t="n">
-        <v>-15.49</v>
+        <v>28.24</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 4.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R61" t="n">
-        <v>43.75</v>
+        <v>70.31</v>
       </c>
       <c r="S61" t="n">
-        <v>38.87</v>
+        <v>60.7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12.05</v>
+        <v>35.45</v>
       </c>
       <c r="C62" t="n">
-        <v>77.05</v>
+        <v>102.06</v>
       </c>
       <c r="D62" t="n">
-        <v>6394000</v>
+        <v>2879000</v>
       </c>
       <c r="E62" t="n">
-        <v>4847570</v>
+        <v>3976310</v>
       </c>
       <c r="F62" t="n">
-        <v>1.32</v>
+        <v>0.72</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5421,13 +5429,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>11.68</v>
+        <v>35.15</v>
       </c>
       <c r="K62" t="n">
-        <v>13.82</v>
+        <v>38.08</v>
       </c>
       <c r="L62" t="n">
-        <v>-12.84</v>
+        <v>-6.92</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5443,14 +5451,14 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>75.76000000000001</v>
+        <v>49.62</v>
       </c>
       <c r="S62" t="n">
-        <v>75.23</v>
+        <v>66.37</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -5460,66 +5468,62 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>53.4</v>
+        <v>17.45</v>
       </c>
       <c r="C63" t="n">
-        <v>58.06</v>
+        <v>422.47</v>
       </c>
       <c r="D63" t="n">
-        <v>1087200</v>
+        <v>24210400</v>
       </c>
       <c r="E63" t="n">
-        <v>748985</v>
+        <v>15856895</v>
       </c>
       <c r="F63" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>45.2</v>
+        <v>31.4</v>
       </c>
       <c r="K63" t="n">
-        <v>44.22</v>
+        <v>47.16</v>
       </c>
       <c r="L63" t="n">
-        <v>20.77</v>
+        <v>-63</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5527,75 +5531,75 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>66.06999999999999</v>
+        <v>33.2</v>
       </c>
       <c r="S63" t="n">
-        <v>57.97</v>
+        <v>26.75</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>47.6</v>
+        <v>12.55</v>
       </c>
       <c r="C64" t="n">
-        <v>23.38</v>
+        <v>52.07</v>
       </c>
       <c r="D64" t="n">
-        <v>491100</v>
+        <v>4148700</v>
       </c>
       <c r="E64" t="n">
-        <v>319145</v>
+        <v>5828665</v>
       </c>
       <c r="F64" t="n">
-        <v>1.54</v>
+        <v>0.71</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>43.2</v>
+        <v>13.08</v>
       </c>
       <c r="K64" t="n">
-        <v>42.5</v>
+        <v>13.6</v>
       </c>
       <c r="L64" t="n">
-        <v>12</v>
+        <v>-7.72</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5607,71 +5611,71 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>53.66</v>
+        <v>45.83</v>
       </c>
       <c r="S64" t="n">
-        <v>43.86</v>
+        <v>38.36</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>35.85</v>
+        <v>18.7</v>
       </c>
       <c r="C65" t="n">
-        <v>116</v>
+        <v>87.66</v>
       </c>
       <c r="D65" t="n">
-        <v>3235600</v>
+        <v>4687800</v>
       </c>
       <c r="E65" t="n">
-        <v>4027830</v>
+        <v>3659255</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8</v>
+        <v>1.28</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>35.15</v>
+        <v>18.88</v>
       </c>
       <c r="K65" t="n">
-        <v>38.08</v>
+        <v>19.43</v>
       </c>
       <c r="L65" t="n">
-        <v>-5.87</v>
+        <v>-3.76</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -5687,47 +5691,47 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>50.38</v>
+        <v>61.97</v>
       </c>
       <c r="S65" t="n">
-        <v>62.51</v>
+        <v>72.84</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>18.6</v>
+        <v>21.2</v>
       </c>
       <c r="C66" t="n">
-        <v>154.4</v>
+        <v>21.62</v>
       </c>
       <c r="D66" t="n">
-        <v>8301300</v>
+        <v>1019900</v>
       </c>
       <c r="E66" t="n">
-        <v>14911325</v>
+        <v>1551545</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5736,26 +5740,26 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>31.4</v>
+        <v>20.6</v>
       </c>
       <c r="K66" t="n">
-        <v>47.16</v>
+        <v>20.13</v>
       </c>
       <c r="L66" t="n">
-        <v>-60.56</v>
+        <v>5.32</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5767,47 +5771,47 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>32.55</v>
+        <v>40.35</v>
       </c>
       <c r="S66" t="n">
-        <v>27.98</v>
+        <v>46.9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>12.55</v>
+        <v>32.3</v>
       </c>
       <c r="C67" t="n">
-        <v>42.85</v>
+        <v>59.54</v>
       </c>
       <c r="D67" t="n">
-        <v>3414700</v>
+        <v>1843300</v>
       </c>
       <c r="E67" t="n">
-        <v>5743205</v>
+        <v>3447040</v>
       </c>
       <c r="F67" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5816,26 +5820,26 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>13.08</v>
+        <v>30.94</v>
       </c>
       <c r="K67" t="n">
-        <v>13.6</v>
+        <v>31.62</v>
       </c>
       <c r="L67" t="n">
-        <v>-7.72</v>
+        <v>2.13</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -5847,51 +5851,51 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>44</v>
+        <v>42.86</v>
       </c>
       <c r="S67" t="n">
-        <v>38.62</v>
+        <v>54.54</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>18.9</v>
+        <v>23.7</v>
       </c>
       <c r="C68" t="n">
-        <v>181.6</v>
+        <v>127.57</v>
       </c>
       <c r="D68" t="n">
-        <v>9608600</v>
+        <v>5382800</v>
       </c>
       <c r="E68" t="n">
-        <v>3673330</v>
+        <v>7947960</v>
       </c>
       <c r="F68" t="n">
-        <v>2.62</v>
+        <v>0.68</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5901,36 +5905,40 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>18.88</v>
+        <v>21.2</v>
       </c>
       <c r="K68" t="n">
-        <v>19.43</v>
+        <v>21.2</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.73</v>
+        <v>11.79</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>62.86</v>
+        <v>45.61</v>
       </c>
       <c r="S68" t="n">
-        <v>66.37</v>
+        <v>44.29</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5944,34 +5952,34 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.7</v>
+        <v>20.95</v>
       </c>
       <c r="C69" t="n">
-        <v>21.53</v>
+        <v>27</v>
       </c>
       <c r="D69" t="n">
-        <v>992100</v>
+        <v>1289000</v>
       </c>
       <c r="E69" t="n">
-        <v>1570955</v>
+        <v>1286955</v>
       </c>
       <c r="F69" t="n">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5981,21 +5989,21 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="K69" t="n">
-        <v>19.6</v>
+        <v>21.92</v>
       </c>
       <c r="L69" t="n">
-        <v>10.69</v>
+        <v>-4.45</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -6007,14 +6015,14 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>48.31</v>
+        <v>22.81</v>
       </c>
       <c r="S69" t="n">
-        <v>46.89</v>
+        <v>32</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -6024,30 +6032,30 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>32.5</v>
+        <v>10.9</v>
       </c>
       <c r="C70" t="n">
-        <v>94.98</v>
+        <v>450.85</v>
       </c>
       <c r="D70" t="n">
-        <v>2922600</v>
+        <v>41362700</v>
       </c>
       <c r="E70" t="n">
-        <v>3481885</v>
+        <v>43948230</v>
       </c>
       <c r="F70" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -6061,21 +6069,21 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>30.94</v>
+        <v>10.9</v>
       </c>
       <c r="K70" t="n">
-        <v>31.62</v>
+        <v>12.48</v>
       </c>
       <c r="L70" t="n">
-        <v>2.77</v>
+        <v>-12.63</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -6087,10 +6095,10 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>41.38</v>
+        <v>46.94</v>
       </c>
       <c r="S70" t="n">
-        <v>50.6</v>
+        <v>38.93</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6104,65 +6112,61 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>23.6</v>
+        <v>12.8</v>
       </c>
       <c r="C71" t="n">
-        <v>121.71</v>
+        <v>167.98</v>
       </c>
       <c r="D71" t="n">
-        <v>5157000</v>
+        <v>13123200</v>
       </c>
       <c r="E71" t="n">
-        <v>7956490</v>
+        <v>11413060</v>
       </c>
       <c r="F71" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>21.2</v>
+        <v>13.32</v>
       </c>
       <c r="K71" t="n">
-        <v>21.2</v>
+        <v>15</v>
       </c>
       <c r="L71" t="n">
-        <v>11.32</v>
+        <v>-14.7</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
@@ -6171,51 +6175,51 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>50.79</v>
+        <v>62.61</v>
       </c>
       <c r="S71" t="n">
-        <v>44.45</v>
+        <v>55.86</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>21.2</v>
+        <v>16.65</v>
       </c>
       <c r="C72" t="n">
-        <v>24.81</v>
+        <v>50.13</v>
       </c>
       <c r="D72" t="n">
-        <v>1170300</v>
+        <v>3011000</v>
       </c>
       <c r="E72" t="n">
-        <v>1276230</v>
+        <v>2278880</v>
       </c>
       <c r="F72" t="n">
-        <v>0.92</v>
+        <v>1.32</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6229,13 +6233,13 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>22.3</v>
+        <v>19.77</v>
       </c>
       <c r="K72" t="n">
-        <v>21.92</v>
+        <v>19.19</v>
       </c>
       <c r="L72" t="n">
-        <v>-3.31</v>
+        <v>-13.21</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -6251,10 +6255,10 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>30.36</v>
+        <v>42</v>
       </c>
       <c r="S72" t="n">
-        <v>39.28</v>
+        <v>38.6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6268,54 +6272,54 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>10.8</v>
+        <v>19.95</v>
       </c>
       <c r="C73" t="n">
-        <v>425.68</v>
+        <v>412.63</v>
       </c>
       <c r="D73" t="n">
-        <v>39415000</v>
+        <v>20683200</v>
       </c>
       <c r="E73" t="n">
-        <v>43768385</v>
+        <v>19776485</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>10.9</v>
+        <v>19.55</v>
       </c>
       <c r="K73" t="n">
-        <v>12.52</v>
+        <v>20.34</v>
       </c>
       <c r="L73" t="n">
-        <v>-13.77</v>
+        <v>-1.94</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -6331,56 +6335,56 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>42.86</v>
+        <v>55</v>
       </c>
       <c r="S73" t="n">
-        <v>32.91</v>
+        <v>48</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>12.9</v>
+        <v>68.5</v>
       </c>
       <c r="C74" t="n">
-        <v>168.07</v>
+        <v>564.05</v>
       </c>
       <c r="D74" t="n">
-        <v>13028600</v>
+        <v>8234300</v>
       </c>
       <c r="E74" t="n">
-        <v>11018130</v>
+        <v>3575655</v>
       </c>
       <c r="F74" t="n">
-        <v>1.18</v>
+        <v>2.3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6389,20 +6393,24 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>13.32</v>
+        <v>70.05</v>
       </c>
       <c r="K74" t="n">
-        <v>15</v>
+        <v>70.05</v>
       </c>
       <c r="L74" t="n">
-        <v>-14.03</v>
+        <v>-2.21</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
@@ -6411,51 +6419,51 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>58.2</v>
+        <v>51.8</v>
       </c>
       <c r="S74" t="n">
-        <v>57.63</v>
+        <v>37.96</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>SZC</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>16.05</v>
+        <v>20.2</v>
       </c>
       <c r="C75" t="n">
-        <v>31.13</v>
+        <v>25.98</v>
       </c>
       <c r="D75" t="n">
-        <v>1939300</v>
+        <v>1286300</v>
       </c>
       <c r="E75" t="n">
-        <v>2266135</v>
+        <v>432405</v>
       </c>
       <c r="F75" t="n">
-        <v>0.86</v>
+        <v>2.97</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6465,17 +6473,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>19.77</v>
+        <v>18.14</v>
       </c>
       <c r="K75" t="n">
-        <v>19.19</v>
+        <v>21.94</v>
       </c>
       <c r="L75" t="n">
-        <v>-16.34</v>
+        <v>-7.91</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6487,18 +6495,18 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.0x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>39.58</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="S75" t="n">
-        <v>29.41</v>
+        <v>87.77</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -6508,30 +6516,30 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20.15</v>
+        <v>34.2</v>
       </c>
       <c r="C76" t="n">
-        <v>384.53</v>
+        <v>557.64</v>
       </c>
       <c r="D76" t="n">
-        <v>19083400</v>
+        <v>16305300</v>
       </c>
       <c r="E76" t="n">
-        <v>19326800</v>
+        <v>17773840</v>
       </c>
       <c r="F76" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -6545,24 +6553,28 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>19.55</v>
+        <v>31.5</v>
       </c>
       <c r="K76" t="n">
-        <v>20.34</v>
+        <v>31.5</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.96</v>
+        <v>8.57</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
@@ -6571,14 +6583,14 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>57.89</v>
+        <v>73.61</v>
       </c>
       <c r="S76" t="n">
-        <v>49.12</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -6588,30 +6600,30 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>64.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="C77" t="n">
-        <v>267.13</v>
+        <v>84.5</v>
       </c>
       <c r="D77" t="n">
-        <v>4167400</v>
+        <v>7042000</v>
       </c>
       <c r="E77" t="n">
-        <v>3244285</v>
+        <v>5103295</v>
       </c>
       <c r="F77" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6625,28 +6637,24 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>70.05</v>
+        <v>11.09</v>
       </c>
       <c r="K77" t="n">
-        <v>70.05</v>
+        <v>13.2</v>
       </c>
       <c r="L77" t="n">
-        <v>-8.49</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
@@ -6655,14 +6663,14 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>28.28</v>
+        <v>72.73</v>
       </c>
       <c r="S77" t="n">
-        <v>23.59</v>
+        <v>75.25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -6672,65 +6680,61 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>34.15</v>
+        <v>29.4</v>
       </c>
       <c r="C78" t="n">
-        <v>498.87</v>
+        <v>98.64</v>
       </c>
       <c r="D78" t="n">
-        <v>14608300</v>
+        <v>3355100</v>
       </c>
       <c r="E78" t="n">
-        <v>18353565</v>
+        <v>2907255</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8</v>
+        <v>1.15</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>31.5</v>
+        <v>31.01</v>
       </c>
       <c r="K78" t="n">
-        <v>31.5</v>
+        <v>32.59</v>
       </c>
       <c r="L78" t="n">
-        <v>8.41</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
@@ -6739,51 +6743,51 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>75</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="S78" t="n">
-        <v>70.11</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C79" t="n">
-        <v>80.16</v>
+        <v>391.19</v>
       </c>
       <c r="D79" t="n">
-        <v>6680200</v>
+        <v>30091200</v>
       </c>
       <c r="E79" t="n">
-        <v>4926610</v>
+        <v>12043425</v>
       </c>
       <c r="F79" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6797,17 +6801,17 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>11.09</v>
+        <v>12.18</v>
       </c>
       <c r="K79" t="n">
-        <v>13.2</v>
+        <v>12.68</v>
       </c>
       <c r="L79" t="n">
-        <v>-9.130000000000001</v>
+        <v>2.56</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -6819,10 +6823,10 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>73.91</v>
+        <v>76.19</v>
       </c>
       <c r="S79" t="n">
-        <v>69.45</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6836,34 +6840,34 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>29.85</v>
+        <v>56.8</v>
       </c>
       <c r="C80" t="n">
-        <v>192.6</v>
+        <v>186.24</v>
       </c>
       <c r="D80" t="n">
-        <v>6452400</v>
+        <v>3278900</v>
       </c>
       <c r="E80" t="n">
-        <v>2829210</v>
+        <v>2991925</v>
       </c>
       <c r="F80" t="n">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6877,13 +6881,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>31.01</v>
+        <v>57</v>
       </c>
       <c r="K80" t="n">
-        <v>32.59</v>
+        <v>59.12</v>
       </c>
       <c r="L80" t="n">
-        <v>-8.41</v>
+        <v>-3.93</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -6899,10 +6903,10 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>68.22</v>
+        <v>47.73</v>
       </c>
       <c r="S80" t="n">
-        <v>72.84999999999999</v>
+        <v>49.31</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6916,34 +6920,34 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TNG</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19.2</v>
+        <v>15.45</v>
       </c>
       <c r="C81" t="n">
-        <v>37.63</v>
+        <v>36.02</v>
       </c>
       <c r="D81" t="n">
-        <v>1959800</v>
+        <v>2331200</v>
       </c>
       <c r="E81" t="n">
-        <v>1026420</v>
+        <v>2254680</v>
       </c>
       <c r="F81" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6953,21 +6957,21 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>16.88</v>
+        <v>14.88</v>
       </c>
       <c r="K81" t="n">
-        <v>17.78</v>
+        <v>17.1</v>
       </c>
       <c r="L81" t="n">
-        <v>7.96</v>
+        <v>-9.68</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6979,10 +6983,10 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>69.12</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="S81" t="n">
-        <v>81.28</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6996,58 +7000,58 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>12.75</v>
+        <v>19.6</v>
       </c>
       <c r="C82" t="n">
-        <v>350.3</v>
+        <v>147.71</v>
       </c>
       <c r="D82" t="n">
-        <v>27474500</v>
+        <v>7536000</v>
       </c>
       <c r="E82" t="n">
-        <v>10977660</v>
+        <v>7923875</v>
       </c>
       <c r="F82" t="n">
-        <v>2.5</v>
+        <v>0.95</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>12.15</v>
+        <v>20.6</v>
       </c>
       <c r="K82" t="n">
-        <v>12.68</v>
+        <v>22.9</v>
       </c>
       <c r="L82" t="n">
-        <v>0.59</v>
+        <v>-14.41</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -7055,55 +7059,55 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.5x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>72.97</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="S82" t="n">
-        <v>71.48999999999999</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>56.3</v>
+        <v>27.95</v>
       </c>
       <c r="C83" t="n">
-        <v>185.23</v>
+        <v>34.75</v>
       </c>
       <c r="D83" t="n">
-        <v>3290100</v>
+        <v>1243300</v>
       </c>
       <c r="E83" t="n">
-        <v>3047485</v>
+        <v>1693245</v>
       </c>
       <c r="F83" t="n">
-        <v>1.08</v>
+        <v>0.73</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7117,13 +7121,13 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>57</v>
+        <v>29.08</v>
       </c>
       <c r="K83" t="n">
-        <v>59.12</v>
+        <v>30.82</v>
       </c>
       <c r="L83" t="n">
-        <v>-4.78</v>
+        <v>-9.33</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7139,10 +7143,10 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>40</v>
+        <v>56.31</v>
       </c>
       <c r="S83" t="n">
-        <v>42.34</v>
+        <v>73.47</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7156,34 +7160,34 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>VGC</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>15.5</v>
+        <v>44.5</v>
       </c>
       <c r="C84" t="n">
-        <v>50.33</v>
+        <v>20.81</v>
       </c>
       <c r="D84" t="n">
-        <v>3246800</v>
+        <v>467600</v>
       </c>
       <c r="E84" t="n">
-        <v>2204390</v>
+        <v>613020</v>
       </c>
       <c r="F84" t="n">
-        <v>1.47</v>
+        <v>0.76</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7193,24 +7197,28 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>14.88</v>
+        <v>40.17</v>
       </c>
       <c r="K84" t="n">
-        <v>17.1</v>
+        <v>40.17</v>
       </c>
       <c r="L84" t="n">
-        <v>-9.380000000000001</v>
+        <v>10.77</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
@@ -7219,14 +7227,14 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>87.93000000000001</v>
+        <v>50</v>
       </c>
       <c r="S84" t="n">
-        <v>79.05</v>
+        <v>47.47</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -7236,30 +7244,30 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>19.5</v>
+        <v>64.3</v>
       </c>
       <c r="C85" t="n">
-        <v>136.49</v>
+        <v>413.23</v>
       </c>
       <c r="D85" t="n">
-        <v>6999500</v>
+        <v>6426600</v>
       </c>
       <c r="E85" t="n">
-        <v>7897660</v>
+        <v>8196050</v>
       </c>
       <c r="F85" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7268,7 +7276,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7277,13 +7285,13 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>20.6</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>22.98</v>
+        <v>70.52</v>
       </c>
       <c r="L85" t="n">
-        <v>-15.13</v>
+        <v>-8.82</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -7299,47 +7307,47 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>62.32</v>
+        <v>41.74</v>
       </c>
       <c r="S85" t="n">
-        <v>60.68</v>
+        <v>40.36</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>VIB</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.2</v>
+        <v>14.2</v>
       </c>
       <c r="C86" t="n">
-        <v>45.73</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="D86" t="n">
-        <v>1621500</v>
+        <v>5024500</v>
       </c>
       <c r="E86" t="n">
-        <v>1698960</v>
+        <v>6051070</v>
       </c>
       <c r="F86" t="n">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7348,26 +7356,26 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>29.08</v>
+        <v>13.52</v>
       </c>
       <c r="K86" t="n">
-        <v>30.82</v>
+        <v>14.16</v>
       </c>
       <c r="L86" t="n">
-        <v>-8.52</v>
+        <v>0.32</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -7379,47 +7387,47 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>58</v>
+        <v>71.05</v>
       </c>
       <c r="S86" t="n">
-        <v>72.81999999999999</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39</v>
+        <v>236.5</v>
       </c>
       <c r="C87" t="n">
-        <v>21.07</v>
+        <v>477.87</v>
       </c>
       <c r="D87" t="n">
-        <v>540200</v>
+        <v>2020600</v>
       </c>
       <c r="E87" t="n">
-        <v>613960</v>
+        <v>2700435</v>
       </c>
       <c r="F87" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -7433,17 +7441,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>36.8</v>
+        <v>229.8</v>
       </c>
       <c r="K87" t="n">
-        <v>36.5</v>
+        <v>221.55</v>
       </c>
       <c r="L87" t="n">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -7459,14 +7467,14 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>74.19</v>
+        <v>53.72</v>
       </c>
       <c r="S87" t="n">
-        <v>67.42</v>
+        <v>36.31</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -7476,65 +7484,61 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VGC</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>44.2</v>
+        <v>12.7</v>
       </c>
       <c r="C88" t="n">
-        <v>24.79</v>
+        <v>506.64</v>
       </c>
       <c r="D88" t="n">
-        <v>560900</v>
+        <v>39893300</v>
       </c>
       <c r="E88" t="n">
-        <v>617615</v>
+        <v>29447510</v>
       </c>
       <c r="F88" t="n">
-        <v>0.91</v>
+        <v>1.35</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>40.17</v>
+        <v>12.82</v>
       </c>
       <c r="K88" t="n">
-        <v>40.17</v>
+        <v>14.95</v>
       </c>
       <c r="L88" t="n">
-        <v>10.02</v>
+        <v>-15.05</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
@@ -7543,51 +7547,51 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>52.23</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="S88" t="n">
-        <v>46.83</v>
+        <v>72.42</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>VJC</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>64</v>
+        <v>129.7</v>
       </c>
       <c r="C89" t="n">
-        <v>884.45</v>
+        <v>114.67</v>
       </c>
       <c r="D89" t="n">
-        <v>13819600</v>
+        <v>884100</v>
       </c>
       <c r="E89" t="n">
-        <v>8447355</v>
+        <v>928415</v>
       </c>
       <c r="F89" t="n">
-        <v>1.64</v>
+        <v>0.95</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7597,17 +7601,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>69.65000000000001</v>
+        <v>128.05</v>
       </c>
       <c r="K89" t="n">
-        <v>70.52</v>
+        <v>132.12</v>
       </c>
       <c r="L89" t="n">
-        <v>-9.25</v>
+        <v>-1.84</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7623,10 +7627,10 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>41.98</v>
+        <v>57.38</v>
       </c>
       <c r="S89" t="n">
-        <v>40.06</v>
+        <v>37.76</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -7640,54 +7644,54 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14.05</v>
+        <v>13.75</v>
       </c>
       <c r="C90" t="n">
-        <v>96.05</v>
+        <v>108.84</v>
       </c>
       <c r="D90" t="n">
-        <v>6836500</v>
+        <v>7915900</v>
       </c>
       <c r="E90" t="n">
-        <v>5909975</v>
+        <v>10023200</v>
       </c>
       <c r="F90" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>13.52</v>
+        <v>15.05</v>
       </c>
       <c r="K90" t="n">
-        <v>14.16</v>
+        <v>15.85</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.74</v>
+        <v>-13.25</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -7703,47 +7707,47 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>69.44</v>
+        <v>57.14</v>
       </c>
       <c r="S90" t="n">
-        <v>74.23</v>
+        <v>54.85</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>232.9</v>
+        <v>57.6</v>
       </c>
       <c r="C91" t="n">
-        <v>603.72</v>
+        <v>103.32</v>
       </c>
       <c r="D91" t="n">
-        <v>2592200</v>
+        <v>1793700</v>
       </c>
       <c r="E91" t="n">
-        <v>2667445</v>
+        <v>1948445</v>
       </c>
       <c r="F91" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7757,21 +7761,21 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>229.8</v>
+        <v>60.65</v>
       </c>
       <c r="K91" t="n">
-        <v>221.55</v>
+        <v>59.5</v>
       </c>
       <c r="L91" t="n">
-        <v>5.12</v>
+        <v>-3.19</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -7783,10 +7787,10 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>56.86</v>
+        <v>53.23</v>
       </c>
       <c r="S91" t="n">
-        <v>36.68</v>
+        <v>53.54</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7800,114 +7804,122 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VPB</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>12.55</v>
+        <v>24.1</v>
       </c>
       <c r="C92" t="n">
-        <v>405.31</v>
+        <v>273.6</v>
       </c>
       <c r="D92" t="n">
-        <v>32295500</v>
+        <v>11352800</v>
       </c>
       <c r="E92" t="n">
-        <v>28412930</v>
+        <v>16304165</v>
       </c>
       <c r="F92" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>12.82</v>
+        <v>21.98</v>
       </c>
       <c r="K92" t="n">
-        <v>14.95</v>
+        <v>21.98</v>
       </c>
       <c r="L92" t="n">
-        <v>-16.05</v>
+        <v>9.67</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>64.70999999999999</v>
+        <v>73.91</v>
       </c>
       <c r="S92" t="n">
-        <v>66.48</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VJC</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>128.6</v>
+        <v>57.4</v>
       </c>
       <c r="C93" t="n">
-        <v>105.46</v>
+        <v>148.57</v>
       </c>
       <c r="D93" t="n">
-        <v>820100</v>
+        <v>2588300</v>
       </c>
       <c r="E93" t="n">
-        <v>928075</v>
+        <v>1787020</v>
       </c>
       <c r="F93" t="n">
-        <v>0.88</v>
+        <v>1.45</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7917,24 +7929,28 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>128.05</v>
+        <v>55.52</v>
       </c>
       <c r="K93" t="n">
-        <v>132.12</v>
+        <v>55.52</v>
       </c>
       <c r="L93" t="n">
-        <v>-2.67</v>
+        <v>3.38</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
@@ -7943,10 +7959,10 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>42.86</v>
+        <v>51.28</v>
       </c>
       <c r="S93" t="n">
-        <v>31.2</v>
+        <v>49.61</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7960,58 +7976,58 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>VPL</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.75</v>
+        <v>86</v>
       </c>
       <c r="C94" t="n">
-        <v>106.84</v>
+        <v>156.66</v>
       </c>
       <c r="D94" t="n">
-        <v>7769900</v>
+        <v>1821600</v>
       </c>
       <c r="E94" t="n">
-        <v>9936985</v>
+        <v>759725</v>
       </c>
       <c r="F94" t="n">
-        <v>0.78</v>
+        <v>2.4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>15.05</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K94" t="n">
-        <v>15.85</v>
+        <v>85.5</v>
       </c>
       <c r="L94" t="n">
-        <v>-13.25</v>
+        <v>0.58</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -8023,51 +8039,51 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>57.89</v>
+        <v>70</v>
       </c>
       <c r="S94" t="n">
-        <v>55.7</v>
+        <v>73.44</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>VRE</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>58.1</v>
+        <v>25</v>
       </c>
       <c r="C95" t="n">
-        <v>71.59999999999999</v>
+        <v>90.02</v>
       </c>
       <c r="D95" t="n">
-        <v>1232300</v>
+        <v>3600900</v>
       </c>
       <c r="E95" t="n">
-        <v>1958640</v>
+        <v>3330395</v>
       </c>
       <c r="F95" t="n">
-        <v>0.63</v>
+        <v>1.08</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8077,17 +8093,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>60.65</v>
+        <v>24.42</v>
       </c>
       <c r="K95" t="n">
-        <v>59.5</v>
+        <v>28.56</v>
       </c>
       <c r="L95" t="n">
-        <v>-2.35</v>
+        <v>-12.46</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -8103,10 +8119,10 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>56.9</v>
+        <v>62.77</v>
       </c>
       <c r="S95" t="n">
-        <v>51.16</v>
+        <v>45.66</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -8120,34 +8136,34 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VPB</t>
+          <t>VSC</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>23.95</v>
+        <v>15.1</v>
       </c>
       <c r="C96" t="n">
-        <v>281.7</v>
+        <v>408.79</v>
       </c>
       <c r="D96" t="n">
-        <v>11762100</v>
+        <v>27072200</v>
       </c>
       <c r="E96" t="n">
-        <v>18078725</v>
+        <v>9880605</v>
       </c>
       <c r="F96" t="n">
-        <v>0.65</v>
+        <v>2.74</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8157,44 +8173,36 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>21.98</v>
+        <v>14.02</v>
       </c>
       <c r="K96" t="n">
-        <v>21.98</v>
+        <v>18.12</v>
       </c>
       <c r="L96" t="n">
-        <v>8.99</v>
+        <v>-16.69</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>73.33</v>
+        <v>78.38</v>
       </c>
       <c r="S96" t="n">
-        <v>65.33</v>
+        <v>75.59</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -8208,30 +8216,30 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>VTZ</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>55.8</v>
+        <v>20.3</v>
       </c>
       <c r="C97" t="n">
-        <v>124.82</v>
+        <v>25.66</v>
       </c>
       <c r="D97" t="n">
-        <v>2236900</v>
+        <v>1264000</v>
       </c>
       <c r="E97" t="n">
-        <v>1746995</v>
+        <v>960130</v>
       </c>
       <c r="F97" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -8249,24 +8257,20 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>55.52</v>
+        <v>20.45</v>
       </c>
       <c r="K97" t="n">
-        <v>55.52</v>
+        <v>21.3</v>
       </c>
       <c r="L97" t="n">
-        <v>0.5</v>
+        <v>-4.69</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
@@ -8275,10 +8279,10 @@
         </is>
       </c>
       <c r="R97" t="n">
-        <v>42.42</v>
+        <v>42.86</v>
       </c>
       <c r="S97" t="n">
-        <v>40.27</v>
+        <v>35.26</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -8292,34 +8296,34 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VPL</t>
+          <t>VVS</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>85.5</v>
+        <v>84</v>
       </c>
       <c r="C98" t="n">
-        <v>86.59999999999999</v>
+        <v>50.32</v>
       </c>
       <c r="D98" t="n">
-        <v>1012900</v>
+        <v>599000</v>
       </c>
       <c r="E98" t="n">
-        <v>689795</v>
+        <v>187715</v>
       </c>
       <c r="F98" t="n">
-        <v>1.47</v>
+        <v>3.19</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8329,17 +8333,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>79.84999999999999</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="K98" t="n">
-        <v>85.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>-1.29</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -8351,14 +8355,14 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.2x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>65.14</v>
+        <v>47.62</v>
       </c>
       <c r="S98" t="n">
-        <v>64.06999999999999</v>
+        <v>47.46</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -8372,487 +8376,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-10-22 21:21:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>VPX</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="C99" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="D99" t="n">
-        <v>1122800</v>
-      </c>
-      <c r="E99" t="n">
-        <v>812910</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>⚡ Có Tín Hiệu</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="K99" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="L99" t="n">
-        <v>-7.14</v>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R99" t="n">
-        <v>43.84</v>
-      </c>
-      <c r="S99" t="n">
-        <v>49.69</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:21:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>VRE</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="C100" t="n">
-        <v>140.52</v>
-      </c>
-      <c r="D100" t="n">
-        <v>5554100</v>
-      </c>
-      <c r="E100" t="n">
-        <v>3343610</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>🔥 Tiền Vào Mạnh</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>🌫️ Trong Mây</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>24.42</v>
-      </c>
-      <c r="K100" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="L100" t="n">
-        <v>-11.41</v>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R100" t="n">
-        <v>68.48</v>
-      </c>
-      <c r="S100" t="n">
-        <v>46.34</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:21:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>VSC</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="C101" t="n">
-        <v>318.01</v>
-      </c>
-      <c r="D101" t="n">
-        <v>21856200</v>
-      </c>
-      <c r="E101" t="n">
-        <v>8817760</v>
-      </c>
-      <c r="F101" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>🔥 Tiền Vào Mạnh</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>🌫️ Trong Mây</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>14.02</v>
-      </c>
-      <c r="K101" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="L101" t="n">
-        <v>-19.72</v>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R101" t="n">
-        <v>76.81</v>
-      </c>
-      <c r="S101" t="n">
-        <v>70.81999999999999</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>🔴 Bán (vùng quá mua)</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:21:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>VTP</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="C102" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="D102" t="n">
-        <v>439000</v>
-      </c>
-      <c r="E102" t="n">
-        <v>696065</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>💤 Tiền Yếu</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>🔴 Giảm</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="K102" t="n">
-        <v>52.76</v>
-      </c>
-      <c r="L102" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R102" t="n">
-        <v>31.19</v>
-      </c>
-      <c r="S102" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>🔴 Tiêu cực</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:21:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>VTZ</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="C103" t="n">
-        <v>26.59</v>
-      </c>
-      <c r="D103" t="n">
-        <v>1309700</v>
-      </c>
-      <c r="E103" t="n">
-        <v>948930</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>⚡ Có Tín Hiệu</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="K103" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="L103" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R103" t="n">
-        <v>50</v>
-      </c>
-      <c r="S103" t="n">
-        <v>32.96</v>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:21:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>VVS</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="C104" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="D104" t="n">
-        <v>253300</v>
-      </c>
-      <c r="E104" t="n">
-        <v>162195</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>🔥 Tiền Vào Mạnh</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>94.15000000000001</v>
-      </c>
-      <c r="K104" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="L104" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R104" t="n">
-        <v>57.23</v>
-      </c>
-      <c r="S104" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>2026-10-22 21:21:04</t>
+          <t>2026-10-23 21:02:24</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAS</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.6</v>
+        <v>21.3</v>
       </c>
       <c r="C2" t="n">
-        <v>25.31</v>
+        <v>188.34</v>
       </c>
       <c r="D2" t="n">
-        <v>2388000</v>
+        <v>8842300</v>
       </c>
       <c r="E2" t="n">
-        <v>1991905</v>
+        <v>8670705</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -556,38 +556,30 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>8.699999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="K2" t="n">
-        <v>8.699999999999999</v>
+        <v>21.58</v>
       </c>
       <c r="L2" t="n">
-        <v>21.84</v>
+        <v>-1.27</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -595,51 +587,51 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>70</v>
+        <v>64.58</v>
       </c>
       <c r="S2" t="n">
-        <v>65.14</v>
+        <v>69.67</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>ACV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.3</v>
+        <v>41.8</v>
       </c>
       <c r="C3" t="n">
-        <v>873.13</v>
+        <v>37.87</v>
       </c>
       <c r="D3" t="n">
-        <v>40992200</v>
+        <v>905900</v>
       </c>
       <c r="E3" t="n">
-        <v>8630695</v>
+        <v>765970</v>
       </c>
       <c r="F3" t="n">
-        <v>4.75</v>
+        <v>1.18</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -649,21 +641,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>21.62</v>
+        <v>40.45</v>
       </c>
       <c r="K3" t="n">
-        <v>21.58</v>
+        <v>41.6</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.27</v>
+        <v>0.48</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -671,18 +663,18 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 4.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>55.36</v>
+        <v>67.12</v>
       </c>
       <c r="S3" t="n">
-        <v>61.06</v>
+        <v>75.12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -692,34 +684,34 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACV</t>
+          <t>BAF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.9</v>
+        <v>29.67</v>
       </c>
       <c r="C4" t="n">
-        <v>37.76</v>
+        <v>107.59</v>
       </c>
       <c r="D4" t="n">
-        <v>880200</v>
+        <v>3626300</v>
       </c>
       <c r="E4" t="n">
-        <v>733215</v>
+        <v>1938025</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -729,17 +721,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>40.45</v>
+        <v>29.12</v>
       </c>
       <c r="K4" t="n">
-        <v>41.6</v>
+        <v>28.4</v>
       </c>
       <c r="L4" t="n">
-        <v>3.12</v>
+        <v>4.47</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -755,14 +747,14 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>79.37</v>
+        <v>53.98</v>
       </c>
       <c r="S4" t="n">
-        <v>78.79000000000001</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -772,34 +764,34 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANV</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.05</v>
+        <v>41.35</v>
       </c>
       <c r="C5" t="n">
-        <v>27.55</v>
+        <v>36.56</v>
       </c>
       <c r="D5" t="n">
-        <v>1446100</v>
+        <v>884100</v>
       </c>
       <c r="E5" t="n">
-        <v>1437380</v>
+        <v>545560</v>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -809,17 +801,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17.4</v>
+        <v>40.45</v>
       </c>
       <c r="K5" t="n">
-        <v>20.35</v>
+        <v>45.55</v>
       </c>
       <c r="L5" t="n">
-        <v>-6.39</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -835,14 +827,14 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>63.41</v>
+        <v>71.92</v>
       </c>
       <c r="S5" t="n">
-        <v>67.15000000000001</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -852,58 +844,58 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAF</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.5</v>
+        <v>33.75</v>
       </c>
       <c r="C6" t="n">
-        <v>106.87</v>
+        <v>102.15</v>
       </c>
       <c r="D6" t="n">
-        <v>3392600</v>
+        <v>3026600</v>
       </c>
       <c r="E6" t="n">
-        <v>1833620</v>
+        <v>3010315</v>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>30.72</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>29.96</v>
+        <v>37.54</v>
       </c>
       <c r="L6" t="n">
-        <v>5.14</v>
+        <v>-10.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -915,47 +907,47 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>62.86</v>
+        <v>40.23</v>
       </c>
       <c r="S6" t="n">
-        <v>77.89</v>
+        <v>49.88</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>BSI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41.65</v>
+        <v>27.3</v>
       </c>
       <c r="C7" t="n">
-        <v>54.08</v>
+        <v>23.65</v>
       </c>
       <c r="D7" t="n">
-        <v>1298500</v>
+        <v>866400</v>
       </c>
       <c r="E7" t="n">
-        <v>543370</v>
+        <v>344610</v>
       </c>
       <c r="F7" t="n">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -973,13 +965,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>40.45</v>
+        <v>26.75</v>
       </c>
       <c r="K7" t="n">
-        <v>45.75</v>
+        <v>30.35</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.960000000000001</v>
+        <v>-10.05</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -991,14 +983,14 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.5x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>71.43000000000001</v>
+        <v>68</v>
       </c>
       <c r="S7" t="n">
-        <v>67.23</v>
+        <v>70.92</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1012,58 +1004,58 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.25</v>
+        <v>29.4</v>
       </c>
       <c r="C8" t="n">
-        <v>121.7</v>
+        <v>262.31</v>
       </c>
       <c r="D8" t="n">
-        <v>3553400</v>
+        <v>8922000</v>
       </c>
       <c r="E8" t="n">
-        <v>3095320</v>
+        <v>9663680</v>
       </c>
       <c r="F8" t="n">
-        <v>1.15</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>35</v>
+        <v>28.07</v>
       </c>
       <c r="K8" t="n">
-        <v>37.54</v>
+        <v>27.96</v>
       </c>
       <c r="L8" t="n">
-        <v>-8.76</v>
+        <v>5.15</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1075,47 +1067,47 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>45.45</v>
+        <v>38.96</v>
       </c>
       <c r="S8" t="n">
-        <v>47.53</v>
+        <v>36.69</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.05</v>
+        <v>68.7</v>
       </c>
       <c r="C9" t="n">
-        <v>205.43</v>
+        <v>36.4</v>
       </c>
       <c r="D9" t="n">
-        <v>7071600</v>
+        <v>529900</v>
       </c>
       <c r="E9" t="n">
-        <v>9912855</v>
+        <v>942415</v>
       </c>
       <c r="F9" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1133,20 +1125,24 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>27.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>27.96</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
@@ -1155,14 +1151,14 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>41.61</v>
+        <v>31.79</v>
       </c>
       <c r="S9" t="n">
-        <v>37.37</v>
+        <v>28.8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1172,34 +1168,34 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>27.6</v>
       </c>
       <c r="C10" t="n">
-        <v>34.78</v>
+        <v>21.54</v>
       </c>
       <c r="D10" t="n">
-        <v>504100</v>
+        <v>780300</v>
       </c>
       <c r="E10" t="n">
-        <v>1087455</v>
+        <v>571660</v>
       </c>
       <c r="F10" t="n">
-        <v>0.46</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1209,28 +1205,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>67.09999999999999</v>
+        <v>26.35</v>
       </c>
       <c r="K10" t="n">
-        <v>67.09999999999999</v>
+        <v>29.9</v>
       </c>
       <c r="L10" t="n">
-        <v>2.83</v>
+        <v>-7.69</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
@@ -1239,14 +1231,14 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>30.9</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>27.16</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -1267,23 +1259,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="C11" t="n">
-        <v>74.27</v>
+        <v>100.15</v>
       </c>
       <c r="D11" t="n">
-        <v>6458200</v>
+        <v>8633500</v>
       </c>
       <c r="E11" t="n">
-        <v>6870825</v>
+        <v>6840505</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1303,7 +1295,7 @@
         <v>13.61</v>
       </c>
       <c r="L11" t="n">
-        <v>-15.5</v>
+        <v>-14.77</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1319,10 +1311,10 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>71.43000000000001</v>
+        <v>70.37</v>
       </c>
       <c r="S11" t="n">
-        <v>83.79000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1336,7 +1328,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -1347,19 +1339,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.95</v>
+        <v>13.6</v>
       </c>
       <c r="C12" t="n">
-        <v>141.36</v>
+        <v>137.94</v>
       </c>
       <c r="D12" t="n">
-        <v>10133300</v>
+        <v>10142400</v>
       </c>
       <c r="E12" t="n">
-        <v>8765315</v>
+        <v>8799285</v>
       </c>
       <c r="F12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1373,7 +1365,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1383,7 +1375,7 @@
         <v>15.85</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.99</v>
+        <v>-14.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1399,10 +1391,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>75.58</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>89.52</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1416,7 +1408,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -1427,23 +1419,23 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>39.75</v>
+        <v>26.78</v>
       </c>
       <c r="D13" t="n">
-        <v>593300</v>
+        <v>402100</v>
       </c>
       <c r="E13" t="n">
-        <v>444575</v>
+        <v>437990</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1463,7 +1455,7 @@
         <v>72.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.59</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1479,10 +1471,10 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>79.87</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>79.14</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1496,7 +1488,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -1507,28 +1499,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.95</v>
+        <v>30.6</v>
       </c>
       <c r="C14" t="n">
-        <v>262.51</v>
+        <v>149.33</v>
       </c>
       <c r="D14" t="n">
-        <v>8481600</v>
+        <v>4880200</v>
       </c>
       <c r="E14" t="n">
-        <v>7483410</v>
+        <v>7104830</v>
       </c>
       <c r="F14" t="n">
-        <v>1.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1543,7 +1535,7 @@
         <v>32.32</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.24</v>
+        <v>-5.32</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1552,31 +1544,35 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>70.31</v>
+        <v>61.76</v>
       </c>
       <c r="S14" t="n">
-        <v>53.44</v>
+        <v>55.69</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -1587,23 +1583,23 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.95</v>
+        <v>22.2</v>
       </c>
       <c r="C15" t="n">
-        <v>36.44</v>
+        <v>61.84</v>
       </c>
       <c r="D15" t="n">
-        <v>1660000</v>
+        <v>2785700</v>
       </c>
       <c r="E15" t="n">
-        <v>1279785</v>
+        <v>1348705</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1613,7 +1609,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1623,7 +1619,7 @@
         <v>24.1</v>
       </c>
       <c r="L15" t="n">
-        <v>-8.92</v>
+        <v>-7.88</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1639,14 +1635,14 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>69.52</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>64.5</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1656,34 +1652,34 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>DCL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.45</v>
+        <v>46.5</v>
       </c>
       <c r="C16" t="n">
-        <v>58.08</v>
+        <v>22.37</v>
       </c>
       <c r="D16" t="n">
-        <v>3530700</v>
+        <v>481100</v>
       </c>
       <c r="E16" t="n">
-        <v>1694805</v>
+        <v>698070</v>
       </c>
       <c r="F16" t="n">
-        <v>2.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1693,21 +1689,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16.32</v>
+        <v>44.65</v>
       </c>
       <c r="K16" t="n">
-        <v>17.77</v>
+        <v>44.05</v>
       </c>
       <c r="L16" t="n">
-        <v>-7.45</v>
+        <v>5.56</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1719,14 +1715,14 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>73.91</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
-        <v>64.56999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1736,30 +1732,30 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>47.95</v>
+        <v>35.4</v>
       </c>
       <c r="C17" t="n">
-        <v>25.48</v>
+        <v>51.83</v>
       </c>
       <c r="D17" t="n">
-        <v>531300</v>
+        <v>1464200</v>
       </c>
       <c r="E17" t="n">
-        <v>757230</v>
+        <v>2269905</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1768,7 +1764,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1777,73 +1773,77 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>44.65</v>
+        <v>32.2</v>
       </c>
       <c r="K17" t="n">
-        <v>44.05</v>
+        <v>36</v>
       </c>
       <c r="L17" t="n">
-        <v>8.85</v>
+        <v>-1.65</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>52.89</v>
+        <v>63.93</v>
       </c>
       <c r="S17" t="n">
-        <v>44.6</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>35.5</v>
+        <v>45.2</v>
       </c>
       <c r="C18" t="n">
-        <v>104.5</v>
+        <v>56.38</v>
       </c>
       <c r="D18" t="n">
-        <v>2943700</v>
+        <v>1247300</v>
       </c>
       <c r="E18" t="n">
-        <v>2422035</v>
+        <v>1543665</v>
       </c>
       <c r="F18" t="n">
-        <v>1.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1857,20 +1857,24 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32.2</v>
+        <v>39.83</v>
       </c>
       <c r="K18" t="n">
-        <v>36.04</v>
+        <v>39.83</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5</v>
+        <v>13.48</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
@@ -1879,14 +1883,14 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>70.83</v>
+        <v>34.73</v>
       </c>
       <c r="S18" t="n">
-        <v>86.25</v>
+        <v>34.49</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1896,34 +1900,34 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46.2</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>57.98</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>1254900</v>
+        <v>7136700</v>
       </c>
       <c r="E19" t="n">
-        <v>1584040</v>
+        <v>5007540</v>
       </c>
       <c r="F19" t="n">
-        <v>0.79</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1933,33 +1937,25 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>39.83</v>
+        <v>9.82</v>
       </c>
       <c r="K19" t="n">
-        <v>39.83</v>
+        <v>11.52</v>
       </c>
       <c r="L19" t="n">
-        <v>15.99</v>
+        <v>-13.67</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1967,14 +1963,14 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>42.21</v>
+        <v>75.19</v>
       </c>
       <c r="S19" t="n">
-        <v>44.11</v>
+        <v>64.12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -1984,39 +1980,39 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.15</v>
+        <v>21.7</v>
       </c>
       <c r="C20" t="n">
-        <v>53.2</v>
+        <v>40.41</v>
       </c>
       <c r="D20" t="n">
-        <v>5241700</v>
+        <v>1862000</v>
       </c>
       <c r="E20" t="n">
-        <v>4929445</v>
+        <v>2199205</v>
       </c>
       <c r="F20" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2025,13 +2021,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>9.82</v>
+        <v>22.18</v>
       </c>
       <c r="K20" t="n">
-        <v>11.52</v>
+        <v>23.76</v>
       </c>
       <c r="L20" t="n">
-        <v>-11.93</v>
+        <v>-8.67</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2047,51 +2043,51 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>91.23999999999999</v>
+        <v>50.94</v>
       </c>
       <c r="S20" t="n">
-        <v>73.81999999999999</v>
+        <v>45.53</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DPG</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30.8</v>
+        <v>14.7</v>
       </c>
       <c r="C21" t="n">
-        <v>32.6</v>
+        <v>27.9</v>
       </c>
       <c r="D21" t="n">
-        <v>1058400</v>
+        <v>1898200</v>
       </c>
       <c r="E21" t="n">
-        <v>453140</v>
+        <v>1807950</v>
       </c>
       <c r="F21" t="n">
-        <v>2.34</v>
+        <v>1.05</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2101,21 +2097,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>28.82</v>
+        <v>14.38</v>
       </c>
       <c r="K21" t="n">
-        <v>35.3</v>
+        <v>14.34</v>
       </c>
       <c r="L21" t="n">
-        <v>-12.76</v>
+        <v>2.55</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2127,14 +2123,14 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>90.52</v>
+        <v>31.91</v>
       </c>
       <c r="S21" t="n">
-        <v>90.73999999999999</v>
+        <v>34.88</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2144,30 +2140,30 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.65</v>
+        <v>10.1</v>
       </c>
       <c r="C22" t="n">
-        <v>51.14</v>
+        <v>104.17</v>
       </c>
       <c r="D22" t="n">
-        <v>2362200</v>
+        <v>10314100</v>
       </c>
       <c r="E22" t="n">
-        <v>2287590</v>
+        <v>9299465</v>
       </c>
       <c r="F22" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2185,13 +2181,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>22.18</v>
+        <v>10.73</v>
       </c>
       <c r="K22" t="n">
-        <v>23.94</v>
+        <v>11.89</v>
       </c>
       <c r="L22" t="n">
-        <v>-9.58</v>
+        <v>-15.02</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2207,10 +2203,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>50.94</v>
+        <v>54.77</v>
       </c>
       <c r="S22" t="n">
-        <v>43.41</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2224,34 +2220,34 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>DXS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10.45</v>
+        <v>5.2</v>
       </c>
       <c r="C23" t="n">
-        <v>65.61</v>
+        <v>22.13</v>
       </c>
       <c r="D23" t="n">
-        <v>6278200</v>
+        <v>4256700</v>
       </c>
       <c r="E23" t="n">
-        <v>9536255</v>
+        <v>1999885</v>
       </c>
       <c r="F23" t="n">
-        <v>0.66</v>
+        <v>2.13</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2265,13 +2261,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10.73</v>
+        <v>5.52</v>
       </c>
       <c r="K23" t="n">
-        <v>11.89</v>
+        <v>6.62</v>
       </c>
       <c r="L23" t="n">
-        <v>-12.07</v>
+        <v>-21.51</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2280,21 +2276,17 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>63.74</v>
+        <v>63.72</v>
       </c>
       <c r="S23" t="n">
-        <v>66.39</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2308,7 +2300,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2319,19 +2311,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.85</v>
+        <v>17.15</v>
       </c>
       <c r="C24" t="n">
-        <v>358.13</v>
+        <v>203.75</v>
       </c>
       <c r="D24" t="n">
-        <v>20063400</v>
+        <v>11880600</v>
       </c>
       <c r="E24" t="n">
-        <v>4456890</v>
+        <v>4828265</v>
       </c>
       <c r="F24" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2340,7 +2332,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2355,7 +2347,7 @@
         <v>19.58</v>
       </c>
       <c r="L24" t="n">
-        <v>-8.81</v>
+        <v>-12.39</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2367,28 +2359,28 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 4.5x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>79.59</v>
+        <v>61.9</v>
       </c>
       <c r="S24" t="n">
-        <v>69.69</v>
+        <v>61.27</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2399,23 +2391,23 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C25" t="n">
-        <v>404.16</v>
+        <v>565.87</v>
       </c>
       <c r="D25" t="n">
-        <v>7090600</v>
+        <v>10104800</v>
       </c>
       <c r="E25" t="n">
-        <v>5682025</v>
+        <v>5929830</v>
       </c>
       <c r="F25" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2435,7 +2427,7 @@
         <v>63.22</v>
       </c>
       <c r="L25" t="n">
-        <v>-9.84</v>
+        <v>-11.42</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2451,10 +2443,10 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>23.66</v>
+        <v>25</v>
       </c>
       <c r="S25" t="n">
-        <v>36.8</v>
+        <v>36.32</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2468,7 +2460,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2479,19 +2471,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" t="n">
-        <v>70.42</v>
+        <v>36.63</v>
       </c>
       <c r="D26" t="n">
-        <v>469500</v>
+        <v>247500</v>
       </c>
       <c r="E26" t="n">
-        <v>623825</v>
+        <v>613300</v>
       </c>
       <c r="F26" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2515,7 +2507,7 @@
         <v>127.5</v>
       </c>
       <c r="L26" t="n">
-        <v>17.65</v>
+        <v>16.08</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2532,7 +2524,11 @@
           <t>⚠️</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>-</t>
@@ -2542,7 +2538,7 @@
         <v>54.75</v>
       </c>
       <c r="S26" t="n">
-        <v>65.37</v>
+        <v>60.81</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2556,7 +2552,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2567,23 +2563,23 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78.3</v>
+        <v>80.5</v>
       </c>
       <c r="C27" t="n">
-        <v>60.68</v>
+        <v>139.98</v>
       </c>
       <c r="D27" t="n">
-        <v>775000</v>
+        <v>1738900</v>
       </c>
       <c r="E27" t="n">
-        <v>952220</v>
+        <v>981260</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2597,13 +2593,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>76.48</v>
+        <v>76.62</v>
       </c>
       <c r="K27" t="n">
         <v>77.69</v>
       </c>
       <c r="L27" t="n">
-        <v>0.78</v>
+        <v>3.61</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2619,10 +2615,10 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>47.45</v>
+        <v>53.85</v>
       </c>
       <c r="S27" t="n">
-        <v>54.79</v>
+        <v>64.2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2636,7 +2632,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2647,19 +2643,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>183.35</v>
+        <v>167.72</v>
       </c>
       <c r="D28" t="n">
-        <v>2528900</v>
+        <v>2382400</v>
       </c>
       <c r="E28" t="n">
-        <v>1487265</v>
+        <v>1528230</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2683,7 +2679,7 @@
         <v>95.83</v>
       </c>
       <c r="L28" t="n">
-        <v>-24.35</v>
+        <v>-26.54</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2699,10 +2695,10 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>53.13</v>
+        <v>50.25</v>
       </c>
       <c r="S28" t="n">
-        <v>54.11</v>
+        <v>50.31</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2727,23 +2723,23 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28.75</v>
+        <v>28.8</v>
       </c>
       <c r="C29" t="n">
-        <v>50.39</v>
+        <v>118.35</v>
       </c>
       <c r="D29" t="n">
-        <v>1752800</v>
+        <v>4109500</v>
       </c>
       <c r="E29" t="n">
-        <v>1340250</v>
+        <v>1483250</v>
       </c>
       <c r="F29" t="n">
-        <v>1.31</v>
+        <v>2.77</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2763,7 +2759,7 @@
         <v>29.42</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.29</v>
+        <v>-2.12</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2775,14 +2771,14 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.8x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>54.02</v>
+        <v>52.38</v>
       </c>
       <c r="S29" t="n">
-        <v>49.33</v>
+        <v>62.55</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2796,7 +2792,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2807,19 +2803,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24.1</v>
+        <v>23.3</v>
       </c>
       <c r="C30" t="n">
-        <v>246.48</v>
+        <v>262</v>
       </c>
       <c r="D30" t="n">
-        <v>10227200</v>
+        <v>11244600</v>
       </c>
       <c r="E30" t="n">
-        <v>7294120</v>
+        <v>7561755</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2828,7 +2824,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2843,7 +2839,7 @@
         <v>28.58</v>
       </c>
       <c r="L30" t="n">
-        <v>-15.66</v>
+        <v>-18.46</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2859,24 +2855,24 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>59.38</v>
+        <v>53.27</v>
       </c>
       <c r="S30" t="n">
-        <v>62.35</v>
+        <v>59.79</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2887,19 +2883,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>57.1</v>
+        <v>55.3</v>
       </c>
       <c r="C31" t="n">
-        <v>108.21</v>
+        <v>116.5</v>
       </c>
       <c r="D31" t="n">
-        <v>1895100</v>
+        <v>2106700</v>
       </c>
       <c r="E31" t="n">
-        <v>1518730</v>
+        <v>1595240</v>
       </c>
       <c r="F31" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2923,7 +2919,7 @@
         <v>51.28</v>
       </c>
       <c r="L31" t="n">
-        <v>11.34</v>
+        <v>7.83</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2943,10 +2939,10 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>73.70999999999999</v>
+        <v>62.99</v>
       </c>
       <c r="S31" t="n">
-        <v>80.40000000000001</v>
+        <v>78.31</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2960,7 +2956,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -2971,19 +2967,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.75</v>
+        <v>32.05</v>
       </c>
       <c r="C32" t="n">
-        <v>50.33</v>
+        <v>49.84</v>
       </c>
       <c r="D32" t="n">
-        <v>1585300</v>
+        <v>1555200</v>
       </c>
       <c r="E32" t="n">
-        <v>2475770</v>
+        <v>2408115</v>
       </c>
       <c r="F32" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3007,7 +3003,7 @@
         <v>32.78</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.13</v>
+        <v>-2.21</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -3023,10 +3019,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>41.44</v>
+        <v>43.48</v>
       </c>
       <c r="S32" t="n">
-        <v>50.78</v>
+        <v>58.26</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3040,7 +3036,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -3051,23 +3047,23 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="C33" t="n">
-        <v>26.91</v>
+        <v>52.54</v>
       </c>
       <c r="D33" t="n">
-        <v>524600</v>
+        <v>1020200</v>
       </c>
       <c r="E33" t="n">
-        <v>1056585</v>
+        <v>1007130</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>1.01</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3087,7 +3083,7 @@
         <v>49.55</v>
       </c>
       <c r="L33" t="n">
-        <v>3.53</v>
+        <v>3.94</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3103,10 +3099,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>49.15</v>
+        <v>54.55</v>
       </c>
       <c r="S33" t="n">
-        <v>57.55</v>
+        <v>65</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3120,7 +3116,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -3131,23 +3127,23 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>24.15</v>
       </c>
       <c r="C34" t="n">
-        <v>87.04000000000001</v>
+        <v>127.71</v>
       </c>
       <c r="D34" t="n">
-        <v>3626600</v>
+        <v>5288300</v>
       </c>
       <c r="E34" t="n">
-        <v>2709910</v>
+        <v>2731205</v>
       </c>
       <c r="F34" t="n">
-        <v>1.34</v>
+        <v>1.94</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3167,7 +3163,7 @@
         <v>24.8</v>
       </c>
       <c r="L34" t="n">
-        <v>-3.23</v>
+        <v>-2.62</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3183,10 +3179,10 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>56.67</v>
+        <v>57.14</v>
       </c>
       <c r="S34" t="n">
-        <v>45.29</v>
+        <v>57.45</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3200,7 +3196,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -3211,19 +3207,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.55</v>
+        <v>22.2</v>
       </c>
       <c r="C35" t="n">
-        <v>272.94</v>
+        <v>245.3</v>
       </c>
       <c r="D35" t="n">
-        <v>12103900</v>
+        <v>11049600</v>
       </c>
       <c r="E35" t="n">
-        <v>16255645</v>
+        <v>16295225</v>
       </c>
       <c r="F35" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3247,7 +3243,7 @@
         <v>21.13</v>
       </c>
       <c r="L35" t="n">
-        <v>6.72</v>
+        <v>5.06</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3267,10 +3263,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>64.56</v>
+        <v>58.42</v>
       </c>
       <c r="S35" t="n">
-        <v>66.5</v>
+        <v>67.09</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3284,7 +3280,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -3295,23 +3291,23 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11.8</v>
+        <v>11.85</v>
       </c>
       <c r="C36" t="n">
-        <v>37.87</v>
+        <v>23</v>
       </c>
       <c r="D36" t="n">
-        <v>3209700</v>
+        <v>1941200</v>
       </c>
       <c r="E36" t="n">
-        <v>1582150</v>
+        <v>1597420</v>
       </c>
       <c r="F36" t="n">
-        <v>2.03</v>
+        <v>1.22</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3331,7 +3327,7 @@
         <v>13.34</v>
       </c>
       <c r="L36" t="n">
-        <v>-11.58</v>
+        <v>-11.2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3347,10 +3343,10 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>91.67</v>
+        <v>91.87</v>
       </c>
       <c r="S36" t="n">
-        <v>78.55</v>
+        <v>88.67</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3364,7 +3360,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -3375,19 +3371,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9.66</v>
+        <v>9.48</v>
       </c>
       <c r="C37" t="n">
-        <v>29.39</v>
+        <v>34.87</v>
       </c>
       <c r="D37" t="n">
-        <v>3042100</v>
+        <v>3678200</v>
       </c>
       <c r="E37" t="n">
-        <v>3028800</v>
+        <v>3048360</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3396,7 +3392,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3411,7 +3407,7 @@
         <v>10.54</v>
       </c>
       <c r="L37" t="n">
-        <v>-8.35</v>
+        <v>-10.06</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3427,24 +3423,24 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>70.92</v>
+        <v>62.5</v>
       </c>
       <c r="S37" t="n">
-        <v>68.45</v>
+        <v>61.34</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -3455,19 +3451,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.95</v>
+        <v>20.9</v>
       </c>
       <c r="C38" t="n">
-        <v>271.28</v>
+        <v>218.99</v>
       </c>
       <c r="D38" t="n">
-        <v>12949000</v>
+        <v>10478100</v>
       </c>
       <c r="E38" t="n">
-        <v>18984740</v>
+        <v>18299405</v>
       </c>
       <c r="F38" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3491,7 +3487,7 @@
         <v>22.94</v>
       </c>
       <c r="L38" t="n">
-        <v>-8.69</v>
+        <v>-8.91</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3511,10 +3507,10 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>57.14</v>
+        <v>56.25</v>
       </c>
       <c r="S38" t="n">
-        <v>66.28</v>
+        <v>68.03</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -3528,54 +3524,54 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11.05</v>
+        <v>12.6</v>
       </c>
       <c r="C39" t="n">
-        <v>40.36</v>
+        <v>21.86</v>
       </c>
       <c r="D39" t="n">
-        <v>3652600</v>
+        <v>1734800</v>
       </c>
       <c r="E39" t="n">
-        <v>3138060</v>
+        <v>2022825</v>
       </c>
       <c r="F39" t="n">
-        <v>1.16</v>
+        <v>0.86</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>10.48</v>
+        <v>13.3</v>
       </c>
       <c r="K39" t="n">
-        <v>11.35</v>
+        <v>14.15</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.64</v>
+        <v>-10.95</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3591,75 +3587,75 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>78.38</v>
+        <v>68.42</v>
       </c>
       <c r="S39" t="n">
-        <v>72.87</v>
+        <v>71.94</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12.5</v>
+        <v>36.5</v>
       </c>
       <c r="C40" t="n">
-        <v>34.6</v>
+        <v>46.3</v>
       </c>
       <c r="D40" t="n">
-        <v>2768100</v>
+        <v>1268500</v>
       </c>
       <c r="E40" t="n">
-        <v>2002995</v>
+        <v>1282235</v>
       </c>
       <c r="F40" t="n">
-        <v>1.38</v>
+        <v>0.99</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>13.3</v>
+        <v>32.95</v>
       </c>
       <c r="K40" t="n">
-        <v>14.25</v>
+        <v>35.67</v>
       </c>
       <c r="L40" t="n">
-        <v>-12.28</v>
+        <v>2.33</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3671,51 +3667,51 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>63.16</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="S40" t="n">
-        <v>60.03</v>
+        <v>72.39</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>KBC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36</v>
+        <v>26.8</v>
       </c>
       <c r="C41" t="n">
-        <v>48.3</v>
+        <v>31.19</v>
       </c>
       <c r="D41" t="n">
-        <v>1341700</v>
+        <v>1163800</v>
       </c>
       <c r="E41" t="n">
-        <v>1295215</v>
+        <v>1259265</v>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3725,21 +3721,21 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>32.55</v>
+        <v>26.55</v>
       </c>
       <c r="K41" t="n">
-        <v>35.98</v>
+        <v>29.68</v>
       </c>
       <c r="L41" t="n">
-        <v>0.07000000000000001</v>
+        <v>-9.69</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3751,10 +3747,10 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>64.09999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="S41" t="n">
-        <v>70.16</v>
+        <v>86.19</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3768,54 +3764,54 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KBC</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27</v>
+        <v>14.75</v>
       </c>
       <c r="C42" t="n">
-        <v>20.84</v>
+        <v>73.48</v>
       </c>
       <c r="D42" t="n">
-        <v>771900</v>
+        <v>4981400</v>
       </c>
       <c r="E42" t="n">
-        <v>1272305</v>
+        <v>4446450</v>
       </c>
       <c r="F42" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>26.55</v>
+        <v>15.04</v>
       </c>
       <c r="K42" t="n">
-        <v>30.05</v>
+        <v>18.38</v>
       </c>
       <c r="L42" t="n">
-        <v>-10.15</v>
+        <v>-19.77</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3824,67 +3820,63 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>91.84</v>
+        <v>71.19</v>
       </c>
       <c r="S42" t="n">
-        <v>75.84</v>
+        <v>75.94</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.1</v>
+        <v>39.4</v>
       </c>
       <c r="C43" t="n">
-        <v>119.07</v>
+        <v>66.73</v>
       </c>
       <c r="D43" t="n">
-        <v>7885300</v>
+        <v>1693700</v>
       </c>
       <c r="E43" t="n">
-        <v>4500095</v>
+        <v>2124070</v>
       </c>
       <c r="F43" t="n">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3893,13 +3885,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>15.04</v>
+        <v>46.6</v>
       </c>
       <c r="K43" t="n">
-        <v>18.43</v>
+        <v>47.85</v>
       </c>
       <c r="L43" t="n">
-        <v>-18.07</v>
+        <v>-17.66</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3915,71 +3907,71 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>76.64</v>
+        <v>33.46</v>
       </c>
       <c r="S43" t="n">
-        <v>76.09999999999999</v>
+        <v>40.28</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>40.4</v>
+        <v>19.55</v>
       </c>
       <c r="C44" t="n">
-        <v>139.82</v>
+        <v>191.19</v>
       </c>
       <c r="D44" t="n">
-        <v>3460900</v>
+        <v>9779700</v>
       </c>
       <c r="E44" t="n">
-        <v>2106095</v>
+        <v>11687310</v>
       </c>
       <c r="F44" t="n">
-        <v>1.64</v>
+        <v>0.84</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>46.6</v>
+        <v>19.49</v>
       </c>
       <c r="K44" t="n">
-        <v>47.85</v>
+        <v>19.7</v>
       </c>
       <c r="L44" t="n">
-        <v>-15.57</v>
+        <v>-0.76</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3995,47 +3987,47 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>40.37</v>
+        <v>56.86</v>
       </c>
       <c r="S44" t="n">
-        <v>49.71</v>
+        <v>53.52</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.8</v>
+        <v>15.4</v>
       </c>
       <c r="C45" t="n">
-        <v>215.84</v>
+        <v>30.48</v>
       </c>
       <c r="D45" t="n">
-        <v>10901100</v>
+        <v>1979000</v>
       </c>
       <c r="E45" t="n">
-        <v>11694455</v>
+        <v>2831430</v>
       </c>
       <c r="F45" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4044,78 +4036,82 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>19.49</v>
+        <v>16.02</v>
       </c>
       <c r="K45" t="n">
-        <v>19.7</v>
+        <v>17.43</v>
       </c>
       <c r="L45" t="n">
-        <v>0.51</v>
+        <v>-11.67</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>63.83</v>
+        <v>50</v>
       </c>
       <c r="S45" t="n">
-        <v>51.39</v>
+        <v>57.82</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.7</v>
+        <v>139.9</v>
       </c>
       <c r="C46" t="n">
-        <v>45.09</v>
+        <v>24.48</v>
       </c>
       <c r="D46" t="n">
-        <v>2871900</v>
+        <v>175000</v>
       </c>
       <c r="E46" t="n">
-        <v>2973375</v>
+        <v>622005</v>
       </c>
       <c r="F46" t="n">
-        <v>0.97</v>
+        <v>0.28</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4124,78 +4120,82 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>16.02</v>
+        <v>138.57</v>
       </c>
       <c r="K46" t="n">
-        <v>17.43</v>
+        <v>134.54</v>
       </c>
       <c r="L46" t="n">
-        <v>-9.949999999999999</v>
+        <v>3.99</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>58.06</v>
+        <v>44.86</v>
       </c>
       <c r="S46" t="n">
-        <v>53.08</v>
+        <v>34.64</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>141.9</v>
+        <v>15.5</v>
       </c>
       <c r="C47" t="n">
-        <v>73.65000000000001</v>
+        <v>100.93</v>
       </c>
       <c r="D47" t="n">
-        <v>519000</v>
+        <v>6511700</v>
       </c>
       <c r="E47" t="n">
-        <v>626625</v>
+        <v>10537480</v>
       </c>
       <c r="F47" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4213,69 +4213,77 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>138.57</v>
+        <v>13.88</v>
       </c>
       <c r="K47" t="n">
-        <v>134.54</v>
+        <v>12.99</v>
       </c>
       <c r="L47" t="n">
-        <v>5.47</v>
+        <v>19.32</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>59.79</v>
+        <v>78.95</v>
       </c>
       <c r="S47" t="n">
-        <v>38.45</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15.5</v>
+        <v>73</v>
       </c>
       <c r="C48" t="n">
-        <v>124.35</v>
+        <v>356.6</v>
       </c>
       <c r="D48" t="n">
-        <v>8022500</v>
+        <v>4884900</v>
       </c>
       <c r="E48" t="n">
-        <v>10699300</v>
+        <v>5489585</v>
       </c>
       <c r="F48" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4284,7 +4292,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4293,25 +4301,21 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>13.86</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>12.96</v>
+        <v>72.05</v>
       </c>
       <c r="L48" t="n">
-        <v>19.55</v>
+        <v>1.32</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4319,47 +4323,47 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>83.33</v>
+        <v>53.52</v>
       </c>
       <c r="S48" t="n">
-        <v>87.83</v>
+        <v>64.19</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>74.2</v>
+        <v>63.7</v>
       </c>
       <c r="C49" t="n">
-        <v>348.82</v>
+        <v>42.23</v>
       </c>
       <c r="D49" t="n">
-        <v>4701100</v>
+        <v>662900</v>
       </c>
       <c r="E49" t="n">
-        <v>5470510</v>
+        <v>2081110</v>
       </c>
       <c r="F49" t="n">
-        <v>0.86</v>
+        <v>0.32</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4377,21 +4381,29 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>68.90000000000001</v>
+        <v>50.57</v>
       </c>
       <c r="K49" t="n">
-        <v>72.05</v>
+        <v>50.57</v>
       </c>
       <c r="L49" t="n">
-        <v>2.98</v>
+        <v>25.96</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4399,14 +4411,14 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>60.58</v>
+        <v>55.39</v>
       </c>
       <c r="S49" t="n">
-        <v>70.66</v>
+        <v>50.2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -4416,30 +4428,30 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63.6</v>
+        <v>74.8</v>
       </c>
       <c r="C50" t="n">
-        <v>76.92</v>
+        <v>126.33</v>
       </c>
       <c r="D50" t="n">
-        <v>1209500</v>
+        <v>1688900</v>
       </c>
       <c r="E50" t="n">
-        <v>2181935</v>
+        <v>2776265</v>
       </c>
       <c r="F50" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4457,40 +4469,36 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>50.57</v>
+        <v>69.02</v>
       </c>
       <c r="K50" t="n">
-        <v>50.57</v>
+        <v>72.83</v>
       </c>
       <c r="L50" t="n">
-        <v>25.77</v>
+        <v>2.7</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>58.06</v>
+        <v>49.04</v>
       </c>
       <c r="S50" t="n">
-        <v>54.7</v>
+        <v>53.03</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4504,34 +4512,34 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>75.5</v>
+        <v>12.55</v>
       </c>
       <c r="C51" t="n">
-        <v>160.61</v>
+        <v>33.8</v>
       </c>
       <c r="D51" t="n">
-        <v>2127300</v>
+        <v>2693000</v>
       </c>
       <c r="E51" t="n">
-        <v>2802570</v>
+        <v>2452050</v>
       </c>
       <c r="F51" t="n">
-        <v>0.76</v>
+        <v>1.1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4545,13 +4553,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>69.02</v>
+        <v>12.05</v>
       </c>
       <c r="K51" t="n">
-        <v>73.36</v>
+        <v>12.25</v>
       </c>
       <c r="L51" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4567,10 +4575,10 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>59.22</v>
+        <v>41.86</v>
       </c>
       <c r="S51" t="n">
-        <v>63</v>
+        <v>53.69</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -4584,34 +4592,34 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.6</v>
+        <v>11.8</v>
       </c>
       <c r="C52" t="n">
-        <v>52.51</v>
+        <v>37.82</v>
       </c>
       <c r="D52" t="n">
-        <v>4167200</v>
+        <v>3204900</v>
       </c>
       <c r="E52" t="n">
-        <v>2404815</v>
+        <v>3696110</v>
       </c>
       <c r="F52" t="n">
-        <v>1.73</v>
+        <v>0.87</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4625,13 +4633,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>12.05</v>
+        <v>10.52</v>
       </c>
       <c r="K52" t="n">
-        <v>12.25</v>
+        <v>11.41</v>
       </c>
       <c r="L52" t="n">
-        <v>2.86</v>
+        <v>3.42</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4647,14 +4655,14 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>52</v>
+        <v>81.77</v>
       </c>
       <c r="S52" t="n">
-        <v>55.26</v>
+        <v>92.52</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -4664,34 +4672,34 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>NLG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C53" t="n">
-        <v>70.11</v>
+        <v>36.26</v>
       </c>
       <c r="D53" t="n">
-        <v>5842600</v>
+        <v>1576700</v>
       </c>
       <c r="E53" t="n">
-        <v>3626080</v>
+        <v>1547630</v>
       </c>
       <c r="F53" t="n">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4701,21 +4709,21 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>10.52</v>
+        <v>22.55</v>
       </c>
       <c r="K53" t="n">
-        <v>11.41</v>
+        <v>23.78</v>
       </c>
       <c r="L53" t="n">
-        <v>5.17</v>
+        <v>-3.26</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4727,10 +4735,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>84.25</v>
+        <v>69.62</v>
       </c>
       <c r="S53" t="n">
-        <v>96.55</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4744,54 +4752,54 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NLG</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>23.3</v>
+        <v>10.55</v>
       </c>
       <c r="C54" t="n">
-        <v>56.98</v>
+        <v>303.45</v>
       </c>
       <c r="D54" t="n">
-        <v>2445300</v>
+        <v>28763200</v>
       </c>
       <c r="E54" t="n">
-        <v>1582055</v>
+        <v>28795899</v>
       </c>
       <c r="F54" t="n">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>22.55</v>
+        <v>11.88</v>
       </c>
       <c r="K54" t="n">
-        <v>23.88</v>
+        <v>14.5</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.41</v>
+        <v>-27.22</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4807,75 +4815,75 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>70.51000000000001</v>
+        <v>54.05</v>
       </c>
       <c r="S54" t="n">
-        <v>68.28</v>
+        <v>54.42</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="C55" t="n">
-        <v>128.29</v>
+        <v>52.11</v>
       </c>
       <c r="D55" t="n">
-        <v>12102900</v>
+        <v>4737200</v>
       </c>
       <c r="E55" t="n">
-        <v>27947159</v>
+        <v>1724000</v>
       </c>
       <c r="F55" t="n">
-        <v>0.43</v>
+        <v>2.75</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>11.88</v>
+        <v>10.46</v>
       </c>
       <c r="K55" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="L55" t="n">
-        <v>-26.87</v>
+        <v>4.81</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4883,55 +4891,55 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>51.28</v>
+        <v>92.44</v>
       </c>
       <c r="S55" t="n">
-        <v>54.48</v>
+        <v>78.5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10.8</v>
+        <v>13.3</v>
       </c>
       <c r="C56" t="n">
-        <v>70.01000000000001</v>
+        <v>21.08</v>
       </c>
       <c r="D56" t="n">
-        <v>6482500</v>
+        <v>1584700</v>
       </c>
       <c r="E56" t="n">
-        <v>1548800</v>
+        <v>1662445</v>
       </c>
       <c r="F56" t="n">
-        <v>4.19</v>
+        <v>0.95</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4941,21 +4949,21 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>10.46</v>
+        <v>13.2</v>
       </c>
       <c r="K56" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="L56" t="n">
-        <v>2.91</v>
+        <v>-4.97</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4963,18 +4971,18 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 4.2x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>90</v>
+        <v>53.85</v>
       </c>
       <c r="S56" t="n">
-        <v>66.84</v>
+        <v>66.16</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -4984,58 +4992,58 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>13.1</v>
+        <v>15.5</v>
       </c>
       <c r="C57" t="n">
-        <v>20.36</v>
+        <v>138.29</v>
       </c>
       <c r="D57" t="n">
-        <v>1553900</v>
+        <v>8922000</v>
       </c>
       <c r="E57" t="n">
-        <v>1694055</v>
+        <v>3750755</v>
       </c>
       <c r="F57" t="n">
-        <v>0.92</v>
+        <v>2.38</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>13.2</v>
+        <v>14.28</v>
       </c>
       <c r="K57" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.4</v>
+        <v>8.77</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -5047,10 +5055,10 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>48</v>
+        <v>80.28</v>
       </c>
       <c r="S57" t="n">
-        <v>58.18</v>
+        <v>80.89</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5059,35 +5067,35 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="C58" t="n">
-        <v>180.83</v>
+        <v>34.95</v>
       </c>
       <c r="D58" t="n">
-        <v>11301600</v>
+        <v>1910000</v>
       </c>
       <c r="E58" t="n">
-        <v>3382455</v>
+        <v>938440</v>
       </c>
       <c r="F58" t="n">
-        <v>3.34</v>
+        <v>2.04</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5096,26 +5104,26 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>14.28</v>
+        <v>19.55</v>
       </c>
       <c r="K58" t="n">
-        <v>14.25</v>
+        <v>21.66</v>
       </c>
       <c r="L58" t="n">
-        <v>12.28</v>
+        <v>-15.49</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5127,10 +5135,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>93.55</v>
+        <v>45.59</v>
       </c>
       <c r="S58" t="n">
-        <v>91.92</v>
+        <v>37.54</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5139,35 +5147,35 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>18.1</v>
+        <v>11.7</v>
       </c>
       <c r="C59" t="n">
-        <v>20.22</v>
+        <v>77.77</v>
       </c>
       <c r="D59" t="n">
-        <v>1117000</v>
+        <v>6647300</v>
       </c>
       <c r="E59" t="n">
-        <v>866865</v>
+        <v>5072250</v>
       </c>
       <c r="F59" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -5176,7 +5184,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5185,13 +5193,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>19.55</v>
+        <v>11.68</v>
       </c>
       <c r="K59" t="n">
-        <v>21.66</v>
+        <v>13.82</v>
       </c>
       <c r="L59" t="n">
-        <v>-16.42</v>
+        <v>-15.37</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5207,51 +5215,51 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>40.3</v>
+        <v>62.79</v>
       </c>
       <c r="S59" t="n">
-        <v>35.86</v>
+        <v>74.42</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>12.15</v>
+        <v>55</v>
       </c>
       <c r="C60" t="n">
-        <v>102.12</v>
+        <v>24.79</v>
       </c>
       <c r="D60" t="n">
-        <v>8405300</v>
+        <v>450700</v>
       </c>
       <c r="E60" t="n">
-        <v>5114055</v>
+        <v>714815</v>
       </c>
       <c r="F60" t="n">
-        <v>1.64</v>
+        <v>0.63</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5261,25 +5269,29 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>11.68</v>
+        <v>45.75</v>
       </c>
       <c r="K60" t="n">
-        <v>13.82</v>
+        <v>44.22</v>
       </c>
       <c r="L60" t="n">
-        <v>-12.12</v>
+        <v>24.39</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5287,14 +5299,14 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>77.14</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="S60" t="n">
-        <v>77</v>
+        <v>62.3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -5304,34 +5316,34 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>56.7</v>
+        <v>46.3</v>
       </c>
       <c r="C61" t="n">
-        <v>83.40000000000001</v>
+        <v>21.39</v>
       </c>
       <c r="D61" t="n">
-        <v>1470900</v>
+        <v>461900</v>
       </c>
       <c r="E61" t="n">
-        <v>734905</v>
+        <v>334510</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5345,25 +5357,21 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>45.2</v>
+        <v>43.2</v>
       </c>
       <c r="K61" t="n">
-        <v>44.22</v>
+        <v>42.5</v>
       </c>
       <c r="L61" t="n">
-        <v>28.24</v>
+        <v>8.94</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
@@ -5371,14 +5379,14 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>70.31</v>
+        <v>35.19</v>
       </c>
       <c r="S61" t="n">
-        <v>60.7</v>
+        <v>26.4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -5388,7 +5396,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -5399,19 +5407,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>35.45</v>
+        <v>35.65</v>
       </c>
       <c r="C62" t="n">
-        <v>102.06</v>
+        <v>97.39</v>
       </c>
       <c r="D62" t="n">
-        <v>2879000</v>
+        <v>2731800</v>
       </c>
       <c r="E62" t="n">
-        <v>3976310</v>
+        <v>3970160</v>
       </c>
       <c r="F62" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -5435,7 +5443,7 @@
         <v>38.08</v>
       </c>
       <c r="L62" t="n">
-        <v>-6.92</v>
+        <v>-6.39</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5451,10 +5459,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>49.62</v>
+        <v>45.53</v>
       </c>
       <c r="S62" t="n">
-        <v>66.37</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5468,7 +5476,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -5482,20 +5490,20 @@
         <v>17.45</v>
       </c>
       <c r="C63" t="n">
-        <v>422.47</v>
+        <v>101.86</v>
       </c>
       <c r="D63" t="n">
-        <v>24210400</v>
+        <v>5837200</v>
       </c>
       <c r="E63" t="n">
-        <v>15856895</v>
+        <v>16042905</v>
       </c>
       <c r="F63" t="n">
-        <v>1.53</v>
+        <v>0.36</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5531,10 +5539,10 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>33.2</v>
+        <v>37.73</v>
       </c>
       <c r="S63" t="n">
-        <v>26.75</v>
+        <v>28.34</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -5548,7 +5556,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -5562,16 +5570,16 @@
         <v>12.55</v>
       </c>
       <c r="C64" t="n">
-        <v>52.07</v>
+        <v>33.65</v>
       </c>
       <c r="D64" t="n">
-        <v>4148700</v>
+        <v>2681100</v>
       </c>
       <c r="E64" t="n">
-        <v>5828665</v>
+        <v>5669935</v>
       </c>
       <c r="F64" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5614,7 +5622,7 @@
         <v>45.83</v>
       </c>
       <c r="S64" t="n">
-        <v>38.36</v>
+        <v>43.18</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5628,7 +5636,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
@@ -5639,28 +5647,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>18.7</v>
+        <v>18.75</v>
       </c>
       <c r="C65" t="n">
-        <v>87.66</v>
+        <v>134.48</v>
       </c>
       <c r="D65" t="n">
-        <v>4687800</v>
+        <v>7172100</v>
       </c>
       <c r="E65" t="n">
-        <v>3659255</v>
+        <v>3773485</v>
       </c>
       <c r="F65" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5669,13 +5677,13 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>18.88</v>
+        <v>18.92</v>
       </c>
       <c r="K65" t="n">
         <v>19.43</v>
       </c>
       <c r="L65" t="n">
-        <v>-3.76</v>
+        <v>-3.5</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -5691,47 +5699,47 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>61.97</v>
+        <v>52.63</v>
       </c>
       <c r="S65" t="n">
-        <v>72.84</v>
+        <v>74.25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>21.2</v>
+        <v>32.1</v>
       </c>
       <c r="C66" t="n">
-        <v>21.62</v>
+        <v>78.25</v>
       </c>
       <c r="D66" t="n">
-        <v>1019900</v>
+        <v>2437800</v>
       </c>
       <c r="E66" t="n">
-        <v>1551545</v>
+        <v>3343425</v>
       </c>
       <c r="F66" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5749,13 +5757,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>20.6</v>
+        <v>30.94</v>
       </c>
       <c r="K66" t="n">
-        <v>20.13</v>
+        <v>31.62</v>
       </c>
       <c r="L66" t="n">
-        <v>5.32</v>
+        <v>1.5</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5771,10 +5779,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>40.35</v>
+        <v>35.85</v>
       </c>
       <c r="S66" t="n">
-        <v>46.9</v>
+        <v>57.48</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5788,30 +5796,30 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.3</v>
+        <v>23.65</v>
       </c>
       <c r="C67" t="n">
-        <v>59.54</v>
+        <v>89.62</v>
       </c>
       <c r="D67" t="n">
-        <v>1843300</v>
+        <v>3789500</v>
       </c>
       <c r="E67" t="n">
-        <v>3447040</v>
+        <v>7861890</v>
       </c>
       <c r="F67" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5829,20 +5837,24 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>30.94</v>
+        <v>21.2</v>
       </c>
       <c r="K67" t="n">
-        <v>31.62</v>
+        <v>21.2</v>
       </c>
       <c r="L67" t="n">
-        <v>2.13</v>
+        <v>11.56</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
@@ -5851,10 +5863,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>42.86</v>
+        <v>42.2</v>
       </c>
       <c r="S67" t="n">
-        <v>54.54</v>
+        <v>40.83</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5868,30 +5880,30 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>23.7</v>
+        <v>20.8</v>
       </c>
       <c r="C68" t="n">
-        <v>127.57</v>
+        <v>22.98</v>
       </c>
       <c r="D68" t="n">
-        <v>5382800</v>
+        <v>1104900</v>
       </c>
       <c r="E68" t="n">
-        <v>7947960</v>
+        <v>1289340</v>
       </c>
       <c r="F68" t="n">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5905,28 +5917,24 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="K68" t="n">
-        <v>21.2</v>
+        <v>21.92</v>
       </c>
       <c r="L68" t="n">
-        <v>11.79</v>
+        <v>-5.13</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
@@ -5935,14 +5943,14 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>45.61</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="S68" t="n">
-        <v>44.29</v>
+        <v>25.21</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -5952,39 +5960,39 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20.95</v>
+        <v>10.7</v>
       </c>
       <c r="C69" t="n">
-        <v>27</v>
+        <v>313.31</v>
       </c>
       <c r="D69" t="n">
-        <v>1289000</v>
+        <v>29281500</v>
       </c>
       <c r="E69" t="n">
-        <v>1286955</v>
+        <v>43476885</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5993,13 +6001,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>22.3</v>
+        <v>10.9</v>
       </c>
       <c r="K69" t="n">
-        <v>21.92</v>
+        <v>12.48</v>
       </c>
       <c r="L69" t="n">
-        <v>-4.45</v>
+        <v>-14.23</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -6015,56 +6023,56 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>22.81</v>
+        <v>45.1</v>
       </c>
       <c r="S69" t="n">
-        <v>32</v>
+        <v>42.31</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="C70" t="n">
-        <v>450.85</v>
+        <v>142.03</v>
       </c>
       <c r="D70" t="n">
-        <v>41362700</v>
+        <v>11453800</v>
       </c>
       <c r="E70" t="n">
-        <v>43948230</v>
+        <v>11300990</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6073,13 +6081,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>10.9</v>
+        <v>13.32</v>
       </c>
       <c r="K70" t="n">
-        <v>12.48</v>
+        <v>15</v>
       </c>
       <c r="L70" t="n">
-        <v>-12.63</v>
+        <v>-17.36</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6095,47 +6103,47 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>46.94</v>
+        <v>50.19</v>
       </c>
       <c r="S70" t="n">
-        <v>38.93</v>
+        <v>58.38</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>12.8</v>
+        <v>15.9</v>
       </c>
       <c r="C71" t="n">
-        <v>167.98</v>
+        <v>47.11</v>
       </c>
       <c r="D71" t="n">
-        <v>13123200</v>
+        <v>2963100</v>
       </c>
       <c r="E71" t="n">
-        <v>11413060</v>
+        <v>2263050</v>
       </c>
       <c r="F71" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6144,7 +6152,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6153,13 +6161,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>13.32</v>
+        <v>19.77</v>
       </c>
       <c r="K71" t="n">
-        <v>15</v>
+        <v>19.19</v>
       </c>
       <c r="L71" t="n">
-        <v>-14.7</v>
+        <v>-17.12</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -6175,51 +6183,51 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>62.61</v>
+        <v>41.18</v>
       </c>
       <c r="S71" t="n">
-        <v>55.86</v>
+        <v>37.78</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>16.65</v>
+        <v>19.8</v>
       </c>
       <c r="C72" t="n">
-        <v>50.13</v>
+        <v>287.42</v>
       </c>
       <c r="D72" t="n">
-        <v>3011000</v>
+        <v>14516100</v>
       </c>
       <c r="E72" t="n">
-        <v>2278880</v>
+        <v>18987315</v>
       </c>
       <c r="F72" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6229,17 +6237,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>19.77</v>
+        <v>19.55</v>
       </c>
       <c r="K72" t="n">
-        <v>19.19</v>
+        <v>20.3</v>
       </c>
       <c r="L72" t="n">
-        <v>-13.21</v>
+        <v>-2.49</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -6255,10 +6263,10 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>42</v>
+        <v>50.82</v>
       </c>
       <c r="S72" t="n">
-        <v>38.6</v>
+        <v>52.25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6272,34 +6280,34 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>19.95</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>412.63</v>
+        <v>132.54</v>
       </c>
       <c r="D73" t="n">
-        <v>20683200</v>
+        <v>1960700</v>
       </c>
       <c r="E73" t="n">
-        <v>19776485</v>
+        <v>3562600</v>
       </c>
       <c r="F73" t="n">
-        <v>1.05</v>
+        <v>0.55</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6309,24 +6317,28 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>19.55</v>
+        <v>70.05</v>
       </c>
       <c r="K73" t="n">
-        <v>20.34</v>
+        <v>70.05</v>
       </c>
       <c r="L73" t="n">
-        <v>-1.94</v>
+        <v>-3.5</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
@@ -6335,10 +6347,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>55</v>
+        <v>49.66</v>
       </c>
       <c r="S73" t="n">
-        <v>48</v>
+        <v>42.74</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -6352,34 +6364,34 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>68.5</v>
+        <v>33.8</v>
       </c>
       <c r="C74" t="n">
-        <v>564.05</v>
+        <v>611.64</v>
       </c>
       <c r="D74" t="n">
-        <v>8234300</v>
+        <v>18096000</v>
       </c>
       <c r="E74" t="n">
-        <v>3575655</v>
+        <v>17599200</v>
       </c>
       <c r="F74" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6389,21 +6401,21 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>70.05</v>
+        <v>31.5</v>
       </c>
       <c r="K74" t="n">
-        <v>70.05</v>
+        <v>31.5</v>
       </c>
       <c r="L74" t="n">
-        <v>-2.21</v>
+        <v>7.3</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6419,10 +6431,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>51.8</v>
+        <v>67.09</v>
       </c>
       <c r="S74" t="n">
-        <v>37.96</v>
+        <v>63.39</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -6436,34 +6448,34 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SZC</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20.2</v>
+        <v>11.9</v>
       </c>
       <c r="C75" t="n">
-        <v>25.98</v>
+        <v>60.18</v>
       </c>
       <c r="D75" t="n">
-        <v>1286300</v>
+        <v>5057300</v>
       </c>
       <c r="E75" t="n">
-        <v>432405</v>
+        <v>4979195</v>
       </c>
       <c r="F75" t="n">
-        <v>2.97</v>
+        <v>1.02</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6477,13 +6489,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>18.14</v>
+        <v>11.09</v>
       </c>
       <c r="K75" t="n">
-        <v>21.94</v>
+        <v>13.2</v>
       </c>
       <c r="L75" t="n">
-        <v>-7.91</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6495,18 +6507,18 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.0x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>91.01000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="S75" t="n">
-        <v>87.77</v>
+        <v>69.97</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -6516,65 +6528,61 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>34.2</v>
+        <v>28.95</v>
       </c>
       <c r="C76" t="n">
-        <v>557.64</v>
+        <v>87.42</v>
       </c>
       <c r="D76" t="n">
-        <v>16305300</v>
+        <v>3019600</v>
       </c>
       <c r="E76" t="n">
-        <v>17773840</v>
+        <v>2927000</v>
       </c>
       <c r="F76" t="n">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>31.5</v>
+        <v>31.01</v>
       </c>
       <c r="K76" t="n">
-        <v>31.5</v>
+        <v>32.59</v>
       </c>
       <c r="L76" t="n">
-        <v>8.57</v>
+        <v>-11.17</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
@@ -6583,47 +6591,47 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>73.61</v>
+        <v>53.27</v>
       </c>
       <c r="S76" t="n">
-        <v>70.31999999999999</v>
+        <v>62.67</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>TNG</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>12</v>
+        <v>19.4</v>
       </c>
       <c r="C77" t="n">
-        <v>84.5</v>
+        <v>21.89</v>
       </c>
       <c r="D77" t="n">
-        <v>7042000</v>
+        <v>1128300</v>
       </c>
       <c r="E77" t="n">
-        <v>5103295</v>
+        <v>1101380</v>
       </c>
       <c r="F77" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6641,17 +6649,17 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>11.09</v>
+        <v>16.98</v>
       </c>
       <c r="K77" t="n">
-        <v>13.2</v>
+        <v>17.78</v>
       </c>
       <c r="L77" t="n">
-        <v>-9.130000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -6663,10 +6671,10 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>72.73</v>
+        <v>65.67</v>
       </c>
       <c r="S77" t="n">
-        <v>75.25</v>
+        <v>77.17</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6680,58 +6688,58 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>29.4</v>
+        <v>12.9</v>
       </c>
       <c r="C78" t="n">
-        <v>98.64</v>
+        <v>286.35</v>
       </c>
       <c r="D78" t="n">
-        <v>3355100</v>
+        <v>22197700</v>
       </c>
       <c r="E78" t="n">
-        <v>2907255</v>
+        <v>12695280</v>
       </c>
       <c r="F78" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>31.01</v>
+        <v>12.2</v>
       </c>
       <c r="K78" t="n">
-        <v>32.59</v>
+        <v>12.68</v>
       </c>
       <c r="L78" t="n">
-        <v>-9.789999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -6743,75 +6751,75 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>64.04000000000001</v>
+        <v>76.19</v>
       </c>
       <c r="S78" t="n">
-        <v>70.01000000000001</v>
+        <v>84.02</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>13</v>
+        <v>56.1</v>
       </c>
       <c r="C79" t="n">
-        <v>391.19</v>
+        <v>202.91</v>
       </c>
       <c r="D79" t="n">
-        <v>30091200</v>
+        <v>3617000</v>
       </c>
       <c r="E79" t="n">
-        <v>12043425</v>
+        <v>2981575</v>
       </c>
       <c r="F79" t="n">
-        <v>2.5</v>
+        <v>1.21</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>12.18</v>
+        <v>57</v>
       </c>
       <c r="K79" t="n">
-        <v>12.68</v>
+        <v>59.12</v>
       </c>
       <c r="L79" t="n">
-        <v>2.56</v>
+        <v>-5.12</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -6823,56 +6831,56 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>76.19</v>
+        <v>37.5</v>
       </c>
       <c r="S79" t="n">
-        <v>78.54000000000001</v>
+        <v>50.41</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>56.8</v>
+        <v>15.15</v>
       </c>
       <c r="C80" t="n">
-        <v>186.24</v>
+        <v>25.19</v>
       </c>
       <c r="D80" t="n">
-        <v>3278900</v>
+        <v>1662600</v>
       </c>
       <c r="E80" t="n">
-        <v>2991925</v>
+        <v>2230265</v>
       </c>
       <c r="F80" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6881,13 +6889,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>57</v>
+        <v>14.88</v>
       </c>
       <c r="K80" t="n">
-        <v>59.12</v>
+        <v>17.1</v>
       </c>
       <c r="L80" t="n">
-        <v>-3.93</v>
+        <v>-11.43</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -6903,71 +6911,71 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>47.73</v>
+        <v>75.86</v>
       </c>
       <c r="S80" t="n">
-        <v>49.31</v>
+        <v>74.78</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>15.45</v>
+        <v>19.15</v>
       </c>
       <c r="C81" t="n">
-        <v>36.02</v>
+        <v>111.45</v>
       </c>
       <c r="D81" t="n">
-        <v>2331200</v>
+        <v>5820000</v>
       </c>
       <c r="E81" t="n">
-        <v>2254680</v>
+        <v>7797560</v>
       </c>
       <c r="F81" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>14.88</v>
+        <v>20.6</v>
       </c>
       <c r="K81" t="n">
-        <v>17.1</v>
+        <v>22.88</v>
       </c>
       <c r="L81" t="n">
-        <v>-9.68</v>
+        <v>-16.28</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6983,47 +6991,47 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>85.70999999999999</v>
+        <v>46.03</v>
       </c>
       <c r="S81" t="n">
-        <v>79.70999999999999</v>
+        <v>57.59</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>19.6</v>
+        <v>27.7</v>
       </c>
       <c r="C82" t="n">
-        <v>147.71</v>
+        <v>33.94</v>
       </c>
       <c r="D82" t="n">
-        <v>7536000</v>
+        <v>1225100</v>
       </c>
       <c r="E82" t="n">
-        <v>7923875</v>
+        <v>1678320</v>
       </c>
       <c r="F82" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -7041,13 +7049,13 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>20.6</v>
+        <v>29.08</v>
       </c>
       <c r="K82" t="n">
-        <v>22.9</v>
+        <v>30.82</v>
       </c>
       <c r="L82" t="n">
-        <v>-14.41</v>
+        <v>-10.14</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -7063,10 +7071,10 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>64.29000000000001</v>
+        <v>47.37</v>
       </c>
       <c r="S82" t="n">
-        <v>65.34999999999999</v>
+        <v>66.23</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -7080,61 +7088,65 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>VGC</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>27.95</v>
+        <v>46.3</v>
       </c>
       <c r="C83" t="n">
-        <v>34.75</v>
+        <v>198.57</v>
       </c>
       <c r="D83" t="n">
-        <v>1243300</v>
+        <v>4288800</v>
       </c>
       <c r="E83" t="n">
-        <v>1693245</v>
+        <v>803665</v>
       </c>
       <c r="F83" t="n">
-        <v>0.73</v>
+        <v>5.34</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>29.08</v>
+        <v>40.8</v>
       </c>
       <c r="K83" t="n">
-        <v>30.82</v>
+        <v>40.8</v>
       </c>
       <c r="L83" t="n">
-        <v>-9.33</v>
+        <v>13.48</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
@@ -7143,47 +7155,47 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>56.31</v>
+        <v>60.99</v>
       </c>
       <c r="S83" t="n">
-        <v>73.47</v>
+        <v>65.89</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VGC</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>44.5</v>
+        <v>63.9</v>
       </c>
       <c r="C84" t="n">
-        <v>20.81</v>
+        <v>464.82</v>
       </c>
       <c r="D84" t="n">
-        <v>467600</v>
+        <v>7274200</v>
       </c>
       <c r="E84" t="n">
-        <v>613020</v>
+        <v>8138550</v>
       </c>
       <c r="F84" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7192,33 +7204,29 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>40.17</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>40.17</v>
+        <v>70.52</v>
       </c>
       <c r="L84" t="n">
-        <v>10.77</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
@@ -7227,47 +7235,47 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>50</v>
+        <v>39.33</v>
       </c>
       <c r="S84" t="n">
-        <v>47.47</v>
+        <v>34.21</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>VIB</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>64.3</v>
+        <v>13.95</v>
       </c>
       <c r="C85" t="n">
-        <v>413.23</v>
+        <v>64.91</v>
       </c>
       <c r="D85" t="n">
-        <v>6426600</v>
+        <v>4652900</v>
       </c>
       <c r="E85" t="n">
-        <v>8196050</v>
+        <v>6079315</v>
       </c>
       <c r="F85" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7281,17 +7289,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>69.65000000000001</v>
+        <v>13.52</v>
       </c>
       <c r="K85" t="n">
-        <v>70.52</v>
+        <v>14.16</v>
       </c>
       <c r="L85" t="n">
-        <v>-8.82</v>
+        <v>-1.45</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -7307,14 +7315,14 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>41.74</v>
+        <v>60.98</v>
       </c>
       <c r="S85" t="n">
-        <v>40.36</v>
+        <v>72.28</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -7324,30 +7332,30 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>14.2</v>
+        <v>237</v>
       </c>
       <c r="C86" t="n">
-        <v>71.34999999999999</v>
+        <v>525.8099999999999</v>
       </c>
       <c r="D86" t="n">
-        <v>5024500</v>
+        <v>2218600</v>
       </c>
       <c r="E86" t="n">
-        <v>6051070</v>
+        <v>2766775</v>
       </c>
       <c r="F86" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7361,17 +7369,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>13.52</v>
+        <v>229.8</v>
       </c>
       <c r="K86" t="n">
-        <v>14.16</v>
+        <v>224.85</v>
       </c>
       <c r="L86" t="n">
-        <v>0.32</v>
+        <v>5.4</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -7387,14 +7395,14 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>71.05</v>
+        <v>54.1</v>
       </c>
       <c r="S86" t="n">
-        <v>77.73999999999999</v>
+        <v>32.96</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -7404,58 +7412,58 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>236.5</v>
+        <v>12.5</v>
       </c>
       <c r="C87" t="n">
-        <v>477.87</v>
+        <v>373.76</v>
       </c>
       <c r="D87" t="n">
-        <v>2020600</v>
+        <v>29900900</v>
       </c>
       <c r="E87" t="n">
-        <v>2700435</v>
+        <v>29626115</v>
       </c>
       <c r="F87" t="n">
-        <v>0.75</v>
+        <v>1.01</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>229.8</v>
+        <v>12.82</v>
       </c>
       <c r="K87" t="n">
-        <v>221.55</v>
+        <v>14.95</v>
       </c>
       <c r="L87" t="n">
-        <v>6.75</v>
+        <v>-16.39</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -7467,47 +7475,47 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>53.72</v>
+        <v>60.71</v>
       </c>
       <c r="S87" t="n">
-        <v>36.31</v>
+        <v>72.53</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VJC</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>12.7</v>
+        <v>132</v>
       </c>
       <c r="C88" t="n">
-        <v>506.64</v>
+        <v>138.59</v>
       </c>
       <c r="D88" t="n">
-        <v>39893300</v>
+        <v>1049900</v>
       </c>
       <c r="E88" t="n">
-        <v>29447510</v>
+        <v>933580</v>
       </c>
       <c r="F88" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7516,22 +7524,22 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>12.82</v>
+        <v>128.05</v>
       </c>
       <c r="K88" t="n">
-        <v>14.95</v>
+        <v>132.12</v>
       </c>
       <c r="L88" t="n">
-        <v>-15.05</v>
+        <v>-0.09</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -7547,47 +7555,47 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>66.04000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="S88" t="n">
-        <v>72.42</v>
+        <v>45.39</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VJC</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>129.7</v>
+        <v>13.55</v>
       </c>
       <c r="C89" t="n">
-        <v>114.67</v>
+        <v>87.63</v>
       </c>
       <c r="D89" t="n">
-        <v>884100</v>
+        <v>6467300</v>
       </c>
       <c r="E89" t="n">
-        <v>928415</v>
+        <v>9664370</v>
       </c>
       <c r="F89" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7596,22 +7604,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>128.05</v>
+        <v>15.05</v>
       </c>
       <c r="K89" t="n">
-        <v>132.12</v>
+        <v>15.85</v>
       </c>
       <c r="L89" t="n">
-        <v>-1.84</v>
+        <v>-14.51</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7627,47 +7635,47 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>57.38</v>
+        <v>44</v>
       </c>
       <c r="S89" t="n">
-        <v>37.76</v>
+        <v>47.16</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>13.75</v>
+        <v>57.6</v>
       </c>
       <c r="C90" t="n">
-        <v>108.84</v>
+        <v>73.72</v>
       </c>
       <c r="D90" t="n">
-        <v>7915900</v>
+        <v>1279800</v>
       </c>
       <c r="E90" t="n">
-        <v>10023200</v>
+        <v>1926265</v>
       </c>
       <c r="F90" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7676,7 +7684,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7685,13 +7693,13 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>15.05</v>
+        <v>60.65</v>
       </c>
       <c r="K90" t="n">
-        <v>15.85</v>
+        <v>59.5</v>
       </c>
       <c r="L90" t="n">
-        <v>-13.25</v>
+        <v>-3.19</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -7707,47 +7715,47 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>57.14</v>
+        <v>42</v>
       </c>
       <c r="S90" t="n">
-        <v>54.85</v>
+        <v>43.57</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>VPB</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>57.6</v>
+        <v>23.6</v>
       </c>
       <c r="C91" t="n">
-        <v>103.32</v>
+        <v>217.66</v>
       </c>
       <c r="D91" t="n">
-        <v>1793700</v>
+        <v>9222700</v>
       </c>
       <c r="E91" t="n">
-        <v>1948445</v>
+        <v>15740110</v>
       </c>
       <c r="F91" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7761,24 +7769,28 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>60.65</v>
+        <v>21.98</v>
       </c>
       <c r="K91" t="n">
-        <v>59.5</v>
+        <v>21.98</v>
       </c>
       <c r="L91" t="n">
-        <v>-3.19</v>
+        <v>7.39</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
@@ -7787,10 +7799,10 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>53.23</v>
+        <v>57.69</v>
       </c>
       <c r="S91" t="n">
-        <v>53.54</v>
+        <v>66.75</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7804,34 +7816,34 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VPB</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.1</v>
+        <v>56.8</v>
       </c>
       <c r="C92" t="n">
-        <v>273.6</v>
+        <v>149.92</v>
       </c>
       <c r="D92" t="n">
-        <v>11352800</v>
+        <v>2639400</v>
       </c>
       <c r="E92" t="n">
-        <v>16304165</v>
+        <v>1862755</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7</v>
+        <v>1.42</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7841,17 +7853,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>21.98</v>
+        <v>55.52</v>
       </c>
       <c r="K92" t="n">
-        <v>21.98</v>
+        <v>55.52</v>
       </c>
       <c r="L92" t="n">
-        <v>9.67</v>
+        <v>2.3</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -7864,25 +7876,21 @@
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R92" t="n">
-        <v>73.91</v>
+        <v>47.94</v>
       </c>
       <c r="S92" t="n">
-        <v>70.79000000000001</v>
+        <v>58.41</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -7892,34 +7900,34 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>VPL</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>57.4</v>
+        <v>86</v>
       </c>
       <c r="C93" t="n">
-        <v>148.57</v>
+        <v>108.9</v>
       </c>
       <c r="D93" t="n">
-        <v>2588300</v>
+        <v>1266300</v>
       </c>
       <c r="E93" t="n">
-        <v>1787020</v>
+        <v>801380</v>
       </c>
       <c r="F93" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7929,28 +7937,24 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>55.52</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K93" t="n">
-        <v>55.52</v>
+        <v>85.5</v>
       </c>
       <c r="L93" t="n">
-        <v>3.38</v>
+        <v>0.58</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
@@ -7959,10 +7963,10 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>51.28</v>
+        <v>64.41</v>
       </c>
       <c r="S93" t="n">
-        <v>49.61</v>
+        <v>63.25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7976,58 +7980,58 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VPL</t>
+          <t>VRE</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>86</v>
+        <v>24.3</v>
       </c>
       <c r="C94" t="n">
-        <v>156.66</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="D94" t="n">
-        <v>1821600</v>
+        <v>3531800</v>
       </c>
       <c r="E94" t="n">
-        <v>759725</v>
+        <v>3382665</v>
       </c>
       <c r="F94" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>79.84999999999999</v>
+        <v>24.42</v>
       </c>
       <c r="K94" t="n">
-        <v>85.5</v>
+        <v>28.56</v>
       </c>
       <c r="L94" t="n">
-        <v>0.58</v>
+        <v>-14.92</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -8039,47 +8043,47 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>70</v>
+        <v>54.63</v>
       </c>
       <c r="S94" t="n">
-        <v>73.44</v>
+        <v>45.73</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VRE</t>
+          <t>VSC</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="C95" t="n">
-        <v>90.02</v>
+        <v>212.99</v>
       </c>
       <c r="D95" t="n">
-        <v>3600900</v>
+        <v>14689200</v>
       </c>
       <c r="E95" t="n">
-        <v>3330395</v>
+        <v>9863710</v>
       </c>
       <c r="F95" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -8097,13 +8101,13 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>24.42</v>
+        <v>14.02</v>
       </c>
       <c r="K95" t="n">
-        <v>28.56</v>
+        <v>18.1</v>
       </c>
       <c r="L95" t="n">
-        <v>-12.46</v>
+        <v>-19.89</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -8119,14 +8123,14 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>62.77</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="S95" t="n">
-        <v>45.66</v>
+        <v>70.31</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -8136,34 +8140,34 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VSC</t>
+          <t>VTZ</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>15.1</v>
+        <v>20.2</v>
       </c>
       <c r="C96" t="n">
-        <v>408.79</v>
+        <v>20.71</v>
       </c>
       <c r="D96" t="n">
-        <v>27072200</v>
+        <v>1025400</v>
       </c>
       <c r="E96" t="n">
-        <v>9880605</v>
+        <v>963185</v>
       </c>
       <c r="F96" t="n">
-        <v>2.74</v>
+        <v>1.06</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8173,17 +8177,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>14.02</v>
+        <v>20.45</v>
       </c>
       <c r="K96" t="n">
-        <v>18.12</v>
+        <v>21.3</v>
       </c>
       <c r="L96" t="n">
-        <v>-16.69</v>
+        <v>-5.16</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -8195,18 +8199,18 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>78.38</v>
+        <v>37.5</v>
       </c>
       <c r="S96" t="n">
-        <v>75.59</v>
+        <v>31.74</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -8216,34 +8220,34 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VTZ</t>
+          <t>VVS</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>20.3</v>
+        <v>80.3</v>
       </c>
       <c r="C97" t="n">
-        <v>25.66</v>
+        <v>29.76</v>
       </c>
       <c r="D97" t="n">
-        <v>1264000</v>
+        <v>370600</v>
       </c>
       <c r="E97" t="n">
-        <v>960130</v>
+        <v>200830</v>
       </c>
       <c r="F97" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -8257,13 +8261,13 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>20.45</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="K97" t="n">
-        <v>21.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L97" t="n">
-        <v>-4.69</v>
+        <v>-5.63</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -8279,10 +8283,10 @@
         </is>
       </c>
       <c r="R97" t="n">
-        <v>42.86</v>
+        <v>38.04</v>
       </c>
       <c r="S97" t="n">
-        <v>35.26</v>
+        <v>39.37</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -8296,87 +8300,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-10-23 21:02:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>VVS</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>84</v>
-      </c>
-      <c r="C98" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="D98" t="n">
-        <v>599000</v>
-      </c>
-      <c r="E98" t="n">
-        <v>187715</v>
-      </c>
-      <c r="F98" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>🔥 Tiền Vào Mạnh</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>94.15000000000001</v>
-      </c>
-      <c r="K98" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="L98" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.2x + giá chiết khấu 129)</t>
-        </is>
-      </c>
-      <c r="R98" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="S98" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>2026-10-23 21:02:24</t>
+          <t>2026-10-26 22:39:46</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V97"/>
+  <dimension ref="A1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,20 +538,20 @@
         <v>21.3</v>
       </c>
       <c r="C2" t="n">
-        <v>188.34</v>
+        <v>178.9</v>
       </c>
       <c r="D2" t="n">
-        <v>8842300</v>
+        <v>8398900</v>
       </c>
       <c r="E2" t="n">
-        <v>8670705</v>
+        <v>8737665</v>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>64.58</v>
+        <v>63.83</v>
       </c>
       <c r="S2" t="n">
-        <v>69.67</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -615,23 +615,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.8</v>
+        <v>41.2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.87</v>
+        <v>26.39</v>
       </c>
       <c r="D3" t="n">
-        <v>905900</v>
+        <v>640600</v>
       </c>
       <c r="E3" t="n">
-        <v>765970</v>
+        <v>788520</v>
       </c>
       <c r="F3" t="n">
-        <v>1.18</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -651,11 +651,11 @@
         <v>41.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.48</v>
+        <v>-0.96</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>67.12</v>
+        <v>52.38</v>
       </c>
       <c r="S3" t="n">
-        <v>75.12</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -684,34 +684,34 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAF</t>
+          <t>ANV</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.67</v>
+        <v>18.55</v>
       </c>
       <c r="C4" t="n">
-        <v>107.59</v>
+        <v>22.32</v>
       </c>
       <c r="D4" t="n">
-        <v>3626300</v>
+        <v>1203000</v>
       </c>
       <c r="E4" t="n">
-        <v>1938025</v>
+        <v>1494140</v>
       </c>
       <c r="F4" t="n">
-        <v>1.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -721,21 +721,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>29.12</v>
+        <v>17.4</v>
       </c>
       <c r="K4" t="n">
-        <v>28.4</v>
+        <v>20.08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.47</v>
+        <v>-7.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>53.98</v>
+        <v>58.87</v>
       </c>
       <c r="S4" t="n">
-        <v>64.29000000000001</v>
+        <v>62.33</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -764,34 +764,34 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>BAF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.35</v>
+        <v>29.95</v>
       </c>
       <c r="C5" t="n">
-        <v>36.56</v>
+        <v>43.28</v>
       </c>
       <c r="D5" t="n">
-        <v>884100</v>
+        <v>1445200</v>
       </c>
       <c r="E5" t="n">
-        <v>545560</v>
+        <v>1915385</v>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -801,21 +801,21 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>40.45</v>
+        <v>29.12</v>
       </c>
       <c r="K5" t="n">
-        <v>45.55</v>
+        <v>28.4</v>
       </c>
       <c r="L5" t="n">
-        <v>-9.220000000000001</v>
+        <v>5.46</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -827,14 +827,14 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>71.92</v>
+        <v>52.63</v>
       </c>
       <c r="S5" t="n">
-        <v>78.01000000000001</v>
+        <v>63.42</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -844,30 +844,30 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.75</v>
+        <v>40.55</v>
       </c>
       <c r="C6" t="n">
-        <v>102.15</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>3026600</v>
+        <v>665800</v>
       </c>
       <c r="E6" t="n">
-        <v>3010315</v>
+        <v>561645</v>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>35</v>
+        <v>40.45</v>
       </c>
       <c r="K6" t="n">
-        <v>37.54</v>
+        <v>45.55</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.1</v>
+        <v>-10.98</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>40.23</v>
+        <v>63.23</v>
       </c>
       <c r="S6" t="n">
-        <v>49.88</v>
+        <v>70.66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BSI</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.3</v>
+        <v>33.65</v>
       </c>
       <c r="C7" t="n">
-        <v>23.65</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>866400</v>
+        <v>2495000</v>
       </c>
       <c r="E7" t="n">
-        <v>344610</v>
+        <v>3024440</v>
       </c>
       <c r="F7" t="n">
-        <v>2.51</v>
+        <v>0.82</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>26.75</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>30.35</v>
+        <v>37.54</v>
       </c>
       <c r="L7" t="n">
-        <v>-10.05</v>
+        <v>-10.36</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -983,55 +983,55 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.5x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>68</v>
+        <v>40.23</v>
       </c>
       <c r="S7" t="n">
-        <v>70.92</v>
+        <v>44.72</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BSI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.4</v>
+        <v>27.95</v>
       </c>
       <c r="C8" t="n">
-        <v>262.31</v>
+        <v>22.09</v>
       </c>
       <c r="D8" t="n">
-        <v>8922000</v>
+        <v>790500</v>
       </c>
       <c r="E8" t="n">
-        <v>9663680</v>
+        <v>374910</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>2.11</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1041,21 +1041,21 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28.07</v>
+        <v>26.75</v>
       </c>
       <c r="K8" t="n">
-        <v>27.96</v>
+        <v>30.35</v>
       </c>
       <c r="L8" t="n">
-        <v>5.15</v>
+        <v>-7.91</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1067,14 +1067,14 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>38.96</v>
+        <v>73.13</v>
       </c>
       <c r="S8" t="n">
-        <v>36.69</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1084,30 +1084,30 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.7</v>
+        <v>28.9</v>
       </c>
       <c r="C9" t="n">
-        <v>36.4</v>
+        <v>161.89</v>
       </c>
       <c r="D9" t="n">
-        <v>529900</v>
+        <v>5601600</v>
       </c>
       <c r="E9" t="n">
-        <v>942415</v>
+        <v>9237460</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1121,28 +1121,24 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>67.09999999999999</v>
+        <v>28.24</v>
       </c>
       <c r="K9" t="n">
-        <v>67.09999999999999</v>
+        <v>27.96</v>
       </c>
       <c r="L9" t="n">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
@@ -1151,14 +1147,14 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>31.79</v>
+        <v>31.13</v>
       </c>
       <c r="S9" t="n">
-        <v>28.8</v>
+        <v>31.54</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1168,34 +1164,34 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.6</v>
+        <v>67.8</v>
       </c>
       <c r="C10" t="n">
-        <v>21.54</v>
+        <v>32.16</v>
       </c>
       <c r="D10" t="n">
-        <v>780300</v>
+        <v>474300</v>
       </c>
       <c r="E10" t="n">
-        <v>571660</v>
+        <v>911810</v>
       </c>
       <c r="F10" t="n">
-        <v>1.36</v>
+        <v>0.52</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1205,21 +1201,21 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26.35</v>
+        <v>67.5</v>
       </c>
       <c r="K10" t="n">
-        <v>29.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.69</v>
+        <v>1.04</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1231,14 +1227,14 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>64.70999999999999</v>
+        <v>28.25</v>
       </c>
       <c r="S10" t="n">
-        <v>75.73999999999999</v>
+        <v>15.17</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1248,7 +1244,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -1259,23 +1255,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="C11" t="n">
-        <v>100.15</v>
+        <v>45.83</v>
       </c>
       <c r="D11" t="n">
-        <v>8633500</v>
+        <v>3985000</v>
       </c>
       <c r="E11" t="n">
-        <v>6840505</v>
+        <v>6750295</v>
       </c>
       <c r="F11" t="n">
-        <v>1.26</v>
+        <v>0.59</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1295,7 +1291,7 @@
         <v>13.61</v>
       </c>
       <c r="L11" t="n">
-        <v>-14.77</v>
+        <v>-15.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1304,17 +1300,21 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>70.37</v>
+        <v>76</v>
       </c>
       <c r="S11" t="n">
-        <v>83.55</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.6</v>
+        <v>13.85</v>
       </c>
       <c r="C12" t="n">
-        <v>137.94</v>
+        <v>186.04</v>
       </c>
       <c r="D12" t="n">
-        <v>10142400</v>
+        <v>13432700</v>
       </c>
       <c r="E12" t="n">
-        <v>8799285</v>
+        <v>9159840</v>
       </c>
       <c r="F12" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1375,7 +1375,7 @@
         <v>15.85</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.2</v>
+        <v>-12.62</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>65.43000000000001</v>
+        <v>73.42</v>
       </c>
       <c r="S12" t="n">
-        <v>81.43000000000001</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -1419,23 +1419,23 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="C13" t="n">
-        <v>26.78</v>
+        <v>44.32</v>
       </c>
       <c r="D13" t="n">
-        <v>402100</v>
+        <v>656600</v>
       </c>
       <c r="E13" t="n">
-        <v>437990</v>
+        <v>454845</v>
       </c>
       <c r="F13" t="n">
-        <v>0.92</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>61.25</v>
+        <v>61.65</v>
       </c>
       <c r="K13" t="n">
         <v>72.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.140000000000001</v>
+        <v>-6.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>76.70999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="S13" t="n">
-        <v>73.84999999999999</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -1499,19 +1499,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.6</v>
+        <v>30.35</v>
       </c>
       <c r="C14" t="n">
-        <v>149.33</v>
+        <v>113.07</v>
       </c>
       <c r="D14" t="n">
-        <v>4880200</v>
+        <v>3725400</v>
       </c>
       <c r="E14" t="n">
-        <v>7104830</v>
+        <v>6915895</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>32.32</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.32</v>
+        <v>-6.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>61.76</v>
+        <v>58.33</v>
       </c>
       <c r="S14" t="n">
-        <v>55.69</v>
+        <v>51.61</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -1583,23 +1583,23 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="C15" t="n">
-        <v>61.84</v>
+        <v>37.9</v>
       </c>
       <c r="D15" t="n">
-        <v>2785700</v>
+        <v>1738600</v>
       </c>
       <c r="E15" t="n">
-        <v>1348705</v>
+        <v>1408255</v>
       </c>
       <c r="F15" t="n">
-        <v>2.07</v>
+        <v>1.23</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1619,7 +1619,7 @@
         <v>24.1</v>
       </c>
       <c r="L15" t="n">
-        <v>-7.88</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>68.93000000000001</v>
+        <v>68.27</v>
       </c>
       <c r="S15" t="n">
-        <v>73.23999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1652,30 +1652,30 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>46.5</v>
+        <v>16.1</v>
       </c>
       <c r="C16" t="n">
-        <v>22.37</v>
+        <v>23.6</v>
       </c>
       <c r="D16" t="n">
-        <v>481100</v>
+        <v>1465600</v>
       </c>
       <c r="E16" t="n">
-        <v>698070</v>
+        <v>1754490</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1684,26 +1684,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>44.65</v>
+        <v>16.32</v>
       </c>
       <c r="K16" t="n">
-        <v>44.05</v>
+        <v>17.66</v>
       </c>
       <c r="L16" t="n">
-        <v>5.56</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1715,47 +1715,47 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>48.6</v>
+        <v>68</v>
       </c>
       <c r="S16" t="n">
-        <v>36.5</v>
+        <v>68.56</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DCL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35.4</v>
+        <v>46</v>
       </c>
       <c r="C17" t="n">
-        <v>51.83</v>
+        <v>24.95</v>
       </c>
       <c r="D17" t="n">
-        <v>1464200</v>
+        <v>542300</v>
       </c>
       <c r="E17" t="n">
-        <v>2269905</v>
+        <v>679400</v>
       </c>
       <c r="F17" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1773,40 +1773,36 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>32.2</v>
+        <v>44.65</v>
       </c>
       <c r="K17" t="n">
-        <v>36</v>
+        <v>44.05</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.65</v>
+        <v>4.43</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>63.93</v>
+        <v>47.54</v>
       </c>
       <c r="S17" t="n">
-        <v>80.40000000000001</v>
+        <v>36.48</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1816,30 +1812,30 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.2</v>
+        <v>34.65</v>
       </c>
       <c r="C18" t="n">
-        <v>56.38</v>
+        <v>47.91</v>
       </c>
       <c r="D18" t="n">
-        <v>1247300</v>
+        <v>1382600</v>
       </c>
       <c r="E18" t="n">
-        <v>1543665</v>
+        <v>2243285</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1857,40 +1853,40 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>39.83</v>
+        <v>32.3</v>
       </c>
       <c r="K18" t="n">
-        <v>39.83</v>
+        <v>36</v>
       </c>
       <c r="L18" t="n">
-        <v>13.48</v>
+        <v>-3.74</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>34.73</v>
+        <v>53.54</v>
       </c>
       <c r="S18" t="n">
-        <v>34.49</v>
+        <v>75.11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1900,34 +1896,34 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.949999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="C19" t="n">
-        <v>71.01000000000001</v>
+        <v>47.89</v>
       </c>
       <c r="D19" t="n">
-        <v>7136700</v>
+        <v>1052500</v>
       </c>
       <c r="E19" t="n">
-        <v>5007540</v>
+        <v>1519055</v>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1937,24 +1933,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9.82</v>
+        <v>39.83</v>
       </c>
       <c r="K19" t="n">
-        <v>11.52</v>
+        <v>39.83</v>
       </c>
       <c r="L19" t="n">
-        <v>-13.67</v>
+        <v>14.24</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
@@ -1963,14 +1963,14 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>75.19</v>
+        <v>39.51</v>
       </c>
       <c r="S19" t="n">
-        <v>64.12</v>
+        <v>34.29</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -1980,30 +1980,30 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.7</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>40.41</v>
+        <v>44.81</v>
       </c>
       <c r="D20" t="n">
-        <v>1862000</v>
+        <v>4581700</v>
       </c>
       <c r="E20" t="n">
-        <v>2199205</v>
+        <v>5020490</v>
       </c>
       <c r="F20" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>22.18</v>
+        <v>9.82</v>
       </c>
       <c r="K20" t="n">
-        <v>23.76</v>
+        <v>11.52</v>
       </c>
       <c r="L20" t="n">
-        <v>-8.67</v>
+        <v>-15.14</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>50.94</v>
+        <v>66.44</v>
       </c>
       <c r="S20" t="n">
-        <v>45.53</v>
+        <v>59.32</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2060,30 +2060,30 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>DPG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.7</v>
+        <v>30.3</v>
       </c>
       <c r="C21" t="n">
-        <v>27.9</v>
+        <v>21.21</v>
       </c>
       <c r="D21" t="n">
-        <v>1898200</v>
+        <v>699900</v>
       </c>
       <c r="E21" t="n">
-        <v>1807950</v>
+        <v>475905</v>
       </c>
       <c r="F21" t="n">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2101,17 +2101,17 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14.38</v>
+        <v>28.82</v>
       </c>
       <c r="K21" t="n">
-        <v>14.34</v>
+        <v>35.3</v>
       </c>
       <c r="L21" t="n">
-        <v>2.55</v>
+        <v>-14.18</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2123,14 +2123,14 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>31.91</v>
+        <v>80</v>
       </c>
       <c r="S21" t="n">
-        <v>34.88</v>
+        <v>85.59</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2140,34 +2140,34 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10.1</v>
+        <v>21.35</v>
       </c>
       <c r="C22" t="n">
-        <v>104.17</v>
+        <v>39.63</v>
       </c>
       <c r="D22" t="n">
-        <v>10314100</v>
+        <v>1856300</v>
       </c>
       <c r="E22" t="n">
-        <v>9299465</v>
+        <v>2127525</v>
       </c>
       <c r="F22" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10.73</v>
+        <v>22.18</v>
       </c>
       <c r="K22" t="n">
-        <v>11.89</v>
+        <v>23.69</v>
       </c>
       <c r="L22" t="n">
-        <v>-15.02</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>54.77</v>
+        <v>45</v>
       </c>
       <c r="S22" t="n">
-        <v>69.15000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2220,58 +2220,58 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DXS</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.2</v>
+        <v>14.4</v>
       </c>
       <c r="C23" t="n">
-        <v>22.13</v>
+        <v>30.43</v>
       </c>
       <c r="D23" t="n">
-        <v>4256700</v>
+        <v>2113300</v>
       </c>
       <c r="E23" t="n">
-        <v>1999885</v>
+        <v>1768360</v>
       </c>
       <c r="F23" t="n">
-        <v>2.13</v>
+        <v>1.2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>5.52</v>
+        <v>14.38</v>
       </c>
       <c r="K23" t="n">
-        <v>6.62</v>
+        <v>14.34</v>
       </c>
       <c r="L23" t="n">
-        <v>-21.51</v>
+        <v>0.45</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2283,51 +2283,51 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>63.72</v>
+        <v>32.61</v>
       </c>
       <c r="S23" t="n">
-        <v>75.48999999999999</v>
+        <v>35.91</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17.15</v>
+        <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>203.75</v>
+        <v>103.42</v>
       </c>
       <c r="D24" t="n">
-        <v>11880600</v>
+        <v>10341600</v>
       </c>
       <c r="E24" t="n">
-        <v>4828265</v>
+        <v>9450525</v>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>1.09</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2337,17 +2337,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>17.2</v>
+        <v>10.73</v>
       </c>
       <c r="K24" t="n">
-        <v>19.58</v>
+        <v>11.89</v>
       </c>
       <c r="L24" t="n">
-        <v>-12.39</v>
+        <v>-15.86</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>61.9</v>
+        <v>55.61</v>
       </c>
       <c r="S24" t="n">
-        <v>61.27</v>
+        <v>63.11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2380,34 +2380,34 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>56</v>
+        <v>16.9</v>
       </c>
       <c r="C25" t="n">
-        <v>565.87</v>
+        <v>112.32</v>
       </c>
       <c r="D25" t="n">
-        <v>10104800</v>
+        <v>6646200</v>
       </c>
       <c r="E25" t="n">
-        <v>5929830</v>
+        <v>4812300</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>61.9</v>
+        <v>17.2</v>
       </c>
       <c r="K25" t="n">
-        <v>63.22</v>
+        <v>19.52</v>
       </c>
       <c r="L25" t="n">
-        <v>-11.42</v>
+        <v>-13.44</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>25</v>
+        <v>57.35</v>
       </c>
       <c r="S25" t="n">
-        <v>36.32</v>
+        <v>57.04</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2460,226 +2460,222 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>148</v>
+        <v>55.4</v>
       </c>
       <c r="C26" t="n">
-        <v>36.63</v>
+        <v>478.98</v>
       </c>
       <c r="D26" t="n">
-        <v>247500</v>
+        <v>8645800</v>
       </c>
       <c r="E26" t="n">
-        <v>613300</v>
+        <v>6206220</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4</v>
+        <v>1.39</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>127.5</v>
+        <v>61.6</v>
       </c>
       <c r="K26" t="n">
-        <v>127.5</v>
+        <v>62.92</v>
       </c>
       <c r="L26" t="n">
-        <v>16.08</v>
+        <v>-11.95</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>54.75</v>
+        <v>25.29</v>
       </c>
       <c r="S26" t="n">
-        <v>60.81</v>
+        <v>35.34</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80.5</v>
+        <v>148.6</v>
       </c>
       <c r="C27" t="n">
-        <v>139.98</v>
+        <v>33.39</v>
       </c>
       <c r="D27" t="n">
-        <v>1738900</v>
+        <v>224700</v>
       </c>
       <c r="E27" t="n">
-        <v>981260</v>
+        <v>586545</v>
       </c>
       <c r="F27" t="n">
-        <v>1.77</v>
+        <v>0.38</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>76.62</v>
+        <v>129.25</v>
       </c>
       <c r="K27" t="n">
-        <v>77.69</v>
+        <v>127.5</v>
       </c>
       <c r="L27" t="n">
-        <v>3.61</v>
+        <v>16.55</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>53.85</v>
+        <v>46.44</v>
       </c>
       <c r="S27" t="n">
-        <v>64.2</v>
+        <v>54.6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>FTS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70.40000000000001</v>
+        <v>19.25</v>
       </c>
       <c r="C28" t="n">
-        <v>167.72</v>
+        <v>21.02</v>
       </c>
       <c r="D28" t="n">
-        <v>2382400</v>
+        <v>1091900</v>
       </c>
       <c r="E28" t="n">
-        <v>1528230</v>
+        <v>767840</v>
       </c>
       <c r="F28" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>66.81999999999999</v>
+        <v>20.38</v>
       </c>
       <c r="K28" t="n">
-        <v>95.83</v>
+        <v>22.88</v>
       </c>
       <c r="L28" t="n">
-        <v>-26.54</v>
+        <v>-15.85</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2695,51 +2691,51 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>50.25</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>50.31</v>
+        <v>64.55</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>118.35</v>
+        <v>54.88</v>
       </c>
       <c r="D29" t="n">
-        <v>4109500</v>
+        <v>695600</v>
       </c>
       <c r="E29" t="n">
-        <v>1483250</v>
+        <v>935960</v>
       </c>
       <c r="F29" t="n">
-        <v>2.77</v>
+        <v>0.74</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2749,21 +2745,21 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>27.15</v>
+        <v>77.31</v>
       </c>
       <c r="K29" t="n">
-        <v>29.42</v>
+        <v>77.69</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.12</v>
+        <v>1.55</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2771,14 +2767,14 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.8x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>52.38</v>
+        <v>51.53</v>
       </c>
       <c r="S29" t="n">
-        <v>62.55</v>
+        <v>60.78</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2792,54 +2788,54 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>262</v>
+        <v>107.32</v>
       </c>
       <c r="D30" t="n">
-        <v>11244600</v>
+        <v>1535300</v>
       </c>
       <c r="E30" t="n">
-        <v>7561755</v>
+        <v>1537805</v>
       </c>
       <c r="F30" t="n">
-        <v>1.49</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>23.45</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>28.58</v>
+        <v>95.83</v>
       </c>
       <c r="L30" t="n">
-        <v>-18.46</v>
+        <v>-27.06</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2855,47 +2851,47 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>53.27</v>
+        <v>52.85</v>
       </c>
       <c r="S30" t="n">
-        <v>59.79</v>
+        <v>48.77</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>55.3</v>
+        <v>28.5</v>
       </c>
       <c r="C31" t="n">
-        <v>116.5</v>
+        <v>51.43</v>
       </c>
       <c r="D31" t="n">
-        <v>2106700</v>
+        <v>1804700</v>
       </c>
       <c r="E31" t="n">
-        <v>1595240</v>
+        <v>1525140</v>
       </c>
       <c r="F31" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2913,24 +2909,20 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>51.28</v>
+        <v>27.15</v>
       </c>
       <c r="K31" t="n">
-        <v>51.28</v>
+        <v>29.42</v>
       </c>
       <c r="L31" t="n">
-        <v>7.83</v>
+        <v>-3.14</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
@@ -2939,14 +2931,14 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>62.99</v>
+        <v>52.38</v>
       </c>
       <c r="S31" t="n">
-        <v>78.31</v>
+        <v>60.62</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -2956,54 +2948,54 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32.05</v>
+        <v>22.85</v>
       </c>
       <c r="C32" t="n">
-        <v>49.84</v>
+        <v>195.55</v>
       </c>
       <c r="D32" t="n">
-        <v>1555200</v>
+        <v>8558100</v>
       </c>
       <c r="E32" t="n">
-        <v>2408115</v>
+        <v>7787080</v>
       </c>
       <c r="F32" t="n">
-        <v>0.65</v>
+        <v>1.1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>30.22</v>
+        <v>23.45</v>
       </c>
       <c r="K32" t="n">
-        <v>32.78</v>
+        <v>28.58</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.21</v>
+        <v>-20.03</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -3019,56 +3011,56 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>43.48</v>
+        <v>51.82</v>
       </c>
       <c r="S32" t="n">
-        <v>58.26</v>
+        <v>57.53</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>51.5</v>
+        <v>53.5</v>
       </c>
       <c r="C33" t="n">
-        <v>52.54</v>
+        <v>174.12</v>
       </c>
       <c r="D33" t="n">
-        <v>1020200</v>
+        <v>3254500</v>
       </c>
       <c r="E33" t="n">
-        <v>1007130</v>
+        <v>1733180</v>
       </c>
       <c r="F33" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3077,13 +3069,13 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>48.2</v>
+        <v>52.48</v>
       </c>
       <c r="K33" t="n">
-        <v>49.55</v>
+        <v>51.28</v>
       </c>
       <c r="L33" t="n">
-        <v>3.94</v>
+        <v>4.32</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3099,51 +3091,51 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>54.55</v>
+        <v>47.15</v>
       </c>
       <c r="S33" t="n">
-        <v>65</v>
+        <v>65.23</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24.15</v>
+        <v>31.55</v>
       </c>
       <c r="C34" t="n">
-        <v>127.71</v>
+        <v>28.67</v>
       </c>
       <c r="D34" t="n">
-        <v>5288300</v>
+        <v>908700</v>
       </c>
       <c r="E34" t="n">
-        <v>2731205</v>
+        <v>2268040</v>
       </c>
       <c r="F34" t="n">
-        <v>1.94</v>
+        <v>0.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3153,17 +3145,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>24.92</v>
+        <v>30.22</v>
       </c>
       <c r="K34" t="n">
-        <v>24.8</v>
+        <v>32.78</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.62</v>
+        <v>-3.74</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3179,14 +3171,14 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>57.14</v>
+        <v>25.74</v>
       </c>
       <c r="S34" t="n">
-        <v>57.45</v>
+        <v>50.45</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3196,30 +3188,30 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>HAH</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.2</v>
+        <v>50.2</v>
       </c>
       <c r="C35" t="n">
-        <v>245.3</v>
+        <v>24.72</v>
       </c>
       <c r="D35" t="n">
-        <v>11049600</v>
+        <v>492500</v>
       </c>
       <c r="E35" t="n">
-        <v>16295225</v>
+        <v>941475</v>
       </c>
       <c r="F35" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3237,24 +3229,20 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>21.13</v>
+        <v>48.2</v>
       </c>
       <c r="K35" t="n">
-        <v>21.13</v>
+        <v>49.55</v>
       </c>
       <c r="L35" t="n">
-        <v>5.06</v>
+        <v>1.31</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -3263,10 +3251,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>58.42</v>
+        <v>38.83</v>
       </c>
       <c r="S35" t="n">
-        <v>67.09</v>
+        <v>56.25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3280,34 +3268,34 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HDC</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11.85</v>
+        <v>23.95</v>
       </c>
       <c r="C36" t="n">
-        <v>23</v>
+        <v>49.55</v>
       </c>
       <c r="D36" t="n">
-        <v>1941200</v>
+        <v>2068700</v>
       </c>
       <c r="E36" t="n">
-        <v>1597420</v>
+        <v>2648595</v>
       </c>
       <c r="F36" t="n">
-        <v>1.22</v>
+        <v>0.78</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3317,17 +3305,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>11.18</v>
+        <v>24.92</v>
       </c>
       <c r="K36" t="n">
-        <v>13.34</v>
+        <v>24.8</v>
       </c>
       <c r="L36" t="n">
-        <v>-11.2</v>
+        <v>-3.43</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3343,14 +3331,14 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>91.87</v>
+        <v>61.18</v>
       </c>
       <c r="S36" t="n">
-        <v>88.67</v>
+        <v>56.21</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -3360,61 +3348,65 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HHV</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9.48</v>
+        <v>22</v>
       </c>
       <c r="C37" t="n">
-        <v>34.87</v>
+        <v>186.56</v>
       </c>
       <c r="D37" t="n">
-        <v>3678200</v>
+        <v>8479800</v>
       </c>
       <c r="E37" t="n">
-        <v>3048360</v>
+        <v>16314590</v>
       </c>
       <c r="F37" t="n">
-        <v>1.21</v>
+        <v>0.52</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9.529999999999999</v>
+        <v>21.13</v>
       </c>
       <c r="K37" t="n">
-        <v>10.54</v>
+        <v>21.13</v>
       </c>
       <c r="L37" t="n">
-        <v>-10.06</v>
+        <v>4.12</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
@@ -3423,56 +3415,56 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>62.5</v>
+        <v>54.95</v>
       </c>
       <c r="S37" t="n">
-        <v>61.34</v>
+        <v>63.67</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HDC</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.9</v>
+        <v>11.45</v>
       </c>
       <c r="C38" t="n">
-        <v>218.99</v>
+        <v>28.72</v>
       </c>
       <c r="D38" t="n">
-        <v>10478100</v>
+        <v>2508300</v>
       </c>
       <c r="E38" t="n">
-        <v>18299405</v>
+        <v>1669845</v>
       </c>
       <c r="F38" t="n">
-        <v>0.57</v>
+        <v>1.5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3481,13 +3473,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>21.12</v>
+        <v>11.18</v>
       </c>
       <c r="K38" t="n">
-        <v>22.94</v>
+        <v>13.34</v>
       </c>
       <c r="L38" t="n">
-        <v>-8.91</v>
+        <v>-14.2</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3496,86 +3488,82 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>56.25</v>
+        <v>77.11</v>
       </c>
       <c r="S38" t="n">
-        <v>68.03</v>
+        <v>77.42</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>HHP</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12.6</v>
+        <v>17.7</v>
       </c>
       <c r="C39" t="n">
-        <v>21.86</v>
+        <v>77.52</v>
       </c>
       <c r="D39" t="n">
-        <v>1734800</v>
+        <v>4379700</v>
       </c>
       <c r="E39" t="n">
-        <v>2022825</v>
+        <v>1314360</v>
       </c>
       <c r="F39" t="n">
-        <v>0.86</v>
+        <v>3.33</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>13.3</v>
+        <v>16.39</v>
       </c>
       <c r="K39" t="n">
-        <v>14.15</v>
+        <v>15.55</v>
       </c>
       <c r="L39" t="n">
-        <v>-10.95</v>
+        <v>13.86</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3587,47 +3575,47 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>68.42</v>
+        <v>51.56</v>
       </c>
       <c r="S39" t="n">
-        <v>71.94</v>
+        <v>67.03</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>HHV</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36.5</v>
+        <v>9.52</v>
       </c>
       <c r="C40" t="n">
-        <v>46.3</v>
+        <v>20.21</v>
       </c>
       <c r="D40" t="n">
-        <v>1268500</v>
+        <v>2122400</v>
       </c>
       <c r="E40" t="n">
-        <v>1282235</v>
+        <v>3046830</v>
       </c>
       <c r="F40" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3636,78 +3624,82 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>32.95</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>35.67</v>
+        <v>10.54</v>
       </c>
       <c r="L40" t="n">
-        <v>2.33</v>
+        <v>-9.68</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>65.84999999999999</v>
+        <v>65.48</v>
       </c>
       <c r="S40" t="n">
-        <v>72.39</v>
+        <v>61.35</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KBC</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.8</v>
+        <v>21</v>
       </c>
       <c r="C41" t="n">
-        <v>31.19</v>
+        <v>200.01</v>
       </c>
       <c r="D41" t="n">
-        <v>1163800</v>
+        <v>9524500</v>
       </c>
       <c r="E41" t="n">
-        <v>1259265</v>
+        <v>17836935</v>
       </c>
       <c r="F41" t="n">
-        <v>0.92</v>
+        <v>0.53</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3716,22 +3708,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>26.55</v>
+        <v>21.12</v>
       </c>
       <c r="K41" t="n">
-        <v>29.68</v>
+        <v>22.61</v>
       </c>
       <c r="L41" t="n">
-        <v>-9.69</v>
+        <v>-7.12</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3740,78 +3732,82 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>84.62</v>
+        <v>60.32</v>
       </c>
       <c r="S41" t="n">
-        <v>86.19</v>
+        <v>67.55</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>14.75</v>
+        <v>11.1</v>
       </c>
       <c r="C42" t="n">
-        <v>73.48</v>
+        <v>54.83</v>
       </c>
       <c r="D42" t="n">
-        <v>4981400</v>
+        <v>4939500</v>
       </c>
       <c r="E42" t="n">
-        <v>4446450</v>
+        <v>3232055</v>
       </c>
       <c r="F42" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>15.04</v>
+        <v>10.5</v>
       </c>
       <c r="K42" t="n">
-        <v>18.38</v>
+        <v>11.35</v>
       </c>
       <c r="L42" t="n">
-        <v>-19.77</v>
+        <v>-2.2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3827,51 +3823,51 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>71.19</v>
+        <v>78.28</v>
       </c>
       <c r="S42" t="n">
-        <v>75.94</v>
+        <v>78.19</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>39.4</v>
+        <v>12.5</v>
       </c>
       <c r="C43" t="n">
-        <v>66.73</v>
+        <v>31.96</v>
       </c>
       <c r="D43" t="n">
-        <v>1693700</v>
+        <v>2556500</v>
       </c>
       <c r="E43" t="n">
-        <v>2124070</v>
+        <v>2099750</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3885,13 +3881,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>46.6</v>
+        <v>13.2</v>
       </c>
       <c r="K43" t="n">
-        <v>47.85</v>
+        <v>14.15</v>
       </c>
       <c r="L43" t="n">
-        <v>-17.66</v>
+        <v>-11.66</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3907,10 +3903,10 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>33.46</v>
+        <v>53.33</v>
       </c>
       <c r="S43" t="n">
-        <v>40.28</v>
+        <v>61.97</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3924,30 +3920,30 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.55</v>
+        <v>36</v>
       </c>
       <c r="C44" t="n">
-        <v>191.19</v>
+        <v>21.68</v>
       </c>
       <c r="D44" t="n">
-        <v>9779700</v>
+        <v>602100</v>
       </c>
       <c r="E44" t="n">
-        <v>11687310</v>
+        <v>1281380</v>
       </c>
       <c r="F44" t="n">
-        <v>0.84</v>
+        <v>0.47</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3961,36 +3957,40 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>19.49</v>
+        <v>32.95</v>
       </c>
       <c r="K44" t="n">
-        <v>19.7</v>
+        <v>34.97</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.76</v>
+        <v>2.95</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>56.86</v>
+        <v>52.86</v>
       </c>
       <c r="S44" t="n">
-        <v>53.52</v>
+        <v>63.11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4004,30 +4004,30 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>KBC</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.4</v>
+        <v>26.95</v>
       </c>
       <c r="C45" t="n">
-        <v>30.48</v>
+        <v>29.79</v>
       </c>
       <c r="D45" t="n">
-        <v>1979000</v>
+        <v>1105500</v>
       </c>
       <c r="E45" t="n">
-        <v>2831430</v>
+        <v>1271530</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>16.02</v>
+        <v>26.55</v>
       </c>
       <c r="K45" t="n">
-        <v>17.43</v>
+        <v>29.68</v>
       </c>
       <c r="L45" t="n">
-        <v>-11.67</v>
+        <v>-9.18</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4060,58 +4060,54 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="S45" t="n">
-        <v>57.82</v>
+        <v>78.36</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>139.9</v>
+        <v>14.7</v>
       </c>
       <c r="C46" t="n">
-        <v>24.48</v>
+        <v>62.09</v>
       </c>
       <c r="D46" t="n">
-        <v>175000</v>
+        <v>4223900</v>
       </c>
       <c r="E46" t="n">
-        <v>622005</v>
+        <v>4430810</v>
       </c>
       <c r="F46" t="n">
-        <v>0.28</v>
+        <v>0.95</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4120,133 +4116,121 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>138.57</v>
+        <v>15.04</v>
       </c>
       <c r="K46" t="n">
-        <v>134.54</v>
+        <v>18.25</v>
       </c>
       <c r="L46" t="n">
-        <v>3.99</v>
+        <v>-19.45</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R46" t="n">
-        <v>44.86</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="S46" t="n">
-        <v>34.64</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15.5</v>
+        <v>38.4</v>
       </c>
       <c r="C47" t="n">
-        <v>100.93</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>6511700</v>
+        <v>2182700</v>
       </c>
       <c r="E47" t="n">
-        <v>10537480</v>
+        <v>2052445</v>
       </c>
       <c r="F47" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>13.88</v>
+        <v>46.6</v>
       </c>
       <c r="K47" t="n">
-        <v>12.99</v>
+        <v>47.85</v>
       </c>
       <c r="L47" t="n">
-        <v>19.32</v>
+        <v>-19.75</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>78.95</v>
+        <v>35.83</v>
       </c>
       <c r="S47" t="n">
-        <v>87.06999999999999</v>
+        <v>39.61</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4255,35 +4239,35 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>73</v>
+        <v>19.65</v>
       </c>
       <c r="C48" t="n">
-        <v>356.6</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>4884900</v>
+        <v>4839900</v>
       </c>
       <c r="E48" t="n">
-        <v>5489585</v>
+        <v>11460220</v>
       </c>
       <c r="F48" t="n">
-        <v>0.89</v>
+        <v>0.42</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4297,36 +4281,40 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>68.90000000000001</v>
+        <v>19.49</v>
       </c>
       <c r="K48" t="n">
-        <v>72.05</v>
+        <v>19.7</v>
       </c>
       <c r="L48" t="n">
-        <v>1.32</v>
+        <v>-0.25</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>53.52</v>
+        <v>60.78</v>
       </c>
       <c r="S48" t="n">
-        <v>64.19</v>
+        <v>49.22</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4340,30 +4328,30 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63.7</v>
+        <v>15.75</v>
       </c>
       <c r="C49" t="n">
-        <v>42.23</v>
+        <v>123.18</v>
       </c>
       <c r="D49" t="n">
-        <v>662900</v>
+        <v>7821200</v>
       </c>
       <c r="E49" t="n">
-        <v>2081110</v>
+        <v>10470395</v>
       </c>
       <c r="F49" t="n">
-        <v>0.32</v>
+        <v>0.75</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4372,7 +4360,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4381,24 +4369,20 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>50.57</v>
+        <v>13.93</v>
       </c>
       <c r="K49" t="n">
-        <v>50.57</v>
+        <v>13.04</v>
       </c>
       <c r="L49" t="n">
-        <v>25.96</v>
+        <v>20.78</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>⚠️</t>
@@ -4411,44 +4395,44 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>55.39</v>
+        <v>78.95</v>
       </c>
       <c r="S49" t="n">
-        <v>50.2</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>74.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>126.33</v>
+        <v>247.68</v>
       </c>
       <c r="D50" t="n">
-        <v>1688900</v>
+        <v>3374400</v>
       </c>
       <c r="E50" t="n">
-        <v>2776265</v>
+        <v>5561930</v>
       </c>
       <c r="F50" t="n">
         <v>0.61</v>
@@ -4469,13 +4453,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>69.02</v>
+        <v>69.45</v>
       </c>
       <c r="K50" t="n">
-        <v>72.83</v>
+        <v>72.05</v>
       </c>
       <c r="L50" t="n">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4495,10 +4479,10 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>49.04</v>
+        <v>42.11</v>
       </c>
       <c r="S50" t="n">
-        <v>53.03</v>
+        <v>52.39</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4512,30 +4496,30 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12.55</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>33.8</v>
+        <v>186.48</v>
       </c>
       <c r="D51" t="n">
-        <v>2693000</v>
+        <v>2766800</v>
       </c>
       <c r="E51" t="n">
-        <v>2452050</v>
+        <v>2136075</v>
       </c>
       <c r="F51" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4553,21 +4537,25 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>12.05</v>
+        <v>51.11</v>
       </c>
       <c r="K51" t="n">
-        <v>12.25</v>
+        <v>50.57</v>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>33.28</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4575,10 +4563,10 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>41.86</v>
+        <v>55.83</v>
       </c>
       <c r="S51" t="n">
-        <v>53.69</v>
+        <v>48.5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -4592,34 +4580,34 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11.8</v>
+        <v>75.7</v>
       </c>
       <c r="C52" t="n">
-        <v>37.82</v>
+        <v>319.53</v>
       </c>
       <c r="D52" t="n">
-        <v>3204900</v>
+        <v>4221000</v>
       </c>
       <c r="E52" t="n">
-        <v>3696110</v>
+        <v>2901475</v>
       </c>
       <c r="F52" t="n">
-        <v>0.87</v>
+        <v>1.45</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4633,13 +4621,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>10.52</v>
+        <v>69.02</v>
       </c>
       <c r="K52" t="n">
-        <v>11.41</v>
+        <v>72.83</v>
       </c>
       <c r="L52" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4655,14 +4643,14 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>81.77</v>
+        <v>43.62</v>
       </c>
       <c r="S52" t="n">
-        <v>92.52</v>
+        <v>51.38</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -4672,27 +4660,27 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NLG</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>23</v>
+        <v>12.7</v>
       </c>
       <c r="C53" t="n">
-        <v>36.26</v>
+        <v>32.38</v>
       </c>
       <c r="D53" t="n">
-        <v>1576700</v>
+        <v>2549400</v>
       </c>
       <c r="E53" t="n">
-        <v>1547630</v>
+        <v>2504535</v>
       </c>
       <c r="F53" t="n">
         <v>1.02</v>
@@ -4709,21 +4697,21 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>22.55</v>
+        <v>12.05</v>
       </c>
       <c r="K53" t="n">
-        <v>23.78</v>
+        <v>12.25</v>
       </c>
       <c r="L53" t="n">
-        <v>-3.26</v>
+        <v>3.67</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4735,14 +4723,14 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>69.62</v>
+        <v>50</v>
       </c>
       <c r="S53" t="n">
-        <v>79.29000000000001</v>
+        <v>60.51</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -4752,58 +4740,58 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.55</v>
+        <v>12.05</v>
       </c>
       <c r="C54" t="n">
-        <v>303.45</v>
+        <v>98.95</v>
       </c>
       <c r="D54" t="n">
-        <v>28763200</v>
+        <v>8211800</v>
       </c>
       <c r="E54" t="n">
-        <v>28795899</v>
+        <v>4031660</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>2.04</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>11.88</v>
+        <v>10.65</v>
       </c>
       <c r="K54" t="n">
-        <v>14.5</v>
+        <v>11.16</v>
       </c>
       <c r="L54" t="n">
-        <v>-27.22</v>
+        <v>7.97</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4815,51 +4803,51 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>54.05</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="S54" t="n">
-        <v>54.42</v>
+        <v>93.36</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>NLG</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11</v>
+        <v>22.85</v>
       </c>
       <c r="C55" t="n">
-        <v>52.11</v>
+        <v>22.49</v>
       </c>
       <c r="D55" t="n">
-        <v>4737200</v>
+        <v>984300</v>
       </c>
       <c r="E55" t="n">
-        <v>1724000</v>
+        <v>1507560</v>
       </c>
       <c r="F55" t="n">
-        <v>2.75</v>
+        <v>0.65</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4869,36 +4857,40 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>10.46</v>
+        <v>22.55</v>
       </c>
       <c r="K55" t="n">
-        <v>10.5</v>
+        <v>23.67</v>
       </c>
       <c r="L55" t="n">
-        <v>4.81</v>
+        <v>-3.48</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>92.44</v>
+        <v>64.94</v>
       </c>
       <c r="S55" t="n">
-        <v>78.5</v>
+        <v>73.59</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4912,30 +4904,30 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>13.3</v>
+        <v>10.55</v>
       </c>
       <c r="C56" t="n">
-        <v>21.08</v>
+        <v>145.62</v>
       </c>
       <c r="D56" t="n">
-        <v>1584700</v>
+        <v>13802700</v>
       </c>
       <c r="E56" t="n">
-        <v>1662445</v>
+        <v>28392729</v>
       </c>
       <c r="F56" t="n">
-        <v>0.95</v>
+        <v>0.49</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4944,22 +4936,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>13.2</v>
+        <v>11.88</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="L56" t="n">
-        <v>-4.97</v>
+        <v>-27.22</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4975,47 +4967,47 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="S56" t="n">
-        <v>66.16</v>
+        <v>56.71</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>15.5</v>
+        <v>10.85</v>
       </c>
       <c r="C57" t="n">
-        <v>138.29</v>
+        <v>69.44</v>
       </c>
       <c r="D57" t="n">
-        <v>8922000</v>
+        <v>6400400</v>
       </c>
       <c r="E57" t="n">
-        <v>3750755</v>
+        <v>1972600</v>
       </c>
       <c r="F57" t="n">
-        <v>2.38</v>
+        <v>3.24</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -5024,7 +5016,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5033,13 +5025,13 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>14.28</v>
+        <v>10.46</v>
       </c>
       <c r="K57" t="n">
-        <v>14.25</v>
+        <v>10.5</v>
       </c>
       <c r="L57" t="n">
-        <v>8.77</v>
+        <v>3.38</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5051,51 +5043,51 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.2x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>80.28</v>
+        <v>82.09</v>
       </c>
       <c r="S57" t="n">
-        <v>80.89</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>18.3</v>
+        <v>15.15</v>
       </c>
       <c r="C58" t="n">
-        <v>34.95</v>
+        <v>130.94</v>
       </c>
       <c r="D58" t="n">
-        <v>1910000</v>
+        <v>8642700</v>
       </c>
       <c r="E58" t="n">
-        <v>938440</v>
+        <v>4121190</v>
       </c>
       <c r="F58" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5104,26 +5096,26 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>19.55</v>
+        <v>14.28</v>
       </c>
       <c r="K58" t="n">
-        <v>21.66</v>
+        <v>14.25</v>
       </c>
       <c r="L58" t="n">
-        <v>-15.49</v>
+        <v>6.32</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5135,10 +5127,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>45.59</v>
+        <v>73.08</v>
       </c>
       <c r="S58" t="n">
-        <v>37.54</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5147,12 +5139,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5163,19 +5155,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="C59" t="n">
-        <v>77.77</v>
+        <v>67.97</v>
       </c>
       <c r="D59" t="n">
-        <v>6647300</v>
+        <v>5859900</v>
       </c>
       <c r="E59" t="n">
-        <v>5072250</v>
+        <v>5169765</v>
       </c>
       <c r="F59" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -5184,7 +5176,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5199,7 +5191,7 @@
         <v>13.82</v>
       </c>
       <c r="L59" t="n">
-        <v>-15.37</v>
+        <v>-16.09</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5215,24 +5207,24 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>62.79</v>
+        <v>60</v>
       </c>
       <c r="S59" t="n">
-        <v>74.42</v>
+        <v>68.2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5243,28 +5235,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>55</v>
+        <v>53.1</v>
       </c>
       <c r="C60" t="n">
-        <v>24.79</v>
+        <v>55.27</v>
       </c>
       <c r="D60" t="n">
-        <v>450700</v>
+        <v>1040900</v>
       </c>
       <c r="E60" t="n">
-        <v>714815</v>
+        <v>680025</v>
       </c>
       <c r="F60" t="n">
-        <v>0.63</v>
+        <v>1.53</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5273,13 +5265,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>45.75</v>
+        <v>46.15</v>
       </c>
       <c r="K60" t="n">
-        <v>44.22</v>
+        <v>44.52</v>
       </c>
       <c r="L60" t="n">
-        <v>24.39</v>
+        <v>19.29</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5299,24 +5291,24 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>64.29000000000001</v>
+        <v>57.32</v>
       </c>
       <c r="S60" t="n">
-        <v>62.3</v>
+        <v>51.57</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5327,23 +5319,23 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>46.3</v>
+        <v>45.4</v>
       </c>
       <c r="C61" t="n">
-        <v>21.39</v>
+        <v>25.38</v>
       </c>
       <c r="D61" t="n">
-        <v>461900</v>
+        <v>559000</v>
       </c>
       <c r="E61" t="n">
-        <v>334510</v>
+        <v>343755</v>
       </c>
       <c r="F61" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5363,7 +5355,7 @@
         <v>42.5</v>
       </c>
       <c r="L61" t="n">
-        <v>8.94</v>
+        <v>6.82</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -5379,10 +5371,10 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>35.19</v>
+        <v>22.55</v>
       </c>
       <c r="S61" t="n">
-        <v>26.4</v>
+        <v>17.04</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5396,7 +5388,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5407,19 +5399,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>35.65</v>
+        <v>35.3</v>
       </c>
       <c r="C62" t="n">
-        <v>97.39</v>
+        <v>57</v>
       </c>
       <c r="D62" t="n">
-        <v>2731800</v>
+        <v>1614700</v>
       </c>
       <c r="E62" t="n">
-        <v>3970160</v>
+        <v>3784700</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -5443,7 +5435,7 @@
         <v>38.08</v>
       </c>
       <c r="L62" t="n">
-        <v>-6.39</v>
+        <v>-7.31</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5459,10 +5451,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>45.53</v>
+        <v>43.08</v>
       </c>
       <c r="S62" t="n">
-        <v>65.51000000000001</v>
+        <v>62.33</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5476,7 +5468,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5487,19 +5479,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>17.45</v>
+        <v>17.05</v>
       </c>
       <c r="C63" t="n">
-        <v>101.86</v>
+        <v>107.13</v>
       </c>
       <c r="D63" t="n">
-        <v>5837200</v>
+        <v>6283300</v>
       </c>
       <c r="E63" t="n">
-        <v>16042905</v>
+        <v>16296555</v>
       </c>
       <c r="F63" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -5517,13 +5509,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>31.4</v>
+        <v>31.28</v>
       </c>
       <c r="K63" t="n">
-        <v>47.16</v>
+        <v>46.8</v>
       </c>
       <c r="L63" t="n">
-        <v>-63</v>
+        <v>-63.57</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5539,10 +5531,10 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>37.73</v>
+        <v>40.89</v>
       </c>
       <c r="S63" t="n">
-        <v>28.34</v>
+        <v>36.49</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -5556,7 +5548,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5567,19 +5559,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>12.55</v>
+        <v>12.4</v>
       </c>
       <c r="C64" t="n">
-        <v>33.65</v>
+        <v>43.96</v>
       </c>
       <c r="D64" t="n">
-        <v>2681100</v>
+        <v>3545000</v>
       </c>
       <c r="E64" t="n">
-        <v>5669935</v>
+        <v>5618245</v>
       </c>
       <c r="F64" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5603,7 +5595,7 @@
         <v>13.6</v>
       </c>
       <c r="L64" t="n">
-        <v>-7.72</v>
+        <v>-8.82</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -5619,10 +5611,10 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>45.83</v>
+        <v>42.31</v>
       </c>
       <c r="S64" t="n">
-        <v>43.18</v>
+        <v>38.16</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5636,7 +5628,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5647,23 +5639,23 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>18.75</v>
+        <v>18.5</v>
       </c>
       <c r="C65" t="n">
-        <v>134.48</v>
+        <v>55.78</v>
       </c>
       <c r="D65" t="n">
-        <v>7172100</v>
+        <v>3015400</v>
       </c>
       <c r="E65" t="n">
-        <v>3773485</v>
+        <v>3701735</v>
       </c>
       <c r="F65" t="n">
-        <v>1.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5683,7 +5675,7 @@
         <v>19.43</v>
       </c>
       <c r="L65" t="n">
-        <v>-3.5</v>
+        <v>-4.79</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -5699,14 +5691,14 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>52.63</v>
+        <v>53.57</v>
       </c>
       <c r="S65" t="n">
-        <v>74.25</v>
+        <v>68.42</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -5716,7 +5708,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5727,19 +5719,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="C66" t="n">
-        <v>78.25</v>
+        <v>42.52</v>
       </c>
       <c r="D66" t="n">
-        <v>2437800</v>
+        <v>1337000</v>
       </c>
       <c r="E66" t="n">
-        <v>3343425</v>
+        <v>3050005</v>
       </c>
       <c r="F66" t="n">
-        <v>0.73</v>
+        <v>0.44</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5763,7 +5755,7 @@
         <v>31.62</v>
       </c>
       <c r="L66" t="n">
-        <v>1.5</v>
+        <v>0.55</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5779,10 +5771,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>35.85</v>
+        <v>33.93</v>
       </c>
       <c r="S66" t="n">
-        <v>57.48</v>
+        <v>52.04</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5796,7 +5788,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5807,19 +5799,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>23.65</v>
+        <v>23.2</v>
       </c>
       <c r="C67" t="n">
-        <v>89.62</v>
+        <v>93.11</v>
       </c>
       <c r="D67" t="n">
-        <v>3789500</v>
+        <v>4013500</v>
       </c>
       <c r="E67" t="n">
-        <v>7861890</v>
+        <v>7262130</v>
       </c>
       <c r="F67" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5843,7 +5835,7 @@
         <v>21.2</v>
       </c>
       <c r="L67" t="n">
-        <v>11.56</v>
+        <v>9.43</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5863,10 +5855,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>42.2</v>
+        <v>35.14</v>
       </c>
       <c r="S67" t="n">
-        <v>40.83</v>
+        <v>32.4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5880,7 +5872,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5894,16 +5886,16 @@
         <v>20.8</v>
       </c>
       <c r="C68" t="n">
-        <v>22.98</v>
+        <v>23.72</v>
       </c>
       <c r="D68" t="n">
-        <v>1104900</v>
+        <v>1140200</v>
       </c>
       <c r="E68" t="n">
-        <v>1289340</v>
+        <v>1271575</v>
       </c>
       <c r="F68" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5943,10 +5935,10 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="S68" t="n">
-        <v>25.21</v>
+        <v>19.03</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5960,7 +5952,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -5971,19 +5963,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="C69" t="n">
-        <v>313.31</v>
+        <v>302.44</v>
       </c>
       <c r="D69" t="n">
-        <v>29281500</v>
+        <v>28003900</v>
       </c>
       <c r="E69" t="n">
-        <v>43476885</v>
+        <v>43555290</v>
       </c>
       <c r="F69" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -6004,10 +5996,10 @@
         <v>10.9</v>
       </c>
       <c r="K69" t="n">
-        <v>12.48</v>
+        <v>12.4</v>
       </c>
       <c r="L69" t="n">
-        <v>-14.23</v>
+        <v>-12.9</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -6023,10 +6015,10 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>45.1</v>
+        <v>50</v>
       </c>
       <c r="S69" t="n">
-        <v>42.31</v>
+        <v>42.4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6040,7 +6032,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -6051,23 +6043,23 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="C70" t="n">
-        <v>142.03</v>
+        <v>75.55</v>
       </c>
       <c r="D70" t="n">
-        <v>11453800</v>
+        <v>6044000</v>
       </c>
       <c r="E70" t="n">
-        <v>11300990</v>
+        <v>11290115</v>
       </c>
       <c r="F70" t="n">
-        <v>1.01</v>
+        <v>0.54</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6081,13 +6073,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>13.32</v>
+        <v>13.23</v>
       </c>
       <c r="K70" t="n">
         <v>15</v>
       </c>
       <c r="L70" t="n">
-        <v>-17.36</v>
+        <v>-16.69</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6103,10 +6095,10 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>50.19</v>
+        <v>58.33</v>
       </c>
       <c r="S70" t="n">
-        <v>58.38</v>
+        <v>54.65</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6120,7 +6112,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -6131,23 +6123,23 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="C71" t="n">
-        <v>47.11</v>
+        <v>33.75</v>
       </c>
       <c r="D71" t="n">
-        <v>2963100</v>
+        <v>2136100</v>
       </c>
       <c r="E71" t="n">
-        <v>2263050</v>
+        <v>2260250</v>
       </c>
       <c r="F71" t="n">
-        <v>1.31</v>
+        <v>0.95</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6167,7 +6159,7 @@
         <v>19.19</v>
       </c>
       <c r="L71" t="n">
-        <v>-17.12</v>
+        <v>-17.64</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -6183,14 +6175,14 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>41.18</v>
+        <v>35.42</v>
       </c>
       <c r="S71" t="n">
-        <v>37.78</v>
+        <v>29.06</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -6200,7 +6192,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -6214,16 +6206,16 @@
         <v>19.8</v>
       </c>
       <c r="C72" t="n">
-        <v>287.42</v>
+        <v>184.56</v>
       </c>
       <c r="D72" t="n">
-        <v>14516100</v>
+        <v>9321400</v>
       </c>
       <c r="E72" t="n">
-        <v>18987315</v>
+        <v>18700615</v>
       </c>
       <c r="F72" t="n">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -6244,10 +6236,10 @@
         <v>19.55</v>
       </c>
       <c r="K72" t="n">
-        <v>20.3</v>
+        <v>20.19</v>
       </c>
       <c r="L72" t="n">
-        <v>-2.49</v>
+        <v>-1.91</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -6256,17 +6248,21 @@
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>50.82</v>
+        <v>52.54</v>
       </c>
       <c r="S72" t="n">
-        <v>52.25</v>
+        <v>48.03</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6280,7 +6276,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -6291,19 +6287,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>67.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>132.54</v>
+        <v>118.39</v>
       </c>
       <c r="D73" t="n">
-        <v>1960700</v>
+        <v>1756600</v>
       </c>
       <c r="E73" t="n">
-        <v>3562600</v>
+        <v>3532580</v>
       </c>
       <c r="F73" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -6327,7 +6323,7 @@
         <v>70.05</v>
       </c>
       <c r="L73" t="n">
-        <v>-3.5</v>
+        <v>-3.78</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -6347,10 +6343,10 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>49.66</v>
+        <v>52.17</v>
       </c>
       <c r="S73" t="n">
-        <v>42.74</v>
+        <v>45.14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -6364,7 +6360,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -6375,19 +6371,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>33.8</v>
+        <v>33.55</v>
       </c>
       <c r="C74" t="n">
-        <v>611.64</v>
+        <v>619.41</v>
       </c>
       <c r="D74" t="n">
-        <v>18096000</v>
+        <v>18462300</v>
       </c>
       <c r="E74" t="n">
-        <v>17599200</v>
+        <v>17767130</v>
       </c>
       <c r="F74" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -6411,7 +6407,7 @@
         <v>31.5</v>
       </c>
       <c r="L74" t="n">
-        <v>7.3</v>
+        <v>6.51</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6431,10 +6427,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>67.09</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="S74" t="n">
-        <v>63.39</v>
+        <v>62.35</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -6448,7 +6444,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -6459,19 +6455,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="C75" t="n">
-        <v>60.18</v>
+        <v>81.84</v>
       </c>
       <c r="D75" t="n">
-        <v>5057300</v>
+        <v>6763800</v>
       </c>
       <c r="E75" t="n">
-        <v>4979195</v>
+        <v>5144015</v>
       </c>
       <c r="F75" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -6495,7 +6491,7 @@
         <v>13.2</v>
       </c>
       <c r="L75" t="n">
-        <v>-9.880000000000001</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6511,14 +6507,14 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>68.18000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="S75" t="n">
-        <v>69.97</v>
+        <v>71.56</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -6528,7 +6524,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -6539,23 +6535,23 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>28.95</v>
+        <v>28.45</v>
       </c>
       <c r="C76" t="n">
-        <v>87.42</v>
+        <v>80.38</v>
       </c>
       <c r="D76" t="n">
-        <v>3019600</v>
+        <v>2825200</v>
       </c>
       <c r="E76" t="n">
-        <v>2927000</v>
+        <v>2936810</v>
       </c>
       <c r="F76" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6575,7 +6571,7 @@
         <v>32.59</v>
       </c>
       <c r="L76" t="n">
-        <v>-11.17</v>
+        <v>-12.7</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6591,10 +6587,10 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>53.27</v>
+        <v>54.81</v>
       </c>
       <c r="S76" t="n">
-        <v>62.67</v>
+        <v>57</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6608,30 +6604,30 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TNG</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>19.4</v>
+        <v>12.7</v>
       </c>
       <c r="C77" t="n">
-        <v>21.89</v>
+        <v>195.52</v>
       </c>
       <c r="D77" t="n">
-        <v>1128300</v>
+        <v>15395300</v>
       </c>
       <c r="E77" t="n">
-        <v>1101380</v>
+        <v>13118910</v>
       </c>
       <c r="F77" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6649,13 +6645,13 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>16.98</v>
+        <v>12.2</v>
       </c>
       <c r="K77" t="n">
-        <v>17.78</v>
+        <v>12.68</v>
       </c>
       <c r="L77" t="n">
-        <v>9.08</v>
+        <v>0.2</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -6671,10 +6667,10 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>65.67</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="S77" t="n">
-        <v>77.17</v>
+        <v>79.92</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6688,34 +6684,34 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>12.9</v>
+        <v>56.1</v>
       </c>
       <c r="C78" t="n">
-        <v>286.35</v>
+        <v>136.78</v>
       </c>
       <c r="D78" t="n">
-        <v>22197700</v>
+        <v>2438200</v>
       </c>
       <c r="E78" t="n">
-        <v>12695280</v>
+        <v>2978715</v>
       </c>
       <c r="F78" t="n">
-        <v>1.75</v>
+        <v>0.82</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6725,21 +6721,21 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>12.2</v>
+        <v>57.3</v>
       </c>
       <c r="K78" t="n">
-        <v>12.68</v>
+        <v>59.12</v>
       </c>
       <c r="L78" t="n">
-        <v>1.78</v>
+        <v>-5.12</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -6751,14 +6747,14 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>76.19</v>
+        <v>38.3</v>
       </c>
       <c r="S78" t="n">
-        <v>84.02</v>
+        <v>45.21</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -6768,54 +6764,54 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>56.1</v>
+        <v>15.25</v>
       </c>
       <c r="C79" t="n">
-        <v>202.91</v>
+        <v>34.72</v>
       </c>
       <c r="D79" t="n">
-        <v>3617000</v>
+        <v>2276600</v>
       </c>
       <c r="E79" t="n">
-        <v>2981575</v>
+        <v>2285960</v>
       </c>
       <c r="F79" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>57</v>
+        <v>14.88</v>
       </c>
       <c r="K79" t="n">
-        <v>59.12</v>
+        <v>17.1</v>
       </c>
       <c r="L79" t="n">
-        <v>-5.12</v>
+        <v>-10.84</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -6831,47 +6827,47 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>37.5</v>
+        <v>77.97</v>
       </c>
       <c r="S79" t="n">
-        <v>50.41</v>
+        <v>75.45</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15.15</v>
+        <v>19.15</v>
       </c>
       <c r="C80" t="n">
-        <v>25.19</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>1662600</v>
+        <v>4794600</v>
       </c>
       <c r="E80" t="n">
-        <v>2230265</v>
+        <v>7685635</v>
       </c>
       <c r="F80" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -6880,7 +6876,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6889,13 +6885,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>14.88</v>
+        <v>20.6</v>
       </c>
       <c r="K80" t="n">
-        <v>17.1</v>
+        <v>22.65</v>
       </c>
       <c r="L80" t="n">
-        <v>-11.43</v>
+        <v>-15.45</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -6904,54 +6900,58 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>75.86</v>
+        <v>50.88</v>
       </c>
       <c r="S80" t="n">
-        <v>74.78</v>
+        <v>53.24</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19.15</v>
+        <v>27.6</v>
       </c>
       <c r="C81" t="n">
-        <v>111.45</v>
+        <v>33.64</v>
       </c>
       <c r="D81" t="n">
-        <v>5820000</v>
+        <v>1218700</v>
       </c>
       <c r="E81" t="n">
-        <v>7797560</v>
+        <v>1679640</v>
       </c>
       <c r="F81" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>20.6</v>
+        <v>29.08</v>
       </c>
       <c r="K81" t="n">
-        <v>22.88</v>
+        <v>30.82</v>
       </c>
       <c r="L81" t="n">
-        <v>-16.28</v>
+        <v>-10.46</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6991,10 +6991,10 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>46.03</v>
+        <v>46.88</v>
       </c>
       <c r="S81" t="n">
-        <v>57.59</v>
+        <v>60.64</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -7008,58 +7008,58 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>27.7</v>
+        <v>38.8</v>
       </c>
       <c r="C82" t="n">
-        <v>33.94</v>
+        <v>29.2</v>
       </c>
       <c r="D82" t="n">
-        <v>1225100</v>
+        <v>752600</v>
       </c>
       <c r="E82" t="n">
-        <v>1678320</v>
+        <v>641935</v>
       </c>
       <c r="F82" t="n">
-        <v>0.73</v>
+        <v>1.17</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>29.08</v>
+        <v>36.85</v>
       </c>
       <c r="K82" t="n">
-        <v>30.82</v>
+        <v>36.5</v>
       </c>
       <c r="L82" t="n">
-        <v>-10.14</v>
+        <v>6.3</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -7071,24 +7071,24 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>47.37</v>
+        <v>70.97</v>
       </c>
       <c r="S82" t="n">
-        <v>66.23</v>
+        <v>68.11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7099,19 +7099,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>46.3</v>
+        <v>44.35</v>
       </c>
       <c r="C83" t="n">
-        <v>198.57</v>
+        <v>57.66</v>
       </c>
       <c r="D83" t="n">
-        <v>4288800</v>
+        <v>1300200</v>
       </c>
       <c r="E83" t="n">
-        <v>803665</v>
+        <v>847825</v>
       </c>
       <c r="F83" t="n">
-        <v>5.34</v>
+        <v>1.53</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>40.8</v>
       </c>
       <c r="L83" t="n">
-        <v>13.48</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>60.99</v>
+        <v>43.88</v>
       </c>
       <c r="S83" t="n">
-        <v>65.89</v>
+        <v>55.32</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7183,19 +7183,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>63.9</v>
+        <v>63.5</v>
       </c>
       <c r="C84" t="n">
-        <v>464.82</v>
+        <v>237.74</v>
       </c>
       <c r="D84" t="n">
-        <v>7274200</v>
+        <v>3743900</v>
       </c>
       <c r="E84" t="n">
-        <v>8138550</v>
+        <v>7955280</v>
       </c>
       <c r="F84" t="n">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>70.52</v>
       </c>
       <c r="L84" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>39.33</v>
+        <v>40.34</v>
       </c>
       <c r="S84" t="n">
-        <v>34.21</v>
+        <v>34.57</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7263,23 +7263,23 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>13.95</v>
+        <v>14.1</v>
       </c>
       <c r="C85" t="n">
-        <v>64.91</v>
+        <v>104.46</v>
       </c>
       <c r="D85" t="n">
-        <v>4652900</v>
+        <v>7408400</v>
       </c>
       <c r="E85" t="n">
-        <v>6079315</v>
+        <v>6251825</v>
       </c>
       <c r="F85" t="n">
-        <v>0.77</v>
+        <v>1.18</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -7299,7 +7299,7 @@
         <v>14.16</v>
       </c>
       <c r="L85" t="n">
-        <v>-1.45</v>
+        <v>-0.39</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>60.98</v>
+        <v>55.56</v>
       </c>
       <c r="S85" t="n">
-        <v>72.28</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7343,19 +7343,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>237</v>
+        <v>240.2</v>
       </c>
       <c r="C86" t="n">
-        <v>525.8099999999999</v>
+        <v>402.72</v>
       </c>
       <c r="D86" t="n">
-        <v>2218600</v>
+        <v>1676600</v>
       </c>
       <c r="E86" t="n">
-        <v>2766775</v>
+        <v>2797780</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -7379,7 +7379,7 @@
         <v>224.85</v>
       </c>
       <c r="L86" t="n">
-        <v>5.4</v>
+        <v>6.83</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -7388,17 +7388,21 @@
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>54.1</v>
+        <v>58.2</v>
       </c>
       <c r="S86" t="n">
-        <v>32.96</v>
+        <v>39.9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -7412,7 +7416,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7423,23 +7427,23 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="C87" t="n">
-        <v>373.76</v>
+        <v>353.91</v>
       </c>
       <c r="D87" t="n">
-        <v>29900900</v>
+        <v>28773200</v>
       </c>
       <c r="E87" t="n">
-        <v>29626115</v>
+        <v>30090345</v>
       </c>
       <c r="F87" t="n">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7459,7 +7463,7 @@
         <v>14.95</v>
       </c>
       <c r="L87" t="n">
-        <v>-16.39</v>
+        <v>-17.73</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -7478,7 +7482,7 @@
         <v>60.71</v>
       </c>
       <c r="S87" t="n">
-        <v>72.53</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -7492,7 +7496,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7503,23 +7507,23 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>132</v>
+        <v>132.9</v>
       </c>
       <c r="C88" t="n">
-        <v>138.59</v>
+        <v>118.36</v>
       </c>
       <c r="D88" t="n">
-        <v>1049900</v>
+        <v>890600</v>
       </c>
       <c r="E88" t="n">
-        <v>933580</v>
+        <v>933245</v>
       </c>
       <c r="F88" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7539,11 +7543,11 @@
         <v>132.12</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.09</v>
+        <v>0.59</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -7555,14 +7559,14 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>69.05</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="S88" t="n">
-        <v>45.39</v>
+        <v>51.95</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -7572,7 +7576,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7583,19 +7587,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>13.55</v>
+        <v>13.35</v>
       </c>
       <c r="C89" t="n">
-        <v>87.63</v>
+        <v>99.58</v>
       </c>
       <c r="D89" t="n">
-        <v>6467300</v>
+        <v>7459100</v>
       </c>
       <c r="E89" t="n">
-        <v>9664370</v>
+        <v>9678375</v>
       </c>
       <c r="F89" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7613,13 +7617,13 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>15.05</v>
+        <v>14.98</v>
       </c>
       <c r="K89" t="n">
         <v>15.85</v>
       </c>
       <c r="L89" t="n">
-        <v>-14.51</v>
+        <v>-15.77</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7635,10 +7639,10 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>44</v>
+        <v>44.9</v>
       </c>
       <c r="S89" t="n">
-        <v>47.16</v>
+        <v>42.56</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -7652,7 +7656,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7666,16 +7670,16 @@
         <v>57.6</v>
       </c>
       <c r="C90" t="n">
-        <v>73.72</v>
+        <v>63.56</v>
       </c>
       <c r="D90" t="n">
-        <v>1279800</v>
+        <v>1103400</v>
       </c>
       <c r="E90" t="n">
-        <v>1926265</v>
+        <v>1918020</v>
       </c>
       <c r="F90" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7693,7 +7697,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>60.65</v>
+        <v>60.7</v>
       </c>
       <c r="K90" t="n">
         <v>59.5</v>
@@ -7715,10 +7719,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>42</v>
+        <v>45.65</v>
       </c>
       <c r="S90" t="n">
-        <v>43.57</v>
+        <v>38.33</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7732,7 +7736,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7743,23 +7747,23 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="C91" t="n">
-        <v>217.66</v>
+        <v>421.47</v>
       </c>
       <c r="D91" t="n">
-        <v>9222700</v>
+        <v>18166900</v>
       </c>
       <c r="E91" t="n">
-        <v>15740110</v>
+        <v>15819040</v>
       </c>
       <c r="F91" t="n">
-        <v>0.59</v>
+        <v>1.15</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7779,7 +7783,7 @@
         <v>21.98</v>
       </c>
       <c r="L91" t="n">
-        <v>7.39</v>
+        <v>5.57</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -7799,10 +7803,10 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>57.69</v>
+        <v>46.43</v>
       </c>
       <c r="S91" t="n">
-        <v>66.75</v>
+        <v>59.59</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7816,7 +7820,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7830,16 +7834,16 @@
         <v>56.8</v>
       </c>
       <c r="C92" t="n">
-        <v>149.92</v>
+        <v>139.89</v>
       </c>
       <c r="D92" t="n">
-        <v>2639400</v>
+        <v>2462800</v>
       </c>
       <c r="E92" t="n">
-        <v>1862755</v>
+        <v>1926765</v>
       </c>
       <c r="F92" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -7886,7 +7890,7 @@
         <v>47.94</v>
       </c>
       <c r="S92" t="n">
-        <v>58.41</v>
+        <v>50.12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7900,7 +7904,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7911,19 +7915,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C93" t="n">
-        <v>108.9</v>
+        <v>111.87</v>
       </c>
       <c r="D93" t="n">
-        <v>1266300</v>
+        <v>1285900</v>
       </c>
       <c r="E93" t="n">
-        <v>801380</v>
+        <v>833245</v>
       </c>
       <c r="F93" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -7941,13 +7945,13 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>79.84999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K93" t="n">
         <v>85.5</v>
       </c>
       <c r="L93" t="n">
-        <v>0.58</v>
+        <v>1.75</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -7963,14 +7967,14 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>64.41</v>
+        <v>72.09</v>
       </c>
       <c r="S93" t="n">
-        <v>63.25</v>
+        <v>65.37</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -7980,7 +7984,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -7991,23 +7995,23 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="C94" t="n">
-        <v>85.81999999999999</v>
+        <v>70.11</v>
       </c>
       <c r="D94" t="n">
-        <v>3531800</v>
+        <v>2873200</v>
       </c>
       <c r="E94" t="n">
-        <v>3382665</v>
+        <v>3370390</v>
       </c>
       <c r="F94" t="n">
-        <v>1.04</v>
+        <v>0.85</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8027,7 +8031,7 @@
         <v>28.56</v>
       </c>
       <c r="L94" t="n">
-        <v>-14.92</v>
+        <v>-14.57</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -8043,10 +8047,10 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>54.63</v>
+        <v>61.62</v>
       </c>
       <c r="S94" t="n">
-        <v>45.73</v>
+        <v>45.47</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -8060,7 +8064,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -8071,23 +8075,23 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="C95" t="n">
-        <v>212.99</v>
+        <v>245.86</v>
       </c>
       <c r="D95" t="n">
-        <v>14689200</v>
+        <v>17193000</v>
       </c>
       <c r="E95" t="n">
-        <v>9863710</v>
+        <v>10338525</v>
       </c>
       <c r="F95" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8104,10 +8108,10 @@
         <v>14.02</v>
       </c>
       <c r="K95" t="n">
-        <v>18.1</v>
+        <v>17.92</v>
       </c>
       <c r="L95" t="n">
-        <v>-19.89</v>
+        <v>-20.22</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -8123,14 +8127,14 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>68.23999999999999</v>
+        <v>60.26</v>
       </c>
       <c r="S95" t="n">
-        <v>70.31</v>
+        <v>60.36</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -8140,7 +8144,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>
@@ -8151,19 +8155,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="C96" t="n">
-        <v>20.71</v>
+        <v>20.23</v>
       </c>
       <c r="D96" t="n">
-        <v>1025400</v>
+        <v>996600</v>
       </c>
       <c r="E96" t="n">
-        <v>963185</v>
+        <v>960460</v>
       </c>
       <c r="F96" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8187,7 +8191,7 @@
         <v>21.3</v>
       </c>
       <c r="L96" t="n">
-        <v>-5.16</v>
+        <v>-4.69</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -8203,10 +8207,10 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="S96" t="n">
-        <v>31.74</v>
+        <v>34.68</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -8220,87 +8224,7 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-10-26 22:39:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>VVS</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="C97" t="n">
-        <v>29.76</v>
-      </c>
-      <c r="D97" t="n">
-        <v>370600</v>
-      </c>
-      <c r="E97" t="n">
-        <v>200830</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>🔥 Tiền Vào Mạnh</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>93.84999999999999</v>
-      </c>
-      <c r="K97" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="L97" t="n">
-        <v>-5.63</v>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R97" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="S97" t="n">
-        <v>39.37</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>2026-10-26 22:39:46</t>
+          <t>2026-10-27 22:05:20</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V96"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,23 +535,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.3</v>
+        <v>21.35</v>
       </c>
       <c r="C2" t="n">
-        <v>178.9</v>
+        <v>228.43</v>
       </c>
       <c r="D2" t="n">
-        <v>8398900</v>
+        <v>10699200</v>
       </c>
       <c r="E2" t="n">
-        <v>8737665</v>
+        <v>8975725</v>
       </c>
       <c r="F2" t="n">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,7 +571,7 @@
         <v>21.58</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.27</v>
+        <v>-1.04</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>63.83</v>
+        <v>73.81</v>
       </c>
       <c r="S2" t="n">
-        <v>74.95999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>26.39</v>
+        <v>20.02</v>
       </c>
       <c r="D3" t="n">
-        <v>640600</v>
+        <v>488300</v>
       </c>
       <c r="E3" t="n">
-        <v>788520</v>
+        <v>800670</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         <v>41.6</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.96</v>
+        <v>-1.44</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>52.38</v>
+        <v>47.54</v>
       </c>
       <c r="S3" t="n">
-        <v>69.84999999999999</v>
+        <v>65.23</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -695,19 +695,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.55</v>
+        <v>17.5</v>
       </c>
       <c r="C4" t="n">
-        <v>22.32</v>
+        <v>22.08</v>
       </c>
       <c r="D4" t="n">
-        <v>1203000</v>
+        <v>1262000</v>
       </c>
       <c r="E4" t="n">
-        <v>1494140</v>
+        <v>1545660</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17.4</v>
+        <v>16.46</v>
       </c>
       <c r="K4" t="n">
-        <v>20.08</v>
+        <v>18.94</v>
       </c>
       <c r="L4" t="n">
         <v>-7.6</v>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>58.87</v>
+        <v>48.54</v>
       </c>
       <c r="S4" t="n">
-        <v>62.33</v>
+        <v>54.71</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.95</v>
+        <v>30.15</v>
       </c>
       <c r="C5" t="n">
-        <v>43.28</v>
+        <v>37.16</v>
       </c>
       <c r="D5" t="n">
-        <v>1445200</v>
+        <v>1232600</v>
       </c>
       <c r="E5" t="n">
-        <v>1915385</v>
+        <v>1900110</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>28.4</v>
       </c>
       <c r="L5" t="n">
-        <v>5.46</v>
+        <v>6.16</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -820,17 +820,21 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>52.63</v>
+        <v>59.14</v>
       </c>
       <c r="S5" t="n">
-        <v>63.42</v>
+        <v>62.28</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -844,7 +848,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -855,19 +859,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.55</v>
+        <v>39.8</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>25.31</v>
       </c>
       <c r="D6" t="n">
-        <v>665800</v>
+        <v>636000</v>
       </c>
       <c r="E6" t="n">
-        <v>561645</v>
+        <v>566030</v>
       </c>
       <c r="F6" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -876,7 +880,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -891,7 +895,7 @@
         <v>45.55</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.98</v>
+        <v>-12.62</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -907,24 +911,24 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>63.23</v>
+        <v>54.14</v>
       </c>
       <c r="S6" t="n">
-        <v>70.66</v>
+        <v>63.27</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -938,20 +942,20 @@
         <v>33.65</v>
       </c>
       <c r="C7" t="n">
-        <v>83.95999999999999</v>
+        <v>146.67</v>
       </c>
       <c r="D7" t="n">
-        <v>2495000</v>
+        <v>4358700</v>
       </c>
       <c r="E7" t="n">
-        <v>3024440</v>
+        <v>3108420</v>
       </c>
       <c r="F7" t="n">
-        <v>0.82</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -987,10 +991,10 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>40.23</v>
+        <v>46.67</v>
       </c>
       <c r="S7" t="n">
-        <v>44.72</v>
+        <v>53.48</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1004,34 +1008,34 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSI</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.95</v>
+        <v>28.75</v>
       </c>
       <c r="C8" t="n">
-        <v>22.09</v>
+        <v>108.54</v>
       </c>
       <c r="D8" t="n">
-        <v>790500</v>
+        <v>3775400</v>
       </c>
       <c r="E8" t="n">
-        <v>374910</v>
+        <v>8772295</v>
       </c>
       <c r="F8" t="n">
-        <v>2.11</v>
+        <v>0.43</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,17 +1049,17 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>26.75</v>
+        <v>28.24</v>
       </c>
       <c r="K8" t="n">
-        <v>30.35</v>
+        <v>27.96</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.91</v>
+        <v>2.83</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1067,14 +1071,14 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>73.13</v>
+        <v>28.19</v>
       </c>
       <c r="S8" t="n">
-        <v>74.29000000000001</v>
+        <v>24.46</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1084,34 +1088,34 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.9</v>
+        <v>69.8</v>
       </c>
       <c r="C9" t="n">
-        <v>161.89</v>
+        <v>61.93</v>
       </c>
       <c r="D9" t="n">
-        <v>5601600</v>
+        <v>887300</v>
       </c>
       <c r="E9" t="n">
-        <v>9237460</v>
+        <v>883110</v>
       </c>
       <c r="F9" t="n">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1121,17 +1125,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28.24</v>
+        <v>67.5</v>
       </c>
       <c r="K9" t="n">
-        <v>27.96</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>3.36</v>
+        <v>4.02</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1147,14 +1151,14 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>31.13</v>
+        <v>26.59</v>
       </c>
       <c r="S9" t="n">
-        <v>31.54</v>
+        <v>12.03</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1164,58 +1168,58 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67.8</v>
+        <v>11.3</v>
       </c>
       <c r="C10" t="n">
-        <v>32.16</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>474300</v>
+        <v>8126000</v>
       </c>
       <c r="E10" t="n">
-        <v>911810</v>
+        <v>6963040</v>
       </c>
       <c r="F10" t="n">
-        <v>0.52</v>
+        <v>1.17</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>67.5</v>
+        <v>11.65</v>
       </c>
       <c r="K10" t="n">
-        <v>67.09999999999999</v>
+        <v>13.61</v>
       </c>
       <c r="L10" t="n">
-        <v>1.04</v>
+        <v>-16.97</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1227,47 +1231,47 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>28.25</v>
+        <v>79.17</v>
       </c>
       <c r="S10" t="n">
-        <v>15.17</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CII</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.5</v>
+        <v>13.75</v>
       </c>
       <c r="C11" t="n">
-        <v>45.83</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>3985000</v>
+        <v>8145100</v>
       </c>
       <c r="E11" t="n">
-        <v>6750295</v>
+        <v>9310220</v>
       </c>
       <c r="F11" t="n">
-        <v>0.59</v>
+        <v>0.87</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1276,22 +1280,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>11.65</v>
+        <v>13.27</v>
       </c>
       <c r="K11" t="n">
-        <v>13.61</v>
+        <v>15.85</v>
       </c>
       <c r="L11" t="n">
-        <v>-15.5</v>
+        <v>-13.25</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1300,58 +1304,54 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>76</v>
+        <v>77.33</v>
       </c>
       <c r="S11" t="n">
-        <v>83.09999999999999</v>
+        <v>80.67</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CII</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.85</v>
+        <v>68</v>
       </c>
       <c r="C12" t="n">
-        <v>186.04</v>
+        <v>31.83</v>
       </c>
       <c r="D12" t="n">
-        <v>13432700</v>
+        <v>468100</v>
       </c>
       <c r="E12" t="n">
-        <v>9159840</v>
+        <v>461770</v>
       </c>
       <c r="F12" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1365,17 +1365,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13.27</v>
+        <v>61.7</v>
       </c>
       <c r="K12" t="n">
-        <v>15.85</v>
+        <v>72.5</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.62</v>
+        <v>-6.21</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>73.42</v>
+        <v>72.8</v>
       </c>
       <c r="S12" t="n">
-        <v>82.76000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1408,34 +1408,34 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CTD</t>
+          <t>CTG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.5</v>
+        <v>30.7</v>
       </c>
       <c r="C13" t="n">
-        <v>44.32</v>
+        <v>209.98</v>
       </c>
       <c r="D13" t="n">
-        <v>656600</v>
+        <v>6839900</v>
       </c>
       <c r="E13" t="n">
-        <v>454845</v>
+        <v>7024280</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>0.97</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1445,17 +1445,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>61.65</v>
+        <v>30.7</v>
       </c>
       <c r="K13" t="n">
-        <v>72.5</v>
+        <v>32.32</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.9</v>
+        <v>-5.01</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>72.58</v>
+        <v>72.06</v>
       </c>
       <c r="S13" t="n">
-        <v>73.98999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1488,30 +1488,30 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CTG</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.35</v>
+        <v>21.7</v>
       </c>
       <c r="C14" t="n">
-        <v>113.07</v>
+        <v>29.36</v>
       </c>
       <c r="D14" t="n">
-        <v>3725400</v>
+        <v>1352800</v>
       </c>
       <c r="E14" t="n">
-        <v>6915895</v>
+        <v>1445440</v>
       </c>
       <c r="F14" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>30.7</v>
+        <v>21.4</v>
       </c>
       <c r="K14" t="n">
-        <v>32.32</v>
+        <v>24.1</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.1</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1544,58 +1544,54 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>58.33</v>
+        <v>70.3</v>
       </c>
       <c r="S14" t="n">
-        <v>51.61</v>
+        <v>70.33</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21.8</v>
+        <v>15.9</v>
       </c>
       <c r="C15" t="n">
-        <v>37.9</v>
+        <v>28.78</v>
       </c>
       <c r="D15" t="n">
-        <v>1738600</v>
+        <v>1809800</v>
       </c>
       <c r="E15" t="n">
-        <v>1408255</v>
+        <v>1805425</v>
       </c>
       <c r="F15" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1604,7 +1600,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1613,13 +1609,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>21.4</v>
+        <v>16.32</v>
       </c>
       <c r="K15" t="n">
-        <v>24.1</v>
+        <v>17.64</v>
       </c>
       <c r="L15" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1635,75 +1631,75 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>68.27</v>
+        <v>57.45</v>
       </c>
       <c r="S15" t="n">
-        <v>72.58</v>
+        <v>59.23</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>DCL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.1</v>
+        <v>46.3</v>
       </c>
       <c r="C16" t="n">
-        <v>23.6</v>
+        <v>38.36</v>
       </c>
       <c r="D16" t="n">
-        <v>1465600</v>
+        <v>828600</v>
       </c>
       <c r="E16" t="n">
-        <v>1754490</v>
+        <v>688655</v>
       </c>
       <c r="F16" t="n">
-        <v>0.84</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16.32</v>
+        <v>44.65</v>
       </c>
       <c r="K16" t="n">
-        <v>17.66</v>
+        <v>44.05</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.859999999999999</v>
+        <v>5.11</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1715,47 +1711,47 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>68</v>
+        <v>37.66</v>
       </c>
       <c r="S16" t="n">
-        <v>68.56</v>
+        <v>39.74</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46</v>
+        <v>34.8</v>
       </c>
       <c r="C17" t="n">
-        <v>24.95</v>
+        <v>55.18</v>
       </c>
       <c r="D17" t="n">
-        <v>542300</v>
+        <v>1585600</v>
       </c>
       <c r="E17" t="n">
-        <v>679400</v>
+        <v>2140700</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1773,17 +1769,17 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>44.65</v>
+        <v>32.3</v>
       </c>
       <c r="K17" t="n">
-        <v>44.05</v>
+        <v>35.83</v>
       </c>
       <c r="L17" t="n">
-        <v>4.43</v>
+        <v>-2.87</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1795,10 +1791,10 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>47.54</v>
+        <v>53.17</v>
       </c>
       <c r="S17" t="n">
-        <v>36.48</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1812,34 +1808,34 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.65</v>
+        <v>42.35</v>
       </c>
       <c r="C18" t="n">
-        <v>47.91</v>
+        <v>251.74</v>
       </c>
       <c r="D18" t="n">
-        <v>1382600</v>
+        <v>5944200</v>
       </c>
       <c r="E18" t="n">
-        <v>2243285</v>
+        <v>1654990</v>
       </c>
       <c r="F18" t="n">
-        <v>0.62</v>
+        <v>3.59</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1849,44 +1845,44 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32.3</v>
+        <v>39.83</v>
       </c>
       <c r="K18" t="n">
-        <v>36</v>
+        <v>39.83</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.74</v>
+        <v>6.33</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>53.54</v>
+        <v>24.77</v>
       </c>
       <c r="S18" t="n">
-        <v>75.11</v>
+        <v>20.8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1896,30 +1892,30 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45.5</v>
+        <v>9.77</v>
       </c>
       <c r="C19" t="n">
-        <v>47.89</v>
+        <v>39.85</v>
       </c>
       <c r="D19" t="n">
-        <v>1052500</v>
+        <v>4079000</v>
       </c>
       <c r="E19" t="n">
-        <v>1519055</v>
+        <v>5089320</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1928,33 +1924,29 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>39.83</v>
+        <v>9.82</v>
       </c>
       <c r="K19" t="n">
-        <v>39.83</v>
+        <v>11.52</v>
       </c>
       <c r="L19" t="n">
-        <v>14.24</v>
+        <v>-15.23</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
@@ -1963,71 +1955,71 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>39.51</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>34.29</v>
+        <v>59.11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>DPG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.779999999999999</v>
+        <v>30.95</v>
       </c>
       <c r="C20" t="n">
-        <v>44.81</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4581700</v>
+        <v>749500</v>
       </c>
       <c r="E20" t="n">
-        <v>5020490</v>
+        <v>502010</v>
       </c>
       <c r="F20" t="n">
-        <v>0.91</v>
+        <v>1.49</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>9.82</v>
+        <v>28.82</v>
       </c>
       <c r="K20" t="n">
-        <v>11.52</v>
+        <v>35.3</v>
       </c>
       <c r="L20" t="n">
-        <v>-15.14</v>
+        <v>-12.34</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2043,71 +2035,71 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>66.44</v>
+        <v>82.98</v>
       </c>
       <c r="S20" t="n">
-        <v>59.32</v>
+        <v>89.02</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DPG</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30.3</v>
+        <v>21.3</v>
       </c>
       <c r="C21" t="n">
-        <v>21.21</v>
+        <v>22.48</v>
       </c>
       <c r="D21" t="n">
-        <v>699900</v>
+        <v>1055500</v>
       </c>
       <c r="E21" t="n">
-        <v>475905</v>
+        <v>2050670</v>
       </c>
       <c r="F21" t="n">
-        <v>1.47</v>
+        <v>0.51</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>28.82</v>
+        <v>22.18</v>
       </c>
       <c r="K21" t="n">
-        <v>35.3</v>
+        <v>23.62</v>
       </c>
       <c r="L21" t="n">
-        <v>-14.18</v>
+        <v>-9.82</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2123,51 +2115,51 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>80</v>
+        <v>33.33</v>
       </c>
       <c r="S21" t="n">
-        <v>85.59</v>
+        <v>28.96</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21.35</v>
+        <v>9.99</v>
       </c>
       <c r="C22" t="n">
-        <v>39.63</v>
+        <v>103.51</v>
       </c>
       <c r="D22" t="n">
-        <v>1856300</v>
+        <v>10360900</v>
       </c>
       <c r="E22" t="n">
-        <v>2127525</v>
+        <v>9625335</v>
       </c>
       <c r="F22" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2181,13 +2173,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>22.18</v>
+        <v>10.73</v>
       </c>
       <c r="K22" t="n">
-        <v>23.69</v>
+        <v>11.89</v>
       </c>
       <c r="L22" t="n">
-        <v>-9.880000000000001</v>
+        <v>-15.94</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2203,10 +2195,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>45</v>
+        <v>60.56</v>
       </c>
       <c r="S22" t="n">
-        <v>39.2</v>
+        <v>61.24</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2220,30 +2212,30 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14.4</v>
+        <v>16.65</v>
       </c>
       <c r="C23" t="n">
-        <v>30.43</v>
+        <v>101.09</v>
       </c>
       <c r="D23" t="n">
-        <v>2113300</v>
+        <v>6071200</v>
       </c>
       <c r="E23" t="n">
-        <v>1768360</v>
+        <v>4886950</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2252,26 +2244,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>14.38</v>
+        <v>17.2</v>
       </c>
       <c r="K23" t="n">
-        <v>14.34</v>
+        <v>19.52</v>
       </c>
       <c r="L23" t="n">
-        <v>0.45</v>
+        <v>-14.72</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2283,51 +2275,51 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>32.61</v>
+        <v>58.21</v>
       </c>
       <c r="S23" t="n">
-        <v>35.91</v>
+        <v>54.61</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C24" t="n">
-        <v>103.42</v>
+        <v>714.1900000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>10341600</v>
+        <v>13225800</v>
       </c>
       <c r="E24" t="n">
-        <v>9450525</v>
+        <v>6715440</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09</v>
+        <v>1.97</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2341,13 +2333,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>10.73</v>
+        <v>60.95</v>
       </c>
       <c r="K24" t="n">
-        <v>11.89</v>
+        <v>62.27</v>
       </c>
       <c r="L24" t="n">
-        <v>-15.86</v>
+        <v>-13.28</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2363,10 +2355,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>55.61</v>
+        <v>21.78</v>
       </c>
       <c r="S24" t="n">
-        <v>63.11</v>
+        <v>33.4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2380,62 +2372,66 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16.9</v>
+        <v>147</v>
       </c>
       <c r="C25" t="n">
-        <v>112.32</v>
+        <v>149.69</v>
       </c>
       <c r="D25" t="n">
-        <v>6646200</v>
+        <v>1018300</v>
       </c>
       <c r="E25" t="n">
-        <v>4812300</v>
+        <v>573745</v>
       </c>
       <c r="F25" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17.2</v>
+        <v>129.4</v>
       </c>
       <c r="K25" t="n">
-        <v>19.52</v>
+        <v>127.5</v>
       </c>
       <c r="L25" t="n">
-        <v>-13.44</v>
+        <v>15.29</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2443,75 +2439,75 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>57.35</v>
+        <v>43.01</v>
       </c>
       <c r="S25" t="n">
-        <v>57.04</v>
+        <v>41.98</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>55.4</v>
+        <v>77.7</v>
       </c>
       <c r="C26" t="n">
-        <v>478.98</v>
+        <v>37.4</v>
       </c>
       <c r="D26" t="n">
-        <v>8645800</v>
+        <v>481400</v>
       </c>
       <c r="E26" t="n">
-        <v>6206220</v>
+        <v>901190</v>
       </c>
       <c r="F26" t="n">
-        <v>1.39</v>
+        <v>0.53</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>61.6</v>
+        <v>77.31</v>
       </c>
       <c r="K26" t="n">
-        <v>62.92</v>
+        <v>77.69</v>
       </c>
       <c r="L26" t="n">
-        <v>-11.95</v>
+        <v>0.01</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2523,47 +2519,47 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>25.29</v>
+        <v>34.53</v>
       </c>
       <c r="S26" t="n">
-        <v>35.34</v>
+        <v>53.13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>148.6</v>
+        <v>69.2</v>
       </c>
       <c r="C27" t="n">
-        <v>33.39</v>
+        <v>63.36</v>
       </c>
       <c r="D27" t="n">
-        <v>224700</v>
+        <v>915600</v>
       </c>
       <c r="E27" t="n">
-        <v>586545</v>
+        <v>1430655</v>
       </c>
       <c r="F27" t="n">
-        <v>0.38</v>
+        <v>0.64</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2572,86 +2568,78 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>129.25</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>127.5</v>
+        <v>95.83</v>
       </c>
       <c r="L27" t="n">
-        <v>16.55</v>
+        <v>-27.79</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>46.44</v>
+        <v>51.78</v>
       </c>
       <c r="S27" t="n">
-        <v>54.6</v>
+        <v>48.59</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FTS</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.25</v>
+        <v>28.25</v>
       </c>
       <c r="C28" t="n">
-        <v>21.02</v>
+        <v>41.8</v>
       </c>
       <c r="D28" t="n">
-        <v>1091900</v>
+        <v>1479700</v>
       </c>
       <c r="E28" t="n">
-        <v>767840</v>
+        <v>1469015</v>
       </c>
       <c r="F28" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2660,22 +2648,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>20.38</v>
+        <v>27.15</v>
       </c>
       <c r="K28" t="n">
-        <v>22.88</v>
+        <v>29.42</v>
       </c>
       <c r="L28" t="n">
-        <v>-15.85</v>
+        <v>-3.99</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2691,47 +2679,47 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>65.79000000000001</v>
+        <v>53.01</v>
       </c>
       <c r="S28" t="n">
-        <v>64.55</v>
+        <v>58.79</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78.90000000000001</v>
+        <v>23.1</v>
       </c>
       <c r="C29" t="n">
-        <v>54.88</v>
+        <v>138.14</v>
       </c>
       <c r="D29" t="n">
-        <v>695600</v>
+        <v>5980200</v>
       </c>
       <c r="E29" t="n">
-        <v>935960</v>
+        <v>7672890</v>
       </c>
       <c r="F29" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2740,26 +2728,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>77.31</v>
+        <v>23.45</v>
       </c>
       <c r="K29" t="n">
-        <v>77.69</v>
+        <v>28.58</v>
       </c>
       <c r="L29" t="n">
-        <v>1.55</v>
+        <v>-19.16</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2771,75 +2759,75 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>51.53</v>
+        <v>63.27</v>
       </c>
       <c r="S29" t="n">
-        <v>60.78</v>
+        <v>58.37</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="C30" t="n">
-        <v>107.32</v>
+        <v>136.22</v>
       </c>
       <c r="D30" t="n">
-        <v>1535300</v>
+        <v>2522500</v>
       </c>
       <c r="E30" t="n">
-        <v>1537805</v>
+        <v>1807550</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>66.81999999999999</v>
+        <v>52.78</v>
       </c>
       <c r="K30" t="n">
-        <v>95.83</v>
+        <v>51.28</v>
       </c>
       <c r="L30" t="n">
-        <v>-27.06</v>
+        <v>5.29</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2851,51 +2839,51 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>52.85</v>
+        <v>49.22</v>
       </c>
       <c r="S30" t="n">
-        <v>48.77</v>
+        <v>57.35</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28.5</v>
+        <v>31.5</v>
       </c>
       <c r="C31" t="n">
-        <v>51.43</v>
+        <v>47.23</v>
       </c>
       <c r="D31" t="n">
-        <v>1804700</v>
+        <v>1499500</v>
       </c>
       <c r="E31" t="n">
-        <v>1525140</v>
+        <v>2086950</v>
       </c>
       <c r="F31" t="n">
-        <v>1.18</v>
+        <v>0.72</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2905,17 +2893,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>27.15</v>
+        <v>30.22</v>
       </c>
       <c r="K31" t="n">
-        <v>29.42</v>
+        <v>32.78</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.14</v>
+        <v>-3.89</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2931,14 +2919,14 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>52.38</v>
+        <v>26.26</v>
       </c>
       <c r="S31" t="n">
-        <v>60.62</v>
+        <v>41.06</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -2948,58 +2936,58 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>HAH</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.85</v>
+        <v>50.6</v>
       </c>
       <c r="C32" t="n">
-        <v>195.55</v>
+        <v>22.17</v>
       </c>
       <c r="D32" t="n">
-        <v>8558100</v>
+        <v>438200</v>
       </c>
       <c r="E32" t="n">
-        <v>7787080</v>
+        <v>865875</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>23.45</v>
+        <v>48.2</v>
       </c>
       <c r="K32" t="n">
-        <v>28.58</v>
+        <v>49.55</v>
       </c>
       <c r="L32" t="n">
-        <v>-20.03</v>
+        <v>2.12</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3011,75 +2999,75 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>51.82</v>
+        <v>44</v>
       </c>
       <c r="S32" t="n">
-        <v>57.53</v>
+        <v>52.24</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53.5</v>
+        <v>23.45</v>
       </c>
       <c r="C33" t="n">
-        <v>174.12</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>3254500</v>
+        <v>3099300</v>
       </c>
       <c r="E33" t="n">
-        <v>1733180</v>
+        <v>2732765</v>
       </c>
       <c r="F33" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>52.48</v>
+        <v>24.92</v>
       </c>
       <c r="K33" t="n">
-        <v>51.28</v>
+        <v>24.8</v>
       </c>
       <c r="L33" t="n">
-        <v>4.32</v>
+        <v>-5.44</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3091,51 +3079,51 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>47.15</v>
+        <v>48.19</v>
       </c>
       <c r="S33" t="n">
-        <v>65.23</v>
+        <v>47.14</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.55</v>
+        <v>22.85</v>
       </c>
       <c r="C34" t="n">
-        <v>28.67</v>
+        <v>546.5700000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>908700</v>
+        <v>23919700</v>
       </c>
       <c r="E34" t="n">
-        <v>2268040</v>
+        <v>17088220</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3145,24 +3133,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>30.22</v>
+        <v>21.13</v>
       </c>
       <c r="K34" t="n">
-        <v>32.78</v>
+        <v>21.13</v>
       </c>
       <c r="L34" t="n">
-        <v>-3.74</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -3171,14 +3163,14 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>25.74</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>50.45</v>
+        <v>63.78</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3188,34 +3180,34 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>HDC</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>50.2</v>
+        <v>11.5</v>
       </c>
       <c r="C35" t="n">
-        <v>24.72</v>
+        <v>24.34</v>
       </c>
       <c r="D35" t="n">
-        <v>492500</v>
+        <v>2116900</v>
       </c>
       <c r="E35" t="n">
-        <v>941475</v>
+        <v>1717555</v>
       </c>
       <c r="F35" t="n">
-        <v>0.52</v>
+        <v>1.23</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3225,21 +3217,21 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>48.2</v>
+        <v>11.18</v>
       </c>
       <c r="K35" t="n">
-        <v>49.55</v>
+        <v>13.34</v>
       </c>
       <c r="L35" t="n">
-        <v>1.31</v>
+        <v>-13.83</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -3251,14 +3243,14 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>38.83</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>56.25</v>
+        <v>73.53</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3268,34 +3260,34 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HHP</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23.95</v>
+        <v>17.75</v>
       </c>
       <c r="C36" t="n">
-        <v>49.55</v>
+        <v>32.24</v>
       </c>
       <c r="D36" t="n">
-        <v>2068700</v>
+        <v>1816300</v>
       </c>
       <c r="E36" t="n">
-        <v>2648595</v>
+        <v>1380905</v>
       </c>
       <c r="F36" t="n">
-        <v>0.78</v>
+        <v>1.32</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3305,21 +3297,21 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>24.92</v>
+        <v>16.39</v>
       </c>
       <c r="K36" t="n">
-        <v>24.8</v>
+        <v>15.55</v>
       </c>
       <c r="L36" t="n">
-        <v>-3.43</v>
+        <v>14.18</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3331,14 +3323,14 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>61.18</v>
+        <v>52.31</v>
       </c>
       <c r="S36" t="n">
-        <v>56.21</v>
+        <v>70.75</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -3348,30 +3340,30 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>HHV</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22</v>
+        <v>9.65</v>
       </c>
       <c r="C37" t="n">
-        <v>186.56</v>
+        <v>26.55</v>
       </c>
       <c r="D37" t="n">
-        <v>8479800</v>
+        <v>2751700</v>
       </c>
       <c r="E37" t="n">
-        <v>16314590</v>
+        <v>3132980</v>
       </c>
       <c r="F37" t="n">
-        <v>0.52</v>
+        <v>0.88</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3385,28 +3377,24 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>21.13</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>21.13</v>
+        <v>10.54</v>
       </c>
       <c r="L37" t="n">
-        <v>4.12</v>
+        <v>-8.44</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
@@ -3415,14 +3403,14 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>54.95</v>
+        <v>71</v>
       </c>
       <c r="S37" t="n">
-        <v>63.67</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3432,39 +3420,39 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HDC</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.45</v>
+        <v>20.75</v>
       </c>
       <c r="C38" t="n">
-        <v>28.72</v>
+        <v>273.99</v>
       </c>
       <c r="D38" t="n">
-        <v>2508300</v>
+        <v>13204500</v>
       </c>
       <c r="E38" t="n">
-        <v>1669845</v>
+        <v>17829645</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5</v>
+        <v>0.74</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3473,13 +3461,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>11.18</v>
+        <v>21.12</v>
       </c>
       <c r="K38" t="n">
-        <v>13.34</v>
+        <v>22.46</v>
       </c>
       <c r="L38" t="n">
-        <v>-14.2</v>
+        <v>-7.59</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3495,51 +3483,51 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>77.11</v>
+        <v>59.38</v>
       </c>
       <c r="S38" t="n">
-        <v>77.42</v>
+        <v>67.34</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HHP</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.7</v>
+        <v>11.1</v>
       </c>
       <c r="C39" t="n">
-        <v>77.52</v>
+        <v>27.82</v>
       </c>
       <c r="D39" t="n">
-        <v>4379700</v>
+        <v>2506600</v>
       </c>
       <c r="E39" t="n">
-        <v>1314360</v>
+        <v>3301225</v>
       </c>
       <c r="F39" t="n">
-        <v>3.33</v>
+        <v>0.76</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3553,17 +3541,17 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>16.39</v>
+        <v>10.5</v>
       </c>
       <c r="K39" t="n">
-        <v>15.55</v>
+        <v>11.35</v>
       </c>
       <c r="L39" t="n">
-        <v>13.86</v>
+        <v>-2.2</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3575,14 +3563,14 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>51.56</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="S39" t="n">
-        <v>67.03</v>
+        <v>77.27</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -3592,30 +3580,30 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HHV</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9.52</v>
+        <v>36</v>
       </c>
       <c r="C40" t="n">
-        <v>20.21</v>
+        <v>36.72</v>
       </c>
       <c r="D40" t="n">
-        <v>2122400</v>
+        <v>1020000</v>
       </c>
       <c r="E40" t="n">
-        <v>3046830</v>
+        <v>1244270</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3624,106 +3612,102 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>9.529999999999999</v>
+        <v>32.95</v>
       </c>
       <c r="K40" t="n">
-        <v>10.54</v>
+        <v>34.97</v>
       </c>
       <c r="L40" t="n">
-        <v>-9.68</v>
+        <v>2.95</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>65.48</v>
+        <v>58.73</v>
       </c>
       <c r="S40" t="n">
-        <v>61.35</v>
+        <v>56.6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>KBC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C41" t="n">
-        <v>200.01</v>
+        <v>44.62</v>
       </c>
       <c r="D41" t="n">
-        <v>9524500</v>
+        <v>1652700</v>
       </c>
       <c r="E41" t="n">
-        <v>17836935</v>
+        <v>1293710</v>
       </c>
       <c r="F41" t="n">
-        <v>0.53</v>
+        <v>1.28</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>21.12</v>
+        <v>26.55</v>
       </c>
       <c r="K41" t="n">
-        <v>22.61</v>
+        <v>29.68</v>
       </c>
       <c r="L41" t="n">
-        <v>-7.12</v>
+        <v>-9.01</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3732,82 +3716,78 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>60.32</v>
+        <v>83.33</v>
       </c>
       <c r="S41" t="n">
-        <v>67.55</v>
+        <v>79.5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11.1</v>
+        <v>14.25</v>
       </c>
       <c r="C42" t="n">
-        <v>54.83</v>
+        <v>74.7</v>
       </c>
       <c r="D42" t="n">
-        <v>4939500</v>
+        <v>5242200</v>
       </c>
       <c r="E42" t="n">
-        <v>3232055</v>
+        <v>4559740</v>
       </c>
       <c r="F42" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>10.5</v>
+        <v>15.04</v>
       </c>
       <c r="K42" t="n">
-        <v>11.35</v>
+        <v>18.2</v>
       </c>
       <c r="L42" t="n">
-        <v>-2.2</v>
+        <v>-21.72</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3823,51 +3803,51 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>78.28</v>
+        <v>66.13</v>
       </c>
       <c r="S42" t="n">
-        <v>78.19</v>
+        <v>67.83</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12.5</v>
+        <v>38.1</v>
       </c>
       <c r="C43" t="n">
-        <v>31.96</v>
+        <v>46.23</v>
       </c>
       <c r="D43" t="n">
-        <v>2556500</v>
+        <v>1213500</v>
       </c>
       <c r="E43" t="n">
-        <v>2099750</v>
+        <v>2055980</v>
       </c>
       <c r="F43" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3881,13 +3861,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>13.2</v>
+        <v>46.6</v>
       </c>
       <c r="K43" t="n">
-        <v>14.15</v>
+        <v>47.85</v>
       </c>
       <c r="L43" t="n">
-        <v>-11.66</v>
+        <v>-20.38</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3903,10 +3883,10 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>53.33</v>
+        <v>39.06</v>
       </c>
       <c r="S43" t="n">
-        <v>61.97</v>
+        <v>41.24</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3920,30 +3900,30 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>36</v>
+        <v>19.7</v>
       </c>
       <c r="C44" t="n">
-        <v>21.68</v>
+        <v>149.87</v>
       </c>
       <c r="D44" t="n">
-        <v>602100</v>
+        <v>7607600</v>
       </c>
       <c r="E44" t="n">
-        <v>1281380</v>
+        <v>11492850</v>
       </c>
       <c r="F44" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3957,21 +3937,21 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>32.95</v>
+        <v>19.49</v>
       </c>
       <c r="K44" t="n">
-        <v>34.97</v>
+        <v>19.7</v>
       </c>
       <c r="L44" t="n">
-        <v>2.95</v>
+        <v>-0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3987,10 +3967,10 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>52.86</v>
+        <v>66.67</v>
       </c>
       <c r="S44" t="n">
-        <v>63.11</v>
+        <v>54.86</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4004,30 +3984,30 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KBC</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>26.95</v>
+        <v>139.8</v>
       </c>
       <c r="C45" t="n">
-        <v>29.79</v>
+        <v>24.74</v>
       </c>
       <c r="D45" t="n">
-        <v>1105500</v>
+        <v>177000</v>
       </c>
       <c r="E45" t="n">
-        <v>1271530</v>
+        <v>610330</v>
       </c>
       <c r="F45" t="n">
-        <v>0.87</v>
+        <v>0.29</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4045,36 +4025,40 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>26.55</v>
+        <v>139.46</v>
       </c>
       <c r="K45" t="n">
-        <v>29.68</v>
+        <v>134.54</v>
       </c>
       <c r="L45" t="n">
-        <v>-9.18</v>
+        <v>3.91</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>84</v>
+        <v>27.71</v>
       </c>
       <c r="S45" t="n">
-        <v>78.36</v>
+        <v>24.67</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -4084,30 +4068,30 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14.7</v>
+        <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>62.09</v>
+        <v>155.41</v>
       </c>
       <c r="D46" t="n">
-        <v>4223900</v>
+        <v>9713300</v>
       </c>
       <c r="E46" t="n">
-        <v>4430810</v>
+        <v>10506140</v>
       </c>
       <c r="F46" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4116,30 +4100,34 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>15.04</v>
+        <v>14.08</v>
       </c>
       <c r="K46" t="n">
-        <v>18.25</v>
+        <v>13.24</v>
       </c>
       <c r="L46" t="n">
-        <v>-19.45</v>
+        <v>20.89</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4147,10 +4135,10 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>69.48999999999999</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="S46" t="n">
-        <v>70.31999999999999</v>
+        <v>86.22</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4159,63 +4147,63 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>38.4</v>
+        <v>74.2</v>
       </c>
       <c r="C47" t="n">
-        <v>83.81999999999999</v>
+        <v>357.2</v>
       </c>
       <c r="D47" t="n">
-        <v>2182700</v>
+        <v>4814000</v>
       </c>
       <c r="E47" t="n">
-        <v>2052445</v>
+        <v>5596525</v>
       </c>
       <c r="F47" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>46.6</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>47.85</v>
+        <v>72.05</v>
       </c>
       <c r="L47" t="n">
-        <v>-19.75</v>
+        <v>2.98</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -4227,47 +4215,47 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>35.83</v>
+        <v>50</v>
       </c>
       <c r="S47" t="n">
-        <v>39.61</v>
+        <v>51.69</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19.65</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>95.09999999999999</v>
+        <v>113.75</v>
       </c>
       <c r="D48" t="n">
-        <v>4839900</v>
+        <v>1663000</v>
       </c>
       <c r="E48" t="n">
-        <v>11460220</v>
+        <v>2123275</v>
       </c>
       <c r="F48" t="n">
-        <v>0.42</v>
+        <v>0.78</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4281,40 +4269,40 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>19.49</v>
+        <v>51.4</v>
       </c>
       <c r="K48" t="n">
-        <v>19.7</v>
+        <v>50.57</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.25</v>
+        <v>35.26</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>60.78</v>
+        <v>50.54</v>
       </c>
       <c r="S48" t="n">
-        <v>49.22</v>
+        <v>46.87</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4328,39 +4316,39 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>15.75</v>
+        <v>76</v>
       </c>
       <c r="C49" t="n">
-        <v>123.18</v>
+        <v>364.1</v>
       </c>
       <c r="D49" t="n">
-        <v>7821200</v>
+        <v>4790800</v>
       </c>
       <c r="E49" t="n">
-        <v>10470395</v>
+        <v>2992715</v>
       </c>
       <c r="F49" t="n">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4369,25 +4357,21 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>13.93</v>
+        <v>69.02</v>
       </c>
       <c r="K49" t="n">
-        <v>13.04</v>
+        <v>72.83</v>
       </c>
       <c r="L49" t="n">
-        <v>20.78</v>
+        <v>4.35</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4395,47 +4379,47 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>78.95</v>
+        <v>49.44</v>
       </c>
       <c r="S49" t="n">
-        <v>85.98999999999999</v>
+        <v>53.13</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>73.40000000000001</v>
+        <v>12.65</v>
       </c>
       <c r="C50" t="n">
-        <v>247.68</v>
+        <v>27.35</v>
       </c>
       <c r="D50" t="n">
-        <v>3374400</v>
+        <v>2162300</v>
       </c>
       <c r="E50" t="n">
-        <v>5561930</v>
+        <v>2546430</v>
       </c>
       <c r="F50" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4453,13 +4437,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>69.45</v>
+        <v>12.05</v>
       </c>
       <c r="K50" t="n">
-        <v>72.05</v>
+        <v>12.25</v>
       </c>
       <c r="L50" t="n">
-        <v>1.87</v>
+        <v>3.27</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4468,21 +4452,17 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>42.11</v>
+        <v>58.33</v>
       </c>
       <c r="S50" t="n">
-        <v>52.39</v>
+        <v>61.41</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4496,30 +4476,30 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>67.40000000000001</v>
+        <v>12.15</v>
       </c>
       <c r="C51" t="n">
-        <v>186.48</v>
+        <v>52.1</v>
       </c>
       <c r="D51" t="n">
-        <v>2766800</v>
+        <v>4288200</v>
       </c>
       <c r="E51" t="n">
-        <v>2136075</v>
+        <v>4185485</v>
       </c>
       <c r="F51" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4537,25 +4517,21 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>51.11</v>
+        <v>10.65</v>
       </c>
       <c r="K51" t="n">
-        <v>50.57</v>
+        <v>11.16</v>
       </c>
       <c r="L51" t="n">
-        <v>33.28</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4563,14 +4539,14 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>55.83</v>
+        <v>89.47</v>
       </c>
       <c r="S51" t="n">
-        <v>48.5</v>
+        <v>95.25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4580,34 +4556,34 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>NLG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>75.7</v>
+        <v>23</v>
       </c>
       <c r="C52" t="n">
-        <v>319.53</v>
+        <v>20.81</v>
       </c>
       <c r="D52" t="n">
-        <v>4221000</v>
+        <v>904800</v>
       </c>
       <c r="E52" t="n">
-        <v>2901475</v>
+        <v>1477335</v>
       </c>
       <c r="F52" t="n">
-        <v>1.45</v>
+        <v>0.61</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4617,36 +4593,40 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>69.02</v>
+        <v>22.55</v>
       </c>
       <c r="K52" t="n">
-        <v>72.83</v>
+        <v>23.67</v>
       </c>
       <c r="L52" t="n">
-        <v>3.94</v>
+        <v>-2.85</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>43.62</v>
+        <v>64</v>
       </c>
       <c r="S52" t="n">
-        <v>51.38</v>
+        <v>69.03</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -4660,34 +4640,34 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>NVB</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12.7</v>
+        <v>14.7</v>
       </c>
       <c r="C53" t="n">
-        <v>32.38</v>
+        <v>20.62</v>
       </c>
       <c r="D53" t="n">
-        <v>2549400</v>
+        <v>1403000</v>
       </c>
       <c r="E53" t="n">
-        <v>2504535</v>
+        <v>2023690</v>
       </c>
       <c r="F53" t="n">
-        <v>1.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4701,20 +4681,24 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>12.05</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>12.25</v>
+        <v>14</v>
       </c>
       <c r="L53" t="n">
-        <v>3.67</v>
+        <v>5</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
@@ -4723,10 +4707,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>50</v>
+        <v>35.38</v>
       </c>
       <c r="S53" t="n">
-        <v>60.51</v>
+        <v>36.94</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4740,58 +4724,58 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>12.05</v>
+        <v>10.5</v>
       </c>
       <c r="C54" t="n">
-        <v>98.95</v>
+        <v>142.61</v>
       </c>
       <c r="D54" t="n">
-        <v>8211800</v>
+        <v>13582300</v>
       </c>
       <c r="E54" t="n">
-        <v>4031660</v>
+        <v>24218894</v>
       </c>
       <c r="F54" t="n">
-        <v>2.04</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>10.65</v>
+        <v>11.88</v>
       </c>
       <c r="K54" t="n">
-        <v>11.16</v>
+        <v>14.5</v>
       </c>
       <c r="L54" t="n">
-        <v>7.97</v>
+        <v>-27.56</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4803,51 +4787,51 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>85.48999999999999</v>
+        <v>57.14</v>
       </c>
       <c r="S54" t="n">
-        <v>93.36</v>
+        <v>58.35</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NLG</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>22.85</v>
+        <v>10.7</v>
       </c>
       <c r="C55" t="n">
-        <v>22.49</v>
+        <v>56.52</v>
       </c>
       <c r="D55" t="n">
-        <v>984300</v>
+        <v>5281900</v>
       </c>
       <c r="E55" t="n">
-        <v>1507560</v>
+        <v>2216985</v>
       </c>
       <c r="F55" t="n">
-        <v>0.65</v>
+        <v>2.38</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4861,36 +4845,32 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>22.55</v>
+        <v>10.46</v>
       </c>
       <c r="K55" t="n">
-        <v>23.67</v>
+        <v>10.5</v>
       </c>
       <c r="L55" t="n">
-        <v>-3.48</v>
+        <v>1.95</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>64.94</v>
+        <v>75.34</v>
       </c>
       <c r="S55" t="n">
-        <v>73.59</v>
+        <v>72.44</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4904,58 +4884,58 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10.55</v>
+        <v>15.3</v>
       </c>
       <c r="C56" t="n">
-        <v>145.62</v>
+        <v>85.12</v>
       </c>
       <c r="D56" t="n">
-        <v>13802700</v>
+        <v>5563700</v>
       </c>
       <c r="E56" t="n">
-        <v>28392729</v>
+        <v>4328045</v>
       </c>
       <c r="F56" t="n">
-        <v>0.49</v>
+        <v>1.29</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>11.88</v>
+        <v>14.28</v>
       </c>
       <c r="K56" t="n">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="L56" t="n">
-        <v>-27.22</v>
+        <v>7.37</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4967,10 +4947,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>57.14</v>
+        <v>75</v>
       </c>
       <c r="S56" t="n">
-        <v>56.71</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4979,63 +4959,63 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10.85</v>
+        <v>11.55</v>
       </c>
       <c r="C57" t="n">
-        <v>69.44</v>
+        <v>57.63</v>
       </c>
       <c r="D57" t="n">
-        <v>6400400</v>
+        <v>4989300</v>
       </c>
       <c r="E57" t="n">
-        <v>1972600</v>
+        <v>5253825</v>
       </c>
       <c r="F57" t="n">
-        <v>3.24</v>
+        <v>0.95</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>10.46</v>
+        <v>11.68</v>
       </c>
       <c r="K57" t="n">
-        <v>10.5</v>
+        <v>13.82</v>
       </c>
       <c r="L57" t="n">
-        <v>3.38</v>
+        <v>-16.46</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -5043,55 +5023,55 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.2x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>82.09</v>
+        <v>60</v>
       </c>
       <c r="S57" t="n">
-        <v>82.90000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>15.15</v>
+        <v>51</v>
       </c>
       <c r="C58" t="n">
-        <v>130.94</v>
+        <v>41.67</v>
       </c>
       <c r="D58" t="n">
-        <v>8642700</v>
+        <v>817100</v>
       </c>
       <c r="E58" t="n">
-        <v>4121190</v>
+        <v>668535</v>
       </c>
       <c r="F58" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5105,13 +5085,13 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>14.28</v>
+        <v>46.15</v>
       </c>
       <c r="K58" t="n">
-        <v>14.25</v>
+        <v>44.52</v>
       </c>
       <c r="L58" t="n">
-        <v>6.32</v>
+        <v>14.57</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5127,10 +5107,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>73.08</v>
+        <v>54.88</v>
       </c>
       <c r="S58" t="n">
-        <v>70.01000000000001</v>
+        <v>49.27</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5144,54 +5124,54 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11.6</v>
+        <v>35.35</v>
       </c>
       <c r="C59" t="n">
-        <v>67.97</v>
+        <v>41.44</v>
       </c>
       <c r="D59" t="n">
-        <v>5859900</v>
+        <v>1172300</v>
       </c>
       <c r="E59" t="n">
-        <v>5169765</v>
+        <v>3707685</v>
       </c>
       <c r="F59" t="n">
-        <v>1.13</v>
+        <v>0.32</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>11.68</v>
+        <v>35.15</v>
       </c>
       <c r="K59" t="n">
-        <v>13.82</v>
+        <v>38.08</v>
       </c>
       <c r="L59" t="n">
-        <v>-16.09</v>
+        <v>-7.18</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5207,83 +5187,79 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>60</v>
+        <v>28.16</v>
       </c>
       <c r="S59" t="n">
-        <v>68.2</v>
+        <v>53.51</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>53.1</v>
+        <v>17.15</v>
       </c>
       <c r="C60" t="n">
-        <v>55.27</v>
+        <v>72.92</v>
       </c>
       <c r="D60" t="n">
-        <v>1040900</v>
+        <v>4251900</v>
       </c>
       <c r="E60" t="n">
-        <v>680025</v>
+        <v>16390435</v>
       </c>
       <c r="F60" t="n">
-        <v>1.53</v>
+        <v>0.26</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>46.15</v>
+        <v>31.28</v>
       </c>
       <c r="K60" t="n">
-        <v>44.52</v>
+        <v>46.8</v>
       </c>
       <c r="L60" t="n">
-        <v>19.29</v>
+        <v>-63.35</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5291,10 +5267,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>57.32</v>
+        <v>44.27</v>
       </c>
       <c r="S60" t="n">
-        <v>51.57</v>
+        <v>40.85</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5303,63 +5279,63 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>45.4</v>
+        <v>12.55</v>
       </c>
       <c r="C61" t="n">
-        <v>25.38</v>
+        <v>51.31</v>
       </c>
       <c r="D61" t="n">
-        <v>559000</v>
+        <v>4088600</v>
       </c>
       <c r="E61" t="n">
-        <v>343755</v>
+        <v>4913515</v>
       </c>
       <c r="F61" t="n">
-        <v>1.63</v>
+        <v>0.83</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>43.2</v>
+        <v>13.08</v>
       </c>
       <c r="K61" t="n">
-        <v>42.5</v>
+        <v>13.6</v>
       </c>
       <c r="L61" t="n">
-        <v>6.82</v>
+        <v>-7.72</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -5371,47 +5347,47 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>22.55</v>
+        <v>51.85</v>
       </c>
       <c r="S61" t="n">
-        <v>17.04</v>
+        <v>45.79</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>35.3</v>
+        <v>18.8</v>
       </c>
       <c r="C62" t="n">
-        <v>57</v>
+        <v>56.44</v>
       </c>
       <c r="D62" t="n">
-        <v>1614700</v>
+        <v>3001900</v>
       </c>
       <c r="E62" t="n">
-        <v>3784700</v>
+        <v>3689705</v>
       </c>
       <c r="F62" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -5425,17 +5401,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>35.15</v>
+        <v>18.92</v>
       </c>
       <c r="K62" t="n">
-        <v>38.08</v>
+        <v>19.43</v>
       </c>
       <c r="L62" t="n">
-        <v>-7.31</v>
+        <v>-3.24</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5451,14 +5427,14 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>43.08</v>
+        <v>59.02</v>
       </c>
       <c r="S62" t="n">
-        <v>62.33</v>
+        <v>75.34</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -5468,61 +5444,65 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>17.05</v>
+        <v>20.15</v>
       </c>
       <c r="C63" t="n">
-        <v>107.13</v>
+        <v>39.42</v>
       </c>
       <c r="D63" t="n">
-        <v>6283300</v>
+        <v>1956100</v>
       </c>
       <c r="E63" t="n">
-        <v>16296555</v>
+        <v>1467330</v>
       </c>
       <c r="F63" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>31.28</v>
+        <v>20.6</v>
       </c>
       <c r="K63" t="n">
-        <v>46.8</v>
+        <v>20.6</v>
       </c>
       <c r="L63" t="n">
-        <v>-63.57</v>
+        <v>-2.21</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
@@ -5531,47 +5511,47 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>40.89</v>
+        <v>17.45</v>
       </c>
       <c r="S63" t="n">
-        <v>36.49</v>
+        <v>23.92</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>12.4</v>
+        <v>32</v>
       </c>
       <c r="C64" t="n">
-        <v>43.96</v>
+        <v>38.28</v>
       </c>
       <c r="D64" t="n">
-        <v>3545000</v>
+        <v>1196400</v>
       </c>
       <c r="E64" t="n">
-        <v>5618245</v>
+        <v>2932875</v>
       </c>
       <c r="F64" t="n">
-        <v>0.63</v>
+        <v>0.41</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5580,26 +5560,26 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>13.08</v>
+        <v>30.94</v>
       </c>
       <c r="K64" t="n">
-        <v>13.6</v>
+        <v>31.62</v>
       </c>
       <c r="L64" t="n">
-        <v>-8.82</v>
+        <v>1.19</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5611,47 +5591,47 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>42.31</v>
+        <v>28.85</v>
       </c>
       <c r="S64" t="n">
-        <v>38.16</v>
+        <v>43.17</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>18.5</v>
+        <v>22.85</v>
       </c>
       <c r="C65" t="n">
-        <v>55.78</v>
+        <v>118.42</v>
       </c>
       <c r="D65" t="n">
-        <v>3015400</v>
+        <v>5182500</v>
       </c>
       <c r="E65" t="n">
-        <v>3701735</v>
+        <v>7107065</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5665,24 +5645,28 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>18.92</v>
+        <v>21.2</v>
       </c>
       <c r="K65" t="n">
-        <v>19.43</v>
+        <v>21.2</v>
       </c>
       <c r="L65" t="n">
-        <v>-4.79</v>
+        <v>7.78</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
@@ -5691,14 +5675,14 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>53.57</v>
+        <v>24.04</v>
       </c>
       <c r="S65" t="n">
-        <v>68.42</v>
+        <v>19.28</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -5708,30 +5692,30 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>31.8</v>
+        <v>20.75</v>
       </c>
       <c r="C66" t="n">
-        <v>42.52</v>
+        <v>22.51</v>
       </c>
       <c r="D66" t="n">
-        <v>1337000</v>
+        <v>1085000</v>
       </c>
       <c r="E66" t="n">
-        <v>3050005</v>
+        <v>1271700</v>
       </c>
       <c r="F66" t="n">
-        <v>0.44</v>
+        <v>0.85</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5745,21 +5729,21 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>30.94</v>
+        <v>22.3</v>
       </c>
       <c r="K66" t="n">
-        <v>31.62</v>
+        <v>21.92</v>
       </c>
       <c r="L66" t="n">
-        <v>0.55</v>
+        <v>-5.36</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5771,14 +5755,14 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>33.93</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S66" t="n">
-        <v>52.04</v>
+        <v>19.14</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -5788,30 +5772,30 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>23.2</v>
+        <v>10.65</v>
       </c>
       <c r="C67" t="n">
-        <v>93.11</v>
+        <v>294.8</v>
       </c>
       <c r="D67" t="n">
-        <v>4013500</v>
+        <v>27680700</v>
       </c>
       <c r="E67" t="n">
-        <v>7262130</v>
+        <v>43467255</v>
       </c>
       <c r="F67" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5820,33 +5804,29 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>21.2</v>
+        <v>10.9</v>
       </c>
       <c r="K67" t="n">
-        <v>21.2</v>
+        <v>12.38</v>
       </c>
       <c r="L67" t="n">
-        <v>9.43</v>
+        <v>-13.94</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
@@ -5855,47 +5835,47 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>35.14</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="S67" t="n">
-        <v>32.4</v>
+        <v>43.53</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.8</v>
+        <v>12.4</v>
       </c>
       <c r="C68" t="n">
-        <v>23.72</v>
+        <v>58.52</v>
       </c>
       <c r="D68" t="n">
-        <v>1140200</v>
+        <v>4719700</v>
       </c>
       <c r="E68" t="n">
-        <v>1271575</v>
+        <v>11139110</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9</v>
+        <v>0.42</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5904,7 +5884,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5913,13 +5893,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>22.3</v>
+        <v>13.23</v>
       </c>
       <c r="K68" t="n">
-        <v>21.92</v>
+        <v>15</v>
       </c>
       <c r="L68" t="n">
-        <v>-5.13</v>
+        <v>-17.36</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5935,56 +5915,56 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="S68" t="n">
-        <v>19.03</v>
+        <v>55.62</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>10.8</v>
+        <v>15.85</v>
       </c>
       <c r="C69" t="n">
-        <v>302.44</v>
+        <v>39.86</v>
       </c>
       <c r="D69" t="n">
-        <v>28003900</v>
+        <v>2514600</v>
       </c>
       <c r="E69" t="n">
-        <v>43555290</v>
+        <v>2290680</v>
       </c>
       <c r="F69" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5993,13 +5973,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>10.9</v>
+        <v>19.77</v>
       </c>
       <c r="K69" t="n">
-        <v>12.4</v>
+        <v>19.19</v>
       </c>
       <c r="L69" t="n">
-        <v>-12.9</v>
+        <v>-17.38</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -6015,47 +5995,47 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>50</v>
+        <v>36.84</v>
       </c>
       <c r="S69" t="n">
-        <v>42.4</v>
+        <v>22.39</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>12.5</v>
+        <v>19.75</v>
       </c>
       <c r="C70" t="n">
-        <v>75.55</v>
+        <v>248.31</v>
       </c>
       <c r="D70" t="n">
-        <v>6044000</v>
+        <v>12572700</v>
       </c>
       <c r="E70" t="n">
-        <v>11290115</v>
+        <v>18578695</v>
       </c>
       <c r="F70" t="n">
-        <v>0.54</v>
+        <v>0.68</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -6064,7 +6044,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6073,13 +6053,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>13.23</v>
+        <v>19.55</v>
       </c>
       <c r="K70" t="n">
-        <v>15</v>
+        <v>20.19</v>
       </c>
       <c r="L70" t="n">
-        <v>-16.69</v>
+        <v>-2.16</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6095,47 +6075,47 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>58.33</v>
+        <v>64.58</v>
       </c>
       <c r="S70" t="n">
-        <v>54.65</v>
+        <v>49.02</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>15.8</v>
+        <v>68</v>
       </c>
       <c r="C71" t="n">
-        <v>33.75</v>
+        <v>208.83</v>
       </c>
       <c r="D71" t="n">
-        <v>2136100</v>
+        <v>3071000</v>
       </c>
       <c r="E71" t="n">
-        <v>2260250</v>
+        <v>3548990</v>
       </c>
       <c r="F71" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6153,20 +6133,24 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>19.77</v>
+        <v>70.05</v>
       </c>
       <c r="K71" t="n">
-        <v>19.19</v>
+        <v>70.05</v>
       </c>
       <c r="L71" t="n">
-        <v>-17.64</v>
+        <v>-2.93</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
@@ -6175,14 +6159,14 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>35.42</v>
+        <v>52.52</v>
       </c>
       <c r="S71" t="n">
-        <v>29.06</v>
+        <v>52.95</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -6192,34 +6176,34 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>19.8</v>
+        <v>22.33</v>
       </c>
       <c r="C72" t="n">
-        <v>184.56</v>
+        <v>560.51</v>
       </c>
       <c r="D72" t="n">
-        <v>9321400</v>
+        <v>25101000</v>
       </c>
       <c r="E72" t="n">
-        <v>18700615</v>
+        <v>18193645</v>
       </c>
       <c r="F72" t="n">
-        <v>0.5</v>
+        <v>1.38</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6229,44 +6213,44 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>19.55</v>
+        <v>21</v>
       </c>
       <c r="K72" t="n">
-        <v>20.19</v>
+        <v>21</v>
       </c>
       <c r="L72" t="n">
-        <v>-1.91</v>
+        <v>6.33</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>52.54</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="S72" t="n">
-        <v>48.03</v>
+        <v>59.45</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -6276,34 +6260,34 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>67.40000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="C73" t="n">
-        <v>118.39</v>
+        <v>68.05</v>
       </c>
       <c r="D73" t="n">
-        <v>1756600</v>
+        <v>5623800</v>
       </c>
       <c r="E73" t="n">
-        <v>3532580</v>
+        <v>5226245</v>
       </c>
       <c r="F73" t="n">
-        <v>0.5</v>
+        <v>1.08</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6313,28 +6297,24 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>70.05</v>
+        <v>11.09</v>
       </c>
       <c r="K73" t="n">
-        <v>70.05</v>
+        <v>13.2</v>
       </c>
       <c r="L73" t="n">
-        <v>-3.78</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
@@ -6343,14 +6323,14 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>52.17</v>
+        <v>94.44</v>
       </c>
       <c r="S73" t="n">
-        <v>45.14</v>
+        <v>76.66</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -6360,34 +6340,34 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>TCM</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>33.55</v>
+        <v>16.3</v>
       </c>
       <c r="C74" t="n">
-        <v>619.41</v>
+        <v>29.13</v>
       </c>
       <c r="D74" t="n">
-        <v>18462300</v>
+        <v>1787300</v>
       </c>
       <c r="E74" t="n">
-        <v>17767130</v>
+        <v>778590</v>
       </c>
       <c r="F74" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6397,28 +6377,24 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>31.5</v>
+        <v>16.23</v>
       </c>
       <c r="K74" t="n">
-        <v>31.5</v>
+        <v>18.27</v>
       </c>
       <c r="L74" t="n">
-        <v>6.51</v>
+        <v>-10.78</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
@@ -6427,14 +6403,14 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>65.43000000000001</v>
+        <v>70.69</v>
       </c>
       <c r="S74" t="n">
-        <v>62.35</v>
+        <v>54.78</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -6444,54 +6420,54 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>12.1</v>
+        <v>28.45</v>
       </c>
       <c r="C75" t="n">
-        <v>81.84</v>
+        <v>53.21</v>
       </c>
       <c r="D75" t="n">
-        <v>6763800</v>
+        <v>1870200</v>
       </c>
       <c r="E75" t="n">
-        <v>5144015</v>
+        <v>2963485</v>
       </c>
       <c r="F75" t="n">
-        <v>1.31</v>
+        <v>0.63</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>11.09</v>
+        <v>31.01</v>
       </c>
       <c r="K75" t="n">
-        <v>13.2</v>
+        <v>32.59</v>
       </c>
       <c r="L75" t="n">
-        <v>-8.369999999999999</v>
+        <v>-12.7</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6507,75 +6483,75 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>79.06999999999999</v>
+        <v>63.33</v>
       </c>
       <c r="S75" t="n">
-        <v>71.56</v>
+        <v>57.4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>TLG</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>28.45</v>
+        <v>53</v>
       </c>
       <c r="C76" t="n">
-        <v>80.38</v>
+        <v>28.29</v>
       </c>
       <c r="D76" t="n">
-        <v>2825200</v>
+        <v>533700</v>
       </c>
       <c r="E76" t="n">
-        <v>2936810</v>
+        <v>255855</v>
       </c>
       <c r="F76" t="n">
-        <v>0.96</v>
+        <v>2.09</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>31.01</v>
+        <v>51.55</v>
       </c>
       <c r="K76" t="n">
-        <v>32.59</v>
+        <v>51.4</v>
       </c>
       <c r="L76" t="n">
-        <v>-12.7</v>
+        <v>3.11</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -6587,47 +6563,47 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>54.81</v>
+        <v>40.63</v>
       </c>
       <c r="S76" t="n">
-        <v>57</v>
+        <v>49.56</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>TNG</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>12.7</v>
+        <v>19.7</v>
       </c>
       <c r="C77" t="n">
-        <v>195.52</v>
+        <v>33.8</v>
       </c>
       <c r="D77" t="n">
-        <v>15395300</v>
+        <v>1715800</v>
       </c>
       <c r="E77" t="n">
-        <v>13118910</v>
+        <v>1221960</v>
       </c>
       <c r="F77" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6645,13 +6621,13 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>12.2</v>
+        <v>17.22</v>
       </c>
       <c r="K77" t="n">
-        <v>12.68</v>
+        <v>17.32</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2</v>
+        <v>13.74</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -6667,14 +6643,14 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>69.56999999999999</v>
+        <v>57.38</v>
       </c>
       <c r="S77" t="n">
-        <v>79.92</v>
+        <v>69.62</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -6684,34 +6660,34 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>56.1</v>
+        <v>13</v>
       </c>
       <c r="C78" t="n">
-        <v>136.78</v>
+        <v>356.25</v>
       </c>
       <c r="D78" t="n">
-        <v>2438200</v>
+        <v>27404100</v>
       </c>
       <c r="E78" t="n">
-        <v>2978715</v>
+        <v>14210650</v>
       </c>
       <c r="F78" t="n">
-        <v>0.82</v>
+        <v>1.93</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6721,21 +6697,21 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>57.3</v>
+        <v>12.2</v>
       </c>
       <c r="K78" t="n">
-        <v>59.12</v>
+        <v>12.68</v>
       </c>
       <c r="L78" t="n">
-        <v>-5.12</v>
+        <v>2.56</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -6747,14 +6723,14 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>38.3</v>
+        <v>79.17</v>
       </c>
       <c r="S78" t="n">
-        <v>45.21</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -6764,34 +6740,34 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>15.25</v>
+        <v>57.5</v>
       </c>
       <c r="C79" t="n">
-        <v>34.72</v>
+        <v>371.09</v>
       </c>
       <c r="D79" t="n">
-        <v>2276600</v>
+        <v>6453700</v>
       </c>
       <c r="E79" t="n">
-        <v>2285960</v>
+        <v>3189960</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2.02</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6805,13 +6781,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>14.88</v>
+        <v>57.35</v>
       </c>
       <c r="K79" t="n">
-        <v>17.1</v>
+        <v>59.12</v>
       </c>
       <c r="L79" t="n">
-        <v>-10.84</v>
+        <v>-2.75</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -6827,14 +6803,14 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>77.97</v>
+        <v>58.18</v>
       </c>
       <c r="S79" t="n">
-        <v>75.45</v>
+        <v>55.21</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -6844,54 +6820,54 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>19.15</v>
+        <v>15.75</v>
       </c>
       <c r="C80" t="n">
-        <v>91.81999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="D80" t="n">
-        <v>4794600</v>
+        <v>4365100</v>
       </c>
       <c r="E80" t="n">
-        <v>7685635</v>
+        <v>2450665</v>
       </c>
       <c r="F80" t="n">
-        <v>0.62</v>
+        <v>1.78</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>20.6</v>
+        <v>14.88</v>
       </c>
       <c r="K80" t="n">
-        <v>22.65</v>
+        <v>17.1</v>
       </c>
       <c r="L80" t="n">
-        <v>-15.45</v>
+        <v>-7.92</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -6900,58 +6876,54 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>50.88</v>
+        <v>81.16</v>
       </c>
       <c r="S80" t="n">
-        <v>53.24</v>
+        <v>77.14</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>27.6</v>
+        <v>19</v>
       </c>
       <c r="C81" t="n">
-        <v>33.64</v>
+        <v>81.16</v>
       </c>
       <c r="D81" t="n">
-        <v>1218700</v>
+        <v>4271500</v>
       </c>
       <c r="E81" t="n">
-        <v>1679640</v>
+        <v>7704510</v>
       </c>
       <c r="F81" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -6969,13 +6941,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>29.08</v>
+        <v>20.6</v>
       </c>
       <c r="K81" t="n">
-        <v>30.82</v>
+        <v>22.65</v>
       </c>
       <c r="L81" t="n">
-        <v>-10.46</v>
+        <v>-16.11</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6991,10 +6963,10 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>46.88</v>
+        <v>59.18</v>
       </c>
       <c r="S81" t="n">
-        <v>60.64</v>
+        <v>55.2</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -7008,87 +6980,91 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>38.8</v>
+        <v>27.45</v>
       </c>
       <c r="C82" t="n">
-        <v>29.2</v>
+        <v>27.47</v>
       </c>
       <c r="D82" t="n">
-        <v>752600</v>
+        <v>1000700</v>
       </c>
       <c r="E82" t="n">
-        <v>641935</v>
+        <v>1661150</v>
       </c>
       <c r="F82" t="n">
-        <v>1.17</v>
+        <v>0.6</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>36.85</v>
+        <v>29.08</v>
       </c>
       <c r="K82" t="n">
-        <v>36.5</v>
+        <v>30.82</v>
       </c>
       <c r="L82" t="n">
-        <v>6.3</v>
+        <v>-10.95</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>70.97</v>
+        <v>56.96</v>
       </c>
       <c r="S82" t="n">
-        <v>68.11</v>
+        <v>61.44</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7099,19 +7075,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>44.35</v>
+        <v>43.4</v>
       </c>
       <c r="C83" t="n">
-        <v>57.66</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>1300200</v>
+        <v>1862900</v>
       </c>
       <c r="E83" t="n">
-        <v>847825</v>
+        <v>814030</v>
       </c>
       <c r="F83" t="n">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7135,7 +7111,7 @@
         <v>40.8</v>
       </c>
       <c r="L83" t="n">
-        <v>8.699999999999999</v>
+        <v>6.37</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7155,10 +7131,10 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>43.88</v>
+        <v>44.33</v>
       </c>
       <c r="S83" t="n">
-        <v>55.32</v>
+        <v>51.42</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7172,7 +7148,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7186,16 +7162,16 @@
         <v>63.5</v>
       </c>
       <c r="C84" t="n">
-        <v>237.74</v>
+        <v>349.43</v>
       </c>
       <c r="D84" t="n">
-        <v>3743900</v>
+        <v>5502900</v>
       </c>
       <c r="E84" t="n">
-        <v>7955280</v>
+        <v>7909640</v>
       </c>
       <c r="F84" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7235,10 +7211,10 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>40.34</v>
+        <v>44.76</v>
       </c>
       <c r="S84" t="n">
-        <v>34.57</v>
+        <v>36.26</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7252,7 +7228,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7263,19 +7239,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>14.1</v>
+        <v>14.15</v>
       </c>
       <c r="C85" t="n">
-        <v>104.46</v>
+        <v>103.77</v>
       </c>
       <c r="D85" t="n">
-        <v>7408400</v>
+        <v>7333400</v>
       </c>
       <c r="E85" t="n">
-        <v>6251825</v>
+        <v>6506235</v>
       </c>
       <c r="F85" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7299,7 +7275,7 @@
         <v>14.16</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.39</v>
+        <v>-0.04</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -7315,10 +7291,10 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="S85" t="n">
-        <v>71.43000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7332,7 +7308,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7343,19 +7319,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>240.2</v>
+        <v>241</v>
       </c>
       <c r="C86" t="n">
-        <v>402.72</v>
+        <v>450.24</v>
       </c>
       <c r="D86" t="n">
-        <v>1676600</v>
+        <v>1868200</v>
       </c>
       <c r="E86" t="n">
-        <v>2797780</v>
+        <v>2811975</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7379,7 +7355,7 @@
         <v>224.85</v>
       </c>
       <c r="L86" t="n">
-        <v>6.83</v>
+        <v>7.18</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -7399,10 +7375,10 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>58.2</v>
+        <v>60.66</v>
       </c>
       <c r="S86" t="n">
-        <v>39.9</v>
+        <v>31.91</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -7416,7 +7392,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7427,19 +7403,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>12.3</v>
+        <v>12.45</v>
       </c>
       <c r="C87" t="n">
-        <v>353.91</v>
+        <v>248.34</v>
       </c>
       <c r="D87" t="n">
-        <v>28773200</v>
+        <v>19947300</v>
       </c>
       <c r="E87" t="n">
-        <v>30090345</v>
+        <v>30033180</v>
       </c>
       <c r="F87" t="n">
-        <v>0.96</v>
+        <v>0.66</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -7463,7 +7439,7 @@
         <v>14.95</v>
       </c>
       <c r="L87" t="n">
-        <v>-17.73</v>
+        <v>-16.72</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -7472,17 +7448,21 @@
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>60.71</v>
+        <v>72.55</v>
       </c>
       <c r="S87" t="n">
-        <v>66.84999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -7496,7 +7476,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7507,19 +7487,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>132.9</v>
+        <v>131.5</v>
       </c>
       <c r="C88" t="n">
-        <v>118.36</v>
+        <v>119.43</v>
       </c>
       <c r="D88" t="n">
-        <v>890600</v>
+        <v>908200</v>
       </c>
       <c r="E88" t="n">
-        <v>933245</v>
+        <v>936810</v>
       </c>
       <c r="F88" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7543,11 +7523,11 @@
         <v>132.12</v>
       </c>
       <c r="L88" t="n">
-        <v>0.59</v>
+        <v>-0.47</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -7559,14 +7539,14 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>78.81999999999999</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="S88" t="n">
-        <v>51.95</v>
+        <v>45.68</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -7576,7 +7556,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7587,19 +7567,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>13.35</v>
+        <v>13.45</v>
       </c>
       <c r="C89" t="n">
-        <v>99.58</v>
+        <v>63.25</v>
       </c>
       <c r="D89" t="n">
-        <v>7459100</v>
+        <v>4702700</v>
       </c>
       <c r="E89" t="n">
-        <v>9678375</v>
+        <v>9661360</v>
       </c>
       <c r="F89" t="n">
-        <v>0.77</v>
+        <v>0.49</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7623,7 +7603,7 @@
         <v>15.85</v>
       </c>
       <c r="L89" t="n">
-        <v>-15.77</v>
+        <v>-15.14</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7639,10 +7619,10 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>44.9</v>
+        <v>58.54</v>
       </c>
       <c r="S89" t="n">
-        <v>42.56</v>
+        <v>44.07</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -7656,7 +7636,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7667,23 +7647,23 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>57.6</v>
+        <v>58.2</v>
       </c>
       <c r="C90" t="n">
-        <v>63.56</v>
+        <v>137.51</v>
       </c>
       <c r="D90" t="n">
-        <v>1103400</v>
+        <v>2362800</v>
       </c>
       <c r="E90" t="n">
-        <v>1918020</v>
+        <v>1947355</v>
       </c>
       <c r="F90" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7703,7 +7683,7 @@
         <v>59.5</v>
       </c>
       <c r="L90" t="n">
-        <v>-3.19</v>
+        <v>-2.18</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -7719,10 +7699,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>45.65</v>
+        <v>52.94</v>
       </c>
       <c r="S90" t="n">
-        <v>38.33</v>
+        <v>48.63</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7736,7 +7716,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7747,23 +7727,23 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="C91" t="n">
-        <v>421.47</v>
+        <v>290.58</v>
       </c>
       <c r="D91" t="n">
-        <v>18166900</v>
+        <v>12365200</v>
       </c>
       <c r="E91" t="n">
-        <v>15819040</v>
+        <v>15598555</v>
       </c>
       <c r="F91" t="n">
-        <v>1.15</v>
+        <v>0.79</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7783,7 +7763,7 @@
         <v>21.98</v>
       </c>
       <c r="L91" t="n">
-        <v>5.57</v>
+        <v>6.94</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -7803,10 +7783,10 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>46.43</v>
+        <v>50.82</v>
       </c>
       <c r="S91" t="n">
-        <v>59.59</v>
+        <v>57.27</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7820,7 +7800,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7831,19 +7811,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>56.8</v>
+        <v>58.1</v>
       </c>
       <c r="C92" t="n">
         <v>139.89</v>
       </c>
       <c r="D92" t="n">
-        <v>2462800</v>
+        <v>2407700</v>
       </c>
       <c r="E92" t="n">
-        <v>1926765</v>
+        <v>1988415</v>
       </c>
       <c r="F92" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -7867,7 +7847,7 @@
         <v>55.52</v>
       </c>
       <c r="L92" t="n">
-        <v>2.3</v>
+        <v>4.64</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -7887,10 +7867,10 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>47.94</v>
+        <v>53.81</v>
       </c>
       <c r="S92" t="n">
-        <v>50.12</v>
+        <v>56.63</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7904,7 +7884,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7915,19 +7895,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>87</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>111.87</v>
+        <v>167.46</v>
       </c>
       <c r="D93" t="n">
-        <v>1285900</v>
+        <v>1883700</v>
       </c>
       <c r="E93" t="n">
-        <v>833245</v>
+        <v>894605</v>
       </c>
       <c r="F93" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -7945,13 +7925,13 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>80.09999999999999</v>
+        <v>80.95</v>
       </c>
       <c r="K93" t="n">
         <v>85.5</v>
       </c>
       <c r="L93" t="n">
-        <v>1.75</v>
+        <v>3.98</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -7967,10 +7947,10 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>72.09</v>
+        <v>73.91</v>
       </c>
       <c r="S93" t="n">
-        <v>65.37</v>
+        <v>73.34</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -7984,7 +7964,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -7995,23 +7975,23 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="C94" t="n">
-        <v>70.11</v>
+        <v>91.03</v>
       </c>
       <c r="D94" t="n">
-        <v>2873200</v>
+        <v>3777200</v>
       </c>
       <c r="E94" t="n">
-        <v>3370390</v>
+        <v>3401940</v>
       </c>
       <c r="F94" t="n">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8031,7 +8011,7 @@
         <v>28.56</v>
       </c>
       <c r="L94" t="n">
-        <v>-14.57</v>
+        <v>-15.62</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -8047,10 +8027,10 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>61.62</v>
+        <v>59.8</v>
       </c>
       <c r="S94" t="n">
-        <v>45.47</v>
+        <v>45.28</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -8064,7 +8044,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>
@@ -8075,23 +8055,23 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="C95" t="n">
-        <v>245.86</v>
+        <v>181.68</v>
       </c>
       <c r="D95" t="n">
-        <v>17193000</v>
+        <v>12529600</v>
       </c>
       <c r="E95" t="n">
-        <v>10338525</v>
+        <v>10542030</v>
       </c>
       <c r="F95" t="n">
-        <v>1.66</v>
+        <v>1.19</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8108,10 +8088,10 @@
         <v>14.02</v>
       </c>
       <c r="K95" t="n">
-        <v>17.92</v>
+        <v>17.73</v>
       </c>
       <c r="L95" t="n">
-        <v>-20.22</v>
+        <v>-18.19</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -8127,10 +8107,10 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>60.26</v>
+        <v>68.92</v>
       </c>
       <c r="S95" t="n">
-        <v>60.36</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -8144,87 +8124,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-10-27 22:05:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>VTZ</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="C96" t="n">
-        <v>20.23</v>
-      </c>
-      <c r="D96" t="n">
-        <v>996600</v>
-      </c>
-      <c r="E96" t="n">
-        <v>960460</v>
-      </c>
-      <c r="F96" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>⚡ Có Tín Hiệu</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>🟡 Sideway</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>🌧️ Dưới Mây</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="K96" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="L96" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R96" t="n">
-        <v>50</v>
-      </c>
-      <c r="S96" t="n">
-        <v>34.68</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>🟡 Trung tính</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>2026-10-27 22:05:20</t>
+          <t>2026-10-28 22:38:20</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,23 +535,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.35</v>
+        <v>21.3</v>
       </c>
       <c r="C2" t="n">
-        <v>228.43</v>
+        <v>143.41</v>
       </c>
       <c r="D2" t="n">
-        <v>10699200</v>
+        <v>6732700</v>
       </c>
       <c r="E2" t="n">
-        <v>8975725</v>
+        <v>9141390</v>
       </c>
       <c r="F2" t="n">
-        <v>1.19</v>
+        <v>0.74</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,7 +571,7 @@
         <v>21.58</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.04</v>
+        <v>-1.27</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>73.81</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>81.44</v>
+        <v>84.39</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -618,16 +618,16 @@
         <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>20.02</v>
+        <v>26.35</v>
       </c>
       <c r="D3" t="n">
-        <v>488300</v>
+        <v>642700</v>
       </c>
       <c r="E3" t="n">
-        <v>800670</v>
+        <v>823605</v>
       </c>
       <c r="F3" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>47.54</v>
+        <v>50.88</v>
       </c>
       <c r="S3" t="n">
-        <v>65.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -695,19 +695,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="C4" t="n">
-        <v>22.08</v>
+        <v>24.96</v>
       </c>
       <c r="D4" t="n">
-        <v>1262000</v>
+        <v>1476700</v>
       </c>
       <c r="E4" t="n">
-        <v>1545660</v>
+        <v>1597870</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -728,10 +728,10 @@
         <v>16.46</v>
       </c>
       <c r="K4" t="n">
-        <v>18.94</v>
+        <v>18.9</v>
       </c>
       <c r="L4" t="n">
-        <v>-7.6</v>
+        <v>-10.56</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>48.54</v>
+        <v>43.12</v>
       </c>
       <c r="S4" t="n">
-        <v>54.71</v>
+        <v>46.61</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.15</v>
+        <v>30.4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.16</v>
+        <v>54.77</v>
       </c>
       <c r="D5" t="n">
-        <v>1232600</v>
+        <v>1801500</v>
       </c>
       <c r="E5" t="n">
-        <v>1900110</v>
+        <v>1915255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -801,17 +801,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29.12</v>
+        <v>29.15</v>
       </c>
       <c r="K5" t="n">
         <v>28.4</v>
       </c>
       <c r="L5" t="n">
-        <v>6.16</v>
+        <v>7.04</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -820,25 +820,21 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>59.14</v>
+        <v>73.77</v>
       </c>
       <c r="S5" t="n">
-        <v>62.28</v>
+        <v>69.38</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -848,7 +844,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -859,19 +855,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.8</v>
+        <v>39.55</v>
       </c>
       <c r="C6" t="n">
         <v>25.31</v>
       </c>
       <c r="D6" t="n">
-        <v>636000</v>
+        <v>639900</v>
       </c>
       <c r="E6" t="n">
-        <v>566030</v>
+        <v>579915</v>
       </c>
       <c r="F6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -895,7 +891,7 @@
         <v>45.55</v>
       </c>
       <c r="L6" t="n">
-        <v>-12.62</v>
+        <v>-13.17</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -911,10 +907,10 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>54.14</v>
+        <v>58.62</v>
       </c>
       <c r="S6" t="n">
-        <v>63.27</v>
+        <v>61.72</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -928,7 +924,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -939,23 +935,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.65</v>
+        <v>33.85</v>
       </c>
       <c r="C7" t="n">
-        <v>146.67</v>
+        <v>211.26</v>
       </c>
       <c r="D7" t="n">
-        <v>4358700</v>
+        <v>6241200</v>
       </c>
       <c r="E7" t="n">
-        <v>3108420</v>
+        <v>3305335</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -975,7 +971,7 @@
         <v>37.54</v>
       </c>
       <c r="L7" t="n">
-        <v>-10.36</v>
+        <v>-9.83</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -991,10 +987,10 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>46.67</v>
+        <v>49.37</v>
       </c>
       <c r="S7" t="n">
-        <v>53.48</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1008,7 +1004,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1019,23 +1015,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.75</v>
+        <v>27.65</v>
       </c>
       <c r="C8" t="n">
-        <v>108.54</v>
+        <v>368.8</v>
       </c>
       <c r="D8" t="n">
-        <v>3775400</v>
+        <v>13338200</v>
       </c>
       <c r="E8" t="n">
-        <v>8772295</v>
+        <v>9050530</v>
       </c>
       <c r="F8" t="n">
-        <v>0.43</v>
+        <v>1.47</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1049,17 +1045,17 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28.24</v>
+        <v>28.34</v>
       </c>
       <c r="K8" t="n">
         <v>27.96</v>
       </c>
       <c r="L8" t="n">
-        <v>2.83</v>
+        <v>-1.11</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1071,10 +1067,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>28.19</v>
+        <v>27.63</v>
       </c>
       <c r="S8" t="n">
-        <v>24.46</v>
+        <v>24.26</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1088,7 +1084,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1099,19 +1095,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69.8</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>61.93</v>
+        <v>88.69</v>
       </c>
       <c r="D9" t="n">
-        <v>887300</v>
+        <v>1285400</v>
       </c>
       <c r="E9" t="n">
-        <v>883110</v>
+        <v>916375</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1135,7 +1131,7 @@
         <v>67.09999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>4.02</v>
+        <v>2.83</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1151,10 +1147,10 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>26.59</v>
+        <v>28.05</v>
       </c>
       <c r="S9" t="n">
-        <v>12.03</v>
+        <v>11.5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1168,7 +1164,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1179,23 +1175,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="C10" t="n">
-        <v>91.81999999999999</v>
+        <v>36.74</v>
       </c>
       <c r="D10" t="n">
-        <v>8126000</v>
+        <v>3310100</v>
       </c>
       <c r="E10" t="n">
-        <v>6963040</v>
+        <v>6936490</v>
       </c>
       <c r="F10" t="n">
-        <v>1.17</v>
+        <v>0.48</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1215,7 +1211,7 @@
         <v>13.61</v>
       </c>
       <c r="L10" t="n">
-        <v>-16.97</v>
+        <v>-18.44</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1231,10 +1227,10 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>79.17</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>79.59999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1248,7 +1244,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1259,19 +1255,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.75</v>
+        <v>13.45</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>86.69</v>
       </c>
       <c r="D11" t="n">
-        <v>8145100</v>
+        <v>6445300</v>
       </c>
       <c r="E11" t="n">
-        <v>9310220</v>
+        <v>9321100</v>
       </c>
       <c r="F11" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1285,7 +1281,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1295,7 +1291,7 @@
         <v>15.85</v>
       </c>
       <c r="L11" t="n">
-        <v>-13.25</v>
+        <v>-15.14</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1311,10 +1307,10 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>77.33</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>80.67</v>
+        <v>75.78</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1328,7 +1324,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1335,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>64.7</v>
       </c>
       <c r="C12" t="n">
-        <v>31.83</v>
+        <v>57.18</v>
       </c>
       <c r="D12" t="n">
-        <v>468100</v>
+        <v>883800</v>
       </c>
       <c r="E12" t="n">
-        <v>461770</v>
+        <v>495050</v>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1375,7 +1371,7 @@
         <v>72.5</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.21</v>
+        <v>-10.76</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1391,14 +1387,14 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>72.8</v>
+        <v>57.59</v>
       </c>
       <c r="S12" t="n">
-        <v>74.09999999999999</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1408,7 +1404,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1422,20 +1418,20 @@
         <v>30.7</v>
       </c>
       <c r="C13" t="n">
-        <v>209.98</v>
+        <v>234.91</v>
       </c>
       <c r="D13" t="n">
-        <v>6839900</v>
+        <v>7651700</v>
       </c>
       <c r="E13" t="n">
-        <v>7024280</v>
+        <v>7122595</v>
       </c>
       <c r="F13" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1471,14 +1467,14 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>72.06</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>57.1</v>
+        <v>64.58</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1488,7 +1484,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1499,23 +1495,23 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.7</v>
+        <v>21.55</v>
       </c>
       <c r="C14" t="n">
-        <v>29.36</v>
+        <v>41.18</v>
       </c>
       <c r="D14" t="n">
-        <v>1352800</v>
+        <v>1911100</v>
       </c>
       <c r="E14" t="n">
-        <v>1445440</v>
+        <v>1496800</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1535,7 +1531,7 @@
         <v>24.1</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.960000000000001</v>
+        <v>-10.58</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1551,10 +1547,10 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>70.3</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>70.33</v>
+        <v>77.03</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1568,7 +1564,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1579,23 +1575,23 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="C15" t="n">
-        <v>28.78</v>
+        <v>28.17</v>
       </c>
       <c r="D15" t="n">
-        <v>1809800</v>
+        <v>1783100</v>
       </c>
       <c r="E15" t="n">
-        <v>1805425</v>
+        <v>1804490</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1615,7 +1611,7 @@
         <v>17.64</v>
       </c>
       <c r="L15" t="n">
-        <v>-9.890000000000001</v>
+        <v>-10.46</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1631,10 +1627,10 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>57.45</v>
+        <v>55.1</v>
       </c>
       <c r="S15" t="n">
-        <v>59.23</v>
+        <v>52.61</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1648,30 +1644,30 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DCL</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>46.3</v>
+        <v>34.2</v>
       </c>
       <c r="C16" t="n">
-        <v>38.36</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>828600</v>
+        <v>2424000</v>
       </c>
       <c r="E16" t="n">
-        <v>688655</v>
+        <v>2180815</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1689,17 +1685,17 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>44.65</v>
+        <v>32.3</v>
       </c>
       <c r="K16" t="n">
-        <v>44.05</v>
+        <v>35.83</v>
       </c>
       <c r="L16" t="n">
-        <v>5.11</v>
+        <v>-4.55</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1711,10 +1707,10 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>37.66</v>
+        <v>44.96</v>
       </c>
       <c r="S16" t="n">
-        <v>39.74</v>
+        <v>58.21</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1728,34 +1724,34 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.8</v>
+        <v>42.5</v>
       </c>
       <c r="C17" t="n">
-        <v>55.18</v>
+        <v>71.91</v>
       </c>
       <c r="D17" t="n">
-        <v>1585600</v>
+        <v>1691900</v>
       </c>
       <c r="E17" t="n">
-        <v>2140700</v>
+        <v>1684080</v>
       </c>
       <c r="F17" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1765,24 +1761,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>32.3</v>
+        <v>39.83</v>
       </c>
       <c r="K17" t="n">
-        <v>35.83</v>
+        <v>39.83</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.87</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
@@ -1791,14 +1791,14 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>53.17</v>
+        <v>27.05</v>
       </c>
       <c r="S17" t="n">
-        <v>67.48999999999999</v>
+        <v>20.53</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1808,34 +1808,34 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DHC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.35</v>
+        <v>37.5</v>
       </c>
       <c r="C18" t="n">
-        <v>251.74</v>
+        <v>20.16</v>
       </c>
       <c r="D18" t="n">
-        <v>5944200</v>
+        <v>537700</v>
       </c>
       <c r="E18" t="n">
-        <v>1654990</v>
+        <v>459120</v>
       </c>
       <c r="F18" t="n">
-        <v>3.59</v>
+        <v>1.17</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1845,28 +1845,24 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>39.83</v>
+        <v>34.06</v>
       </c>
       <c r="K18" t="n">
-        <v>39.83</v>
+        <v>33.86</v>
       </c>
       <c r="L18" t="n">
-        <v>6.33</v>
+        <v>10.75</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
@@ -1875,14 +1871,14 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>24.77</v>
+        <v>59.8</v>
       </c>
       <c r="S18" t="n">
-        <v>20.8</v>
+        <v>50.68</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1892,7 +1888,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1903,19 +1899,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.77</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>39.85</v>
+        <v>29.15</v>
       </c>
       <c r="D19" t="n">
-        <v>4079000</v>
+        <v>2977200</v>
       </c>
       <c r="E19" t="n">
-        <v>5089320</v>
+        <v>5100105</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1939,7 +1935,7 @@
         <v>11.52</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.23</v>
+        <v>-15.05</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1955,10 +1951,10 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>65.98999999999999</v>
+        <v>64.03</v>
       </c>
       <c r="S19" t="n">
-        <v>59.11</v>
+        <v>56.84</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1972,7 +1968,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -1983,19 +1979,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.95</v>
+        <v>30.2</v>
       </c>
       <c r="C20" t="n">
-        <v>23.2</v>
+        <v>20.66</v>
       </c>
       <c r="D20" t="n">
-        <v>749500</v>
+        <v>684100</v>
       </c>
       <c r="E20" t="n">
-        <v>502010</v>
+        <v>518010</v>
       </c>
       <c r="F20" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2019,7 +2015,7 @@
         <v>35.3</v>
       </c>
       <c r="L20" t="n">
-        <v>-12.34</v>
+        <v>-14.46</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2035,10 +2031,10 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>82.98</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>89.02</v>
+        <v>81.36</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2052,7 +2048,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -2063,23 +2059,23 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="C21" t="n">
-        <v>22.48</v>
+        <v>60.24</v>
       </c>
       <c r="D21" t="n">
-        <v>1055500</v>
+        <v>2882200</v>
       </c>
       <c r="E21" t="n">
-        <v>2050670</v>
+        <v>2082395</v>
       </c>
       <c r="F21" t="n">
-        <v>0.51</v>
+        <v>1.38</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2099,7 +2095,7 @@
         <v>23.62</v>
       </c>
       <c r="L21" t="n">
-        <v>-9.82</v>
+        <v>-11.52</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2115,10 +2111,10 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>33.33</v>
+        <v>31.48</v>
       </c>
       <c r="S21" t="n">
-        <v>28.96</v>
+        <v>28.03</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2132,54 +2128,54 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>DPR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.99</v>
+        <v>38.8</v>
       </c>
       <c r="C22" t="n">
-        <v>103.51</v>
+        <v>42.79</v>
       </c>
       <c r="D22" t="n">
-        <v>10360900</v>
+        <v>1102900</v>
       </c>
       <c r="E22" t="n">
-        <v>9625335</v>
+        <v>439310</v>
       </c>
       <c r="F22" t="n">
-        <v>1.08</v>
+        <v>2.51</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10.73</v>
+        <v>37.1</v>
       </c>
       <c r="K22" t="n">
-        <v>11.89</v>
+        <v>39.65</v>
       </c>
       <c r="L22" t="n">
-        <v>-15.94</v>
+        <v>-2.14</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2191,55 +2187,55 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.5x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>60.56</v>
+        <v>63.22</v>
       </c>
       <c r="S22" t="n">
-        <v>61.24</v>
+        <v>53.56</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16.65</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>101.09</v>
+        <v>67.59</v>
       </c>
       <c r="D23" t="n">
-        <v>6071200</v>
+        <v>6841000</v>
       </c>
       <c r="E23" t="n">
-        <v>4886950</v>
+        <v>9734240</v>
       </c>
       <c r="F23" t="n">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2253,13 +2249,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>17.2</v>
+        <v>10.73</v>
       </c>
       <c r="K23" t="n">
-        <v>19.52</v>
+        <v>11.89</v>
       </c>
       <c r="L23" t="n">
-        <v>-14.72</v>
+        <v>-16.87</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2275,10 +2271,10 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>58.21</v>
+        <v>53.67</v>
       </c>
       <c r="S23" t="n">
-        <v>54.61</v>
+        <v>54.98</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2292,34 +2288,34 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>54</v>
+        <v>16.8</v>
       </c>
       <c r="C24" t="n">
-        <v>714.1900000000001</v>
+        <v>51.95</v>
       </c>
       <c r="D24" t="n">
-        <v>13225800</v>
+        <v>3092000</v>
       </c>
       <c r="E24" t="n">
-        <v>6715440</v>
+        <v>4870420</v>
       </c>
       <c r="F24" t="n">
-        <v>1.97</v>
+        <v>0.63</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2329,17 +2325,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>60.95</v>
+        <v>17.2</v>
       </c>
       <c r="K24" t="n">
-        <v>62.27</v>
+        <v>19.48</v>
       </c>
       <c r="L24" t="n">
-        <v>-13.28</v>
+        <v>-13.74</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2355,10 +2351,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>21.78</v>
+        <v>60</v>
       </c>
       <c r="S24" t="n">
-        <v>33.4</v>
+        <v>59.08</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2372,30 +2368,30 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>147</v>
+        <v>52.7</v>
       </c>
       <c r="C25" t="n">
-        <v>149.69</v>
+        <v>663.55</v>
       </c>
       <c r="D25" t="n">
-        <v>1018300</v>
+        <v>12591100</v>
       </c>
       <c r="E25" t="n">
-        <v>573745</v>
+        <v>7174345</v>
       </c>
       <c r="F25" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2404,34 +2400,30 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>129.4</v>
+        <v>60.25</v>
       </c>
       <c r="K25" t="n">
-        <v>127.5</v>
+        <v>61.57</v>
       </c>
       <c r="L25" t="n">
-        <v>15.29</v>
+        <v>-14.41</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2439,51 +2431,51 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>43.01</v>
+        <v>22.92</v>
       </c>
       <c r="S25" t="n">
-        <v>41.98</v>
+        <v>33.19</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>77.7</v>
+        <v>147.7</v>
       </c>
       <c r="C26" t="n">
-        <v>37.4</v>
+        <v>96.14</v>
       </c>
       <c r="D26" t="n">
-        <v>481400</v>
+        <v>650900</v>
       </c>
       <c r="E26" t="n">
-        <v>901190</v>
+        <v>563795</v>
       </c>
       <c r="F26" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2493,25 +2485,29 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>77.31</v>
+        <v>129.4</v>
       </c>
       <c r="K26" t="n">
-        <v>77.69</v>
+        <v>127.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01</v>
+        <v>15.84</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2519,10 +2515,10 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>34.53</v>
+        <v>46.52</v>
       </c>
       <c r="S26" t="n">
-        <v>53.13</v>
+        <v>41.26</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2536,34 +2532,34 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>69.2</v>
+        <v>76</v>
       </c>
       <c r="C27" t="n">
-        <v>63.36</v>
+        <v>196.17</v>
       </c>
       <c r="D27" t="n">
-        <v>915600</v>
+        <v>2581200</v>
       </c>
       <c r="E27" t="n">
-        <v>1430655</v>
+        <v>997730</v>
       </c>
       <c r="F27" t="n">
-        <v>0.64</v>
+        <v>2.59</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2573,17 +2569,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>66.81999999999999</v>
+        <v>77.31</v>
       </c>
       <c r="K27" t="n">
-        <v>95.83</v>
+        <v>77.69</v>
       </c>
       <c r="L27" t="n">
-        <v>-27.79</v>
+        <v>-2.18</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2595,14 +2591,14 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>51.78</v>
+        <v>33.57</v>
       </c>
       <c r="S27" t="n">
-        <v>48.59</v>
+        <v>39.81</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2616,34 +2612,34 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.25</v>
+        <v>67</v>
       </c>
       <c r="C28" t="n">
-        <v>41.8</v>
+        <v>85.73999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>1479700</v>
+        <v>1279700</v>
       </c>
       <c r="E28" t="n">
-        <v>1469015</v>
+        <v>1427400</v>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2653,17 +2649,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>27.15</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>29.42</v>
+        <v>95.83</v>
       </c>
       <c r="L28" t="n">
-        <v>-3.99</v>
+        <v>-30.08</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2679,10 +2675,10 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>53.01</v>
+        <v>41.21</v>
       </c>
       <c r="S28" t="n">
-        <v>58.79</v>
+        <v>42.61</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2696,54 +2692,54 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23.1</v>
+        <v>27.3</v>
       </c>
       <c r="C29" t="n">
-        <v>138.14</v>
+        <v>46.3</v>
       </c>
       <c r="D29" t="n">
-        <v>5980200</v>
+        <v>1695900</v>
       </c>
       <c r="E29" t="n">
-        <v>7672890</v>
+        <v>1467540</v>
       </c>
       <c r="F29" t="n">
-        <v>0.78</v>
+        <v>1.16</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>23.45</v>
+        <v>27.15</v>
       </c>
       <c r="K29" t="n">
-        <v>28.58</v>
+        <v>29.42</v>
       </c>
       <c r="L29" t="n">
-        <v>-19.16</v>
+        <v>-7.22</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2759,75 +2755,75 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>63.27</v>
+        <v>43.14</v>
       </c>
       <c r="S29" t="n">
-        <v>58.37</v>
+        <v>56.82</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C30" t="n">
-        <v>136.22</v>
+        <v>157.25</v>
       </c>
       <c r="D30" t="n">
-        <v>2522500</v>
+        <v>6837000</v>
       </c>
       <c r="E30" t="n">
-        <v>1807550</v>
+        <v>7625375</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>52.78</v>
+        <v>23.45</v>
       </c>
       <c r="K30" t="n">
-        <v>51.28</v>
+        <v>28.58</v>
       </c>
       <c r="L30" t="n">
-        <v>5.29</v>
+        <v>-19.51</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2839,10 +2835,10 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>49.22</v>
+        <v>58.24</v>
       </c>
       <c r="S30" t="n">
-        <v>57.35</v>
+        <v>58.03</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2851,39 +2847,39 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31.5</v>
+        <v>52.1</v>
       </c>
       <c r="C31" t="n">
-        <v>47.23</v>
+        <v>99.95</v>
       </c>
       <c r="D31" t="n">
-        <v>1499500</v>
+        <v>1918400</v>
       </c>
       <c r="E31" t="n">
-        <v>2086950</v>
+        <v>1838535</v>
       </c>
       <c r="F31" t="n">
-        <v>0.72</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2893,21 +2889,21 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>30.22</v>
+        <v>52.78</v>
       </c>
       <c r="K31" t="n">
-        <v>32.78</v>
+        <v>51.28</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.89</v>
+        <v>1.59</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2919,14 +2915,14 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>26.26</v>
+        <v>39.57</v>
       </c>
       <c r="S31" t="n">
-        <v>41.06</v>
+        <v>55.94</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -2936,34 +2932,34 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>50.6</v>
+        <v>31.95</v>
       </c>
       <c r="C32" t="n">
-        <v>22.17</v>
+        <v>123.61</v>
       </c>
       <c r="D32" t="n">
-        <v>438200</v>
+        <v>3868800</v>
       </c>
       <c r="E32" t="n">
-        <v>865875</v>
+        <v>2123265</v>
       </c>
       <c r="F32" t="n">
-        <v>0.51</v>
+        <v>1.82</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2977,17 +2973,17 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>48.2</v>
+        <v>30.22</v>
       </c>
       <c r="K32" t="n">
-        <v>49.55</v>
+        <v>32.78</v>
       </c>
       <c r="L32" t="n">
-        <v>2.12</v>
+        <v>-2.52</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2999,10 +2995,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>44</v>
+        <v>39.77</v>
       </c>
       <c r="S32" t="n">
-        <v>52.24</v>
+        <v>56.44</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3016,34 +3012,34 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HAH</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.45</v>
+        <v>49.05</v>
       </c>
       <c r="C33" t="n">
-        <v>72.68000000000001</v>
+        <v>32.79</v>
       </c>
       <c r="D33" t="n">
-        <v>3099300</v>
+        <v>668600</v>
       </c>
       <c r="E33" t="n">
-        <v>2732765</v>
+        <v>852175</v>
       </c>
       <c r="F33" t="n">
-        <v>1.13</v>
+        <v>0.78</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3053,17 +3049,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>24.92</v>
+        <v>48.2</v>
       </c>
       <c r="K33" t="n">
-        <v>24.8</v>
+        <v>49.55</v>
       </c>
       <c r="L33" t="n">
-        <v>-5.44</v>
+        <v>-1.01</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3079,10 +3075,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>48.19</v>
+        <v>43.78</v>
       </c>
       <c r="S33" t="n">
-        <v>47.14</v>
+        <v>55.76</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3096,34 +3092,34 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.85</v>
+        <v>23.05</v>
       </c>
       <c r="C34" t="n">
-        <v>546.5700000000001</v>
+        <v>55.05</v>
       </c>
       <c r="D34" t="n">
-        <v>23919700</v>
+        <v>2388400</v>
       </c>
       <c r="E34" t="n">
-        <v>17088220</v>
+        <v>2733905</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4</v>
+        <v>0.87</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3133,28 +3129,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>21.13</v>
+        <v>24.92</v>
       </c>
       <c r="K34" t="n">
-        <v>21.13</v>
+        <v>24.8</v>
       </c>
       <c r="L34" t="n">
-        <v>8.140000000000001</v>
+        <v>-7.06</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -3163,10 +3155,10 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>64.20999999999999</v>
+        <v>48.78</v>
       </c>
       <c r="S34" t="n">
-        <v>63.78</v>
+        <v>47.23</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3180,34 +3172,34 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HDC</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11.5</v>
+        <v>22.7</v>
       </c>
       <c r="C35" t="n">
-        <v>24.34</v>
+        <v>358.08</v>
       </c>
       <c r="D35" t="n">
-        <v>2116900</v>
+        <v>15774500</v>
       </c>
       <c r="E35" t="n">
-        <v>1717555</v>
+        <v>17242570</v>
       </c>
       <c r="F35" t="n">
-        <v>1.23</v>
+        <v>0.91</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3217,24 +3209,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>11.18</v>
+        <v>21.13</v>
       </c>
       <c r="K35" t="n">
-        <v>13.34</v>
+        <v>21.13</v>
       </c>
       <c r="L35" t="n">
-        <v>-13.83</v>
+        <v>7.43</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -3243,14 +3239,14 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>81.40000000000001</v>
+        <v>53.85</v>
       </c>
       <c r="S35" t="n">
-        <v>73.53</v>
+        <v>60.96</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3260,7 +3256,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -3271,23 +3267,23 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.75</v>
+        <v>17.6</v>
       </c>
       <c r="C36" t="n">
-        <v>32.24</v>
+        <v>20.63</v>
       </c>
       <c r="D36" t="n">
-        <v>1816300</v>
+        <v>1172200</v>
       </c>
       <c r="E36" t="n">
-        <v>1380905</v>
+        <v>1425335</v>
       </c>
       <c r="F36" t="n">
-        <v>1.32</v>
+        <v>0.82</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3307,7 +3303,7 @@
         <v>15.55</v>
       </c>
       <c r="L36" t="n">
-        <v>14.18</v>
+        <v>13.22</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3323,14 +3319,14 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>52.31</v>
+        <v>49.25</v>
       </c>
       <c r="S36" t="n">
-        <v>70.75</v>
+        <v>66.48</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -3340,34 +3336,34 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HHV</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9.65</v>
+        <v>21.2</v>
       </c>
       <c r="C37" t="n">
-        <v>26.55</v>
+        <v>771.91</v>
       </c>
       <c r="D37" t="n">
-        <v>2751700</v>
+        <v>36410800</v>
       </c>
       <c r="E37" t="n">
-        <v>3132980</v>
+        <v>19095330</v>
       </c>
       <c r="F37" t="n">
-        <v>0.88</v>
+        <v>1.91</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3381,13 +3377,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9.529999999999999</v>
+        <v>21.12</v>
       </c>
       <c r="K37" t="n">
-        <v>10.54</v>
+        <v>22.3</v>
       </c>
       <c r="L37" t="n">
-        <v>-8.44</v>
+        <v>-4.93</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3403,10 +3399,10 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>71</v>
+        <v>65.28</v>
       </c>
       <c r="S37" t="n">
-        <v>66.18000000000001</v>
+        <v>76.05</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3420,54 +3416,54 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.75</v>
+        <v>11.15</v>
       </c>
       <c r="C38" t="n">
-        <v>273.99</v>
+        <v>58.26</v>
       </c>
       <c r="D38" t="n">
-        <v>13204500</v>
+        <v>5224800</v>
       </c>
       <c r="E38" t="n">
-        <v>17829645</v>
+        <v>3476630</v>
       </c>
       <c r="F38" t="n">
-        <v>0.74</v>
+        <v>1.5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>21.12</v>
+        <v>10.55</v>
       </c>
       <c r="K38" t="n">
-        <v>22.46</v>
+        <v>11.35</v>
       </c>
       <c r="L38" t="n">
-        <v>-7.59</v>
+        <v>-1.76</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3483,47 +3479,47 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>59.38</v>
+        <v>82.05</v>
       </c>
       <c r="S38" t="n">
-        <v>67.34</v>
+        <v>81.95</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11.1</v>
+        <v>35.6</v>
       </c>
       <c r="C39" t="n">
-        <v>27.82</v>
+        <v>22.6</v>
       </c>
       <c r="D39" t="n">
-        <v>2506600</v>
+        <v>634900</v>
       </c>
       <c r="E39" t="n">
-        <v>3301225</v>
+        <v>1245215</v>
       </c>
       <c r="F39" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3541,36 +3537,40 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>10.5</v>
+        <v>32.95</v>
       </c>
       <c r="K39" t="n">
-        <v>11.35</v>
+        <v>34.75</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>81.15000000000001</v>
+        <v>50.82</v>
       </c>
       <c r="S39" t="n">
-        <v>77.27</v>
+        <v>48.34</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -3580,30 +3580,30 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>KBC</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>26.5</v>
       </c>
       <c r="C40" t="n">
-        <v>36.72</v>
+        <v>29.11</v>
       </c>
       <c r="D40" t="n">
-        <v>1020000</v>
+        <v>1098600</v>
       </c>
       <c r="E40" t="n">
-        <v>1244270</v>
+        <v>1268460</v>
       </c>
       <c r="F40" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3612,26 +3612,26 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>32.95</v>
+        <v>26.55</v>
       </c>
       <c r="K40" t="n">
-        <v>34.97</v>
+        <v>29.68</v>
       </c>
       <c r="L40" t="n">
-        <v>2.95</v>
+        <v>-10.7</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3643,71 +3643,71 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>58.73</v>
+        <v>67.86</v>
       </c>
       <c r="S40" t="n">
-        <v>56.6</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KBC</t>
+          <t>KDH</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C41" t="n">
-        <v>44.62</v>
+        <v>57.32</v>
       </c>
       <c r="D41" t="n">
-        <v>1652700</v>
+        <v>4094000</v>
       </c>
       <c r="E41" t="n">
-        <v>1293710</v>
+        <v>4601390</v>
       </c>
       <c r="F41" t="n">
-        <v>1.28</v>
+        <v>0.89</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>26.55</v>
+        <v>15.04</v>
       </c>
       <c r="K41" t="n">
-        <v>29.68</v>
+        <v>18.2</v>
       </c>
       <c r="L41" t="n">
-        <v>-9.01</v>
+        <v>-23.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3723,51 +3723,51 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>83.33</v>
+        <v>59.38</v>
       </c>
       <c r="S41" t="n">
-        <v>79.5</v>
+        <v>61.22</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KDH</t>
+          <t>KHG</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>14.25</v>
+        <v>4.5</v>
       </c>
       <c r="C42" t="n">
-        <v>74.7</v>
+        <v>31.12</v>
       </c>
       <c r="D42" t="n">
-        <v>5242200</v>
+        <v>6915000</v>
       </c>
       <c r="E42" t="n">
-        <v>4559740</v>
+        <v>3001905</v>
       </c>
       <c r="F42" t="n">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>15.04</v>
+        <v>4.66</v>
       </c>
       <c r="K42" t="n">
-        <v>18.2</v>
+        <v>4.96</v>
       </c>
       <c r="L42" t="n">
-        <v>-21.72</v>
+        <v>-9.27</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>66.13</v>
+        <v>39.13</v>
       </c>
       <c r="S42" t="n">
-        <v>67.83</v>
+        <v>49.61</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -3831,19 +3831,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>38.1</v>
+        <v>37.3</v>
       </c>
       <c r="C43" t="n">
-        <v>46.23</v>
+        <v>61</v>
       </c>
       <c r="D43" t="n">
-        <v>1213500</v>
+        <v>1635300</v>
       </c>
       <c r="E43" t="n">
-        <v>2055980</v>
+        <v>2038585</v>
       </c>
       <c r="F43" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>46.6</v>
+        <v>46</v>
       </c>
       <c r="K43" t="n">
         <v>47.85</v>
       </c>
       <c r="L43" t="n">
-        <v>-20.38</v>
+        <v>-22.05</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>39.06</v>
+        <v>36.29</v>
       </c>
       <c r="S43" t="n">
-        <v>41.24</v>
+        <v>41.77</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -3914,16 +3914,16 @@
         <v>19.7</v>
       </c>
       <c r="C44" t="n">
-        <v>149.87</v>
+        <v>142.52</v>
       </c>
       <c r="D44" t="n">
-        <v>7607600</v>
+        <v>7234600</v>
       </c>
       <c r="E44" t="n">
-        <v>11492850</v>
+        <v>11475935</v>
       </c>
       <c r="F44" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3944,14 +3944,14 @@
         <v>19.49</v>
       </c>
       <c r="K44" t="n">
-        <v>19.7</v>
+        <v>19.52</v>
       </c>
       <c r="L44" t="n">
-        <v>-0</v>
+        <v>0.9</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>66.67</v>
+        <v>64.44</v>
       </c>
       <c r="S44" t="n">
-        <v>54.86</v>
+        <v>61.75</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3984,30 +3984,30 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>139.8</v>
+        <v>15.3</v>
       </c>
       <c r="C45" t="n">
-        <v>24.74</v>
+        <v>28.65</v>
       </c>
       <c r="D45" t="n">
-        <v>177000</v>
+        <v>1872800</v>
       </c>
       <c r="E45" t="n">
-        <v>610330</v>
+        <v>2670060</v>
       </c>
       <c r="F45" t="n">
-        <v>0.29</v>
+        <v>0.7</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4016,82 +4016,78 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>139.46</v>
+        <v>15.95</v>
       </c>
       <c r="K45" t="n">
-        <v>134.54</v>
+        <v>17.43</v>
       </c>
       <c r="L45" t="n">
-        <v>3.91</v>
+        <v>-12.25</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>27.71</v>
+        <v>61.54</v>
       </c>
       <c r="S45" t="n">
-        <v>24.67</v>
+        <v>59.72</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>16</v>
+        <v>137.3</v>
       </c>
       <c r="C46" t="n">
-        <v>155.41</v>
+        <v>41.23</v>
       </c>
       <c r="D46" t="n">
-        <v>9713300</v>
+        <v>300300</v>
       </c>
       <c r="E46" t="n">
-        <v>10506140</v>
+        <v>619930</v>
       </c>
       <c r="F46" t="n">
-        <v>0.92</v>
+        <v>0.48</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4100,34 +4096,30 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>14.08</v>
+        <v>139.46</v>
       </c>
       <c r="K46" t="n">
-        <v>13.24</v>
+        <v>134.54</v>
       </c>
       <c r="L46" t="n">
-        <v>20.89</v>
+        <v>2.06</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4135,47 +4127,47 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>80.48999999999999</v>
+        <v>22.33</v>
       </c>
       <c r="S46" t="n">
-        <v>86.22</v>
+        <v>26.18</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>74.2</v>
+        <v>16.05</v>
       </c>
       <c r="C47" t="n">
-        <v>357.2</v>
+        <v>94.11</v>
       </c>
       <c r="D47" t="n">
-        <v>4814000</v>
+        <v>5863300</v>
       </c>
       <c r="E47" t="n">
-        <v>5596525</v>
+        <v>10311415</v>
       </c>
       <c r="F47" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4184,7 +4176,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4193,69 +4185,77 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>69.65000000000001</v>
+        <v>14.13</v>
       </c>
       <c r="K47" t="n">
-        <v>72.05</v>
+        <v>13.28</v>
       </c>
       <c r="L47" t="n">
-        <v>2.98</v>
+        <v>20.81</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>50</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="S47" t="n">
-        <v>51.69</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>113.75</v>
+        <v>385.04</v>
       </c>
       <c r="D48" t="n">
-        <v>1663000</v>
+        <v>5340400</v>
       </c>
       <c r="E48" t="n">
-        <v>2123275</v>
+        <v>5563140</v>
       </c>
       <c r="F48" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4273,25 +4273,21 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>51.4</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>50.57</v>
+        <v>72.05</v>
       </c>
       <c r="L48" t="n">
-        <v>35.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4299,10 +4295,10 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>50.54</v>
+        <v>42.11</v>
       </c>
       <c r="S48" t="n">
-        <v>46.87</v>
+        <v>51.53</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4316,34 +4312,34 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>76</v>
+        <v>64.03</v>
       </c>
       <c r="C49" t="n">
-        <v>364.1</v>
+        <v>139.28</v>
       </c>
       <c r="D49" t="n">
-        <v>4790800</v>
+        <v>2175300</v>
       </c>
       <c r="E49" t="n">
-        <v>2992715</v>
+        <v>2032580</v>
       </c>
       <c r="F49" t="n">
-        <v>1.6</v>
+        <v>1.07</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4357,21 +4353,25 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>69.02</v>
+        <v>50.54</v>
       </c>
       <c r="K49" t="n">
-        <v>72.83</v>
+        <v>49.06</v>
       </c>
       <c r="L49" t="n">
-        <v>4.35</v>
+        <v>30.51</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>49.44</v>
+        <v>45.35</v>
       </c>
       <c r="S49" t="n">
-        <v>53.13</v>
+        <v>37.8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4396,30 +4396,30 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12.65</v>
+        <v>75.8</v>
       </c>
       <c r="C50" t="n">
-        <v>27.35</v>
+        <v>148.95</v>
       </c>
       <c r="D50" t="n">
-        <v>2162300</v>
+        <v>1965100</v>
       </c>
       <c r="E50" t="n">
-        <v>2546430</v>
+        <v>2956090</v>
       </c>
       <c r="F50" t="n">
-        <v>0.85</v>
+        <v>0.66</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4437,13 +4437,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>12.05</v>
+        <v>69.02</v>
       </c>
       <c r="K50" t="n">
-        <v>12.25</v>
+        <v>72.83</v>
       </c>
       <c r="L50" t="n">
-        <v>3.27</v>
+        <v>4.08</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4452,17 +4452,21 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>58.33</v>
+        <v>49.44</v>
       </c>
       <c r="S50" t="n">
-        <v>61.41</v>
+        <v>54.44</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4476,34 +4480,34 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12.15</v>
+        <v>12.65</v>
       </c>
       <c r="C51" t="n">
-        <v>52.1</v>
+        <v>28.19</v>
       </c>
       <c r="D51" t="n">
-        <v>4288200</v>
+        <v>2228200</v>
       </c>
       <c r="E51" t="n">
-        <v>4185485</v>
+        <v>2583455</v>
       </c>
       <c r="F51" t="n">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4517,13 +4521,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>10.65</v>
+        <v>12.05</v>
       </c>
       <c r="K51" t="n">
-        <v>11.16</v>
+        <v>12.25</v>
       </c>
       <c r="L51" t="n">
-        <v>8.869999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4539,14 +4543,14 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>89.47</v>
+        <v>65.63</v>
       </c>
       <c r="S51" t="n">
-        <v>95.25</v>
+        <v>62.38</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4556,34 +4560,34 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NLG</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>23</v>
+        <v>12.1</v>
       </c>
       <c r="C52" t="n">
-        <v>20.81</v>
+        <v>116.24</v>
       </c>
       <c r="D52" t="n">
-        <v>904800</v>
+        <v>9606600</v>
       </c>
       <c r="E52" t="n">
-        <v>1477335</v>
+        <v>4563905</v>
       </c>
       <c r="F52" t="n">
-        <v>0.61</v>
+        <v>2.1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4593,44 +4597,40 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>22.55</v>
+        <v>10.75</v>
       </c>
       <c r="K52" t="n">
-        <v>23.67</v>
+        <v>11.16</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.85</v>
+        <v>8.42</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>64</v>
+        <v>87.87</v>
       </c>
       <c r="S52" t="n">
-        <v>69.03</v>
+        <v>82.73</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -4640,30 +4640,30 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVB</t>
+          <t>NLG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>14.7</v>
+        <v>23</v>
       </c>
       <c r="C53" t="n">
-        <v>20.62</v>
+        <v>22.59</v>
       </c>
       <c r="D53" t="n">
-        <v>1403000</v>
+        <v>982200</v>
       </c>
       <c r="E53" t="n">
-        <v>2023690</v>
+        <v>1392055</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4677,28 +4677,24 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>22.55</v>
       </c>
       <c r="K53" t="n">
-        <v>14</v>
+        <v>23.67</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>-2.85</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
@@ -4707,10 +4703,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>35.38</v>
+        <v>64.86</v>
       </c>
       <c r="S53" t="n">
-        <v>36.94</v>
+        <v>68.66</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4724,7 +4720,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -4735,19 +4731,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.5</v>
+        <v>10.35</v>
       </c>
       <c r="C54" t="n">
-        <v>142.61</v>
+        <v>141.41</v>
       </c>
       <c r="D54" t="n">
-        <v>13582300</v>
+        <v>13662600</v>
       </c>
       <c r="E54" t="n">
-        <v>24218894</v>
+        <v>24119064</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4771,7 +4767,7 @@
         <v>14.5</v>
       </c>
       <c r="L54" t="n">
-        <v>-27.56</v>
+        <v>-28.6</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4787,10 +4783,10 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>57.14</v>
+        <v>25</v>
       </c>
       <c r="S54" t="n">
-        <v>58.35</v>
+        <v>43.02</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4804,34 +4800,34 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OCB</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10.7</v>
+        <v>12.7</v>
       </c>
       <c r="C55" t="n">
-        <v>56.52</v>
+        <v>28.85</v>
       </c>
       <c r="D55" t="n">
-        <v>5281900</v>
+        <v>2271400</v>
       </c>
       <c r="E55" t="n">
-        <v>2216985</v>
+        <v>1598500</v>
       </c>
       <c r="F55" t="n">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4841,21 +4837,21 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>10.46</v>
+        <v>13.93</v>
       </c>
       <c r="K55" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="L55" t="n">
-        <v>1.95</v>
+        <v>-9.25</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4867,14 +4863,14 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>75.34</v>
+        <v>30.77</v>
       </c>
       <c r="S55" t="n">
-        <v>72.44</v>
+        <v>37.48</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -4884,7 +4880,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -4895,19 +4891,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>15.3</v>
+        <v>14.75</v>
       </c>
       <c r="C56" t="n">
-        <v>85.12</v>
+        <v>74.05</v>
       </c>
       <c r="D56" t="n">
-        <v>5563700</v>
+        <v>5020300</v>
       </c>
       <c r="E56" t="n">
-        <v>4328045</v>
+        <v>4470360</v>
       </c>
       <c r="F56" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4931,7 +4927,7 @@
         <v>14.25</v>
       </c>
       <c r="L56" t="n">
-        <v>7.37</v>
+        <v>3.51</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4947,10 +4943,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>75</v>
+        <v>65.56</v>
       </c>
       <c r="S56" t="n">
-        <v>65.73999999999999</v>
+        <v>60.27</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4964,34 +4960,34 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>11.55</v>
+        <v>17.5</v>
       </c>
       <c r="C57" t="n">
-        <v>57.63</v>
+        <v>32.08</v>
       </c>
       <c r="D57" t="n">
-        <v>4989300</v>
+        <v>1832900</v>
       </c>
       <c r="E57" t="n">
-        <v>5253825</v>
+        <v>1045210</v>
       </c>
       <c r="F57" t="n">
-        <v>0.95</v>
+        <v>1.75</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5005,13 +5001,13 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>11.68</v>
+        <v>19.42</v>
       </c>
       <c r="K57" t="n">
-        <v>13.82</v>
+        <v>21.53</v>
       </c>
       <c r="L57" t="n">
-        <v>-16.46</v>
+        <v>-18.72</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5027,10 +5023,10 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>60</v>
+        <v>31.43</v>
       </c>
       <c r="S57" t="n">
-        <v>67.75</v>
+        <v>30.16</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5044,58 +5040,58 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>51</v>
+        <v>11.4</v>
       </c>
       <c r="C58" t="n">
-        <v>41.67</v>
+        <v>53.1</v>
       </c>
       <c r="D58" t="n">
-        <v>817100</v>
+        <v>4657800</v>
       </c>
       <c r="E58" t="n">
-        <v>668535</v>
+        <v>5266880</v>
       </c>
       <c r="F58" t="n">
-        <v>1.22</v>
+        <v>0.88</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>46.15</v>
+        <v>11.68</v>
       </c>
       <c r="K58" t="n">
-        <v>44.52</v>
+        <v>13.82</v>
       </c>
       <c r="L58" t="n">
-        <v>14.57</v>
+        <v>-17.54</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5107,10 +5103,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>54.88</v>
+        <v>52.27</v>
       </c>
       <c r="S58" t="n">
-        <v>49.27</v>
+        <v>59.68</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5119,39 +5115,39 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>PHP</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>35.35</v>
+        <v>43.5</v>
       </c>
       <c r="C59" t="n">
-        <v>41.44</v>
+        <v>38.9</v>
       </c>
       <c r="D59" t="n">
-        <v>1172300</v>
+        <v>894300</v>
       </c>
       <c r="E59" t="n">
-        <v>3707685</v>
+        <v>387580</v>
       </c>
       <c r="F59" t="n">
-        <v>0.32</v>
+        <v>2.31</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5165,17 +5161,17 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>35.15</v>
+        <v>43.2</v>
       </c>
       <c r="K59" t="n">
-        <v>38.08</v>
+        <v>42.5</v>
       </c>
       <c r="L59" t="n">
-        <v>-7.18</v>
+        <v>2.35</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -5187,10 +5183,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>28.16</v>
+        <v>22.55</v>
       </c>
       <c r="S59" t="n">
-        <v>53.51</v>
+        <v>15.38</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5204,34 +5200,34 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17.15</v>
+        <v>34</v>
       </c>
       <c r="C60" t="n">
-        <v>72.92</v>
+        <v>254.54</v>
       </c>
       <c r="D60" t="n">
-        <v>4251900</v>
+        <v>7486600</v>
       </c>
       <c r="E60" t="n">
-        <v>16390435</v>
+        <v>3726895</v>
       </c>
       <c r="F60" t="n">
-        <v>0.26</v>
+        <v>2.01</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5245,13 +5241,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>31.28</v>
+        <v>35.15</v>
       </c>
       <c r="K60" t="n">
-        <v>46.8</v>
+        <v>38.08</v>
       </c>
       <c r="L60" t="n">
-        <v>-63.35</v>
+        <v>-10.73</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5267,10 +5263,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>44.27</v>
+        <v>23.2</v>
       </c>
       <c r="S60" t="n">
-        <v>40.85</v>
+        <v>36.55</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5284,30 +5280,30 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>12.55</v>
+        <v>16.05</v>
       </c>
       <c r="C61" t="n">
-        <v>51.31</v>
+        <v>191.14</v>
       </c>
       <c r="D61" t="n">
-        <v>4088600</v>
+        <v>11909200</v>
       </c>
       <c r="E61" t="n">
-        <v>4913515</v>
+        <v>16902015</v>
       </c>
       <c r="F61" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5325,13 +5321,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>13.08</v>
+        <v>30.78</v>
       </c>
       <c r="K61" t="n">
-        <v>13.6</v>
+        <v>44.2</v>
       </c>
       <c r="L61" t="n">
-        <v>-7.72</v>
+        <v>-63.69</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -5347,10 +5343,10 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>51.85</v>
+        <v>31.75</v>
       </c>
       <c r="S61" t="n">
-        <v>45.79</v>
+        <v>35.13</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -5364,39 +5360,39 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>18.8</v>
+        <v>12.4</v>
       </c>
       <c r="C62" t="n">
-        <v>56.44</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>3001900</v>
+        <v>5447100</v>
       </c>
       <c r="E62" t="n">
-        <v>3689705</v>
+        <v>4999495</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5405,13 +5401,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>18.92</v>
+        <v>13.08</v>
       </c>
       <c r="K62" t="n">
-        <v>19.43</v>
+        <v>13.6</v>
       </c>
       <c r="L62" t="n">
-        <v>-3.24</v>
+        <v>-8.82</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5427,47 +5423,47 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>59.02</v>
+        <v>48.28</v>
       </c>
       <c r="S62" t="n">
-        <v>75.34</v>
+        <v>45.56</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>20.15</v>
+        <v>18.35</v>
       </c>
       <c r="C63" t="n">
-        <v>39.42</v>
+        <v>98.41</v>
       </c>
       <c r="D63" t="n">
-        <v>1956100</v>
+        <v>5362900</v>
       </c>
       <c r="E63" t="n">
-        <v>1467330</v>
+        <v>3837945</v>
       </c>
       <c r="F63" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -5481,28 +5477,24 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>20.6</v>
+        <v>18.92</v>
       </c>
       <c r="K63" t="n">
-        <v>20.6</v>
+        <v>19.43</v>
       </c>
       <c r="L63" t="n">
-        <v>-2.21</v>
+        <v>-5.56</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
@@ -5511,14 +5503,14 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>17.45</v>
+        <v>52.17</v>
       </c>
       <c r="S63" t="n">
-        <v>23.92</v>
+        <v>65.28</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -5528,34 +5520,34 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>32</v>
+        <v>18.75</v>
       </c>
       <c r="C64" t="n">
-        <v>38.28</v>
+        <v>55.27</v>
       </c>
       <c r="D64" t="n">
-        <v>1196400</v>
+        <v>2947600</v>
       </c>
       <c r="E64" t="n">
-        <v>2932875</v>
+        <v>1548635</v>
       </c>
       <c r="F64" t="n">
-        <v>0.41</v>
+        <v>1.9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5565,24 +5557,28 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>30.94</v>
+        <v>20.6</v>
       </c>
       <c r="K64" t="n">
-        <v>31.62</v>
+        <v>20.6</v>
       </c>
       <c r="L64" t="n">
-        <v>1.19</v>
+        <v>-9</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
@@ -5591,10 +5587,10 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>28.85</v>
+        <v>16.35</v>
       </c>
       <c r="S64" t="n">
-        <v>43.17</v>
+        <v>22.51</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -5608,65 +5604,61 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>22.85</v>
+        <v>30.5</v>
       </c>
       <c r="C65" t="n">
-        <v>118.42</v>
+        <v>142.12</v>
       </c>
       <c r="D65" t="n">
-        <v>5182500</v>
+        <v>4659800</v>
       </c>
       <c r="E65" t="n">
-        <v>7107065</v>
+        <v>2904305</v>
       </c>
       <c r="F65" t="n">
-        <v>0.73</v>
+        <v>1.6</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>21.2</v>
+        <v>30.94</v>
       </c>
       <c r="K65" t="n">
-        <v>21.2</v>
+        <v>31.62</v>
       </c>
       <c r="L65" t="n">
-        <v>7.78</v>
+        <v>-3.56</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
@@ -5675,51 +5667,51 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>24.04</v>
+        <v>23.44</v>
       </c>
       <c r="S65" t="n">
-        <v>19.28</v>
+        <v>28.81</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>20.75</v>
+        <v>21.3</v>
       </c>
       <c r="C66" t="n">
-        <v>22.51</v>
+        <v>452.68</v>
       </c>
       <c r="D66" t="n">
-        <v>1085000</v>
+        <v>21252400</v>
       </c>
       <c r="E66" t="n">
-        <v>1271700</v>
+        <v>7778745</v>
       </c>
       <c r="F66" t="n">
-        <v>0.85</v>
+        <v>2.73</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5729,36 +5721,40 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>22.3</v>
+        <v>21.2</v>
       </c>
       <c r="K66" t="n">
-        <v>21.92</v>
+        <v>21.2</v>
       </c>
       <c r="L66" t="n">
-        <v>-5.36</v>
+        <v>0.47</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>9.800000000000001</v>
+        <v>19.53</v>
       </c>
       <c r="S66" t="n">
-        <v>19.14</v>
+        <v>16.99</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -5772,30 +5768,30 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>10.65</v>
+        <v>20.75</v>
       </c>
       <c r="C67" t="n">
-        <v>294.8</v>
+        <v>22.34</v>
       </c>
       <c r="D67" t="n">
-        <v>27680700</v>
+        <v>1076700</v>
       </c>
       <c r="E67" t="n">
-        <v>43467255</v>
+        <v>1272185</v>
       </c>
       <c r="F67" t="n">
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5804,7 +5800,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5813,13 +5809,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>10.9</v>
+        <v>22.3</v>
       </c>
       <c r="K67" t="n">
-        <v>12.38</v>
+        <v>21.92</v>
       </c>
       <c r="L67" t="n">
-        <v>-13.94</v>
+        <v>-5.36</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5835,47 +5831,47 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>65.79000000000001</v>
+        <v>8</v>
       </c>
       <c r="S67" t="n">
-        <v>43.53</v>
+        <v>19.3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="C68" t="n">
-        <v>58.52</v>
+        <v>260.81</v>
       </c>
       <c r="D68" t="n">
-        <v>4719700</v>
+        <v>24374800</v>
       </c>
       <c r="E68" t="n">
-        <v>11139110</v>
+        <v>42953580</v>
       </c>
       <c r="F68" t="n">
-        <v>0.42</v>
+        <v>0.57</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5893,13 +5889,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>13.23</v>
+        <v>10.9</v>
       </c>
       <c r="K68" t="n">
-        <v>15</v>
+        <v>12.2</v>
       </c>
       <c r="L68" t="n">
-        <v>-17.36</v>
+        <v>-12.3</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5915,10 +5911,10 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>70</v>
+        <v>68.42</v>
       </c>
       <c r="S68" t="n">
-        <v>55.62</v>
+        <v>52.31</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5932,39 +5928,39 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>15.85</v>
+        <v>12.4</v>
       </c>
       <c r="C69" t="n">
-        <v>39.86</v>
+        <v>78.62</v>
       </c>
       <c r="D69" t="n">
-        <v>2514600</v>
+        <v>6340600</v>
       </c>
       <c r="E69" t="n">
-        <v>2290680</v>
+        <v>10964165</v>
       </c>
       <c r="F69" t="n">
-        <v>1.1</v>
+        <v>0.58</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5973,13 +5969,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>19.77</v>
+        <v>13.23</v>
       </c>
       <c r="K69" t="n">
-        <v>19.19</v>
+        <v>15</v>
       </c>
       <c r="L69" t="n">
-        <v>-17.38</v>
+        <v>-17.36</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -5995,47 +5991,47 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>36.84</v>
+        <v>68.42</v>
       </c>
       <c r="S69" t="n">
-        <v>22.39</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>19.75</v>
+        <v>15.6</v>
       </c>
       <c r="C70" t="n">
-        <v>248.31</v>
+        <v>31.62</v>
       </c>
       <c r="D70" t="n">
-        <v>12572700</v>
+        <v>2026900</v>
       </c>
       <c r="E70" t="n">
-        <v>18578695</v>
+        <v>2257095</v>
       </c>
       <c r="F70" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -6053,13 +6049,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>19.55</v>
+        <v>19.77</v>
       </c>
       <c r="K70" t="n">
-        <v>20.19</v>
+        <v>19.19</v>
       </c>
       <c r="L70" t="n">
-        <v>-2.16</v>
+        <v>-18.69</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6075,14 +6071,14 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>64.58</v>
+        <v>37.23</v>
       </c>
       <c r="S70" t="n">
-        <v>49.02</v>
+        <v>22.96</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -6092,30 +6088,30 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>68</v>
+        <v>19.6</v>
       </c>
       <c r="C71" t="n">
-        <v>208.83</v>
+        <v>270.08</v>
       </c>
       <c r="D71" t="n">
-        <v>3071000</v>
+        <v>13779800</v>
       </c>
       <c r="E71" t="n">
-        <v>3548990</v>
+        <v>18167815</v>
       </c>
       <c r="F71" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6129,28 +6125,24 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>70.05</v>
+        <v>19.55</v>
       </c>
       <c r="K71" t="n">
-        <v>70.05</v>
+        <v>20.19</v>
       </c>
       <c r="L71" t="n">
-        <v>-2.93</v>
+        <v>-2.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
@@ -6159,10 +6151,10 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>52.52</v>
+        <v>62</v>
       </c>
       <c r="S71" t="n">
-        <v>52.95</v>
+        <v>51.58</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -6176,34 +6168,34 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>22.33</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="C72" t="n">
-        <v>560.51</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>25101000</v>
+        <v>1352200</v>
       </c>
       <c r="E72" t="n">
-        <v>18193645</v>
+        <v>3353395</v>
       </c>
       <c r="F72" t="n">
-        <v>1.38</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6213,21 +6205,21 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>21</v>
+        <v>70.05</v>
       </c>
       <c r="K72" t="n">
-        <v>21</v>
+        <v>70.05</v>
       </c>
       <c r="L72" t="n">
-        <v>6.33</v>
+        <v>-4.5</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6236,21 +6228,25 @@
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>71.54000000000001</v>
+        <v>48.67</v>
       </c>
       <c r="S72" t="n">
-        <v>59.45</v>
+        <v>48.43</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -6260,30 +6256,30 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>12.1</v>
+        <v>22.35</v>
       </c>
       <c r="C73" t="n">
-        <v>68.05</v>
+        <v>528.41</v>
       </c>
       <c r="D73" t="n">
-        <v>5623800</v>
+        <v>23642700</v>
       </c>
       <c r="E73" t="n">
-        <v>5226245</v>
+        <v>18520925</v>
       </c>
       <c r="F73" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -6301,20 +6297,24 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>11.09</v>
+        <v>21</v>
       </c>
       <c r="K73" t="n">
-        <v>13.2</v>
+        <v>21</v>
       </c>
       <c r="L73" t="n">
-        <v>-8.369999999999999</v>
+        <v>6.43</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
@@ -6323,14 +6323,14 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>94.44</v>
+        <v>67.89</v>
       </c>
       <c r="S73" t="n">
-        <v>76.66</v>
+        <v>60.79</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -6340,34 +6340,34 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TCM</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
       <c r="C74" t="n">
-        <v>29.13</v>
+        <v>59.46</v>
       </c>
       <c r="D74" t="n">
-        <v>1787300</v>
+        <v>4873600</v>
       </c>
       <c r="E74" t="n">
-        <v>778590</v>
+        <v>5344415</v>
       </c>
       <c r="F74" t="n">
-        <v>2.3</v>
+        <v>0.91</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6377,17 +6377,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>16.23</v>
+        <v>11.09</v>
       </c>
       <c r="K74" t="n">
-        <v>18.27</v>
+        <v>13.2</v>
       </c>
       <c r="L74" t="n">
-        <v>-10.78</v>
+        <v>-7.61</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>70.69</v>
+        <v>93.94</v>
       </c>
       <c r="S74" t="n">
-        <v>54.78</v>
+        <v>83.48</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -6431,23 +6431,23 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.45</v>
+        <v>27.8</v>
       </c>
       <c r="C75" t="n">
-        <v>53.21</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>1870200</v>
+        <v>3237800</v>
       </c>
       <c r="E75" t="n">
-        <v>2963485</v>
+        <v>3008515</v>
       </c>
       <c r="F75" t="n">
-        <v>0.63</v>
+        <v>1.08</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6467,7 +6467,7 @@
         <v>32.59</v>
       </c>
       <c r="L75" t="n">
-        <v>-12.7</v>
+        <v>-14.7</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>63.33</v>
+        <v>57.58</v>
       </c>
       <c r="S75" t="n">
-        <v>57.4</v>
+        <v>57.06</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -6511,19 +6511,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="C76" t="n">
-        <v>28.29</v>
+        <v>29.12</v>
       </c>
       <c r="D76" t="n">
-        <v>533700</v>
+        <v>554600</v>
       </c>
       <c r="E76" t="n">
-        <v>255855</v>
+        <v>270400</v>
       </c>
       <c r="F76" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>51.4</v>
       </c>
       <c r="L76" t="n">
-        <v>3.11</v>
+        <v>2.14</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>40.63</v>
+        <v>41.94</v>
       </c>
       <c r="S76" t="n">
-        <v>49.56</v>
+        <v>46.54</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6580,58 +6580,58 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TNG</t>
+          <t>TOS</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>19.7</v>
+        <v>76.3</v>
       </c>
       <c r="C77" t="n">
-        <v>33.8</v>
+        <v>51.95</v>
       </c>
       <c r="D77" t="n">
-        <v>1715800</v>
+        <v>680800</v>
       </c>
       <c r="E77" t="n">
-        <v>1221960</v>
+        <v>84605</v>
       </c>
       <c r="F77" t="n">
-        <v>1.4</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>17.22</v>
+        <v>90.5</v>
       </c>
       <c r="K77" t="n">
-        <v>17.32</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>13.74</v>
+        <v>-17.33</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -6639,28 +6639,28 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 8.0x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>57.38</v>
+        <v>52.56</v>
       </c>
       <c r="S77" t="n">
-        <v>69.62</v>
+        <v>42.05</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -6671,23 +6671,23 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="C78" t="n">
-        <v>356.25</v>
+        <v>279.58</v>
       </c>
       <c r="D78" t="n">
-        <v>27404100</v>
+        <v>21673100</v>
       </c>
       <c r="E78" t="n">
-        <v>14210650</v>
+        <v>14466515</v>
       </c>
       <c r="F78" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6701,13 +6701,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="K78" t="n">
         <v>12.68</v>
       </c>
       <c r="L78" t="n">
-        <v>2.56</v>
+        <v>1.78</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -6723,10 +6723,10 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>79.17</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="S78" t="n">
-        <v>84.54000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -6751,23 +6751,23 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>57.5</v>
+        <v>57.2</v>
       </c>
       <c r="C79" t="n">
-        <v>371.09</v>
+        <v>231.65</v>
       </c>
       <c r="D79" t="n">
-        <v>6453700</v>
+        <v>4049800</v>
       </c>
       <c r="E79" t="n">
-        <v>3189960</v>
+        <v>3233850</v>
       </c>
       <c r="F79" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6787,7 +6787,7 @@
         <v>59.12</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.75</v>
+        <v>-3.26</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>58.18</v>
+        <v>54.39</v>
       </c>
       <c r="S79" t="n">
-        <v>55.21</v>
+        <v>62.72</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -6831,23 +6831,23 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15.75</v>
+        <v>15.3</v>
       </c>
       <c r="C80" t="n">
-        <v>68.75</v>
+        <v>21.77</v>
       </c>
       <c r="D80" t="n">
-        <v>4365100</v>
+        <v>1422900</v>
       </c>
       <c r="E80" t="n">
-        <v>2450665</v>
+        <v>2471555</v>
       </c>
       <c r="F80" t="n">
-        <v>1.78</v>
+        <v>0.58</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6867,7 +6867,7 @@
         <v>17.1</v>
       </c>
       <c r="L80" t="n">
-        <v>-7.92</v>
+        <v>-10.55</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -6876,17 +6876,21 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>81.16</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="S80" t="n">
-        <v>77.14</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6900,7 +6904,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -6914,16 +6918,16 @@
         <v>19</v>
       </c>
       <c r="C81" t="n">
-        <v>81.16</v>
+        <v>111.21</v>
       </c>
       <c r="D81" t="n">
-        <v>4271500</v>
+        <v>5852900</v>
       </c>
       <c r="E81" t="n">
-        <v>7704510</v>
+        <v>7729900</v>
       </c>
       <c r="F81" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -6944,10 +6948,10 @@
         <v>20.6</v>
       </c>
       <c r="K81" t="n">
-        <v>22.65</v>
+        <v>22.6</v>
       </c>
       <c r="L81" t="n">
-        <v>-16.11</v>
+        <v>-15.93</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -6966,7 +6970,7 @@
         <v>59.18</v>
       </c>
       <c r="S81" t="n">
-        <v>55.2</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -6980,7 +6984,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
@@ -6991,19 +6995,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>27.45</v>
+        <v>27.25</v>
       </c>
       <c r="C82" t="n">
-        <v>27.47</v>
+        <v>29.26</v>
       </c>
       <c r="D82" t="n">
-        <v>1000700</v>
+        <v>1073700</v>
       </c>
       <c r="E82" t="n">
-        <v>1661150</v>
+        <v>1649130</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -7027,7 +7031,7 @@
         <v>30.82</v>
       </c>
       <c r="L82" t="n">
-        <v>-10.95</v>
+        <v>-11.6</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -7036,21 +7040,17 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>56.96</v>
+        <v>60</v>
       </c>
       <c r="S82" t="n">
-        <v>61.44</v>
+        <v>63.46</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -7064,30 +7064,30 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VGC</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>43.4</v>
+        <v>37.8</v>
       </c>
       <c r="C83" t="n">
-        <v>80.84999999999999</v>
+        <v>49.42</v>
       </c>
       <c r="D83" t="n">
-        <v>1862900</v>
+        <v>1307500</v>
       </c>
       <c r="E83" t="n">
-        <v>814030</v>
+        <v>675120</v>
       </c>
       <c r="F83" t="n">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -7105,24 +7105,20 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>40.8</v>
+        <v>36.85</v>
       </c>
       <c r="K83" t="n">
-        <v>40.8</v>
+        <v>36.5</v>
       </c>
       <c r="L83" t="n">
-        <v>6.37</v>
+        <v>3.56</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
@@ -7131,10 +7127,10 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>44.33</v>
+        <v>52.38</v>
       </c>
       <c r="S83" t="n">
-        <v>51.42</v>
+        <v>62.38</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7148,30 +7144,30 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>VGC</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>63.5</v>
+        <v>42.3</v>
       </c>
       <c r="C84" t="n">
-        <v>349.43</v>
+        <v>30.84</v>
       </c>
       <c r="D84" t="n">
-        <v>5502900</v>
+        <v>729000</v>
       </c>
       <c r="E84" t="n">
-        <v>7909640</v>
+        <v>829355</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7180,29 +7176,33 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>69.65000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="K84" t="n">
-        <v>70.52</v>
+        <v>40.8</v>
       </c>
       <c r="L84" t="n">
-        <v>-9.949999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
@@ -7211,51 +7211,51 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>44.76</v>
+        <v>45.74</v>
       </c>
       <c r="S84" t="n">
-        <v>36.26</v>
+        <v>52.97</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>VGS</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>14.15</v>
+        <v>19.3</v>
       </c>
       <c r="C85" t="n">
-        <v>103.77</v>
+        <v>22.78</v>
       </c>
       <c r="D85" t="n">
-        <v>7333400</v>
+        <v>1180500</v>
       </c>
       <c r="E85" t="n">
-        <v>6506235</v>
+        <v>374790</v>
       </c>
       <c r="F85" t="n">
-        <v>1.13</v>
+        <v>3.15</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7269,17 +7269,17 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>13.52</v>
+        <v>17.15</v>
       </c>
       <c r="K85" t="n">
-        <v>14.16</v>
+        <v>18.73</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.04</v>
+        <v>3.07</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -7287,14 +7287,14 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 3.1x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>60</v>
+        <v>88.89</v>
       </c>
       <c r="S85" t="n">
-        <v>72.5</v>
+        <v>75.09</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7308,30 +7308,30 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>241</v>
+        <v>62.1</v>
       </c>
       <c r="C86" t="n">
-        <v>450.24</v>
+        <v>331.81</v>
       </c>
       <c r="D86" t="n">
-        <v>1868200</v>
+        <v>5343200</v>
       </c>
       <c r="E86" t="n">
-        <v>2811975</v>
+        <v>7845585</v>
       </c>
       <c r="F86" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7340,106 +7340,102 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>229.8</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>224.85</v>
+        <v>70.52</v>
       </c>
       <c r="L86" t="n">
-        <v>7.18</v>
+        <v>-11.94</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R86" t="n">
-        <v>60.66</v>
+        <v>41.18</v>
       </c>
       <c r="S86" t="n">
-        <v>31.91</v>
+        <v>36.75</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VIB</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>12.45</v>
+        <v>14</v>
       </c>
       <c r="C87" t="n">
-        <v>248.34</v>
+        <v>138.22</v>
       </c>
       <c r="D87" t="n">
-        <v>19947300</v>
+        <v>9873000</v>
       </c>
       <c r="E87" t="n">
-        <v>30033180</v>
+        <v>6711330</v>
       </c>
       <c r="F87" t="n">
-        <v>0.66</v>
+        <v>1.47</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>12.82</v>
+        <v>13.59</v>
       </c>
       <c r="K87" t="n">
-        <v>14.95</v>
+        <v>14.16</v>
       </c>
       <c r="L87" t="n">
-        <v>-16.72</v>
+        <v>-1.1</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -7448,58 +7444,54 @@
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>72.55</v>
+        <v>60</v>
       </c>
       <c r="S87" t="n">
-        <v>68.20999999999999</v>
+        <v>80.14</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VJC</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>131.5</v>
+        <v>241</v>
       </c>
       <c r="C88" t="n">
-        <v>119.43</v>
+        <v>405.05</v>
       </c>
       <c r="D88" t="n">
-        <v>908200</v>
+        <v>1680700</v>
       </c>
       <c r="E88" t="n">
-        <v>936810</v>
+        <v>2710190</v>
       </c>
       <c r="F88" t="n">
-        <v>0.97</v>
+        <v>0.62</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7517,32 +7509,36 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>128.05</v>
+        <v>229.8</v>
       </c>
       <c r="K88" t="n">
-        <v>132.12</v>
+        <v>224.85</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.47</v>
+        <v>7.18</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>65.95999999999999</v>
+        <v>63.25</v>
       </c>
       <c r="S88" t="n">
-        <v>45.68</v>
+        <v>38.37</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -7556,30 +7552,30 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>13.45</v>
+        <v>12.4</v>
       </c>
       <c r="C89" t="n">
-        <v>63.25</v>
+        <v>285.45</v>
       </c>
       <c r="D89" t="n">
-        <v>4702700</v>
+        <v>23020400</v>
       </c>
       <c r="E89" t="n">
-        <v>9661360</v>
+        <v>29850690</v>
       </c>
       <c r="F89" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7597,13 +7593,13 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>14.98</v>
+        <v>12.82</v>
       </c>
       <c r="K89" t="n">
-        <v>15.85</v>
+        <v>14.95</v>
       </c>
       <c r="L89" t="n">
-        <v>-15.14</v>
+        <v>-17.06</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7619,10 +7615,10 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>58.54</v>
+        <v>66.67</v>
       </c>
       <c r="S89" t="n">
-        <v>44.07</v>
+        <v>66.72</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -7636,34 +7632,34 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>VJC</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>58.2</v>
+        <v>131.6</v>
       </c>
       <c r="C90" t="n">
-        <v>137.51</v>
+        <v>115.44</v>
       </c>
       <c r="D90" t="n">
-        <v>2362800</v>
+        <v>877200</v>
       </c>
       <c r="E90" t="n">
-        <v>1947355</v>
+        <v>934855</v>
       </c>
       <c r="F90" t="n">
-        <v>1.21</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7673,17 +7669,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>60.7</v>
+        <v>128.05</v>
       </c>
       <c r="K90" t="n">
-        <v>59.5</v>
+        <v>132.12</v>
       </c>
       <c r="L90" t="n">
-        <v>-2.18</v>
+        <v>-0.4</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -7699,10 +7695,10 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>52.94</v>
+        <v>64.44</v>
       </c>
       <c r="S90" t="n">
-        <v>48.63</v>
+        <v>39.64</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -7716,30 +7712,30 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VPB</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23.5</v>
+        <v>13.6</v>
       </c>
       <c r="C91" t="n">
-        <v>290.58</v>
+        <v>118.16</v>
       </c>
       <c r="D91" t="n">
-        <v>12365200</v>
+        <v>8688000</v>
       </c>
       <c r="E91" t="n">
-        <v>15598555</v>
+        <v>9641640</v>
       </c>
       <c r="F91" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7748,33 +7744,29 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>21.98</v>
+        <v>14.98</v>
       </c>
       <c r="K91" t="n">
-        <v>21.98</v>
+        <v>15.85</v>
       </c>
       <c r="L91" t="n">
-        <v>6.94</v>
+        <v>-14.2</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
@@ -7783,51 +7775,51 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>50.82</v>
+        <v>59.52</v>
       </c>
       <c r="S91" t="n">
-        <v>57.27</v>
+        <v>53.89</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>58.1</v>
+        <v>57.7</v>
       </c>
       <c r="C92" t="n">
-        <v>139.89</v>
+        <v>77.05</v>
       </c>
       <c r="D92" t="n">
-        <v>2407700</v>
+        <v>1335300</v>
       </c>
       <c r="E92" t="n">
-        <v>1988415</v>
+        <v>1829610</v>
       </c>
       <c r="F92" t="n">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7841,24 +7833,20 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>55.52</v>
+        <v>60.7</v>
       </c>
       <c r="K92" t="n">
-        <v>55.52</v>
+        <v>59.5</v>
       </c>
       <c r="L92" t="n">
-        <v>4.64</v>
+        <v>-3.03</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
@@ -7867,10 +7855,10 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>53.81</v>
+        <v>50</v>
       </c>
       <c r="S92" t="n">
-        <v>56.63</v>
+        <v>48.68</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7884,30 +7872,30 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VPL</t>
+          <t>VOS</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>88.90000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="C93" t="n">
-        <v>167.46</v>
+        <v>24.71</v>
       </c>
       <c r="D93" t="n">
-        <v>1883700</v>
+        <v>2226100</v>
       </c>
       <c r="E93" t="n">
-        <v>894605</v>
+        <v>1319430</v>
       </c>
       <c r="F93" t="n">
-        <v>2.11</v>
+        <v>1.69</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -7925,20 +7913,24 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>80.95</v>
+        <v>11.1</v>
       </c>
       <c r="K93" t="n">
-        <v>85.5</v>
+        <v>11.1</v>
       </c>
       <c r="L93" t="n">
-        <v>3.98</v>
+        <v>0.05</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
@@ -7947,14 +7939,14 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>73.91</v>
+        <v>32.14</v>
       </c>
       <c r="S93" t="n">
-        <v>73.34</v>
+        <v>25.77</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -7964,61 +7956,65 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VRE</t>
+          <t>VPB</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="C94" t="n">
-        <v>91.03</v>
+        <v>272.86</v>
       </c>
       <c r="D94" t="n">
-        <v>3777200</v>
+        <v>11761400</v>
       </c>
       <c r="E94" t="n">
-        <v>3401940</v>
+        <v>15609570</v>
       </c>
       <c r="F94" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>24.42</v>
+        <v>21.98</v>
       </c>
       <c r="K94" t="n">
-        <v>28.56</v>
+        <v>21.98</v>
       </c>
       <c r="L94" t="n">
-        <v>-15.62</v>
+        <v>5.57</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
@@ -8027,51 +8023,51 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>59.8</v>
+        <v>40</v>
       </c>
       <c r="S94" t="n">
-        <v>45.28</v>
+        <v>50.21</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VSC</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14.5</v>
+        <v>57.9</v>
       </c>
       <c r="C95" t="n">
-        <v>181.68</v>
+        <v>106.7</v>
       </c>
       <c r="D95" t="n">
-        <v>12529600</v>
+        <v>1842800</v>
       </c>
       <c r="E95" t="n">
-        <v>10542030</v>
+        <v>2007560</v>
       </c>
       <c r="F95" t="n">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8081,24 +8077,28 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>14.02</v>
+        <v>55.52</v>
       </c>
       <c r="K95" t="n">
-        <v>17.73</v>
+        <v>55.52</v>
       </c>
       <c r="L95" t="n">
-        <v>-18.19</v>
+        <v>4.28</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
@@ -8107,10 +8107,10 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>68.92</v>
+        <v>56.38</v>
       </c>
       <c r="S95" t="n">
-        <v>67.15000000000001</v>
+        <v>62.32</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -8124,7 +8124,407 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-10-28 22:38:20</t>
+          <t>2026-10-29 22:42:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>VPL</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="C96" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1043000</v>
+      </c>
+      <c r="E96" t="n">
+        <v>913865</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>☁️ Trên Mây</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="K96" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="L96" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R96" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="S96" t="n">
+        <v>74.33</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>🔴 Bán (vùng quá mua)</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-10-29 22:42:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>VRE</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="C97" t="n">
+        <v>45.87</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1899200</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3314780</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>💤 Tiền Yếu</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="K97" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-15.44</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R97" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="S97" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-10-29 22:42:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>VSC</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C98" t="n">
+        <v>269.85</v>
+      </c>
+      <c r="D98" t="n">
+        <v>19554500</v>
+      </c>
+      <c r="E98" t="n">
+        <v>11024280</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="K98" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R98" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="S98" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-10-29 22:42:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VTZ</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C99" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1258800</v>
+      </c>
+      <c r="E99" t="n">
+        <v>957145</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>⚡ Có Tín Hiệu</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>🔴 Giảm</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>🌫️ Trong Mây</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="K99" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="S99" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>🔴 Tiêu cực</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-10-29 22:42:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>VVS</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="C100" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="D100" t="n">
+        <v>422800</v>
+      </c>
+      <c r="E100" t="n">
+        <v>207245</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>🔥 Tiền Vào Mạnh</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>🟡 Sideway</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>🌧️ Dưới Mây</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="K100" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R100" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="S100" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>⏸️ Chờ (giữa biên độ)</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>🟡 Trung tính</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-10-29 22:42:26</t>
         </is>
       </c>
     </row>

--- a/screener_cache.xlsx
+++ b/screener_cache.xlsx
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>143.41</v>
+        <v>169.77</v>
       </c>
       <c r="D2" t="n">
-        <v>6732700</v>
+        <v>8084100</v>
       </c>
       <c r="E2" t="n">
-        <v>9141390</v>
+        <v>9218340</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         <v>21.58</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.27</v>
+        <v>-2.67</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>79.48999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>84.39</v>
+        <v>77.73</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>39.7</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35</v>
+        <v>32.92</v>
       </c>
       <c r="D3" t="n">
-        <v>642700</v>
+        <v>829200</v>
       </c>
       <c r="E3" t="n">
-        <v>823605</v>
+        <v>851785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -641,17 +641,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40.45</v>
+        <v>41.1</v>
       </c>
       <c r="K3" t="n">
         <v>41.6</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.44</v>
+        <v>-4.57</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>50.88</v>
+        <v>40.58</v>
       </c>
       <c r="S3" t="n">
-        <v>64.29000000000001</v>
+        <v>57.54</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
@@ -695,19 +695,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.9</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>24.96</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>1476700</v>
+        <v>1374700</v>
       </c>
       <c r="E4" t="n">
-        <v>1597870</v>
+        <v>1525545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -716,22 +716,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>16.46</v>
       </c>
       <c r="K4" t="n">
-        <v>18.9</v>
+        <v>18.77</v>
       </c>
       <c r="L4" t="n">
-        <v>-10.56</v>
+        <v>-14.78</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -747,24 +747,24 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>43.12</v>
+        <v>37.79</v>
       </c>
       <c r="S4" t="n">
-        <v>46.61</v>
+        <v>46.77</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="C5" t="n">
-        <v>54.77</v>
+        <v>43.92</v>
       </c>
       <c r="D5" t="n">
-        <v>1801500</v>
+        <v>1435300</v>
       </c>
       <c r="E5" t="n">
-        <v>1915255</v>
+        <v>1920860</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29.15</v>
+        <v>29.22</v>
       </c>
       <c r="K5" t="n">
         <v>28.4</v>
       </c>
       <c r="L5" t="n">
-        <v>7.04</v>
+        <v>7.75</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>73.77</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>69.38</v>
+        <v>71.16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -844,30 +844,30 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.55</v>
+        <v>33.4</v>
       </c>
       <c r="C6" t="n">
-        <v>25.31</v>
+        <v>110.03</v>
       </c>
       <c r="D6" t="n">
-        <v>639900</v>
+        <v>3294200</v>
       </c>
       <c r="E6" t="n">
-        <v>579915</v>
+        <v>3266820</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>40.45</v>
+        <v>35.38</v>
       </c>
       <c r="K6" t="n">
-        <v>45.55</v>
+        <v>37.54</v>
       </c>
       <c r="L6" t="n">
-        <v>-13.17</v>
+        <v>-11.03</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -907,71 +907,71 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>58.62</v>
+        <v>44.83</v>
       </c>
       <c r="S6" t="n">
-        <v>61.72</v>
+        <v>58.04</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>BSR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.85</v>
+        <v>27.6</v>
       </c>
       <c r="C7" t="n">
-        <v>211.26</v>
+        <v>153.4</v>
       </c>
       <c r="D7" t="n">
-        <v>6241200</v>
+        <v>5557900</v>
       </c>
       <c r="E7" t="n">
-        <v>3305335</v>
+        <v>8578150</v>
       </c>
       <c r="F7" t="n">
-        <v>1.89</v>
+        <v>0.65</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>35</v>
+        <v>28.72</v>
       </c>
       <c r="K7" t="n">
-        <v>37.54</v>
+        <v>27.96</v>
       </c>
       <c r="L7" t="n">
-        <v>-9.83</v>
+        <v>-1.29</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -987,47 +987,47 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>49.37</v>
+        <v>29.17</v>
       </c>
       <c r="S7" t="n">
-        <v>64.20999999999999</v>
+        <v>24.96</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSR</t>
+          <t>BVH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.65</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>368.8</v>
+        <v>63.3</v>
       </c>
       <c r="D8" t="n">
-        <v>13338200</v>
+        <v>917400</v>
       </c>
       <c r="E8" t="n">
-        <v>9050530</v>
+        <v>908775</v>
       </c>
       <c r="F8" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28.34</v>
+        <v>67.8</v>
       </c>
       <c r="K8" t="n">
-        <v>27.96</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.11</v>
+        <v>2.83</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>27.63</v>
+        <v>28.4</v>
       </c>
       <c r="S8" t="n">
-        <v>24.26</v>
+        <v>18.49</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1084,58 +1084,58 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BVH</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>11.1</v>
       </c>
       <c r="C9" t="n">
-        <v>88.69</v>
+        <v>58.15</v>
       </c>
       <c r="D9" t="n">
-        <v>1285400</v>
+        <v>5238300</v>
       </c>
       <c r="E9" t="n">
-        <v>916375</v>
+        <v>6948845</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>0.75</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>67.5</v>
+        <v>11.65</v>
       </c>
       <c r="K9" t="n">
-        <v>67.09999999999999</v>
+        <v>13.61</v>
       </c>
       <c r="L9" t="n">
-        <v>2.83</v>
+        <v>-18.44</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>28.05</v>
+        <v>66.67</v>
       </c>
       <c r="S9" t="n">
-        <v>11.5</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>CII</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="C10" t="n">
-        <v>36.74</v>
+        <v>127.88</v>
       </c>
       <c r="D10" t="n">
-        <v>3310100</v>
+        <v>9687600</v>
       </c>
       <c r="E10" t="n">
-        <v>6936490</v>
+        <v>9379245</v>
       </c>
       <c r="F10" t="n">
-        <v>0.48</v>
+        <v>1.03</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11.65</v>
+        <v>13.27</v>
       </c>
       <c r="K10" t="n">
-        <v>13.61</v>
+        <v>15.85</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.44</v>
+        <v>-16.72</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>68.18000000000001</v>
+        <v>62.16</v>
       </c>
       <c r="S10" t="n">
-        <v>73.78</v>
+        <v>69.61</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1244,30 +1244,30 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CII</t>
+          <t>CTD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.45</v>
+        <v>64</v>
       </c>
       <c r="C11" t="n">
-        <v>86.69</v>
+        <v>26.84</v>
       </c>
       <c r="D11" t="n">
-        <v>6445300</v>
+        <v>419300</v>
       </c>
       <c r="E11" t="n">
-        <v>9321100</v>
+        <v>496620</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13.27</v>
+        <v>62.55</v>
       </c>
       <c r="K11" t="n">
-        <v>15.85</v>
+        <v>72.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-15.14</v>
+        <v>-11.72</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1307,14 +1307,14 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>69.73999999999999</v>
+        <v>53.46</v>
       </c>
       <c r="S11" t="n">
-        <v>75.78</v>
+        <v>63.86</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1324,34 +1324,34 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CTD</t>
+          <t>CTG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64.7</v>
+        <v>30.3</v>
       </c>
       <c r="C12" t="n">
-        <v>57.18</v>
+        <v>123.5</v>
       </c>
       <c r="D12" t="n">
-        <v>883800</v>
+        <v>4075800</v>
       </c>
       <c r="E12" t="n">
-        <v>495050</v>
+        <v>7047615</v>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>0.58</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>61.7</v>
+        <v>30.92</v>
       </c>
       <c r="K12" t="n">
-        <v>72.5</v>
+        <v>32.32</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.76</v>
+        <v>-6.25</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1380,17 +1380,21 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>57.59</v>
+        <v>60.29</v>
       </c>
       <c r="S12" t="n">
-        <v>69.18000000000001</v>
+        <v>60.23</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1404,39 +1408,39 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CTG</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.7</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>234.91</v>
+        <v>30.32</v>
       </c>
       <c r="D13" t="n">
-        <v>7651700</v>
+        <v>1443900</v>
       </c>
       <c r="E13" t="n">
-        <v>7122595</v>
+        <v>1521115</v>
       </c>
       <c r="F13" t="n">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1445,13 +1449,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>30.7</v>
+        <v>21.4</v>
       </c>
       <c r="K13" t="n">
-        <v>32.32</v>
+        <v>24.1</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.01</v>
+        <v>-12.86</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1467,47 +1471,47 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>69.34999999999999</v>
+        <v>63.39</v>
       </c>
       <c r="S13" t="n">
-        <v>64.58</v>
+        <v>74.02</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>DCL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.55</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
-        <v>41.18</v>
+        <v>28.18</v>
       </c>
       <c r="D14" t="n">
-        <v>1911100</v>
+        <v>640500</v>
       </c>
       <c r="E14" t="n">
-        <v>1496800</v>
+        <v>612540</v>
       </c>
       <c r="F14" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1521,17 +1525,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>21.4</v>
+        <v>44.65</v>
       </c>
       <c r="K14" t="n">
-        <v>24.1</v>
+        <v>44.05</v>
       </c>
       <c r="L14" t="n">
-        <v>-10.58</v>
+        <v>-0.11</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1547,14 +1551,14 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>68.93000000000001</v>
+        <v>38.41</v>
       </c>
       <c r="S14" t="n">
-        <v>77.03</v>
+        <v>39.29</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1564,30 +1568,30 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.8</v>
+        <v>33.3</v>
       </c>
       <c r="C15" t="n">
-        <v>28.17</v>
+        <v>30.42</v>
       </c>
       <c r="D15" t="n">
-        <v>1783100</v>
+        <v>913400</v>
       </c>
       <c r="E15" t="n">
-        <v>1804490</v>
+        <v>2071710</v>
       </c>
       <c r="F15" t="n">
-        <v>0.99</v>
+        <v>0.44</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1596,22 +1600,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16.32</v>
+        <v>33.08</v>
       </c>
       <c r="K15" t="n">
-        <v>17.64</v>
+        <v>35.83</v>
       </c>
       <c r="L15" t="n">
-        <v>-10.46</v>
+        <v>-7.06</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1627,51 +1631,51 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>55.1</v>
+        <v>46.4</v>
       </c>
       <c r="S15" t="n">
-        <v>52.61</v>
+        <v>59.09</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>DGW</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34.2</v>
+        <v>40.95</v>
       </c>
       <c r="C16" t="n">
-        <v>82.90000000000001</v>
+        <v>58.76</v>
       </c>
       <c r="D16" t="n">
-        <v>2424000</v>
+        <v>1435000</v>
       </c>
       <c r="E16" t="n">
-        <v>2180815</v>
+        <v>1673720</v>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1681,21 +1685,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>32.3</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>35.83</v>
+        <v>39.83</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.55</v>
+        <v>2.81</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1707,14 +1711,14 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>44.96</v>
+        <v>24.14</v>
       </c>
       <c r="S16" t="n">
-        <v>58.21</v>
+        <v>20.17</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1724,34 +1728,34 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DGW</t>
+          <t>DHC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.5</v>
+        <v>36.8</v>
       </c>
       <c r="C17" t="n">
-        <v>71.91</v>
+        <v>40.67</v>
       </c>
       <c r="D17" t="n">
-        <v>1691900</v>
+        <v>1105200</v>
       </c>
       <c r="E17" t="n">
-        <v>1684080</v>
+        <v>494795</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2.23</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1761,28 +1765,24 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.83</v>
+        <v>34.86</v>
       </c>
       <c r="K17" t="n">
-        <v>39.83</v>
+        <v>33.86</v>
       </c>
       <c r="L17" t="n">
-        <v>6.7</v>
+        <v>8.68</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
@@ -1791,14 +1791,14 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>27.05</v>
+        <v>52.17</v>
       </c>
       <c r="S17" t="n">
-        <v>20.53</v>
+        <v>46.86</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1808,30 +1808,30 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHC</t>
+          <t>DIG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>20.16</v>
+        <v>50.51</v>
       </c>
       <c r="D18" t="n">
-        <v>537700</v>
+        <v>5289300</v>
       </c>
       <c r="E18" t="n">
-        <v>459120</v>
+        <v>5204845</v>
       </c>
       <c r="F18" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1840,26 +1840,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>34.06</v>
+        <v>9.82</v>
       </c>
       <c r="K18" t="n">
-        <v>33.86</v>
+        <v>11.52</v>
       </c>
       <c r="L18" t="n">
-        <v>10.75</v>
+        <v>-17.14</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1871,71 +1871,71 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>59.8</v>
+        <v>52.87</v>
       </c>
       <c r="S18" t="n">
-        <v>50.68</v>
+        <v>50.29</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIG</t>
+          <t>DPG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.789999999999999</v>
+        <v>28.85</v>
       </c>
       <c r="C19" t="n">
-        <v>29.15</v>
+        <v>25.35</v>
       </c>
       <c r="D19" t="n">
-        <v>2977200</v>
+        <v>878800</v>
       </c>
       <c r="E19" t="n">
-        <v>5100105</v>
+        <v>545915</v>
       </c>
       <c r="F19" t="n">
-        <v>0.58</v>
+        <v>1.61</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9.82</v>
+        <v>28.92</v>
       </c>
       <c r="K19" t="n">
-        <v>11.52</v>
+        <v>35.3</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.05</v>
+        <v>-18.28</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1951,71 +1951,71 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>64.03</v>
+        <v>58.75</v>
       </c>
       <c r="S19" t="n">
-        <v>56.84</v>
+        <v>73.02</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DPG</t>
+          <t>DPM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.2</v>
+        <v>20.4</v>
       </c>
       <c r="C20" t="n">
-        <v>20.66</v>
+        <v>65.03</v>
       </c>
       <c r="D20" t="n">
-        <v>684100</v>
+        <v>3187800</v>
       </c>
       <c r="E20" t="n">
-        <v>518010</v>
+        <v>2028445</v>
       </c>
       <c r="F20" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>28.82</v>
+        <v>22.08</v>
       </c>
       <c r="K20" t="n">
-        <v>35.3</v>
+        <v>23.52</v>
       </c>
       <c r="L20" t="n">
-        <v>-14.46</v>
+        <v>-13.27</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2031,47 +2031,47 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>73.09999999999999</v>
+        <v>29.31</v>
       </c>
       <c r="S20" t="n">
-        <v>81.36</v>
+        <v>26.58</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DPM</t>
+          <t>DXG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="C21" t="n">
-        <v>60.24</v>
+        <v>136.33</v>
       </c>
       <c r="D21" t="n">
-        <v>2882200</v>
+        <v>13497800</v>
       </c>
       <c r="E21" t="n">
-        <v>2082395</v>
+        <v>10155975</v>
       </c>
       <c r="F21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>22.18</v>
+        <v>10.73</v>
       </c>
       <c r="K21" t="n">
-        <v>23.62</v>
+        <v>11.89</v>
       </c>
       <c r="L21" t="n">
-        <v>-11.52</v>
+        <v>-15.02</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>31.48</v>
+        <v>55.43</v>
       </c>
       <c r="S21" t="n">
-        <v>28.03</v>
+        <v>57.22</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2128,54 +2128,54 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DPR</t>
+          <t>EIB</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38.8</v>
+        <v>16.1</v>
       </c>
       <c r="C22" t="n">
-        <v>42.79</v>
+        <v>88.03</v>
       </c>
       <c r="D22" t="n">
-        <v>1102900</v>
+        <v>5467400</v>
       </c>
       <c r="E22" t="n">
-        <v>439310</v>
+        <v>4996835</v>
       </c>
       <c r="F22" t="n">
-        <v>2.51</v>
+        <v>1.09</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>37.1</v>
+        <v>17.2</v>
       </c>
       <c r="K22" t="n">
-        <v>39.65</v>
+        <v>19.48</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.14</v>
+        <v>-17.33</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2187,51 +2187,51 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.5x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>63.22</v>
+        <v>50</v>
       </c>
       <c r="S22" t="n">
-        <v>53.56</v>
+        <v>54.68</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DXG</t>
+          <t>FPT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.880000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="C23" t="n">
-        <v>67.59</v>
+        <v>298.37</v>
       </c>
       <c r="D23" t="n">
-        <v>6841000</v>
+        <v>5661600</v>
       </c>
       <c r="E23" t="n">
-        <v>9734240</v>
+        <v>7297445</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10.73</v>
+        <v>60.2</v>
       </c>
       <c r="K23" t="n">
-        <v>11.89</v>
+        <v>61.52</v>
       </c>
       <c r="L23" t="n">
-        <v>-16.87</v>
+        <v>-14.34</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>53.67</v>
+        <v>25</v>
       </c>
       <c r="S23" t="n">
-        <v>54.98</v>
+        <v>33.43</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2288,62 +2288,66 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EIB</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.8</v>
+        <v>148.7</v>
       </c>
       <c r="C24" t="n">
-        <v>51.95</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>3092000</v>
+        <v>586300</v>
       </c>
       <c r="E24" t="n">
-        <v>4870420</v>
+        <v>565505</v>
       </c>
       <c r="F24" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>17.2</v>
+        <v>130.3</v>
       </c>
       <c r="K24" t="n">
-        <v>19.48</v>
+        <v>127.5</v>
       </c>
       <c r="L24" t="n">
-        <v>-13.74</v>
+        <v>16.63</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2351,78 +2355,82 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>60</v>
+        <v>48.58</v>
       </c>
       <c r="S24" t="n">
-        <v>59.08</v>
+        <v>42.12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FPT</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52.7</v>
+        <v>78</v>
       </c>
       <c r="C25" t="n">
-        <v>663.55</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>12591100</v>
+        <v>985200</v>
       </c>
       <c r="E25" t="n">
-        <v>7174345</v>
+        <v>964820</v>
       </c>
       <c r="F25" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>60.25</v>
+        <v>77.69</v>
       </c>
       <c r="K25" t="n">
-        <v>61.57</v>
+        <v>77.69</v>
       </c>
       <c r="L25" t="n">
-        <v>-14.41</v>
+        <v>0.39</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
@@ -2431,83 +2439,79 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>22.92</v>
+        <v>46.58</v>
       </c>
       <c r="S25" t="n">
-        <v>33.19</v>
+        <v>46.36</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>GEE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>147.7</v>
+        <v>66.3</v>
       </c>
       <c r="C26" t="n">
-        <v>96.14</v>
+        <v>82.23</v>
       </c>
       <c r="D26" t="n">
-        <v>650900</v>
+        <v>1240300</v>
       </c>
       <c r="E26" t="n">
-        <v>563795</v>
+        <v>1421155</v>
       </c>
       <c r="F26" t="n">
-        <v>1.15</v>
+        <v>0.87</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>129.4</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>127.5</v>
+        <v>95.83</v>
       </c>
       <c r="L26" t="n">
-        <v>15.84</v>
+        <v>-30.81</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2515,51 +2519,51 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>46.52</v>
+        <v>42.93</v>
       </c>
       <c r="S26" t="n">
-        <v>41.26</v>
+        <v>36.86</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>76</v>
+        <v>27.1</v>
       </c>
       <c r="C27" t="n">
-        <v>196.17</v>
+        <v>35.12</v>
       </c>
       <c r="D27" t="n">
-        <v>2581200</v>
+        <v>1296000</v>
       </c>
       <c r="E27" t="n">
-        <v>997730</v>
+        <v>1478155</v>
       </c>
       <c r="F27" t="n">
-        <v>2.59</v>
+        <v>0.88</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2573,13 +2577,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>77.31</v>
+        <v>27.62</v>
       </c>
       <c r="K27" t="n">
-        <v>77.69</v>
+        <v>29.42</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.18</v>
+        <v>-7.9</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2591,14 +2595,14 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>33.57</v>
+        <v>44</v>
       </c>
       <c r="S27" t="n">
-        <v>39.81</v>
+        <v>54.82</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2612,30 +2616,30 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GEE</t>
+          <t>GEX</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67</v>
+        <v>22.2</v>
       </c>
       <c r="C28" t="n">
-        <v>85.73999999999999</v>
+        <v>150.7</v>
       </c>
       <c r="D28" t="n">
-        <v>1279700</v>
+        <v>6788200</v>
       </c>
       <c r="E28" t="n">
-        <v>1427400</v>
+        <v>7479035</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2649,17 +2653,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>66.81999999999999</v>
+        <v>23.8</v>
       </c>
       <c r="K28" t="n">
-        <v>95.83</v>
+        <v>28.58</v>
       </c>
       <c r="L28" t="n">
-        <v>-30.08</v>
+        <v>-22.31</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2675,10 +2679,10 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>41.21</v>
+        <v>50.96</v>
       </c>
       <c r="S28" t="n">
-        <v>42.61</v>
+        <v>53.43</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2692,34 +2696,34 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GEL</t>
+          <t>GMD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27.3</v>
+        <v>52.7</v>
       </c>
       <c r="C29" t="n">
-        <v>46.3</v>
+        <v>58.02</v>
       </c>
       <c r="D29" t="n">
-        <v>1695900</v>
+        <v>1100900</v>
       </c>
       <c r="E29" t="n">
-        <v>1467540</v>
+        <v>1839910</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16</v>
+        <v>0.6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2729,21 +2733,21 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>27.15</v>
+        <v>53.25</v>
       </c>
       <c r="K29" t="n">
-        <v>29.42</v>
+        <v>51.28</v>
       </c>
       <c r="L29" t="n">
-        <v>-7.22</v>
+        <v>2.76</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2755,10 +2759,10 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>43.14</v>
+        <v>44.85</v>
       </c>
       <c r="S29" t="n">
-        <v>56.82</v>
+        <v>50.41</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2772,30 +2776,30 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GEX</t>
+          <t>GVR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23</v>
+        <v>31.25</v>
       </c>
       <c r="C30" t="n">
-        <v>157.25</v>
+        <v>40.24</v>
       </c>
       <c r="D30" t="n">
-        <v>6837000</v>
+        <v>1287800</v>
       </c>
       <c r="E30" t="n">
-        <v>7625375</v>
+        <v>2043320</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9</v>
+        <v>0.63</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2804,22 +2808,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>23.45</v>
+        <v>30.6</v>
       </c>
       <c r="K30" t="n">
-        <v>28.58</v>
+        <v>32.78</v>
       </c>
       <c r="L30" t="n">
-        <v>-19.51</v>
+        <v>-4.65</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2835,47 +2839,47 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>58.24</v>
+        <v>37.63</v>
       </c>
       <c r="S30" t="n">
-        <v>58.03</v>
+        <v>57.96</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GMD</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>52.1</v>
+        <v>23.2</v>
       </c>
       <c r="C31" t="n">
-        <v>99.95</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>1918400</v>
+        <v>3114600</v>
       </c>
       <c r="E31" t="n">
-        <v>1838535</v>
+        <v>2724285</v>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2889,21 +2893,21 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>52.78</v>
+        <v>24.92</v>
       </c>
       <c r="K31" t="n">
-        <v>51.28</v>
+        <v>24.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.59</v>
+        <v>-6.45</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2915,10 +2919,10 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>39.57</v>
+        <v>50</v>
       </c>
       <c r="S31" t="n">
-        <v>55.94</v>
+        <v>45.38</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2932,34 +2936,34 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GVR</t>
+          <t>HDB</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.95</v>
+        <v>22.4</v>
       </c>
       <c r="C32" t="n">
-        <v>123.61</v>
+        <v>289.09</v>
       </c>
       <c r="D32" t="n">
-        <v>3868800</v>
+        <v>12905700</v>
       </c>
       <c r="E32" t="n">
-        <v>2123265</v>
+        <v>17106810</v>
       </c>
       <c r="F32" t="n">
-        <v>1.82</v>
+        <v>0.75</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2973,20 +2977,24 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>30.22</v>
+        <v>21.15</v>
       </c>
       <c r="K32" t="n">
-        <v>32.78</v>
+        <v>21.13</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.52</v>
+        <v>6.01</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>⚖️ Hợp lý</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
@@ -2995,10 +3003,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>39.77</v>
+        <v>47.5</v>
       </c>
       <c r="S32" t="n">
-        <v>56.44</v>
+        <v>55.05</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3012,34 +3020,34 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HAH</t>
+          <t>HDC</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>49.05</v>
+        <v>11.25</v>
       </c>
       <c r="C33" t="n">
-        <v>32.79</v>
+        <v>30.51</v>
       </c>
       <c r="D33" t="n">
-        <v>668600</v>
+        <v>2712400</v>
       </c>
       <c r="E33" t="n">
-        <v>852175</v>
+        <v>1804520</v>
       </c>
       <c r="F33" t="n">
-        <v>0.78</v>
+        <v>1.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3049,17 +3057,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>48.2</v>
+        <v>11.18</v>
       </c>
       <c r="K33" t="n">
-        <v>49.55</v>
+        <v>13.34</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.01</v>
+        <v>-15.7</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3075,10 +3083,10 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>43.78</v>
+        <v>70</v>
       </c>
       <c r="S33" t="n">
-        <v>55.76</v>
+        <v>64.87</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3092,39 +3100,39 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HHS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23.05</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>55.05</v>
+        <v>20.96</v>
       </c>
       <c r="D34" t="n">
-        <v>2388400</v>
+        <v>2218200</v>
       </c>
       <c r="E34" t="n">
-        <v>2733905</v>
+        <v>1185325</v>
       </c>
       <c r="F34" t="n">
-        <v>0.87</v>
+        <v>1.87</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3133,13 +3141,13 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>24.92</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>24.8</v>
+        <v>11.05</v>
       </c>
       <c r="L34" t="n">
-        <v>-7.06</v>
+        <v>-14.48</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3155,47 +3163,47 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>48.78</v>
+        <v>72.52</v>
       </c>
       <c r="S34" t="n">
-        <v>47.23</v>
+        <v>73.47</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HDB</t>
+          <t>HHV</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>358.08</v>
+        <v>24.72</v>
       </c>
       <c r="D35" t="n">
-        <v>15774500</v>
+        <v>2658200</v>
       </c>
       <c r="E35" t="n">
-        <v>17242570</v>
+        <v>3144285</v>
       </c>
       <c r="F35" t="n">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3204,33 +3212,29 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>21.13</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>21.13</v>
+        <v>10.44</v>
       </c>
       <c r="L35" t="n">
-        <v>7.43</v>
+        <v>-10.96</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -3239,75 +3243,75 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>53.85</v>
+        <v>57.35</v>
       </c>
       <c r="S35" t="n">
-        <v>60.96</v>
+        <v>61.83</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HHP</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.6</v>
+        <v>21</v>
       </c>
       <c r="C36" t="n">
-        <v>20.63</v>
+        <v>520.23</v>
       </c>
       <c r="D36" t="n">
-        <v>1172200</v>
+        <v>24773000</v>
       </c>
       <c r="E36" t="n">
-        <v>1425335</v>
+        <v>18565045</v>
       </c>
       <c r="F36" t="n">
-        <v>0.82</v>
+        <v>1.33</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>16.39</v>
+        <v>21.12</v>
       </c>
       <c r="K36" t="n">
-        <v>15.55</v>
+        <v>22.3</v>
       </c>
       <c r="L36" t="n">
-        <v>13.22</v>
+        <v>-5.83</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3319,51 +3323,51 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>49.25</v>
+        <v>54.69</v>
       </c>
       <c r="S36" t="n">
-        <v>66.48</v>
+        <v>65.48</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HSG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>21.2</v>
+        <v>10.85</v>
       </c>
       <c r="C37" t="n">
-        <v>771.91</v>
+        <v>29.08</v>
       </c>
       <c r="D37" t="n">
-        <v>36410800</v>
+        <v>2679900</v>
       </c>
       <c r="E37" t="n">
-        <v>19095330</v>
+        <v>3484820</v>
       </c>
       <c r="F37" t="n">
-        <v>1.91</v>
+        <v>0.77</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3373,17 +3377,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>21.12</v>
+        <v>10.58</v>
       </c>
       <c r="K37" t="n">
-        <v>22.3</v>
+        <v>11.35</v>
       </c>
       <c r="L37" t="n">
-        <v>-4.93</v>
+        <v>-4.41</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>65.28</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="S37" t="n">
-        <v>76.05</v>
+        <v>76.17</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3416,54 +3420,54 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSG</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.15</v>
+        <v>12.4</v>
       </c>
       <c r="C38" t="n">
-        <v>58.26</v>
+        <v>20.95</v>
       </c>
       <c r="D38" t="n">
-        <v>5224800</v>
+        <v>1689200</v>
       </c>
       <c r="E38" t="n">
-        <v>3476630</v>
+        <v>2007335</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5</v>
+        <v>0.84</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10.55</v>
+        <v>13.15</v>
       </c>
       <c r="K38" t="n">
-        <v>11.35</v>
+        <v>14.05</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.76</v>
+        <v>-11.74</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3479,24 +3483,24 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>82.05</v>
+        <v>52.94</v>
       </c>
       <c r="S38" t="n">
-        <v>81.95</v>
+        <v>50.65</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
@@ -3507,19 +3511,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35.6</v>
+        <v>34.2</v>
       </c>
       <c r="C39" t="n">
-        <v>22.6</v>
+        <v>31.68</v>
       </c>
       <c r="D39" t="n">
-        <v>634900</v>
+        <v>926200</v>
       </c>
       <c r="E39" t="n">
-        <v>1245215</v>
+        <v>1234025</v>
       </c>
       <c r="F39" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3543,30 +3547,26 @@
         <v>34.75</v>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>-1.58</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>50.82</v>
+        <v>42.47</v>
       </c>
       <c r="S39" t="n">
-        <v>48.34</v>
+        <v>48.45</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
@@ -3591,23 +3591,23 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="C40" t="n">
-        <v>29.11</v>
+        <v>33.01</v>
       </c>
       <c r="D40" t="n">
-        <v>1098600</v>
+        <v>1269500</v>
       </c>
       <c r="E40" t="n">
-        <v>1268460</v>
+        <v>1235445</v>
       </c>
       <c r="F40" t="n">
-        <v>0.87</v>
+        <v>1.03</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3627,7 +3627,7 @@
         <v>29.68</v>
       </c>
       <c r="L40" t="n">
-        <v>-10.7</v>
+        <v>-12.38</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>67.86</v>
+        <v>59.38</v>
       </c>
       <c r="S40" t="n">
-        <v>72.45999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="C41" t="n">
-        <v>57.32</v>
+        <v>46.45</v>
       </c>
       <c r="D41" t="n">
-        <v>4094000</v>
+        <v>3341400</v>
       </c>
       <c r="E41" t="n">
-        <v>4601390</v>
+        <v>4609975</v>
       </c>
       <c r="F41" t="n">
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>18.2</v>
       </c>
       <c r="L41" t="n">
-        <v>-23.1</v>
+        <v>-23.65</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>59.38</v>
+        <v>53.33</v>
       </c>
       <c r="S41" t="n">
-        <v>61.22</v>
+        <v>56.93</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="C42" t="n">
-        <v>31.12</v>
+        <v>30.06</v>
       </c>
       <c r="D42" t="n">
-        <v>6915000</v>
+        <v>6695400</v>
       </c>
       <c r="E42" t="n">
-        <v>3001905</v>
+        <v>3242850</v>
       </c>
       <c r="F42" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>4.96</v>
       </c>
       <c r="L42" t="n">
-        <v>-9.27</v>
+        <v>-9.48</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>39.13</v>
       </c>
       <c r="S42" t="n">
-        <v>49.61</v>
+        <v>41.47</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3820,34 +3820,34 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LPB</t>
+          <t>KOS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>37.3</v>
+        <v>4.06</v>
       </c>
       <c r="C43" t="n">
-        <v>61</v>
+        <v>307.22</v>
       </c>
       <c r="D43" t="n">
-        <v>1635300</v>
+        <v>75670704</v>
       </c>
       <c r="E43" t="n">
-        <v>2038585</v>
+        <v>4148905</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8</v>
+        <v>18.24</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>46</v>
+        <v>19.67</v>
       </c>
       <c r="K43" t="n">
-        <v>47.85</v>
+        <v>21.67</v>
       </c>
       <c r="L43" t="n">
-        <v>-22.05</v>
+        <v>-81.26000000000001</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3879,14 +3879,14 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 18.2x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R43" t="n">
-        <v>36.29</v>
+        <v>4.27</v>
       </c>
       <c r="S43" t="n">
-        <v>41.77</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3900,118 +3900,114 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MBB</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.7</v>
+        <v>12.75</v>
       </c>
       <c r="C44" t="n">
-        <v>142.52</v>
+        <v>21.22</v>
       </c>
       <c r="D44" t="n">
-        <v>7234600</v>
+        <v>1664300</v>
       </c>
       <c r="E44" t="n">
-        <v>11475935</v>
+        <v>888785</v>
       </c>
       <c r="F44" t="n">
-        <v>0.63</v>
+        <v>1.87</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>19.49</v>
+        <v>13.48</v>
       </c>
       <c r="K44" t="n">
-        <v>19.52</v>
+        <v>14.28</v>
       </c>
       <c r="L44" t="n">
-        <v>0.9</v>
+        <v>-10.68</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>64.44</v>
+        <v>39.66</v>
       </c>
       <c r="S44" t="n">
-        <v>61.75</v>
+        <v>55.54</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MBS</t>
+          <t>LPB</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15.3</v>
+        <v>36.1</v>
       </c>
       <c r="C45" t="n">
-        <v>28.65</v>
+        <v>84.92</v>
       </c>
       <c r="D45" t="n">
-        <v>1872800</v>
+        <v>2352300</v>
       </c>
       <c r="E45" t="n">
-        <v>2670060</v>
+        <v>2016185</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7</v>
+        <v>1.17</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4025,13 +4021,13 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>15.95</v>
+        <v>45.3</v>
       </c>
       <c r="K45" t="n">
-        <v>17.43</v>
+        <v>47.3</v>
       </c>
       <c r="L45" t="n">
-        <v>-12.25</v>
+        <v>-23.68</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4047,10 +4043,10 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>61.54</v>
+        <v>34.22</v>
       </c>
       <c r="S45" t="n">
-        <v>59.72</v>
+        <v>40.49</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4064,30 +4060,30 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>MBB</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>137.3</v>
+        <v>19.3</v>
       </c>
       <c r="C46" t="n">
-        <v>41.23</v>
+        <v>182.84</v>
       </c>
       <c r="D46" t="n">
-        <v>300300</v>
+        <v>9473400</v>
       </c>
       <c r="E46" t="n">
-        <v>619930</v>
+        <v>11350770</v>
       </c>
       <c r="F46" t="n">
-        <v>0.48</v>
+        <v>0.83</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4105,17 +4101,17 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>139.46</v>
+        <v>19.74</v>
       </c>
       <c r="K46" t="n">
-        <v>134.54</v>
+        <v>19.52</v>
       </c>
       <c r="L46" t="n">
-        <v>2.06</v>
+        <v>-1.15</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4127,14 +4123,14 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>22.33</v>
+        <v>52.94</v>
       </c>
       <c r="S46" t="n">
-        <v>26.18</v>
+        <v>55.66</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4144,30 +4140,30 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MSB</t>
+          <t>MBS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16.05</v>
+        <v>15</v>
       </c>
       <c r="C47" t="n">
-        <v>94.11</v>
+        <v>31.26</v>
       </c>
       <c r="D47" t="n">
-        <v>5863300</v>
+        <v>2083700</v>
       </c>
       <c r="E47" t="n">
-        <v>10311415</v>
+        <v>2681245</v>
       </c>
       <c r="F47" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -4176,49 +4172,41 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>14.13</v>
+        <v>15.95</v>
       </c>
       <c r="K47" t="n">
-        <v>13.28</v>
+        <v>17.43</v>
       </c>
       <c r="L47" t="n">
-        <v>20.81</v>
+        <v>-13.97</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>📈 Đắt (mua bằng lòng tham)</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>87.18000000000001</v>
+        <v>57.14</v>
       </c>
       <c r="S47" t="n">
-        <v>86.90000000000001</v>
+        <v>53.81</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4227,35 +4215,35 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>72.09999999999999</v>
+        <v>135</v>
       </c>
       <c r="C48" t="n">
-        <v>385.04</v>
+        <v>29.47</v>
       </c>
       <c r="D48" t="n">
-        <v>5340400</v>
+        <v>218300</v>
       </c>
       <c r="E48" t="n">
-        <v>5563140</v>
+        <v>619400</v>
       </c>
       <c r="F48" t="n">
-        <v>0.96</v>
+        <v>0.35</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4269,17 +4257,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>69.65000000000001</v>
+        <v>139.45</v>
       </c>
       <c r="K48" t="n">
-        <v>72.05</v>
+        <v>134.54</v>
       </c>
       <c r="L48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4295,14 +4283,14 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>42.11</v>
+        <v>19.01</v>
       </c>
       <c r="S48" t="n">
-        <v>51.53</v>
+        <v>29.52</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -4312,39 +4300,39 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>MSB</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64.03</v>
+        <v>15.8</v>
       </c>
       <c r="C49" t="n">
-        <v>139.28</v>
+        <v>162.94</v>
       </c>
       <c r="D49" t="n">
-        <v>2175300</v>
+        <v>10312400</v>
       </c>
       <c r="E49" t="n">
-        <v>2032580</v>
+        <v>10542500</v>
       </c>
       <c r="F49" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4353,13 +4341,13 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>50.54</v>
+        <v>14.13</v>
       </c>
       <c r="K49" t="n">
-        <v>49.06</v>
+        <v>13.28</v>
       </c>
       <c r="L49" t="n">
-        <v>30.51</v>
+        <v>18.93</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4379,47 +4367,47 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>45.35</v>
+        <v>80.95</v>
       </c>
       <c r="S49" t="n">
-        <v>37.8</v>
+        <v>81.7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MWG</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>75.8</v>
+        <v>70</v>
       </c>
       <c r="C50" t="n">
-        <v>148.95</v>
+        <v>372.13</v>
       </c>
       <c r="D50" t="n">
-        <v>1965100</v>
+        <v>5316200</v>
       </c>
       <c r="E50" t="n">
-        <v>2956090</v>
+        <v>5384945</v>
       </c>
       <c r="F50" t="n">
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4437,36 +4425,32 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>69.02</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>72.83</v>
+        <v>72.05</v>
       </c>
       <c r="L50" t="n">
-        <v>4.08</v>
+        <v>-2.85</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>49.44</v>
+        <v>39.16</v>
       </c>
       <c r="S50" t="n">
-        <v>54.44</v>
+        <v>50.91</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -4480,34 +4464,34 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12.65</v>
+        <v>61.2</v>
       </c>
       <c r="C51" t="n">
-        <v>28.19</v>
+        <v>173.83</v>
       </c>
       <c r="D51" t="n">
-        <v>2228200</v>
+        <v>2840400</v>
       </c>
       <c r="E51" t="n">
-        <v>2583455</v>
+        <v>2013285</v>
       </c>
       <c r="F51" t="n">
-        <v>0.86</v>
+        <v>1.41</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4521,21 +4505,25 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>12.05</v>
+        <v>50.86</v>
       </c>
       <c r="K51" t="n">
-        <v>12.25</v>
+        <v>49.06</v>
       </c>
       <c r="L51" t="n">
-        <v>3.27</v>
+        <v>24.75</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📈 Đắt (mua bằng lòng tham)</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4543,10 +4531,10 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>65.63</v>
+        <v>40.21</v>
       </c>
       <c r="S51" t="n">
-        <v>62.38</v>
+        <v>36.27</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -4560,30 +4548,30 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NKG</t>
+          <t>MST</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12.1</v>
+        <v>8.9</v>
       </c>
       <c r="C52" t="n">
-        <v>116.24</v>
+        <v>20.03</v>
       </c>
       <c r="D52" t="n">
-        <v>9606600</v>
+        <v>2250200</v>
       </c>
       <c r="E52" t="n">
-        <v>4563905</v>
+        <v>1094030</v>
       </c>
       <c r="F52" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -4597,21 +4585,21 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>10.75</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>11.16</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>8.42</v>
+        <v>-1.66</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4623,14 +4611,14 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>87.87</v>
+        <v>31.25</v>
       </c>
       <c r="S52" t="n">
-        <v>82.73</v>
+        <v>33.14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -4640,30 +4628,30 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NLG</t>
+          <t>MWG</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="C53" t="n">
-        <v>22.59</v>
+        <v>169.76</v>
       </c>
       <c r="D53" t="n">
-        <v>982200</v>
+        <v>2294100</v>
       </c>
       <c r="E53" t="n">
-        <v>1392055</v>
+        <v>2942205</v>
       </c>
       <c r="F53" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4677,21 +4665,21 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>22.55</v>
+        <v>70.53</v>
       </c>
       <c r="K53" t="n">
-        <v>23.67</v>
+        <v>72.83</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.85</v>
+        <v>1.61</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4703,10 +4691,10 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>64.86</v>
+        <v>42.31</v>
       </c>
       <c r="S53" t="n">
-        <v>68.66</v>
+        <v>53.26</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -4720,30 +4708,30 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NVL</t>
+          <t>NAB</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.35</v>
+        <v>12.65</v>
       </c>
       <c r="C54" t="n">
-        <v>141.41</v>
+        <v>27.05</v>
       </c>
       <c r="D54" t="n">
-        <v>13662600</v>
+        <v>2138500</v>
       </c>
       <c r="E54" t="n">
-        <v>24119064</v>
+        <v>2558335</v>
       </c>
       <c r="F54" t="n">
-        <v>0.57</v>
+        <v>0.84</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4752,26 +4740,26 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>11.88</v>
+        <v>12.05</v>
       </c>
       <c r="K54" t="n">
-        <v>14.5</v>
+        <v>12.25</v>
       </c>
       <c r="L54" t="n">
-        <v>-28.6</v>
+        <v>3.27</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4783,47 +4771,47 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>25</v>
+        <v>62.07</v>
       </c>
       <c r="S54" t="n">
-        <v>43.02</v>
+        <v>62.52</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NKG</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>12.7</v>
+        <v>11.9</v>
       </c>
       <c r="C55" t="n">
-        <v>28.85</v>
+        <v>73.19</v>
       </c>
       <c r="D55" t="n">
-        <v>2271400</v>
+        <v>6150800</v>
       </c>
       <c r="E55" t="n">
-        <v>1598500</v>
+        <v>4780715</v>
       </c>
       <c r="F55" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4837,21 +4825,21 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>13.93</v>
+        <v>10.75</v>
       </c>
       <c r="K55" t="n">
-        <v>14</v>
+        <v>11.16</v>
       </c>
       <c r="L55" t="n">
-        <v>-9.25</v>
+        <v>6.63</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -4863,14 +4851,14 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>30.77</v>
+        <v>80.12</v>
       </c>
       <c r="S55" t="n">
-        <v>37.48</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -4880,58 +4868,58 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>NLG</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>14.75</v>
+        <v>22</v>
       </c>
       <c r="C56" t="n">
-        <v>74.05</v>
+        <v>22.98</v>
       </c>
       <c r="D56" t="n">
-        <v>5020300</v>
+        <v>1044600</v>
       </c>
       <c r="E56" t="n">
-        <v>4470360</v>
+        <v>1334415</v>
       </c>
       <c r="F56" t="n">
-        <v>1.12</v>
+        <v>0.78</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>🟢 Tăng</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>14.28</v>
+        <v>23.17</v>
       </c>
       <c r="K56" t="n">
-        <v>14.25</v>
+        <v>23.67</v>
       </c>
       <c r="L56" t="n">
-        <v>3.51</v>
+        <v>-7.07</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -4943,51 +4931,51 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>65.56</v>
+        <v>50.54</v>
       </c>
       <c r="S56" t="n">
-        <v>60.27</v>
+        <v>66.08</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>🟢 Tích cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>NVL</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>17.5</v>
+        <v>10.4</v>
       </c>
       <c r="C57" t="n">
-        <v>32.08</v>
+        <v>153.28</v>
       </c>
       <c r="D57" t="n">
-        <v>1832900</v>
+        <v>14738700</v>
       </c>
       <c r="E57" t="n">
-        <v>1045210</v>
+        <v>22814834</v>
       </c>
       <c r="F57" t="n">
-        <v>1.75</v>
+        <v>0.65</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5001,13 +4989,13 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>19.42</v>
+        <v>11.88</v>
       </c>
       <c r="K57" t="n">
-        <v>21.53</v>
+        <v>14.5</v>
       </c>
       <c r="L57" t="n">
-        <v>-18.72</v>
+        <v>-28.25</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5023,10 +5011,10 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>31.43</v>
+        <v>14.29</v>
       </c>
       <c r="S57" t="n">
-        <v>30.16</v>
+        <v>35.95</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5040,58 +5028,58 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PDR</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
       <c r="C58" t="n">
-        <v>53.1</v>
+        <v>24.91</v>
       </c>
       <c r="D58" t="n">
-        <v>4657800</v>
+        <v>2349600</v>
       </c>
       <c r="E58" t="n">
-        <v>5266880</v>
+        <v>2300415</v>
       </c>
       <c r="F58" t="n">
-        <v>0.88</v>
+        <v>1.02</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>11.68</v>
+        <v>10.46</v>
       </c>
       <c r="K58" t="n">
-        <v>13.82</v>
+        <v>10.5</v>
       </c>
       <c r="L58" t="n">
-        <v>-17.54</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5103,51 +5091,51 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>52.27</v>
+        <v>67.52</v>
       </c>
       <c r="S58" t="n">
-        <v>59.68</v>
+        <v>69.08</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PHP</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>43.5</v>
+        <v>13</v>
       </c>
       <c r="C59" t="n">
-        <v>38.9</v>
+        <v>21.66</v>
       </c>
       <c r="D59" t="n">
-        <v>894300</v>
+        <v>1666400</v>
       </c>
       <c r="E59" t="n">
-        <v>387580</v>
+        <v>1623740</v>
       </c>
       <c r="F59" t="n">
-        <v>2.31</v>
+        <v>1.03</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5157,24 +5145,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>43.2</v>
+        <v>13.98</v>
       </c>
       <c r="K59" t="n">
-        <v>42.5</v>
+        <v>14</v>
       </c>
       <c r="L59" t="n">
-        <v>2.35</v>
+        <v>-7.11</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
@@ -5183,14 +5175,14 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>22.55</v>
+        <v>44</v>
       </c>
       <c r="S59" t="n">
-        <v>15.38</v>
+        <v>45.88</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -5200,30 +5192,30 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>ORS</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>34</v>
+        <v>14.15</v>
       </c>
       <c r="C60" t="n">
-        <v>254.54</v>
+        <v>131.25</v>
       </c>
       <c r="D60" t="n">
-        <v>7486600</v>
+        <v>9275500</v>
       </c>
       <c r="E60" t="n">
-        <v>3726895</v>
+        <v>4860800</v>
       </c>
       <c r="F60" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5232,22 +5224,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>35.15</v>
+        <v>14.38</v>
       </c>
       <c r="K60" t="n">
-        <v>38.08</v>
+        <v>14.25</v>
       </c>
       <c r="L60" t="n">
-        <v>-10.73</v>
+        <v>-0.7</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5263,47 +5255,47 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>23.2</v>
+        <v>57.43</v>
       </c>
       <c r="S60" t="n">
-        <v>36.55</v>
+        <v>53.41</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PNJ</t>
+          <t>PDR</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>16.05</v>
+        <v>11.3</v>
       </c>
       <c r="C61" t="n">
-        <v>191.14</v>
+        <v>44.65</v>
       </c>
       <c r="D61" t="n">
-        <v>11909200</v>
+        <v>3951700</v>
       </c>
       <c r="E61" t="n">
-        <v>16902015</v>
+        <v>5281195</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5312,7 +5304,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5321,13 +5313,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>30.78</v>
+        <v>11.75</v>
       </c>
       <c r="K61" t="n">
-        <v>44.2</v>
+        <v>13.82</v>
       </c>
       <c r="L61" t="n">
-        <v>-63.69</v>
+        <v>-18.26</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -5343,75 +5335,75 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>31.75</v>
+        <v>51.11</v>
       </c>
       <c r="S61" t="n">
-        <v>35.13</v>
+        <v>54.75</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12.4</v>
+        <v>51.1</v>
       </c>
       <c r="C62" t="n">
-        <v>67.54000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="D62" t="n">
-        <v>5447100</v>
+        <v>1078300</v>
       </c>
       <c r="E62" t="n">
-        <v>4999495</v>
+        <v>666550</v>
       </c>
       <c r="F62" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>13.08</v>
+        <v>46.5</v>
       </c>
       <c r="K62" t="n">
-        <v>13.6</v>
+        <v>44.69</v>
       </c>
       <c r="L62" t="n">
-        <v>-8.82</v>
+        <v>14.34</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -5423,10 +5415,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>48.28</v>
+        <v>52.05</v>
       </c>
       <c r="S62" t="n">
-        <v>45.56</v>
+        <v>48.2</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -5435,39 +5427,39 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>18.35</v>
+        <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>98.41</v>
+        <v>59.36</v>
       </c>
       <c r="D63" t="n">
-        <v>5362900</v>
+        <v>1746000</v>
       </c>
       <c r="E63" t="n">
-        <v>3837945</v>
+        <v>3651140</v>
       </c>
       <c r="F63" t="n">
-        <v>1.4</v>
+        <v>0.48</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5481,13 +5473,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>18.92</v>
+        <v>35.58</v>
       </c>
       <c r="K63" t="n">
-        <v>19.43</v>
+        <v>38.08</v>
       </c>
       <c r="L63" t="n">
-        <v>-5.56</v>
+        <v>-10.73</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5503,14 +5495,14 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>52.17</v>
+        <v>28.43</v>
       </c>
       <c r="S63" t="n">
-        <v>65.28</v>
+        <v>38.13</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -5520,65 +5512,61 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PVP</t>
+          <t>PNJ</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>18.75</v>
+        <v>15.5</v>
       </c>
       <c r="C64" t="n">
-        <v>55.27</v>
+        <v>145.64</v>
       </c>
       <c r="D64" t="n">
-        <v>2947600</v>
+        <v>9396300</v>
       </c>
       <c r="E64" t="n">
-        <v>1548635</v>
+        <v>13568390</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>20.6</v>
+        <v>30.48</v>
       </c>
       <c r="K64" t="n">
-        <v>20.6</v>
+        <v>42.8</v>
       </c>
       <c r="L64" t="n">
-        <v>-9</v>
+        <v>-63.79</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
@@ -5587,51 +5575,51 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>16.35</v>
+        <v>34.68</v>
       </c>
       <c r="S64" t="n">
-        <v>22.51</v>
+        <v>37.91</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PVS</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30.5</v>
+        <v>12.2</v>
       </c>
       <c r="C65" t="n">
-        <v>142.12</v>
+        <v>46.13</v>
       </c>
       <c r="D65" t="n">
-        <v>4659800</v>
+        <v>3781000</v>
       </c>
       <c r="E65" t="n">
-        <v>2904305</v>
+        <v>4793415</v>
       </c>
       <c r="F65" t="n">
-        <v>1.6</v>
+        <v>0.79</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5645,13 +5633,13 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>30.94</v>
+        <v>13.08</v>
       </c>
       <c r="K65" t="n">
-        <v>31.62</v>
+        <v>13.6</v>
       </c>
       <c r="L65" t="n">
-        <v>-3.56</v>
+        <v>-10.29</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -5667,10 +5655,10 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>23.44</v>
+        <v>42.42</v>
       </c>
       <c r="S65" t="n">
-        <v>28.81</v>
+        <v>40</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -5684,34 +5672,34 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PVT</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>21.3</v>
+        <v>17.95</v>
       </c>
       <c r="C66" t="n">
-        <v>452.68</v>
+        <v>40.61</v>
       </c>
       <c r="D66" t="n">
-        <v>21252400</v>
+        <v>2262400</v>
       </c>
       <c r="E66" t="n">
-        <v>7778745</v>
+        <v>3790075</v>
       </c>
       <c r="F66" t="n">
-        <v>2.73</v>
+        <v>0.6</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5721,44 +5709,40 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>21.2</v>
+        <v>18.92</v>
       </c>
       <c r="K66" t="n">
-        <v>21.2</v>
+        <v>19.43</v>
       </c>
       <c r="L66" t="n">
-        <v>0.47</v>
+        <v>-7.62</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 2.7x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R66" t="n">
-        <v>19.53</v>
+        <v>50.7</v>
       </c>
       <c r="S66" t="n">
-        <v>16.99</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -5768,34 +5752,34 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SBT</t>
+          <t>PVP</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20.75</v>
+        <v>18.2</v>
       </c>
       <c r="C67" t="n">
-        <v>22.34</v>
+        <v>28.73</v>
       </c>
       <c r="D67" t="n">
-        <v>1076700</v>
+        <v>1578300</v>
       </c>
       <c r="E67" t="n">
-        <v>1272185</v>
+        <v>1557485</v>
       </c>
       <c r="F67" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5805,24 +5789,28 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="K67" t="n">
-        <v>21.92</v>
+        <v>20.6</v>
       </c>
       <c r="L67" t="n">
-        <v>-5.36</v>
+        <v>-11.67</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
@@ -5831,10 +5819,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>8</v>
+        <v>15.85</v>
       </c>
       <c r="S67" t="n">
-        <v>19.3</v>
+        <v>23.37</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -5848,30 +5836,30 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>PVS</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>10.7</v>
+        <v>30.5</v>
       </c>
       <c r="C68" t="n">
-        <v>260.81</v>
+        <v>51.83</v>
       </c>
       <c r="D68" t="n">
-        <v>24374800</v>
+        <v>1699200</v>
       </c>
       <c r="E68" t="n">
-        <v>42953580</v>
+        <v>2863460</v>
       </c>
       <c r="F68" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5889,13 +5877,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>10.9</v>
+        <v>30.94</v>
       </c>
       <c r="K68" t="n">
-        <v>12.2</v>
+        <v>31.62</v>
       </c>
       <c r="L68" t="n">
-        <v>-12.3</v>
+        <v>-3.56</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5911,10 +5899,10 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>68.42</v>
+        <v>25</v>
       </c>
       <c r="S68" t="n">
-        <v>52.31</v>
+        <v>29.66</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -5928,30 +5916,30 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>PVT</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>12.4</v>
+        <v>21.25</v>
       </c>
       <c r="C69" t="n">
-        <v>78.62</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>6340600</v>
+        <v>4680400</v>
       </c>
       <c r="E69" t="n">
-        <v>10964165</v>
+        <v>7615810</v>
       </c>
       <c r="F69" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5960,26 +5948,26 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>13.23</v>
+        <v>21.5</v>
       </c>
       <c r="K69" t="n">
-        <v>15</v>
+        <v>21.2</v>
       </c>
       <c r="L69" t="n">
-        <v>-17.36</v>
+        <v>0.24</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -5991,47 +5979,47 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>68.42</v>
+        <v>19.53</v>
       </c>
       <c r="S69" t="n">
-        <v>64.70999999999999</v>
+        <v>18.03</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>SBT</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>15.6</v>
+        <v>20.7</v>
       </c>
       <c r="C70" t="n">
-        <v>31.62</v>
+        <v>22.73</v>
       </c>
       <c r="D70" t="n">
-        <v>2026900</v>
+        <v>1098200</v>
       </c>
       <c r="E70" t="n">
-        <v>2257095</v>
+        <v>1266295</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -6049,13 +6037,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>19.77</v>
+        <v>22.32</v>
       </c>
       <c r="K70" t="n">
-        <v>19.19</v>
+        <v>21.92</v>
       </c>
       <c r="L70" t="n">
-        <v>-18.69</v>
+        <v>-5.59</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6071,10 +6059,10 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>37.23</v>
+        <v>6</v>
       </c>
       <c r="S70" t="n">
-        <v>22.96</v>
+        <v>12.5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -6088,30 +6076,30 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>19.6</v>
+        <v>10.65</v>
       </c>
       <c r="C71" t="n">
-        <v>270.08</v>
+        <v>219.65</v>
       </c>
       <c r="D71" t="n">
-        <v>13779800</v>
+        <v>20624200</v>
       </c>
       <c r="E71" t="n">
-        <v>18167815</v>
+        <v>42456115</v>
       </c>
       <c r="F71" t="n">
-        <v>0.76</v>
+        <v>0.49</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6120,22 +6108,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>19.55</v>
+        <v>10.9</v>
       </c>
       <c r="K71" t="n">
-        <v>20.19</v>
+        <v>12.15</v>
       </c>
       <c r="L71" t="n">
-        <v>-2.9</v>
+        <v>-12.35</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -6151,47 +6139,47 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>62</v>
+        <v>58.06</v>
       </c>
       <c r="S71" t="n">
-        <v>51.58</v>
+        <v>45.83</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>66.90000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="C72" t="n">
-        <v>90.45999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="D72" t="n">
-        <v>1352200</v>
+        <v>5371300</v>
       </c>
       <c r="E72" t="n">
-        <v>3353395</v>
+        <v>10923035</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -6200,7 +6188,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6209,81 +6197,73 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>70.05</v>
+        <v>13.23</v>
       </c>
       <c r="K72" t="n">
-        <v>70.05</v>
+        <v>15</v>
       </c>
       <c r="L72" t="n">
-        <v>-4.5</v>
+        <v>-18.69</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>48.67</v>
+        <v>61.9</v>
       </c>
       <c r="S72" t="n">
-        <v>48.43</v>
+        <v>61.33</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>22.35</v>
+        <v>15.05</v>
       </c>
       <c r="C73" t="n">
-        <v>528.41</v>
+        <v>32.11</v>
       </c>
       <c r="D73" t="n">
-        <v>23642700</v>
+        <v>2133600</v>
       </c>
       <c r="E73" t="n">
-        <v>18520925</v>
+        <v>2245575</v>
       </c>
       <c r="F73" t="n">
-        <v>1.28</v>
+        <v>0.95</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6293,28 +6273,24 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>21</v>
+        <v>19.77</v>
       </c>
       <c r="K73" t="n">
-        <v>21</v>
+        <v>19.19</v>
       </c>
       <c r="L73" t="n">
-        <v>6.43</v>
+        <v>-21.55</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
@@ -6323,14 +6299,14 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>67.89</v>
+        <v>37.23</v>
       </c>
       <c r="S73" t="n">
-        <v>60.79</v>
+        <v>23.09</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -6340,30 +6316,30 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>12.2</v>
+        <v>19.3</v>
       </c>
       <c r="C74" t="n">
-        <v>59.46</v>
+        <v>275.59</v>
       </c>
       <c r="D74" t="n">
-        <v>4873600</v>
+        <v>14279200</v>
       </c>
       <c r="E74" t="n">
-        <v>5344415</v>
+        <v>17636165</v>
       </c>
       <c r="F74" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -6377,17 +6353,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>11.09</v>
+        <v>20.06</v>
       </c>
       <c r="K74" t="n">
-        <v>13.2</v>
+        <v>20.19</v>
       </c>
       <c r="L74" t="n">
-        <v>-7.61</v>
+        <v>-4.38</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6403,14 +6379,14 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>93.94</v>
+        <v>54.55</v>
       </c>
       <c r="S74" t="n">
-        <v>83.48</v>
+        <v>50.82</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -6420,39 +6396,39 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>27.8</v>
+        <v>66.3</v>
       </c>
       <c r="C75" t="n">
-        <v>90.01000000000001</v>
+        <v>175.07</v>
       </c>
       <c r="D75" t="n">
-        <v>3237800</v>
+        <v>2640500</v>
       </c>
       <c r="E75" t="n">
-        <v>3008515</v>
+        <v>3245505</v>
       </c>
       <c r="F75" t="n">
-        <v>1.08</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6461,20 +6437,24 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>31.01</v>
+        <v>70.05</v>
       </c>
       <c r="K75" t="n">
-        <v>32.59</v>
+        <v>70.05</v>
       </c>
       <c r="L75" t="n">
-        <v>-14.7</v>
+        <v>-5.35</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
@@ -6483,51 +6463,51 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>57.58</v>
+        <v>48.03</v>
       </c>
       <c r="S75" t="n">
-        <v>57.06</v>
+        <v>42.89</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TLG</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>52.5</v>
+        <v>21.6</v>
       </c>
       <c r="C76" t="n">
-        <v>29.12</v>
+        <v>381.12</v>
       </c>
       <c r="D76" t="n">
-        <v>554600</v>
+        <v>17644300</v>
       </c>
       <c r="E76" t="n">
-        <v>270400</v>
+        <v>18694035</v>
       </c>
       <c r="F76" t="n">
-        <v>2.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6537,17 +6517,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>51.55</v>
+        <v>21.12</v>
       </c>
       <c r="K76" t="n">
-        <v>51.4</v>
+        <v>21</v>
       </c>
       <c r="L76" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6563,10 +6543,10 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>41.94</v>
+        <v>47.65</v>
       </c>
       <c r="S76" t="n">
-        <v>46.54</v>
+        <v>54.03</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6580,30 +6560,30 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TOS</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>76.3</v>
+        <v>11.85</v>
       </c>
       <c r="C77" t="n">
-        <v>51.95</v>
+        <v>166.35</v>
       </c>
       <c r="D77" t="n">
-        <v>680800</v>
+        <v>14038100</v>
       </c>
       <c r="E77" t="n">
-        <v>84605</v>
+        <v>5872880</v>
       </c>
       <c r="F77" t="n">
-        <v>8.050000000000001</v>
+        <v>2.39</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6612,22 +6592,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>90.5</v>
+        <v>11.27</v>
       </c>
       <c r="K77" t="n">
-        <v>92.29000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="L77" t="n">
-        <v>-17.33</v>
+        <v>-10.26</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -6639,51 +6619,51 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 8.0x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>52.56</v>
+        <v>76.92</v>
       </c>
       <c r="S77" t="n">
-        <v>42.05</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>12.9</v>
+        <v>27.5</v>
       </c>
       <c r="C78" t="n">
-        <v>279.58</v>
+        <v>105.11</v>
       </c>
       <c r="D78" t="n">
-        <v>21673100</v>
+        <v>3822200</v>
       </c>
       <c r="E78" t="n">
-        <v>14466515</v>
+        <v>3075755</v>
       </c>
       <c r="F78" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -6692,26 +6672,26 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>12.3</v>
+        <v>31.01</v>
       </c>
       <c r="K78" t="n">
-        <v>12.68</v>
+        <v>32.59</v>
       </c>
       <c r="L78" t="n">
-        <v>1.78</v>
+        <v>-15.62</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -6723,51 +6703,51 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>80.84999999999999</v>
+        <v>53.85</v>
       </c>
       <c r="S78" t="n">
-        <v>88.2</v>
+        <v>51.41</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>TNG</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>57.2</v>
+        <v>17.9</v>
       </c>
       <c r="C79" t="n">
-        <v>231.65</v>
+        <v>40.9</v>
       </c>
       <c r="D79" t="n">
-        <v>4049800</v>
+        <v>2284800</v>
       </c>
       <c r="E79" t="n">
-        <v>3233850</v>
+        <v>1321300</v>
       </c>
       <c r="F79" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6777,21 +6757,21 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>57.35</v>
+        <v>18</v>
       </c>
       <c r="K79" t="n">
-        <v>59.12</v>
+        <v>17.13</v>
       </c>
       <c r="L79" t="n">
-        <v>-3.26</v>
+        <v>4.5</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -6803,10 +6783,10 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>54.39</v>
+        <v>43.48</v>
       </c>
       <c r="S79" t="n">
-        <v>62.72</v>
+        <v>58.14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -6820,30 +6800,30 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VCG</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15.3</v>
+        <v>12.65</v>
       </c>
       <c r="C80" t="n">
-        <v>21.77</v>
+        <v>100.87</v>
       </c>
       <c r="D80" t="n">
-        <v>1422900</v>
+        <v>7974000</v>
       </c>
       <c r="E80" t="n">
-        <v>2471555</v>
+        <v>14306305</v>
       </c>
       <c r="F80" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -6857,17 +6837,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>14.88</v>
+        <v>12.3</v>
       </c>
       <c r="K80" t="n">
-        <v>17.1</v>
+        <v>12.68</v>
       </c>
       <c r="L80" t="n">
-        <v>-10.55</v>
+        <v>-0.2</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -6887,10 +6867,10 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>71.43000000000001</v>
+        <v>72.55</v>
       </c>
       <c r="S80" t="n">
-        <v>77.29000000000001</v>
+        <v>85.08</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -6904,58 +6884,58 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VCI</t>
+          <t>TVN</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C81" t="n">
-        <v>111.21</v>
+        <v>25.58</v>
       </c>
       <c r="D81" t="n">
-        <v>5852900</v>
+        <v>2610000</v>
       </c>
       <c r="E81" t="n">
-        <v>7729900</v>
+        <v>1019555</v>
       </c>
       <c r="F81" t="n">
-        <v>0.76</v>
+        <v>2.56</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>20.6</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>22.6</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>-15.93</v>
+        <v>0.82</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -6963,60 +6943,60 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🎯 BẮT ĐÁY (Vol 2.6x + giá chiết khấu 129)</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>59.18</v>
+        <v>50</v>
       </c>
       <c r="S81" t="n">
-        <v>64.06999999999999</v>
+        <v>60.27</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VCK</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>27.25</v>
+        <v>56.3</v>
       </c>
       <c r="C82" t="n">
-        <v>29.26</v>
+        <v>203.9</v>
       </c>
       <c r="D82" t="n">
-        <v>1073700</v>
+        <v>3621700</v>
       </c>
       <c r="E82" t="n">
-        <v>1649130</v>
+        <v>3239315</v>
       </c>
       <c r="F82" t="n">
-        <v>0.65</v>
+        <v>1.12</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7025,13 +7005,13 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>29.08</v>
+        <v>57.7</v>
       </c>
       <c r="K82" t="n">
-        <v>30.82</v>
+        <v>59.12</v>
       </c>
       <c r="L82" t="n">
-        <v>-11.6</v>
+        <v>-4.78</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -7047,75 +7027,75 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>60</v>
+        <v>46.97</v>
       </c>
       <c r="S82" t="n">
-        <v>63.46</v>
+        <v>56.44</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>VCG</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>37.8</v>
+        <v>14.8</v>
       </c>
       <c r="C83" t="n">
-        <v>49.42</v>
+        <v>48.49</v>
       </c>
       <c r="D83" t="n">
-        <v>1307500</v>
+        <v>3276200</v>
       </c>
       <c r="E83" t="n">
-        <v>675120</v>
+        <v>2544810</v>
       </c>
       <c r="F83" t="n">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>36.85</v>
+        <v>14.88</v>
       </c>
       <c r="K83" t="n">
-        <v>36.5</v>
+        <v>17.1</v>
       </c>
       <c r="L83" t="n">
-        <v>3.56</v>
+        <v>-13.48</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -7127,47 +7107,47 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>52.38</v>
+        <v>59.49</v>
       </c>
       <c r="S83" t="n">
-        <v>62.38</v>
+        <v>68.88</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VGC</t>
+          <t>VCI</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>42.3</v>
+        <v>18.5</v>
       </c>
       <c r="C84" t="n">
-        <v>30.84</v>
+        <v>109.53</v>
       </c>
       <c r="D84" t="n">
-        <v>729000</v>
+        <v>5920600</v>
       </c>
       <c r="E84" t="n">
-        <v>829355</v>
+        <v>7557350</v>
       </c>
       <c r="F84" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7176,33 +7156,29 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>40.8</v>
+        <v>20.6</v>
       </c>
       <c r="K84" t="n">
-        <v>40.8</v>
+        <v>22.55</v>
       </c>
       <c r="L84" t="n">
-        <v>3.68</v>
+        <v>-17.96</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
@@ -7211,75 +7187,75 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>45.74</v>
+        <v>50.88</v>
       </c>
       <c r="S84" t="n">
-        <v>52.97</v>
+        <v>64.09</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VGS</t>
+          <t>VCK</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>19.3</v>
+        <v>27</v>
       </c>
       <c r="C85" t="n">
-        <v>22.78</v>
+        <v>36.66</v>
       </c>
       <c r="D85" t="n">
-        <v>1180500</v>
+        <v>1357900</v>
       </c>
       <c r="E85" t="n">
-        <v>374790</v>
+        <v>1623405</v>
       </c>
       <c r="F85" t="n">
-        <v>3.15</v>
+        <v>0.84</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>17.15</v>
+        <v>29.08</v>
       </c>
       <c r="K85" t="n">
-        <v>18.73</v>
+        <v>30.82</v>
       </c>
       <c r="L85" t="n">
-        <v>3.07</v>
+        <v>-12.41</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -7287,79 +7263,79 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>🎯 BẮT ĐÁY (Vol 3.1x + giá chiết khấu 129)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>88.89</v>
+        <v>55.13</v>
       </c>
       <c r="S85" t="n">
-        <v>75.09</v>
+        <v>63.07</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>62.1</v>
+        <v>37.3</v>
       </c>
       <c r="C86" t="n">
-        <v>331.81</v>
+        <v>28.32</v>
       </c>
       <c r="D86" t="n">
-        <v>5343200</v>
+        <v>759200</v>
       </c>
       <c r="E86" t="n">
-        <v>7845585</v>
+        <v>696870</v>
       </c>
       <c r="F86" t="n">
-        <v>0.68</v>
+        <v>1.09</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>69.65000000000001</v>
+        <v>36.85</v>
       </c>
       <c r="K86" t="n">
-        <v>70.52</v>
+        <v>36.55</v>
       </c>
       <c r="L86" t="n">
-        <v>-11.94</v>
+        <v>2.05</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -7371,10 +7347,10 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>41.18</v>
+        <v>37.5</v>
       </c>
       <c r="S86" t="n">
-        <v>36.75</v>
+        <v>55.47</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -7383,44 +7359,44 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>VGC</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14</v>
+        <v>42.2</v>
       </c>
       <c r="C87" t="n">
-        <v>138.22</v>
+        <v>23.62</v>
       </c>
       <c r="D87" t="n">
-        <v>9873000</v>
+        <v>559600</v>
       </c>
       <c r="E87" t="n">
-        <v>6711330</v>
+        <v>834080</v>
       </c>
       <c r="F87" t="n">
-        <v>1.47</v>
+        <v>0.67</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🟢 Tăng</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7429,17 +7405,17 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>13.59</v>
+        <v>41.55</v>
       </c>
       <c r="K87" t="n">
-        <v>14.16</v>
+        <v>40.8</v>
       </c>
       <c r="L87" t="n">
-        <v>-1.1</v>
+        <v>3.43</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -7451,131 +7427,127 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>60</v>
+        <v>44.09</v>
       </c>
       <c r="S87" t="n">
-        <v>80.14</v>
+        <v>52.27</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🟢 Tích cực</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>241</v>
+        <v>63</v>
       </c>
       <c r="C88" t="n">
-        <v>405.05</v>
+        <v>849.48</v>
       </c>
       <c r="D88" t="n">
-        <v>1680700</v>
+        <v>13483800</v>
       </c>
       <c r="E88" t="n">
-        <v>2710190</v>
+        <v>8208965</v>
       </c>
       <c r="F88" t="n">
-        <v>0.62</v>
+        <v>1.64</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>229.8</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>224.85</v>
+        <v>70.52</v>
       </c>
       <c r="L88" t="n">
-        <v>7.18</v>
+        <v>-10.66</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
+          <t>📉 Rẻ (dưới/sát 129)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>⚠️</t>
-        </is>
-      </c>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>63.25</v>
+        <v>47.85</v>
       </c>
       <c r="S88" t="n">
-        <v>38.37</v>
+        <v>34.34</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>VIB</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>12.4</v>
+        <v>13.8</v>
       </c>
       <c r="C89" t="n">
-        <v>285.45</v>
+        <v>79.5</v>
       </c>
       <c r="D89" t="n">
-        <v>23020400</v>
+        <v>5760900</v>
       </c>
       <c r="E89" t="n">
-        <v>29850690</v>
+        <v>6725715</v>
       </c>
       <c r="F89" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7584,22 +7556,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>🌫️ Trong Mây</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>12.82</v>
+        <v>13.66</v>
       </c>
       <c r="K89" t="n">
-        <v>14.95</v>
+        <v>14.16</v>
       </c>
       <c r="L89" t="n">
-        <v>-17.06</v>
+        <v>-2.51</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -7615,51 +7587,51 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>66.67</v>
+        <v>52.63</v>
       </c>
       <c r="S89" t="n">
-        <v>66.72</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VJC</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>131.6</v>
+        <v>241</v>
       </c>
       <c r="C90" t="n">
-        <v>115.44</v>
+        <v>1216.91</v>
       </c>
       <c r="D90" t="n">
-        <v>877200</v>
+        <v>5049400</v>
       </c>
       <c r="E90" t="n">
-        <v>934855</v>
+        <v>2802705</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7673,17 +7645,17 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>128.05</v>
+        <v>229.8</v>
       </c>
       <c r="K90" t="n">
-        <v>132.12</v>
+        <v>224.85</v>
       </c>
       <c r="L90" t="n">
-        <v>-0.4</v>
+        <v>7.18</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -7695,14 +7667,14 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>64.44</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="S90" t="n">
-        <v>39.64</v>
+        <v>35.47</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -7712,30 +7684,30 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="C91" t="n">
-        <v>118.16</v>
+        <v>326.17</v>
       </c>
       <c r="D91" t="n">
-        <v>8688000</v>
+        <v>27180500</v>
       </c>
       <c r="E91" t="n">
-        <v>9641640</v>
+        <v>29574055</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7753,13 +7725,13 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>14.98</v>
+        <v>12.82</v>
       </c>
       <c r="K91" t="n">
-        <v>15.85</v>
+        <v>14.95</v>
       </c>
       <c r="L91" t="n">
-        <v>-14.2</v>
+        <v>-19.73</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -7775,10 +7747,10 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>59.52</v>
+        <v>55.77</v>
       </c>
       <c r="S91" t="n">
-        <v>53.89</v>
+        <v>61</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -7792,34 +7764,34 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>VJC</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>57.7</v>
+        <v>131.6</v>
       </c>
       <c r="C92" t="n">
-        <v>77.05</v>
+        <v>146.97</v>
       </c>
       <c r="D92" t="n">
-        <v>1335300</v>
+        <v>1116800</v>
       </c>
       <c r="E92" t="n">
-        <v>1829610</v>
+        <v>944750</v>
       </c>
       <c r="F92" t="n">
-        <v>0.73</v>
+        <v>1.18</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7829,17 +7801,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>60.7</v>
+        <v>128.05</v>
       </c>
       <c r="K92" t="n">
-        <v>59.5</v>
+        <v>132.12</v>
       </c>
       <c r="L92" t="n">
-        <v>-3.03</v>
+        <v>-0.4</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -7855,10 +7827,10 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>50</v>
+        <v>64.44</v>
       </c>
       <c r="S92" t="n">
-        <v>48.68</v>
+        <v>47.23</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -7872,65 +7844,61 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VOS</t>
+          <t>VND</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>11.1</v>
+        <v>13.4</v>
       </c>
       <c r="C93" t="n">
-        <v>24.71</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="D93" t="n">
-        <v>2226100</v>
+        <v>5093700</v>
       </c>
       <c r="E93" t="n">
-        <v>1319430</v>
+        <v>9299035</v>
       </c>
       <c r="F93" t="n">
-        <v>1.69</v>
+        <v>0.55</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>🟡 Sideway</t>
+          <t>🔴 Giảm</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>11.1</v>
+        <v>14.98</v>
       </c>
       <c r="K93" t="n">
-        <v>11.1</v>
+        <v>15.85</v>
       </c>
       <c r="L93" t="n">
-        <v>0.05</v>
+        <v>-15.46</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
@@ -7939,51 +7907,51 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>32.14</v>
+        <v>55.56</v>
       </c>
       <c r="S93" t="n">
-        <v>25.77</v>
+        <v>49.93</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>🟢 Mua (vùng quá bán)</t>
+          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>🟡 Trung tính</t>
+          <t>🔴 Tiêu cực</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VPB</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>23.2</v>
+        <v>56.9</v>
       </c>
       <c r="C94" t="n">
-        <v>272.86</v>
+        <v>169.69</v>
       </c>
       <c r="D94" t="n">
-        <v>11761400</v>
+        <v>2982300</v>
       </c>
       <c r="E94" t="n">
-        <v>15609570</v>
+        <v>1799760</v>
       </c>
       <c r="F94" t="n">
-        <v>0.75</v>
+        <v>1.66</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>🔥 Tiền Vào Mạnh</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7993,28 +7961,24 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>21.98</v>
+        <v>60.55</v>
       </c>
       <c r="K94" t="n">
-        <v>21.98</v>
+        <v>59.5</v>
       </c>
       <c r="L94" t="n">
-        <v>5.57</v>
+        <v>-4.37</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>⚖️ Hợp lý</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>📉 Rẻ (dưới/sát 129)</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
@@ -8023,10 +7987,10 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="S94" t="n">
-        <v>50.21</v>
+        <v>39.51</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -8040,30 +8004,30 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>VPB</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>57.9</v>
+        <v>22.95</v>
       </c>
       <c r="C95" t="n">
-        <v>106.7</v>
+        <v>337.12</v>
       </c>
       <c r="D95" t="n">
-        <v>1842800</v>
+        <v>14689300</v>
       </c>
       <c r="E95" t="n">
-        <v>2007560</v>
+        <v>15646965</v>
       </c>
       <c r="F95" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -8077,28 +8041,24 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>55.52</v>
+        <v>22.08</v>
       </c>
       <c r="K95" t="n">
-        <v>55.52</v>
+        <v>21.98</v>
       </c>
       <c r="L95" t="n">
-        <v>4.28</v>
+        <v>4.44</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
@@ -8107,14 +8067,14 @@
         </is>
       </c>
       <c r="R95" t="n">
-        <v>56.38</v>
+        <v>22.64</v>
       </c>
       <c r="S95" t="n">
-        <v>62.32</v>
+        <v>38.66</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>⏸️ Chờ (giữa biên độ)</t>
+          <t>🟢 Mua (vùng quá bán)</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -8124,34 +8084,34 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VPL</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>90.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="C96" t="n">
-        <v>93.97</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="D96" t="n">
-        <v>1043000</v>
+        <v>1550500</v>
       </c>
       <c r="E96" t="n">
-        <v>913865</v>
+        <v>1992530</v>
       </c>
       <c r="F96" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>⚡ Có Tín Hiệu</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8161,24 +8121,28 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>☁️ Trên Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>81.45</v>
+        <v>55.52</v>
       </c>
       <c r="K96" t="n">
-        <v>85.5</v>
+        <v>55.52</v>
       </c>
       <c r="L96" t="n">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>⚖️ Hợp lý</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
@@ -8187,14 +8151,14 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>74.59999999999999</v>
+        <v>57.92</v>
       </c>
       <c r="S96" t="n">
-        <v>74.33</v>
+        <v>61.32</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>🔴 Bán (vùng quá mua)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -8204,58 +8168,58 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VRE</t>
+          <t>VPL</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24.15</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>45.87</v>
+        <v>99.16</v>
       </c>
       <c r="D97" t="n">
-        <v>1899200</v>
+        <v>1100600</v>
       </c>
       <c r="E97" t="n">
-        <v>3314780</v>
+        <v>937245</v>
       </c>
       <c r="F97" t="n">
-        <v>0.57</v>
+        <v>1.17</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>💤 Tiền Yếu</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>🌧️ Dưới Mây</t>
+          <t>☁️ Trên Mây</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>24.42</v>
+        <v>82</v>
       </c>
       <c r="K97" t="n">
-        <v>28.56</v>
+        <v>85.5</v>
       </c>
       <c r="L97" t="n">
-        <v>-15.44</v>
+        <v>5.38</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>📉 Rẻ (dưới/sát 129)</t>
+          <t>⚖️ Hợp lý</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -8267,71 +8231,71 @@
         </is>
       </c>
       <c r="R97" t="n">
-        <v>59.8</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="S97" t="n">
-        <v>45.96</v>
+        <v>70.89</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>🔴 Bán (vùng quá mua)</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VSC</t>
+          <t>VRE</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>13.8</v>
+        <v>24.05</v>
       </c>
       <c r="C98" t="n">
-        <v>269.85</v>
+        <v>60.51</v>
       </c>
       <c r="D98" t="n">
-        <v>19554500</v>
+        <v>2516100</v>
       </c>
       <c r="E98" t="n">
-        <v>11024280</v>
+        <v>3279265</v>
       </c>
       <c r="F98" t="n">
-        <v>1.77</v>
+        <v>0.77</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>💤 Tiền Yếu</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>🔴 Giảm</t>
+          <t>🟡 Sideway</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>14.02</v>
+        <v>24.6</v>
       </c>
       <c r="K98" t="n">
-        <v>17.62</v>
+        <v>28.56</v>
       </c>
       <c r="L98" t="n">
-        <v>-21.7</v>
+        <v>-15.79</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -8347,47 +8311,47 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>57.47</v>
+        <v>63.54</v>
       </c>
       <c r="S98" t="n">
-        <v>61.75</v>
+        <v>45.65</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>— (đang có xu hướng, không dùng MFI/RSI)</t>
+          <t>⏸️ Chờ (giữa biên độ)</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>🔴 Tiêu cực</t>
+          <t>🟡 Trung tính</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VTZ</t>
+          <t>VSC</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.4</v>
+        <v>13.2</v>
       </c>
       <c r="C99" t="n">
-        <v>25.68</v>
+        <v>171.46</v>
       </c>
       <c r="D99" t="n">
-        <v>1258800</v>
+        <v>12989200</v>
       </c>
       <c r="E99" t="n">
-        <v>957145</v>
+        <v>11365685</v>
       </c>
       <c r="F99" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8401,17 +8365,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>🌫️ Trong Mây</t>
+          <t>🌧️ Dưới Mây</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>20.45</v>
+        <v>14.02</v>
       </c>
       <c r="K99" t="n">
-        <v>21.3</v>
+        <v>17.62</v>
       </c>
       <c r="L99" t="n">
-        <v>-4.23</v>
+        <v>-25.11</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -8427,10 +8391,10 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>57.14</v>
+        <v>52.63</v>
       </c>
       <c r="S99" t="n">
-        <v>40.34</v>
+        <v>59.31</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -8444,34 +8408,34 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VVS</t>
+          <t>VTZ</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>76.8</v>
+        <v>20.3</v>
       </c>
       <c r="C100" t="n">
-        <v>32.47</v>
+        <v>24.41</v>
       </c>
       <c r="D100" t="n">
-        <v>422800</v>
+        <v>1202400</v>
       </c>
       <c r="E100" t="n">
-        <v>207245</v>
+        <v>966575</v>
       </c>
       <c r="F100" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>🔥 Tiền Vào Mạnh</t>
+          <t>⚡ Có Tín Hiệu</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8485,13 +8449,13 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>91.40000000000001</v>
+        <v>20.45</v>
       </c>
       <c r="K100" t="n">
-        <v>85.09999999999999</v>
+        <v>21.35</v>
       </c>
       <c r="L100" t="n">
-        <v>-9.75</v>
+        <v>-4.92</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -8507,10 +8471,10 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>37.5</v>
+        <v>57.14</v>
       </c>
       <c r="S100" t="n">
-        <v>36.55</v>
+        <v>47.76</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -8524,7 +8488,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-10-29 22:42:26</t>
+          <t>2026-10-30 22:26:44</t>
         </is>
       </c>
     </row>
